--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -526,6 +526,18 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>UPSON INTERNATIONAL CORP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2nd floor SM Cyberzone SM City Sta. Rosa, Tagapo, City Of Santa Rosa, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-03-03-0771</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1174-419</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -536,6 +548,33 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1146-031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
     <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
@@ -3973,7 +4012,7 @@
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
         <x:v>167</x:v>
@@ -3991,19 +4030,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I6" s="32">
-        <x:v>46084</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K6" s="13" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>78</x:v>
@@ -4014,7 +4053,7 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>171</x:v>
@@ -4032,85 +4071,243 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I7" s="32">
         <x:v>46084</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N7" s="7" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B8" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I8" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I9" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L11" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="20" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="22" t="s"/>
-      <x:c r="F10" s="22" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>165</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5086,14 +5283,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B10:F10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -536,6 +536,45 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1174-419</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06698-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
@@ -4053,13 +4092,13 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>171</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
         <x:v>172</x:v>
@@ -4071,34 +4110,34 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46084</x:v>
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I7" s="12">
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
         <x:v>175</x:v>
@@ -4110,33 +4149,33 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I8" s="19">
-        <x:v>46104</x:v>
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
         <x:v>178</x:v>
@@ -4148,33 +4187,33 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I9" s="19">
-        <x:v>46097</x:v>
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
         <x:v>181</x:v>
@@ -4186,27 +4225,27 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46098</x:v>
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
         <x:v>184</x:v>
@@ -4224,95 +4263,253 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I11" s="19">
         <x:v>46084</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L15" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="20" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="23" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
         <x:v>165</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5283,15 +5480,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -524,6 +524,18 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERALD BEBIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94 Magsaysay, Poblacion, Cavinti, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03009-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1189-403</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -4051,14 +4063,12 @@
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
+      <x:c r="D6" s="11" t="s"/>
       <x:c r="E6" s="11" t="s">
         <x:v>168</x:v>
       </x:c>
@@ -4069,19 +4079,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
-        <x:v>46095</x:v>
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I6" s="12">
+        <x:v>46091.3107986111</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511778</x:v>
       </x:c>
       <x:c r="K6" s="13" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>78</x:v>
@@ -4092,13 +4102,13 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>171</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
         <x:v>172</x:v>
@@ -4110,22 +4120,22 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46085.1709375</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
@@ -4134,34 +4144,34 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>23</x:v>
@@ -4172,25 +4182,25 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
         <x:v>1507966</x:v>
@@ -4199,7 +4209,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>23</x:v>
@@ -4210,34 +4220,34 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>23</x:v>
@@ -4245,13 +4255,13 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
         <x:v>185</x:v>
@@ -4263,22 +4273,22 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46084</x:v>
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -4286,34 +4296,34 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46104</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>78</x:v>
@@ -4324,34 +4334,34 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46097</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>78</x:v>
@@ -4362,34 +4372,34 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46098</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>78</x:v>
@@ -4397,10 +4407,10 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>52</x:v>
@@ -4415,103 +4425,150 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H15" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="I16" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L15" s="18">
+      <x:c r="L16" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="20" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
+      <x:c r="C19" s="21" t="s"/>
+      <x:c r="D19" s="21" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="22" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="23" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="s">
         <x:v>165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="26" t="s">
-        <x:v>73</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C21" s="27" t="s"/>
       <x:c r="D21" s="27" t="s"/>
       <x:c r="E21" s="27" t="s"/>
       <x:c r="F21" s="28" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>87</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
       <x:c r="E22" s="27" t="s"/>
       <x:c r="F22" s="28" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="26" t="s">
-        <x:v>137</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C23" s="27" t="s"/>
       <x:c r="D23" s="27" t="s"/>
       <x:c r="E23" s="27" t="s"/>
       <x:c r="F23" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="26" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="26" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C26" s="30" t="s"/>
+      <x:c r="D26" s="30" t="s"/>
+      <x:c r="E26" s="30" t="s"/>
+      <x:c r="F26" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5480,16 +5537,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B19:F19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -536,6 +536,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1189-403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAKE C. PASILAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103, Banlic, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03010-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -958,7 +970,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1029,11 +1041,8 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1150,10 +1159,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -4102,14 +4107,12 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
+      <x:c r="D7" s="11" t="s"/>
       <x:c r="E7" s="11" t="s">
         <x:v>172</x:v>
       </x:c>
@@ -4120,19 +4123,19 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46095</x:v>
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I7" s="12">
+        <x:v>46093.1585185185</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511815</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>3030</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
         <x:v>78</x:v>
@@ -4141,13 +4144,13 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
         <x:v>175</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
         <x:v>176</x:v>
@@ -4159,22 +4162,22 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I8" s="19">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -4182,34 +4185,34 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>23</x:v>
@@ -4220,25 +4223,25 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
         <x:v>1507966</x:v>
@@ -4247,7 +4250,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>23</x:v>
@@ -4258,34 +4261,34 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>23</x:v>
@@ -4293,13 +4296,13 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>188</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
         <x:v>189</x:v>
@@ -4311,22 +4314,22 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46084</x:v>
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
@@ -4334,34 +4337,34 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46104</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>78</x:v>
@@ -4372,34 +4375,34 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46097</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>78</x:v>
@@ -4410,34 +4413,34 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46098</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>78</x:v>
@@ -4445,10 +4448,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>201</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>52</x:v>
@@ -4463,82 +4466,109 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="H16" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="I17" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J17" s="15" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L16" s="18">
+      <x:c r="L17" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="20" t="s">
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="20" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="s"/>
-      <x:c r="D19" s="21" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="22" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="23" t="s">
+      <x:c r="C20" s="21" t="s"/>
+      <x:c r="D20" s="21" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="22" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="23" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="s">
+      <x:c r="C21" s="24" t="s"/>
+      <x:c r="D21" s="24" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="25" t="s">
         <x:v>165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
       <x:c r="E22" s="27" t="s"/>
       <x:c r="F22" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="26" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C23" s="27" t="s"/>
       <x:c r="D23" s="27" t="s"/>
       <x:c r="E23" s="27" t="s"/>
       <x:c r="F23" s="28" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="26" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C24" s="27" t="s"/>
       <x:c r="D24" s="27" t="s"/>
@@ -4549,27 +4579,37 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="26" t="s">
-        <x:v>137</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C25" s="27" t="s"/>
       <x:c r="D25" s="27" t="s"/>
       <x:c r="E25" s="27" t="s"/>
       <x:c r="F25" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="26" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="29" t="s">
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C26" s="30" t="s"/>
-      <x:c r="D26" s="30" t="s"/>
-      <x:c r="E26" s="30" t="s"/>
-      <x:c r="F26" s="31" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5540,14 +5580,14 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -550,6 +550,78 @@
     <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
+    <x:t>GLOBAL ANGLE MARKETING INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06915-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1178-478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>X-DOT CONNECTION INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3 UNIT 103, BATONG MALAKE, Los Baños, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06900-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1177-099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1155-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-02-25-0452R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -601,6 +673,18 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
+    <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#95 CZ 28 3RD, FLOOR SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-16-05-1938</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1162-745</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -638,6 +722,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>257-G SM City Molino Molino Road, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1194-347</x:t>
   </x:si>
   <x:si>
     <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
@@ -4144,13 +4240,13 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
         <x:v>175</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
         <x:v>176</x:v>
@@ -4162,247 +4258,247 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I8" s="19">
-        <x:v>46095</x:v>
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511203</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46090.2109953704</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46090.2110069444</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511204</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46093.3080092593</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46084</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>196</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46104</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>78</x:v>
@@ -4410,215 +4506,521 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>200</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>201</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46097</x:v>
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>202</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>204</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46098</x:v>
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>206</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>207</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>208</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46084</x:v>
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46083.1543634259</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="20" t="s">
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="20" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C20" s="21" t="s"/>
-      <x:c r="D20" s="21" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="22" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="23" t="s">
+      <x:c r="C28" s="21" t="s"/>
+      <x:c r="D28" s="21" t="s"/>
+      <x:c r="E28" s="22" t="s"/>
+      <x:c r="F28" s="22" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B29" s="23" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="s">
+      <x:c r="C29" s="24" t="s"/>
+      <x:c r="D29" s="24" t="s"/>
+      <x:c r="E29" s="24" t="s"/>
+      <x:c r="F29" s="25" t="s">
         <x:v>165</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="29" t="s">
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B36" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C36" s="30" t="s"/>
+      <x:c r="D36" s="30" t="s"/>
+      <x:c r="E36" s="30" t="s"/>
+      <x:c r="F36" s="31" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5577,17 +5979,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:F28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -154,6 +154,18 @@
     <x:t>NEW</x:t>
   </x:si>
   <x:si>
+    <x:t>2F 2106 SM CITY LIPA JP LAUREL, San Antonio, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-26-02-0981</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1080-857</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deniel Puyo</x:t>
+  </x:si>
+  <x:si>
     <x:t>LOWER GROUND LEVEL SPACE 41 AYALA MALL SERIN, SILANG JUNCTION NORTH, Tagaytay City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -163,18 +175,6 @@
     <x:t>43A-2-2026-1105-857</x:t>
   </x:si>
   <x:si>
-    <x:t>Deniel Puyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2F 2106 SM CITY LIPA JP LAUREL, San Antonio, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-26-02-0981</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1080-857</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -592,6 +592,15 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -601,15 +610,6 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
@@ -637,6 +637,24 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06698-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1169-102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
     <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -655,24 +673,6 @@
     <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
-    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-0002C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1170-469</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRRP-ROIV-A-06698-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1169-102</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -697,6 +697,24 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -704,24 +722,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1176-385</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-03-2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
@@ -1845,10 +1845,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46072.3184259259</x:v>
+        <x:v>46067.3600231481</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46072.3184375</x:v>
+        <x:v>46067.3600462963</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
         <x:v>1505803</x:v>
@@ -1857,7 +1857,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46079.2696990741</x:v>
+        <x:v>46079.2730092593</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>46</x:v>
@@ -1883,10 +1883,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46067.3600231481</x:v>
+        <x:v>46072.3184259259</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46067.3600462963</x:v>
+        <x:v>46072.3184375</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
         <x:v>1505803</x:v>
@@ -1895,7 +1895,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46079.2730092593</x:v>
+        <x:v>46079.2696990741</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>46</x:v>
@@ -4372,19 +4372,19 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46084.2250115741</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I11" s="19">
-        <x:v>46144</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1511224</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46093.3804398148</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>179</x:v>
@@ -4410,19 +4410,19 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46084.2250115741</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46133</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511224</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46093.3804398148</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>179</x:v>
@@ -4524,19 +4524,19 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>23</x:v>
@@ -4562,10 +4562,10 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
         <x:v>1507966</x:v>
@@ -4574,7 +4574,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>23</x:v>
@@ -4600,19 +4600,19 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>23</x:v>
@@ -4638,19 +4638,19 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J18" s="15" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>23</x:v>
@@ -4752,19 +4752,19 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46104</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J21" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>78</x:v>
@@ -4828,19 +4828,19 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46098</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>78</x:v>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -620,6 +620,15 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0775 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1192-904</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -4471,75 +4480,75 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
       <x:c r="H14" s="16">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46095</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
       <x:c r="H15" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -4547,7 +4556,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>42</x:v>
@@ -4562,19 +4571,19 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>23</x:v>
@@ -4585,7 +4594,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>42</x:v>
@@ -4600,19 +4609,19 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46085.1709375</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>23</x:v>
@@ -4623,7 +4632,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>42</x:v>
@@ -4638,19 +4647,19 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J18" s="15" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>23</x:v>
@@ -4658,40 +4667,40 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
       <x:c r="H19" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>46145</x:v>
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J19" s="15" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -4699,37 +4708,37 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
       <x:c r="H20" s="16">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I20" s="19">
-        <x:v>46084</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J20" s="15" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46083.104224537</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -4737,7 +4746,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
         <x:v>52</x:v>
@@ -4752,19 +4761,19 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46098</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J21" s="15" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>78</x:v>
@@ -4775,7 +4784,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>52</x:v>
@@ -4790,19 +4799,19 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46097</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J22" s="15" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>78</x:v>
@@ -4813,7 +4822,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>52</x:v>
@@ -4828,19 +4837,19 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46104</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>78</x:v>
@@ -4848,40 +4857,40 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
       <x:c r="H24" s="16">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46094</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J24" s="15" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46093.3109375</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -4889,75 +4898,102 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>237</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
       <x:c r="H25" s="16">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46092.9637847222</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46084</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J25" s="15" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1511219</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L25" s="18">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="s">
+      <x:c r="M26" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="20" t="s">
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="20" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C28" s="21" t="s"/>
-      <x:c r="D28" s="21" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="22" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="23" t="s">
+      <x:c r="C29" s="21" t="s"/>
+      <x:c r="D29" s="21" t="s"/>
+      <x:c r="E29" s="22" t="s"/>
+      <x:c r="F29" s="22" t="s"/>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B30" s="23" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="C29" s="24" t="s"/>
-      <x:c r="D29" s="24" t="s"/>
-      <x:c r="E29" s="24" t="s"/>
-      <x:c r="F29" s="25" t="s">
+      <x:c r="C30" s="24" t="s"/>
+      <x:c r="D30" s="24" t="s"/>
+      <x:c r="E30" s="24" t="s"/>
+      <x:c r="F30" s="25" t="s">
         <x:v>165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="26" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C31" s="27" t="s"/>
       <x:c r="D31" s="27" t="s"/>
@@ -4968,60 +5004,70 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="26" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="27" t="s"/>
       <x:c r="D32" s="27" t="s"/>
       <x:c r="E32" s="27" t="s"/>
       <x:c r="F32" s="28" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="26" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C33" s="27" t="s"/>
       <x:c r="D33" s="27" t="s"/>
       <x:c r="E33" s="27" t="s"/>
       <x:c r="F33" s="28" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="26" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C34" s="27" t="s"/>
       <x:c r="D34" s="27" t="s"/>
       <x:c r="E34" s="27" t="s"/>
       <x:c r="F34" s="28" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="26" t="s">
-        <x:v>137</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C35" s="27" t="s"/>
       <x:c r="D35" s="27" t="s"/>
       <x:c r="E35" s="27" t="s"/>
       <x:c r="F35" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="26" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="s"/>
+      <x:c r="D36" s="27" t="s"/>
+      <x:c r="E36" s="27" t="s"/>
+      <x:c r="F36" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B36" s="29" t="s">
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C36" s="30" t="s"/>
-      <x:c r="D36" s="30" t="s"/>
-      <x:c r="E36" s="30" t="s"/>
-      <x:c r="F36" s="31" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C37" s="30" t="s"/>
+      <x:c r="D37" s="30" t="s"/>
+      <x:c r="E37" s="30" t="s"/>
+      <x:c r="F37" s="31" t="n">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5982,8 +6028,7 @@
   <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B28:F28"/>
-    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B29:F29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
@@ -5991,6 +6036,7 @@
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -10,58 +10,22 @@
     <x:sheet name="March 2026" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -553,6 +517,18 @@
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06919-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1179-857</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -562,9 +538,6 @@
     <x:t>43A-3-2026-1178-478</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -577,6 +550,60 @@
     <x:t>43A-3-2026-1177-099</x:t>
   </x:si>
   <x:si>
+    <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0781 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1144-933</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELL EVER MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 424 Cyberzone 4th flr., SM City Bacoor, Habay II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-456b-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1154-964</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLBLITZ MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY BATANGAS, PALLOCAN KANLURAN, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 23- 019R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1095-163</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
@@ -589,9 +616,27 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -610,9 +655,87 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLIXTEC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/F BLDG. D DAANG HARI ROAD, PASONG BUAYA I, Imus City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-456R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1086-471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTO GADGETS TOO INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 440 SM City Bacoor, Habay II,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0773 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1152-831</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONE DOTCOM CELL INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ SM City Bacoor, Habay II,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0778 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1153-796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3 03714 ROBINSONS PLACE DASMARIÑAS, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-018R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1094-777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-468R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1161-717</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 24-471R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1108-762</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -655,6 +778,24 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
     <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
   </x:si>
   <x:si>
@@ -664,24 +805,6 @@
     <x:t>43A-3-2026-1170-469</x:t>
   </x:si>
   <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1171-081</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -694,6 +817,15 @@
     <x:t>43A-3-2026-1162-745</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-21-03-2265</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1157-256</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -706,6 +838,24 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
     <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -713,24 +863,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1173-016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1176-385</x:t>
   </x:si>
   <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
@@ -764,7 +896,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -791,12 +923,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -804,6 +930,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -818,13 +965,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -869,6 +1009,17 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
@@ -883,17 +1034,6 @@
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -1075,7 +1215,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1086,73 +1226,82 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
@@ -1160,109 +1309,118 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1526,1530 +1684,1506 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
+      <x:c r="H6" s="13">
+        <x:v>46069.0835185185</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46069.1006712963</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1506161</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>46069.1133333333</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="F7" s="16" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="G7" s="16" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="H7" s="17">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
+      <x:c r="D8" s="19" t="s"/>
+      <x:c r="E8" s="19" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="F8" s="19" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="G8" s="19" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="H8" s="20">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I8" s="20">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="D9" s="19" t="s"/>
+      <x:c r="E9" s="19" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="F9" s="19" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I9" s="20">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46069.1133333333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="L9" s="20">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D10" s="12" t="s"/>
+      <x:c r="E10" s="11" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F10" s="11" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="G10" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I10" s="13">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="L10" s="15">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D11" s="12" t="s"/>
+      <x:c r="E11" s="11" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F11" s="11" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G11" s="11" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="H11" s="13">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I11" s="13">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="L11" s="15">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="C12" s="11" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="D12" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="E12" s="11" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="F12" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46067.3600231481</x:v>
+      </x:c>
+      <x:c r="I12" s="13">
+        <x:v>46067.3600462963</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="15">
+        <x:v>46079.2730092593</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I13" s="13">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="15">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I14" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="15">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I15" s="22">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="15">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="15">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="15">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="15">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I19" s="13">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="15">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I20" s="13">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L20" s="15">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I21" s="13">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L21" s="15">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M21" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H22" s="13">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I22" s="22">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L22" s="15">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M22" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H23" s="13">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I23" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J23" s="12" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="15">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M23" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H24" s="13">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I24" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J24" s="12" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K24" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="15">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M24" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H25" s="13">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I25" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J25" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="15">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M25" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H26" s="13">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I26" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J26" s="12" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="15">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M26" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H27" s="13">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I27" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="12" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K27" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="15">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M27" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H28" s="13">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I28" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="15">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M28" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H29" s="13">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I29" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K29" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="15">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M29" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H30" s="13">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I30" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="12" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K30" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="15">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M30" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H31" s="13">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I31" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="12" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K31" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="15">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M31" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H32" s="13">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I32" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="12" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K32" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="15">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M32" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H33" s="13">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I33" s="22">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J33" s="12" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K33" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="15">
+        <x:v>46077.1078819444</x:v>
+      </x:c>
+      <x:c r="M33" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="11" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C34" s="11" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H34" s="13">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I34" s="13">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J34" s="12" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K34" s="14" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L34" s="15">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M34" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H35" s="13">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I35" s="22">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J35" s="12" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K35" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L35" s="15">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M35" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C36" s="11" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="D36" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="E36" s="11" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G36" s="11" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H36" s="13">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I36" s="22">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J36" s="12" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K36" s="14" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L36" s="15">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M36" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D37" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I28" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I29" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="18">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I30" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="15" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="18">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C31" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E31" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G31" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H31" s="16">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I31" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="15" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K31" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="18">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M31" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C32" s="14" t="s">
+      <x:c r="E37" s="11" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H37" s="13">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I37" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J37" s="12" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K37" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L37" s="15">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M37" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="11" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E32" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G32" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H32" s="16">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I32" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="15" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K32" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="18">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M32" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I33" s="19">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J33" s="15" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K33" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="18">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M33" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C34" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E34" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H34" s="16">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I34" s="16">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K34" s="17" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L34" s="18">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M34" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C35" s="14" t="s">
+      <x:c r="C38" s="11" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E35" s="14" t="s">
+      <x:c r="D38" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="F35" s="14" t="s">
+      <x:c r="F38" s="11" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G35" s="14" t="s">
+      <x:c r="G38" s="11" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="H35" s="16">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I35" s="19">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K35" s="17" t="n">
+      <x:c r="H38" s="13">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I38" s="22">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J38" s="12" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K38" s="14" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L35" s="18">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C36" s="14" t="s">
+      <x:c r="L38" s="15">
+        <x:v>46078.3266203704</x:v>
+      </x:c>
+      <x:c r="M38" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="11" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
+      <x:c r="C39" s="11" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F36" s="14" t="s">
+      <x:c r="D39" s="12" t="s"/>
+      <x:c r="E39" s="11" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G36" s="14" t="s">
+      <x:c r="F39" s="11" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="H36" s="16">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I36" s="19">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J36" s="15" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K36" s="17" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L36" s="18">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
+      <x:c r="G39" s="11" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
+      <x:c r="H39" s="13">
+        <x:v>46080.2342361111</x:v>
+      </x:c>
+      <x:c r="I39" s="13">
+        <x:v>46080.2342592593</x:v>
+      </x:c>
+      <x:c r="J39" s="12" t="n">
+        <x:v>1507884</x:v>
+      </x:c>
+      <x:c r="K39" s="14" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L39" s="15">
+        <x:v>46080.3353356481</x:v>
+      </x:c>
+      <x:c r="M39" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="11" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="F37" s="14" t="s">
+      <x:c r="D40" s="12" t="s"/>
+      <x:c r="E40" s="11" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G37" s="14" t="s">
+      <x:c r="F40" s="11" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="H37" s="16">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I37" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J37" s="15" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K37" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L37" s="18">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
+      <x:c r="G40" s="11" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H38" s="16">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I38" s="19">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J38" s="15" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K38" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L38" s="18">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D39" s="15" t="s"/>
-      <x:c r="E39" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G39" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I39" s="16">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J39" s="15" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K39" s="17" t="n">
+      <x:c r="H40" s="13">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I40" s="13">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J40" s="12" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K40" s="14" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L39" s="18">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M39" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C40" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D40" s="15" t="s"/>
-      <x:c r="E40" s="14" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G40" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H40" s="16">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I40" s="16">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J40" s="15" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K40" s="17" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L40" s="18">
+      <x:c r="L40" s="15">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M40" s="14" t="s">
-        <x:v>23</x:v>
+      <x:c r="M40" s="11" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B43" s="20" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="C43" s="21" t="s"/>
-      <x:c r="D43" s="21" t="s"/>
-      <x:c r="E43" s="22" t="s"/>
-      <x:c r="F43" s="22" t="s"/>
+      <x:c r="B43" s="23" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C43" s="24" t="s"/>
+      <x:c r="D43" s="24" t="s"/>
+      <x:c r="E43" s="25" t="s"/>
+      <x:c r="F43" s="25" t="s"/>
     </x:row>
     <x:row r="44" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B44" s="23" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="C44" s="24" t="s"/>
-      <x:c r="D44" s="24" t="s"/>
-      <x:c r="E44" s="24" t="s"/>
-      <x:c r="F44" s="25" t="s">
-        <x:v>165</x:v>
+      <x:c r="B44" s="26" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C44" s="27" t="s"/>
+      <x:c r="D44" s="27" t="s"/>
+      <x:c r="E44" s="27" t="s"/>
+      <x:c r="F44" s="28" t="s">
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B45" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C45" s="27" t="s"/>
-      <x:c r="D45" s="27" t="s"/>
-      <x:c r="E45" s="27" t="s"/>
-      <x:c r="F45" s="28" t="n">
+      <x:c r="B45" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C45" s="30" t="s"/>
+      <x:c r="D45" s="30" t="s"/>
+      <x:c r="E45" s="30" t="s"/>
+      <x:c r="F45" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C46" s="27" t="s"/>
-      <x:c r="D46" s="27" t="s"/>
-      <x:c r="E46" s="27" t="s"/>
-      <x:c r="F46" s="28" t="n">
+      <x:c r="B46" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C46" s="30" t="s"/>
+      <x:c r="D46" s="30" t="s"/>
+      <x:c r="E46" s="30" t="s"/>
+      <x:c r="F46" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="26" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C47" s="27" t="s"/>
-      <x:c r="D47" s="27" t="s"/>
-      <x:c r="E47" s="27" t="s"/>
-      <x:c r="F47" s="28" t="n">
+      <x:c r="B47" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C47" s="30" t="s"/>
+      <x:c r="D47" s="30" t="s"/>
+      <x:c r="E47" s="30" t="s"/>
+      <x:c r="F47" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="26" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C48" s="27" t="s"/>
-      <x:c r="D48" s="27" t="s"/>
-      <x:c r="E48" s="27" t="s"/>
-      <x:c r="F48" s="28" t="n">
+      <x:c r="B48" s="29" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C48" s="30" t="s"/>
+      <x:c r="D48" s="30" t="s"/>
+      <x:c r="E48" s="30" t="s"/>
+      <x:c r="F48" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="26" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C49" s="27" t="s"/>
-      <x:c r="D49" s="27" t="s"/>
-      <x:c r="E49" s="27" t="s"/>
-      <x:c r="F49" s="28" t="n">
+      <x:c r="B49" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C49" s="30" t="s"/>
+      <x:c r="D49" s="30" t="s"/>
+      <x:c r="E49" s="30" t="s"/>
+      <x:c r="F49" s="31" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="26" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C50" s="27" t="s"/>
-      <x:c r="D50" s="27" t="s"/>
-      <x:c r="E50" s="27" t="s"/>
-      <x:c r="F50" s="28" t="n">
+      <x:c r="B50" s="29" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C50" s="30" t="s"/>
+      <x:c r="D50" s="30" t="s"/>
+      <x:c r="E50" s="30" t="s"/>
+      <x:c r="F50" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="26" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C51" s="27" t="s"/>
-      <x:c r="D51" s="27" t="s"/>
-      <x:c r="E51" s="27" t="s"/>
-      <x:c r="F51" s="28" t="n">
+      <x:c r="B51" s="29" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C51" s="30" t="s"/>
+      <x:c r="D51" s="30" t="s"/>
+      <x:c r="E51" s="30" t="s"/>
+      <x:c r="F51" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="26" t="s">
+      <x:c r="B52" s="29" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="s"/>
+      <x:c r="D52" s="30" t="s"/>
+      <x:c r="E52" s="30" t="s"/>
+      <x:c r="F52" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B53" s="32" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C52" s="27" t="s"/>
-      <x:c r="D52" s="27" t="s"/>
-      <x:c r="E52" s="27" t="s"/>
-      <x:c r="F52" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B53" s="29" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C53" s="30" t="s"/>
-      <x:c r="D53" s="30" t="s"/>
-      <x:c r="E53" s="30" t="s"/>
-      <x:c r="F53" s="31" t="n">
+      <x:c r="C53" s="33" t="s"/>
+      <x:c r="D53" s="33" t="s"/>
+      <x:c r="E53" s="33" t="s"/>
+      <x:c r="F53" s="34" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
@@ -4083,1007 +4217,1575 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H8" s="20">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I8" s="20">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46097.2890740741</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="19" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I9" s="20">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="20">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I10" s="13">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="15">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I11" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="15">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I12" s="22">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="15">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I13" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="15">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I14" s="22">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="15">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I15" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="15">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="15">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="15">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="15">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I19" s="22">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="15">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I20" s="22">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="15">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I21" s="22">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="15">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M21" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H22" s="13">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I22" s="22">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L22" s="15">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M22" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H23" s="13">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I23" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J23" s="12" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="15">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M23" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H24" s="13">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I24" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J24" s="12" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K24" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="15">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M24" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H25" s="13">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I25" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J25" s="12" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="15">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M25" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H26" s="13">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I26" s="22">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J26" s="12" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="15">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M26" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="H27" s="13">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I27" s="22">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J27" s="12" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K27" s="14" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L27" s="15">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M27" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H28" s="13">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I28" s="22">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J28" s="12" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L28" s="15">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M28" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H29" s="13">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I29" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J29" s="12" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K29" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="15">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M29" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="H30" s="13">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I30" s="22">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J30" s="12" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K30" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="15">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M30" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H31" s="13">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I31" s="13">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J31" s="12" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K31" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L31" s="15">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M31" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="H32" s="13">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I32" s="13">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J32" s="12" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K32" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L32" s="15">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M32" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H33" s="13">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I33" s="13">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J33" s="12" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K33" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L33" s="15">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M33" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C34" s="11" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H34" s="13">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I34" s="13">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J34" s="12" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K34" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L34" s="15">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M34" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H35" s="13">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I35" s="22">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J35" s="12" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K35" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="15">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M35" s="11" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C36" s="11" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="E36" s="11" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G36" s="11" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="H36" s="13">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I36" s="22">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J36" s="12" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K36" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="15">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M36" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D37" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="E37" s="11" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H37" s="13">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I37" s="22">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J37" s="12" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K37" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="L37" s="15">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M37" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C38" s="11" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G38" s="11" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H38" s="13">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I38" s="22">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J38" s="12" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K38" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="L38" s="15">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M38" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D39" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H39" s="13">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I39" s="22">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J39" s="12" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K39" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="L39" s="15">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M39" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G40" s="11" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H40" s="13">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I40" s="22">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J40" s="12" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K40" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
+      <x:c r="L40" s="15">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M40" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D41" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G41" s="11" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H41" s="13">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I41" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J41" s="12" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K41" s="14" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L41" s="15">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M41" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C42" s="11" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="G42" s="11" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="H42" s="13">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I42" s="22">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
+      <x:c r="J42" s="12" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K42" s="14" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
+      <x:c r="L42" s="15">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="20" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="C29" s="21" t="s"/>
-      <x:c r="D29" s="21" t="s"/>
-      <x:c r="E29" s="22" t="s"/>
-      <x:c r="F29" s="22" t="s"/>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B30" s="23" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="C30" s="24" t="s"/>
-      <x:c r="D30" s="24" t="s"/>
-      <x:c r="E30" s="24" t="s"/>
-      <x:c r="F30" s="25" t="s">
-        <x:v>165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="29" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C37" s="30" t="s"/>
-      <x:c r="D37" s="30" t="s"/>
-      <x:c r="E37" s="30" t="s"/>
-      <x:c r="F37" s="31" t="n">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="M42" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="23" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C45" s="24" t="s"/>
+      <x:c r="D45" s="24" t="s"/>
+      <x:c r="E45" s="25" t="s"/>
+      <x:c r="F45" s="25" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B46" s="26" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C46" s="27" t="s"/>
+      <x:c r="D46" s="27" t="s"/>
+      <x:c r="E46" s="27" t="s"/>
+      <x:c r="F46" s="28" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C47" s="30" t="s"/>
+      <x:c r="D47" s="30" t="s"/>
+      <x:c r="E47" s="30" t="s"/>
+      <x:c r="F47" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C48" s="30" t="s"/>
+      <x:c r="D48" s="30" t="s"/>
+      <x:c r="E48" s="30" t="s"/>
+      <x:c r="F48" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C49" s="30" t="s"/>
+      <x:c r="D49" s="30" t="s"/>
+      <x:c r="E49" s="30" t="s"/>
+      <x:c r="F49" s="31" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="29" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C50" s="30" t="s"/>
+      <x:c r="D50" s="30" t="s"/>
+      <x:c r="E50" s="30" t="s"/>
+      <x:c r="F50" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C51" s="30" t="s"/>
+      <x:c r="D51" s="30" t="s"/>
+      <x:c r="E51" s="30" t="s"/>
+      <x:c r="F51" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="29" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="s"/>
+      <x:c r="D52" s="30" t="s"/>
+      <x:c r="E52" s="30" t="s"/>
+      <x:c r="F52" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B53" s="32" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C53" s="33" t="s"/>
+      <x:c r="D53" s="33" t="s"/>
+      <x:c r="E53" s="33" t="s"/>
+      <x:c r="F53" s="34" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6028,15 +6730,15 @@
   <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B29:F29"/>
-    <x:mergeCell ref="B30:E30"/>
-    <x:mergeCell ref="B31:E31"/>
-    <x:mergeCell ref="B32:E32"/>
-    <x:mergeCell ref="B33:E33"/>
-    <x:mergeCell ref="B34:E34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B45:F45"/>
+    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B49:E49"/>
+    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B51:E51"/>
+    <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>PERMIT SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -1293,7 +1293,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1329,6 +1329,50 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1348,32 +1392,12 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1686,7 +1710,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46054</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1747,7 +1771,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -1785,7 +1809,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>
@@ -1897,1298 +1921,1324 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+      <x:c r="B10" s="22" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="C10" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s"/>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="D10" s="23" t="s"/>
+      <x:c r="E10" s="22" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="F10" s="22" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="G10" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="H10" s="24">
         <x:v>46063.2819560185</x:v>
       </x:c>
-      <x:c r="I10" s="13">
+      <x:c r="I10" s="24">
         <x:v>46063.2922685185</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="23" t="n">
         <x:v>1507682</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="25" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="26">
         <x:v>46063.2957638889</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
+      <x:c r="M10" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
+      <x:c r="B11" s="22" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="s">
+      <x:c r="C11" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s"/>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="D11" s="23" t="s"/>
+      <x:c r="E11" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="F11" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="G11" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="H11" s="24">
         <x:v>46058.4859837963</x:v>
       </x:c>
-      <x:c r="I11" s="13">
+      <x:c r="I11" s="24">
         <x:v>46062.157025463</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="23" t="n">
         <x:v>1507672</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="25" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="26">
         <x:v>46062.1881944444</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
+      <x:c r="M11" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="s">
+      <x:c r="C12" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="s">
+      <x:c r="D12" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="s">
+      <x:c r="E12" s="22" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="F12" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="G12" s="22" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="H12" s="24">
         <x:v>46067.3600231481</x:v>
       </x:c>
-      <x:c r="I12" s="13">
+      <x:c r="I12" s="24">
         <x:v>46067.3600462963</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="23" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="K12" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="15">
+      <x:c r="L12" s="26">
         <x:v>46079.2730092593</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
+      <x:c r="M12" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="s">
+      <x:c r="C13" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s">
+      <x:c r="D13" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="s">
+      <x:c r="E13" s="22" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="F13" s="22" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="G13" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="H13" s="24">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I13" s="13">
+      <x:c r="I13" s="24">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="23" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="K13" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="15">
+      <x:c r="L13" s="26">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
+      <x:c r="M13" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="C14" s="22" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="s">
+      <x:c r="D14" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="E14" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="F14" s="22" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="G14" s="22" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H14" s="13">
+      <x:c r="H14" s="24">
         <x:v>46067.1596643518</x:v>
       </x:c>
-      <x:c r="I14" s="22">
+      <x:c r="I14" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="n">
+      <x:c r="J14" s="23" t="n">
         <x:v>1505804</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="n">
+      <x:c r="K14" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="15">
+      <x:c r="L14" s="26">
         <x:v>46079.2772569444</x:v>
       </x:c>
-      <x:c r="M14" s="11" t="s">
+      <x:c r="M14" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="s">
+      <x:c r="C15" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="s">
+      <x:c r="D15" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="s">
+      <x:c r="E15" s="22" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="s">
+      <x:c r="F15" s="22" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="s">
+      <x:c r="G15" s="22" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H15" s="13">
+      <x:c r="H15" s="24">
         <x:v>46067.2222106481</x:v>
       </x:c>
-      <x:c r="I15" s="22">
+      <x:c r="I15" s="27">
         <x:v>46089</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="n">
+      <x:c r="J15" s="23" t="n">
         <x:v>1505805</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="n">
+      <x:c r="K15" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="15">
+      <x:c r="L15" s="26">
         <x:v>46079.2763078704</x:v>
       </x:c>
-      <x:c r="M15" s="11" t="s">
+      <x:c r="M15" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="s">
+      <x:c r="C16" s="22" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="D16" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="E16" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
+      <x:c r="F16" s="22" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="s">
+      <x:c r="G16" s="22" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H16" s="13">
+      <x:c r="H16" s="24">
         <x:v>46072.3605555556</x:v>
       </x:c>
-      <x:c r="I16" s="22">
+      <x:c r="I16" s="27">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="n">
+      <x:c r="J16" s="23" t="n">
         <x:v>1507784</x:v>
       </x:c>
-      <x:c r="K16" s="14" t="n">
+      <x:c r="K16" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="15">
+      <x:c r="L16" s="26">
         <x:v>46073.2284953704</x:v>
       </x:c>
-      <x:c r="M16" s="11" t="s">
+      <x:c r="M16" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="s">
+      <x:c r="C17" s="22" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="s">
+      <x:c r="D17" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="s">
+      <x:c r="E17" s="22" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="s">
+      <x:c r="F17" s="22" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="s">
+      <x:c r="G17" s="22" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H17" s="13">
+      <x:c r="H17" s="24">
         <x:v>46072.3529513889</x:v>
       </x:c>
-      <x:c r="I17" s="22">
+      <x:c r="I17" s="27">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="n">
+      <x:c r="J17" s="23" t="n">
         <x:v>1507785</x:v>
       </x:c>
-      <x:c r="K17" s="14" t="n">
+      <x:c r="K17" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="15">
+      <x:c r="L17" s="26">
         <x:v>46073.2314351852</x:v>
       </x:c>
-      <x:c r="M17" s="11" t="s">
+      <x:c r="M17" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="s">
+      <x:c r="C18" s="22" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D18" s="12" t="s">
+      <x:c r="D18" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="s">
+      <x:c r="E18" s="22" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="s">
+      <x:c r="F18" s="22" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="s">
+      <x:c r="G18" s="22" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H18" s="13">
+      <x:c r="H18" s="24">
         <x:v>46063.1352777778</x:v>
       </x:c>
-      <x:c r="I18" s="22">
+      <x:c r="I18" s="27">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="n">
+      <x:c r="J18" s="23" t="n">
         <x:v>1511010</x:v>
       </x:c>
-      <x:c r="K18" s="14" t="n">
+      <x:c r="K18" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="15">
+      <x:c r="L18" s="26">
         <x:v>46063.2367708333</x:v>
       </x:c>
-      <x:c r="M18" s="11" t="s">
+      <x:c r="M18" s="22" t="s">
         <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="s">
+      <x:c r="C19" s="22" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="s">
+      <x:c r="D19" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="s">
+      <x:c r="E19" s="22" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="s">
+      <x:c r="F19" s="22" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="s">
+      <x:c r="G19" s="22" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H19" s="13">
+      <x:c r="H19" s="24">
         <x:v>46079.3584722222</x:v>
       </x:c>
-      <x:c r="I19" s="13">
+      <x:c r="I19" s="24">
         <x:v>46079.3584953704</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="n">
+      <x:c r="J19" s="23" t="n">
         <x:v>1511622</x:v>
       </x:c>
-      <x:c r="K19" s="14" t="n">
+      <x:c r="K19" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L19" s="15">
+      <x:c r="L19" s="26">
         <x:v>46080.2311226852</x:v>
       </x:c>
-      <x:c r="M19" s="11" t="s">
+      <x:c r="M19" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="11" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="C20" s="22" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D20" s="12" t="s">
+      <x:c r="D20" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="s">
+      <x:c r="E20" s="22" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="s">
+      <x:c r="F20" s="22" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="s">
+      <x:c r="G20" s="22" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H20" s="13">
+      <x:c r="H20" s="24">
         <x:v>46079.3539699074</x:v>
       </x:c>
-      <x:c r="I20" s="13">
+      <x:c r="I20" s="24">
         <x:v>46079.3539814815</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="n">
+      <x:c r="J20" s="23" t="n">
         <x:v>1511627</x:v>
       </x:c>
-      <x:c r="K20" s="14" t="n">
+      <x:c r="K20" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L20" s="15">
+      <x:c r="L20" s="26">
         <x:v>46080.2440856481</x:v>
       </x:c>
-      <x:c r="M20" s="11" t="s">
+      <x:c r="M20" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="11" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="s">
+      <x:c r="C21" s="22" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D21" s="12" t="s">
+      <x:c r="D21" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="s">
+      <x:c r="E21" s="22" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="s">
+      <x:c r="F21" s="22" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="s">
+      <x:c r="G21" s="22" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="H21" s="13">
+      <x:c r="H21" s="24">
         <x:v>46058.1529282407</x:v>
       </x:c>
-      <x:c r="I21" s="13">
+      <x:c r="I21" s="24">
         <x:v>46058.1529398148</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="n">
+      <x:c r="J21" s="23" t="n">
         <x:v>1507657</x:v>
       </x:c>
-      <x:c r="K21" s="14" t="n">
+      <x:c r="K21" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L21" s="15">
+      <x:c r="L21" s="26">
         <x:v>46058.2410648148</x:v>
       </x:c>
-      <x:c r="M21" s="11" t="s">
+      <x:c r="M21" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="11" t="s">
+      <x:c r="B22" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="s">
+      <x:c r="C22" s="22" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D22" s="12" t="s">
+      <x:c r="D22" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="s">
+      <x:c r="E22" s="22" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="s">
+      <x:c r="F22" s="22" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G22" s="11" t="s">
+      <x:c r="G22" s="22" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H22" s="13">
+      <x:c r="H22" s="24">
         <x:v>46072.2635300926</x:v>
       </x:c>
-      <x:c r="I22" s="22">
+      <x:c r="I22" s="27">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="n">
+      <x:c r="J22" s="23" t="n">
         <x:v>1507790</x:v>
       </x:c>
-      <x:c r="K22" s="14" t="n">
+      <x:c r="K22" s="25" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L22" s="15">
+      <x:c r="L22" s="26">
         <x:v>46073.3091087963</x:v>
       </x:c>
-      <x:c r="M22" s="11" t="s">
+      <x:c r="M22" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="11" t="s">
+      <x:c r="B23" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="s">
+      <x:c r="C23" s="22" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="s">
+      <x:c r="D23" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="s">
+      <x:c r="E23" s="22" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="s">
+      <x:c r="F23" s="22" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G23" s="11" t="s">
+      <x:c r="G23" s="22" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H23" s="13">
+      <x:c r="H23" s="24">
         <x:v>46079.3873148148</x:v>
       </x:c>
-      <x:c r="I23" s="22">
+      <x:c r="I23" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="n">
+      <x:c r="J23" s="23" t="n">
         <x:v>1511623</x:v>
       </x:c>
-      <x:c r="K23" s="14" t="n">
+      <x:c r="K23" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="15">
+      <x:c r="L23" s="26">
         <x:v>46080.2360763889</x:v>
       </x:c>
-      <x:c r="M23" s="11" t="s">
+      <x:c r="M23" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="11" t="s">
+      <x:c r="B24" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C24" s="11" t="s">
+      <x:c r="C24" s="22" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="s">
+      <x:c r="D24" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E24" s="11" t="s">
+      <x:c r="E24" s="22" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="F24" s="11" t="s">
+      <x:c r="F24" s="22" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G24" s="11" t="s">
+      <x:c r="G24" s="22" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="H24" s="13">
+      <x:c r="H24" s="24">
         <x:v>46079.2523032407</x:v>
       </x:c>
-      <x:c r="I24" s="22">
+      <x:c r="I24" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="n">
+      <x:c r="J24" s="23" t="n">
         <x:v>1511631</x:v>
       </x:c>
-      <x:c r="K24" s="14" t="n">
+      <x:c r="K24" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="15">
+      <x:c r="L24" s="26">
         <x:v>46080.2925810185</x:v>
       </x:c>
-      <x:c r="M24" s="11" t="s">
+      <x:c r="M24" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="11" t="s">
+      <x:c r="B25" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="s">
+      <x:c r="C25" s="22" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D25" s="12" t="s">
+      <x:c r="D25" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="s">
+      <x:c r="E25" s="22" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="s">
+      <x:c r="F25" s="22" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G25" s="11" t="s">
+      <x:c r="G25" s="22" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H25" s="13">
+      <x:c r="H25" s="24">
         <x:v>46079.2430555556</x:v>
       </x:c>
-      <x:c r="I25" s="22">
+      <x:c r="I25" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J25" s="12" t="n">
+      <x:c r="J25" s="23" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K25" s="14" t="n">
+      <x:c r="K25" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="15">
+      <x:c r="L25" s="26">
         <x:v>46080.2801273148</x:v>
       </x:c>
-      <x:c r="M25" s="11" t="s">
+      <x:c r="M25" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="11" t="s">
+      <x:c r="B26" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C26" s="11" t="s">
+      <x:c r="C26" s="22" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D26" s="12" t="s">
+      <x:c r="D26" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="s">
+      <x:c r="E26" s="22" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F26" s="11" t="s">
+      <x:c r="F26" s="22" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G26" s="11" t="s">
+      <x:c r="G26" s="22" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H26" s="13">
+      <x:c r="H26" s="24">
         <x:v>46079.3651967593</x:v>
       </x:c>
-      <x:c r="I26" s="22">
+      <x:c r="I26" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J26" s="12" t="n">
+      <x:c r="J26" s="23" t="n">
         <x:v>1511626</x:v>
       </x:c>
-      <x:c r="K26" s="14" t="n">
+      <x:c r="K26" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L26" s="15">
+      <x:c r="L26" s="26">
         <x:v>46080.2425462963</x:v>
       </x:c>
-      <x:c r="M26" s="11" t="s">
+      <x:c r="M26" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="11" t="s">
+      <x:c r="B27" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C27" s="11" t="s">
+      <x:c r="C27" s="22" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D27" s="12" t="s">
+      <x:c r="D27" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="s">
+      <x:c r="E27" s="22" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="s">
+      <x:c r="F27" s="22" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G27" s="11" t="s">
+      <x:c r="G27" s="22" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H27" s="13">
+      <x:c r="H27" s="24">
         <x:v>46080.2923611111</x:v>
       </x:c>
-      <x:c r="I27" s="22">
+      <x:c r="I27" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J27" s="12" t="n">
+      <x:c r="J27" s="23" t="n">
         <x:v>1511635</x:v>
       </x:c>
-      <x:c r="K27" s="14" t="n">
+      <x:c r="K27" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L27" s="15">
+      <x:c r="L27" s="26">
         <x:v>46080.3208564815</x:v>
       </x:c>
-      <x:c r="M27" s="11" t="s">
+      <x:c r="M27" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="11" t="s">
+      <x:c r="B28" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C28" s="11" t="s">
+      <x:c r="C28" s="22" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D28" s="12" t="s">
+      <x:c r="D28" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E28" s="11" t="s">
+      <x:c r="E28" s="22" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F28" s="11" t="s">
+      <x:c r="F28" s="22" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G28" s="11" t="s">
+      <x:c r="G28" s="22" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="H28" s="13">
+      <x:c r="H28" s="24">
         <x:v>46079.31625</x:v>
       </x:c>
-      <x:c r="I28" s="22">
+      <x:c r="I28" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J28" s="12" t="n">
+      <x:c r="J28" s="23" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K28" s="14" t="n">
+      <x:c r="K28" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L28" s="15">
+      <x:c r="L28" s="26">
         <x:v>46080.2883680556</x:v>
       </x:c>
-      <x:c r="M28" s="11" t="s">
+      <x:c r="M28" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="11" t="s">
+      <x:c r="B29" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C29" s="11" t="s">
+      <x:c r="C29" s="22" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="D29" s="12" t="s">
+      <x:c r="D29" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E29" s="11" t="s">
+      <x:c r="E29" s="22" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F29" s="11" t="s">
+      <x:c r="F29" s="22" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G29" s="11" t="s">
+      <x:c r="G29" s="22" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H29" s="13">
+      <x:c r="H29" s="24">
         <x:v>46079.3059375</x:v>
       </x:c>
-      <x:c r="I29" s="22">
+      <x:c r="I29" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J29" s="12" t="n">
+      <x:c r="J29" s="23" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K29" s="14" t="n">
+      <x:c r="K29" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L29" s="15">
+      <x:c r="L29" s="26">
         <x:v>46080.2896875</x:v>
       </x:c>
-      <x:c r="M29" s="11" t="s">
+      <x:c r="M29" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="11" t="s">
+      <x:c r="B30" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C30" s="11" t="s">
+      <x:c r="C30" s="22" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D30" s="12" t="s">
+      <x:c r="D30" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E30" s="11" t="s">
+      <x:c r="E30" s="22" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F30" s="11" t="s">
+      <x:c r="F30" s="22" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G30" s="11" t="s">
+      <x:c r="G30" s="22" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H30" s="13">
+      <x:c r="H30" s="24">
         <x:v>46079.2943981482</x:v>
       </x:c>
-      <x:c r="I30" s="22">
+      <x:c r="I30" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J30" s="12" t="n">
+      <x:c r="J30" s="23" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K30" s="14" t="n">
+      <x:c r="K30" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L30" s="15">
+      <x:c r="L30" s="26">
         <x:v>46080.2916782407</x:v>
       </x:c>
-      <x:c r="M30" s="11" t="s">
+      <x:c r="M30" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="11" t="s">
+      <x:c r="B31" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C31" s="11" t="s">
+      <x:c r="C31" s="22" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="D31" s="12" t="s">
+      <x:c r="D31" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E31" s="11" t="s">
+      <x:c r="E31" s="22" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="F31" s="11" t="s">
+      <x:c r="F31" s="22" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G31" s="11" t="s">
+      <x:c r="G31" s="22" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H31" s="13">
+      <x:c r="H31" s="24">
         <x:v>46079.378900463</x:v>
       </x:c>
-      <x:c r="I31" s="22">
+      <x:c r="I31" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J31" s="12" t="n">
+      <x:c r="J31" s="23" t="n">
         <x:v>1511624</x:v>
       </x:c>
-      <x:c r="K31" s="14" t="n">
+      <x:c r="K31" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L31" s="15">
+      <x:c r="L31" s="26">
         <x:v>46080.2376041667</x:v>
       </x:c>
-      <x:c r="M31" s="11" t="s">
+      <x:c r="M31" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="11" t="s">
+      <x:c r="B32" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C32" s="11" t="s">
+      <x:c r="C32" s="22" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D32" s="12" t="s">
+      <x:c r="D32" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E32" s="11" t="s">
+      <x:c r="E32" s="22" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="F32" s="11" t="s">
+      <x:c r="F32" s="22" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G32" s="11" t="s">
+      <x:c r="G32" s="22" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H32" s="13">
+      <x:c r="H32" s="24">
         <x:v>46079.3728240741</x:v>
       </x:c>
-      <x:c r="I32" s="22">
+      <x:c r="I32" s="27">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J32" s="12" t="n">
+      <x:c r="J32" s="23" t="n">
         <x:v>1511625</x:v>
       </x:c>
-      <x:c r="K32" s="14" t="n">
+      <x:c r="K32" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L32" s="15">
+      <x:c r="L32" s="26">
         <x:v>46080.2394328704</x:v>
       </x:c>
-      <x:c r="M32" s="11" t="s">
+      <x:c r="M32" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="11" t="s">
+      <x:c r="B33" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C33" s="11" t="s">
+      <x:c r="C33" s="22" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D33" s="12" t="s">
+      <x:c r="D33" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E33" s="11" t="s">
+      <x:c r="E33" s="22" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="F33" s="11" t="s">
+      <x:c r="F33" s="22" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="G33" s="11" t="s">
+      <x:c r="G33" s="22" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="H33" s="13">
+      <x:c r="H33" s="24">
         <x:v>46077.0697337963</x:v>
       </x:c>
-      <x:c r="I33" s="22">
+      <x:c r="I33" s="27">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J33" s="12" t="n">
+      <x:c r="J33" s="23" t="n">
         <x:v>1511576</x:v>
       </x:c>
-      <x:c r="K33" s="14" t="n">
+      <x:c r="K33" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L33" s="15">
+      <x:c r="L33" s="26">
         <x:v>46077.1078819444</x:v>
       </x:c>
-      <x:c r="M33" s="11" t="s">
+      <x:c r="M33" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="11" t="s">
+      <x:c r="B34" s="22" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C34" s="11" t="s">
+      <x:c r="C34" s="22" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D34" s="12" t="s">
+      <x:c r="D34" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E34" s="11" t="s">
+      <x:c r="E34" s="22" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F34" s="11" t="s">
+      <x:c r="F34" s="22" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G34" s="11" t="s">
+      <x:c r="G34" s="22" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="H34" s="13">
+      <x:c r="H34" s="24">
         <x:v>46062.1590162037</x:v>
       </x:c>
-      <x:c r="I34" s="13">
+      <x:c r="I34" s="24">
         <x:v>46062.1590277778</x:v>
       </x:c>
-      <x:c r="J34" s="12" t="n">
+      <x:c r="J34" s="23" t="n">
         <x:v>1510925</x:v>
       </x:c>
-      <x:c r="K34" s="14" t="n">
+      <x:c r="K34" s="25" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L34" s="15">
+      <x:c r="L34" s="26">
         <x:v>46062.1863194444</x:v>
       </x:c>
-      <x:c r="M34" s="11" t="s">
+      <x:c r="M34" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="11" t="s">
+      <x:c r="B35" s="22" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C35" s="11" t="s">
+      <x:c r="C35" s="22" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D35" s="12" t="s">
+      <x:c r="D35" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E35" s="11" t="s">
+      <x:c r="E35" s="22" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F35" s="11" t="s">
+      <x:c r="F35" s="22" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G35" s="11" t="s">
+      <x:c r="G35" s="22" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="H35" s="13">
+      <x:c r="H35" s="24">
         <x:v>46066.2180208333</x:v>
       </x:c>
-      <x:c r="I35" s="22">
+      <x:c r="I35" s="27">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J35" s="12" t="n">
+      <x:c r="J35" s="23" t="n">
         <x:v>1507743</x:v>
       </x:c>
-      <x:c r="K35" s="14" t="n">
+      <x:c r="K35" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L35" s="15">
+      <x:c r="L35" s="26">
         <x:v>46066.2724421296</x:v>
       </x:c>
-      <x:c r="M35" s="11" t="s">
+      <x:c r="M35" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="11" t="s">
+      <x:c r="B36" s="22" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C36" s="11" t="s">
+      <x:c r="C36" s="22" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D36" s="12" t="s">
+      <x:c r="D36" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E36" s="11" t="s">
+      <x:c r="E36" s="22" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="F36" s="11" t="s">
+      <x:c r="F36" s="22" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G36" s="11" t="s">
+      <x:c r="G36" s="22" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="H36" s="13">
+      <x:c r="H36" s="24">
         <x:v>46071.0492476852</x:v>
       </x:c>
-      <x:c r="I36" s="22">
+      <x:c r="I36" s="27">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J36" s="12" t="n">
+      <x:c r="J36" s="23" t="n">
         <x:v>1511502</x:v>
       </x:c>
-      <x:c r="K36" s="14" t="n">
+      <x:c r="K36" s="25" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L36" s="15">
+      <x:c r="L36" s="26">
         <x:v>46071.0606134259</x:v>
       </x:c>
-      <x:c r="M36" s="11" t="s">
+      <x:c r="M36" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="11" t="s">
+      <x:c r="B37" s="22" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C37" s="11" t="s">
+      <x:c r="C37" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D37" s="12" t="s">
+      <x:c r="D37" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E37" s="11" t="s">
+      <x:c r="E37" s="22" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="F37" s="11" t="s">
+      <x:c r="F37" s="22" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G37" s="11" t="s">
+      <x:c r="G37" s="22" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="H37" s="13">
+      <x:c r="H37" s="24">
         <x:v>46066.2275347222</x:v>
       </x:c>
-      <x:c r="I37" s="22">
+      <x:c r="I37" s="27">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J37" s="12" t="n">
+      <x:c r="J37" s="23" t="n">
         <x:v>1507742</x:v>
       </x:c>
-      <x:c r="K37" s="14" t="n">
+      <x:c r="K37" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L37" s="15">
+      <x:c r="L37" s="26">
         <x:v>46066.2701736111</x:v>
       </x:c>
-      <x:c r="M37" s="11" t="s">
+      <x:c r="M37" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="11" t="s">
+      <x:c r="B38" s="22" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C38" s="11" t="s">
+      <x:c r="C38" s="22" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D38" s="12" t="s">
+      <x:c r="D38" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E38" s="11" t="s">
+      <x:c r="E38" s="22" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="F38" s="11" t="s">
+      <x:c r="F38" s="22" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G38" s="11" t="s">
+      <x:c r="G38" s="22" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="H38" s="13">
+      <x:c r="H38" s="24">
         <x:v>46078.2436226852</x:v>
       </x:c>
-      <x:c r="I38" s="22">
+      <x:c r="I38" s="27">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J38" s="12" t="n">
+      <x:c r="J38" s="23" t="n">
         <x:v>1507839</x:v>
       </x:c>
-      <x:c r="K38" s="14" t="n">
+      <x:c r="K38" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L38" s="15">
+      <x:c r="L38" s="26">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M38" s="11" t="s">
+      <x:c r="M38" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="11" t="s">
+      <x:c r="B39" s="22" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C39" s="11" t="s">
+      <x:c r="C39" s="22" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D39" s="12" t="s"/>
-      <x:c r="E39" s="11" t="s">
+      <x:c r="D39" s="23" t="s"/>
+      <x:c r="E39" s="22" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="F39" s="11" t="s">
+      <x:c r="F39" s="22" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G39" s="11" t="s">
+      <x:c r="G39" s="22" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H39" s="13">
+      <x:c r="H39" s="24">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I39" s="13">
+      <x:c r="I39" s="24">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J39" s="12" t="n">
+      <x:c r="J39" s="23" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K39" s="14" t="n">
+      <x:c r="K39" s="25" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L39" s="15">
+      <x:c r="L39" s="26">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M39" s="11" t="s">
+      <x:c r="M39" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="11" t="s">
+      <x:c r="B40" s="22" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C40" s="11" t="s">
+      <x:c r="C40" s="22" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D40" s="12" t="s"/>
-      <x:c r="E40" s="11" t="s">
+      <x:c r="D40" s="23" t="s"/>
+      <x:c r="E40" s="22" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F40" s="11" t="s">
+      <x:c r="F40" s="22" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G40" s="11" t="s">
+      <x:c r="G40" s="22" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H40" s="13">
+      <x:c r="H40" s="24">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I40" s="13">
+      <x:c r="I40" s="24">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J40" s="12" t="n">
+      <x:c r="J40" s="23" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K40" s="14" t="n">
+      <x:c r="K40" s="25" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L40" s="15">
+      <x:c r="L40" s="26">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M40" s="11" t="s">
+      <x:c r="M40" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B43" s="23" t="s">
+    <x:row r="41" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B41" s="28" t="s"/>
+      <x:c r="C41" s="28" t="s"/>
+      <x:c r="D41" s="28" t="s"/>
+      <x:c r="E41" s="28" t="s"/>
+      <x:c r="F41" s="28" t="s"/>
+      <x:c r="G41" s="28" t="s"/>
+      <x:c r="H41" s="28" t="s"/>
+      <x:c r="I41" s="28" t="s"/>
+      <x:c r="J41" s="28" t="s"/>
+      <x:c r="K41" s="28" t="s"/>
+      <x:c r="L41" s="28" t="s"/>
+      <x:c r="M41" s="28" t="s"/>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B42" s="28" t="s"/>
+      <x:c r="C42" s="28" t="s"/>
+      <x:c r="D42" s="28" t="s"/>
+      <x:c r="E42" s="28" t="s"/>
+      <x:c r="F42" s="28" t="s"/>
+      <x:c r="G42" s="28" t="s"/>
+      <x:c r="H42" s="28" t="s"/>
+      <x:c r="I42" s="28" t="s"/>
+      <x:c r="J42" s="28" t="s"/>
+      <x:c r="K42" s="28" t="s"/>
+      <x:c r="L42" s="28" t="s"/>
+      <x:c r="M42" s="28" t="s"/>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="29" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="C43" s="24" t="s"/>
-      <x:c r="D43" s="24" t="s"/>
-      <x:c r="E43" s="25" t="s"/>
-      <x:c r="F43" s="25" t="s"/>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B44" s="26" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C44" s="27" t="s"/>
-      <x:c r="D44" s="27" t="s"/>
-      <x:c r="E44" s="27" t="s"/>
-      <x:c r="F44" s="28" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B45" s="29" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="C45" s="30" t="s"/>
       <x:c r="D45" s="30" t="s"/>
-      <x:c r="E45" s="30" t="s"/>
-      <x:c r="F45" s="31" t="n">
+      <x:c r="E45" s="31" t="s"/>
+      <x:c r="F45" s="31" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B46" s="32" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C46" s="33" t="s"/>
+      <x:c r="D46" s="33" t="s"/>
+      <x:c r="E46" s="33" t="s"/>
+      <x:c r="F46" s="34" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="35" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C47" s="36" t="s"/>
+      <x:c r="D47" s="36" t="s"/>
+      <x:c r="E47" s="36" t="s"/>
+      <x:c r="F47" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="29" t="s">
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="35" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C46" s="30" t="s"/>
-      <x:c r="D46" s="30" t="s"/>
-      <x:c r="E46" s="30" t="s"/>
-      <x:c r="F46" s="31" t="n">
+      <x:c r="C48" s="36" t="s"/>
+      <x:c r="D48" s="36" t="s"/>
+      <x:c r="E48" s="36" t="s"/>
+      <x:c r="F48" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="29" t="s">
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="35" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C47" s="30" t="s"/>
-      <x:c r="D47" s="30" t="s"/>
-      <x:c r="E47" s="30" t="s"/>
-      <x:c r="F47" s="31" t="n">
+      <x:c r="C49" s="36" t="s"/>
+      <x:c r="D49" s="36" t="s"/>
+      <x:c r="E49" s="36" t="s"/>
+      <x:c r="F49" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="29" t="s">
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="35" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C48" s="30" t="s"/>
-      <x:c r="D48" s="30" t="s"/>
-      <x:c r="E48" s="30" t="s"/>
-      <x:c r="F48" s="31" t="n">
+      <x:c r="C50" s="36" t="s"/>
+      <x:c r="D50" s="36" t="s"/>
+      <x:c r="E50" s="36" t="s"/>
+      <x:c r="F50" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="29" t="s">
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="35" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C49" s="30" t="s"/>
-      <x:c r="D49" s="30" t="s"/>
-      <x:c r="E49" s="30" t="s"/>
-      <x:c r="F49" s="31" t="n">
+      <x:c r="C51" s="36" t="s"/>
+      <x:c r="D51" s="36" t="s"/>
+      <x:c r="E51" s="36" t="s"/>
+      <x:c r="F51" s="37" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="29" t="s">
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="35" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C50" s="30" t="s"/>
-      <x:c r="D50" s="30" t="s"/>
-      <x:c r="E50" s="30" t="s"/>
-      <x:c r="F50" s="31" t="n">
+      <x:c r="C52" s="36" t="s"/>
+      <x:c r="D52" s="36" t="s"/>
+      <x:c r="E52" s="36" t="s"/>
+      <x:c r="F52" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="29" t="s">
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="35" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C51" s="30" t="s"/>
-      <x:c r="D51" s="30" t="s"/>
-      <x:c r="E51" s="30" t="s"/>
-      <x:c r="F51" s="31" t="n">
+      <x:c r="C53" s="36" t="s"/>
+      <x:c r="D53" s="36" t="s"/>
+      <x:c r="E53" s="36" t="s"/>
+      <x:c r="F53" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="29" t="s">
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="35" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C52" s="30" t="s"/>
-      <x:c r="D52" s="30" t="s"/>
-      <x:c r="E52" s="30" t="s"/>
-      <x:c r="F52" s="31" t="n">
+      <x:c r="C54" s="36" t="s"/>
+      <x:c r="D54" s="36" t="s"/>
+      <x:c r="E54" s="36" t="s"/>
+      <x:c r="F54" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B53" s="32" t="s">
+    <x:row r="55" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B55" s="38" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C53" s="33" t="s"/>
-      <x:c r="D53" s="33" t="s"/>
-      <x:c r="E53" s="33" t="s"/>
-      <x:c r="F53" s="34" t="n">
+      <x:c r="C55" s="39" t="s"/>
+      <x:c r="D55" s="39" t="s"/>
+      <x:c r="E55" s="39" t="s"/>
+      <x:c r="F55" s="40" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4128,12 +4178,11 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="13">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B43:F43"/>
-    <x:mergeCell ref="B44:E44"/>
-    <x:mergeCell ref="B45:E45"/>
+  <x:mergeCells count="14">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B45:F45"/>
     <x:mergeCell ref="B46:E46"/>
     <x:mergeCell ref="B47:E47"/>
     <x:mergeCell ref="B48:E48"/>
@@ -4142,6 +4191,8 @@
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B55:E55"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -4280,7 +4331,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -4318,7 +4369,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>
@@ -4434,1360 +4485,1386 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+      <x:c r="B10" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="C10" s="22" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s">
+      <x:c r="D10" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="E10" s="22" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="F10" s="22" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="G10" s="22" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="H10" s="24">
         <x:v>46090.2109953704</x:v>
       </x:c>
-      <x:c r="I10" s="13">
+      <x:c r="I10" s="24">
         <x:v>46090.2110069444</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="23" t="n">
         <x:v>1511204</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="26">
         <x:v>46093.3080092593</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
+      <x:c r="M10" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
+      <x:c r="B11" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="s">
+      <x:c r="C11" s="22" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s">
+      <x:c r="D11" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="E11" s="22" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="F11" s="22" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="G11" s="22" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="H11" s="24">
         <x:v>46080.4532523148</x:v>
       </x:c>
-      <x:c r="I11" s="22">
+      <x:c r="I11" s="27">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="23" t="n">
         <x:v>1511232</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="26">
         <x:v>46097.1461689815</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
+      <x:c r="M11" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="s">
+      <x:c r="C12" s="22" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="s">
+      <x:c r="D12" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="s">
+      <x:c r="E12" s="22" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="F12" s="22" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="G12" s="22" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="H12" s="24">
         <x:v>46083.2322337963</x:v>
       </x:c>
-      <x:c r="I12" s="22">
+      <x:c r="I12" s="27">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="23" t="n">
         <x:v>1511233</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="K12" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="15">
+      <x:c r="L12" s="26">
         <x:v>46097.149525463</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
+      <x:c r="M12" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="s">
+      <x:c r="C13" s="22" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s">
+      <x:c r="D13" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="s">
+      <x:c r="E13" s="22" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="F13" s="22" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="G13" s="22" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="H13" s="24">
         <x:v>46083.2380439815</x:v>
       </x:c>
-      <x:c r="I13" s="22">
+      <x:c r="I13" s="27">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="23" t="n">
         <x:v>1511234</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="K13" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="15">
+      <x:c r="L13" s="26">
         <x:v>46097.1564351852</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
+      <x:c r="M13" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="C14" s="22" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="s">
+      <x:c r="D14" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="E14" s="22" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="F14" s="22" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="G14" s="22" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="H14" s="13">
+      <x:c r="H14" s="24">
         <x:v>46083.2599189815</x:v>
       </x:c>
-      <x:c r="I14" s="22">
+      <x:c r="I14" s="27">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="n">
+      <x:c r="J14" s="23" t="n">
         <x:v>1511237</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="n">
+      <x:c r="K14" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="15">
+      <x:c r="L14" s="26">
         <x:v>46097.1652314815</x:v>
       </x:c>
-      <x:c r="M14" s="11" t="s">
+      <x:c r="M14" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="s">
+      <x:c r="C15" s="22" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="s">
+      <x:c r="D15" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="s">
+      <x:c r="E15" s="22" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="s">
+      <x:c r="F15" s="22" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="s">
+      <x:c r="G15" s="22" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="H15" s="13">
+      <x:c r="H15" s="24">
         <x:v>46069.3514814815</x:v>
       </x:c>
-      <x:c r="I15" s="22">
+      <x:c r="I15" s="27">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="n">
+      <x:c r="J15" s="23" t="n">
         <x:v>1511194</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="n">
+      <x:c r="K15" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="15">
+      <x:c r="L15" s="26">
         <x:v>46097.2437384259</x:v>
       </x:c>
-      <x:c r="M15" s="11" t="s">
+      <x:c r="M15" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="s">
+      <x:c r="C16" s="22" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="D16" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="E16" s="22" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
+      <x:c r="F16" s="22" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="s">
+      <x:c r="G16" s="22" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="H16" s="13">
+      <x:c r="H16" s="24">
         <x:v>46084.0854513889</x:v>
       </x:c>
-      <x:c r="I16" s="22">
+      <x:c r="I16" s="27">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="n">
+      <x:c r="J16" s="23" t="n">
         <x:v>1511225</x:v>
       </x:c>
-      <x:c r="K16" s="14" t="n">
+      <x:c r="K16" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="15">
+      <x:c r="L16" s="26">
         <x:v>46093.3956365741</x:v>
       </x:c>
-      <x:c r="M16" s="11" t="s">
+      <x:c r="M16" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="s">
+      <x:c r="C17" s="22" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="s">
+      <x:c r="D17" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="s">
+      <x:c r="E17" s="22" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="s">
+      <x:c r="F17" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="s">
+      <x:c r="G17" s="22" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="H17" s="13">
+      <x:c r="H17" s="24">
         <x:v>46084.0996759259</x:v>
       </x:c>
-      <x:c r="I17" s="22">
+      <x:c r="I17" s="27">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="n">
+      <x:c r="J17" s="23" t="n">
         <x:v>1511192</x:v>
       </x:c>
-      <x:c r="K17" s="14" t="n">
+      <x:c r="K17" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="15">
+      <x:c r="L17" s="26">
         <x:v>46097.2414583333</x:v>
       </x:c>
-      <x:c r="M17" s="11" t="s">
+      <x:c r="M17" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="s">
+      <x:c r="C18" s="22" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D18" s="12" t="s">
+      <x:c r="D18" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="s">
+      <x:c r="E18" s="22" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="s">
+      <x:c r="F18" s="22" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="s">
+      <x:c r="G18" s="22" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="H18" s="13">
+      <x:c r="H18" s="24">
         <x:v>46069.3573032407</x:v>
       </x:c>
-      <x:c r="I18" s="22">
+      <x:c r="I18" s="27">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="n">
+      <x:c r="J18" s="23" t="n">
         <x:v>1511193</x:v>
       </x:c>
-      <x:c r="K18" s="14" t="n">
+      <x:c r="K18" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="15">
+      <x:c r="L18" s="26">
         <x:v>46097.2426388889</x:v>
       </x:c>
-      <x:c r="M18" s="11" t="s">
+      <x:c r="M18" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="s">
+      <x:c r="C19" s="22" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="s">
+      <x:c r="D19" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="s">
+      <x:c r="E19" s="22" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="s">
+      <x:c r="F19" s="22" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="s">
+      <x:c r="G19" s="22" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="H19" s="13">
+      <x:c r="H19" s="24">
         <x:v>46084.2189236111</x:v>
       </x:c>
-      <x:c r="I19" s="22">
+      <x:c r="I19" s="27">
         <x:v>46133</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="n">
+      <x:c r="J19" s="23" t="n">
         <x:v>1511223</x:v>
       </x:c>
-      <x:c r="K19" s="14" t="n">
+      <x:c r="K19" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="15">
+      <x:c r="L19" s="26">
         <x:v>46093.3723842593</x:v>
       </x:c>
-      <x:c r="M19" s="11" t="s">
+      <x:c r="M19" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="11" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="C20" s="22" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D20" s="12" t="s">
+      <x:c r="D20" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="s">
+      <x:c r="E20" s="22" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="s">
+      <x:c r="F20" s="22" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="s">
+      <x:c r="G20" s="22" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="H20" s="13">
+      <x:c r="H20" s="24">
         <x:v>46084.2250115741</x:v>
       </x:c>
-      <x:c r="I20" s="22">
+      <x:c r="I20" s="27">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="n">
+      <x:c r="J20" s="23" t="n">
         <x:v>1511224</x:v>
       </x:c>
-      <x:c r="K20" s="14" t="n">
+      <x:c r="K20" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="15">
+      <x:c r="L20" s="26">
         <x:v>46093.3804398148</x:v>
       </x:c>
-      <x:c r="M20" s="11" t="s">
+      <x:c r="M20" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="11" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="s">
+      <x:c r="C21" s="22" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D21" s="12" t="s">
+      <x:c r="D21" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="s">
+      <x:c r="E21" s="22" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="s">
+      <x:c r="F21" s="22" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="s">
+      <x:c r="G21" s="22" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="H21" s="13">
+      <x:c r="H21" s="24">
         <x:v>46069.1542013889</x:v>
       </x:c>
-      <x:c r="I21" s="22">
+      <x:c r="I21" s="27">
         <x:v>46035</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="n">
+      <x:c r="J21" s="23" t="n">
         <x:v>1511206</x:v>
       </x:c>
-      <x:c r="K21" s="14" t="n">
+      <x:c r="K21" s="25" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L21" s="15">
+      <x:c r="L21" s="26">
         <x:v>46097.2466550926</x:v>
       </x:c>
-      <x:c r="M21" s="11" t="s">
+      <x:c r="M21" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="11" t="s">
+      <x:c r="B22" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="s">
+      <x:c r="C22" s="22" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="D22" s="12" t="s">
+      <x:c r="D22" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="s">
+      <x:c r="E22" s="22" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="s">
+      <x:c r="F22" s="22" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="G22" s="11" t="s">
+      <x:c r="G22" s="22" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="H22" s="13">
+      <x:c r="H22" s="24">
         <x:v>46069.2178703704</x:v>
       </x:c>
-      <x:c r="I22" s="22">
+      <x:c r="I22" s="27">
         <x:v>46051</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="n">
+      <x:c r="J22" s="23" t="n">
         <x:v>1511196</x:v>
       </x:c>
-      <x:c r="K22" s="14" t="n">
+      <x:c r="K22" s="25" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L22" s="15">
+      <x:c r="L22" s="26">
         <x:v>46097.2456365741</x:v>
       </x:c>
-      <x:c r="M22" s="11" t="s">
+      <x:c r="M22" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="11" t="s">
+      <x:c r="B23" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="s">
+      <x:c r="C23" s="22" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="s">
+      <x:c r="D23" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="s">
+      <x:c r="E23" s="22" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="s">
+      <x:c r="F23" s="22" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G23" s="11" t="s">
+      <x:c r="G23" s="22" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="H23" s="13">
+      <x:c r="H23" s="24">
         <x:v>46083.2443865741</x:v>
       </x:c>
-      <x:c r="I23" s="22">
+      <x:c r="I23" s="27">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="n">
+      <x:c r="J23" s="23" t="n">
         <x:v>1511235</x:v>
       </x:c>
-      <x:c r="K23" s="14" t="n">
+      <x:c r="K23" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="15">
+      <x:c r="L23" s="26">
         <x:v>46097.1600115741</x:v>
       </x:c>
-      <x:c r="M23" s="11" t="s">
+      <x:c r="M23" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="11" t="s">
+      <x:c r="B24" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C24" s="11" t="s">
+      <x:c r="C24" s="22" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="s">
+      <x:c r="D24" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E24" s="11" t="s">
+      <x:c r="E24" s="22" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F24" s="11" t="s">
+      <x:c r="F24" s="22" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G24" s="11" t="s">
+      <x:c r="G24" s="22" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="H24" s="13">
+      <x:c r="H24" s="24">
         <x:v>46083.2521064815</x:v>
       </x:c>
-      <x:c r="I24" s="22">
+      <x:c r="I24" s="27">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="n">
+      <x:c r="J24" s="23" t="n">
         <x:v>1511236</x:v>
       </x:c>
-      <x:c r="K24" s="14" t="n">
+      <x:c r="K24" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="15">
+      <x:c r="L24" s="26">
         <x:v>46097.1628935185</x:v>
       </x:c>
-      <x:c r="M24" s="11" t="s">
+      <x:c r="M24" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="11" t="s">
+      <x:c r="B25" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="s">
+      <x:c r="C25" s="22" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="D25" s="12" t="s">
+      <x:c r="D25" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="s">
+      <x:c r="E25" s="22" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="s">
+      <x:c r="F25" s="22" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G25" s="11" t="s">
+      <x:c r="G25" s="22" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="H25" s="13">
+      <x:c r="H25" s="24">
         <x:v>46069.3341087963</x:v>
       </x:c>
-      <x:c r="I25" s="22">
+      <x:c r="I25" s="27">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J25" s="12" t="n">
+      <x:c r="J25" s="23" t="n">
         <x:v>1511195</x:v>
       </x:c>
-      <x:c r="K25" s="14" t="n">
+      <x:c r="K25" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="15">
+      <x:c r="L25" s="26">
         <x:v>46097.2447337963</x:v>
       </x:c>
-      <x:c r="M25" s="11" t="s">
+      <x:c r="M25" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="11" t="s">
+      <x:c r="B26" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C26" s="11" t="s">
+      <x:c r="C26" s="22" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="D26" s="12" t="s">
+      <x:c r="D26" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="s">
+      <x:c r="E26" s="22" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="F26" s="11" t="s">
+      <x:c r="F26" s="22" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G26" s="11" t="s">
+      <x:c r="G26" s="22" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="H26" s="13">
+      <x:c r="H26" s="24">
         <x:v>46084.1512962963</x:v>
       </x:c>
-      <x:c r="I26" s="22">
+      <x:c r="I26" s="27">
         <x:v>46102</x:v>
       </x:c>
-      <x:c r="J26" s="12" t="n">
+      <x:c r="J26" s="23" t="n">
         <x:v>1511211</x:v>
       </x:c>
-      <x:c r="K26" s="14" t="n">
+      <x:c r="K26" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L26" s="15">
+      <x:c r="L26" s="26">
         <x:v>46097.2494560185</x:v>
       </x:c>
-      <x:c r="M26" s="11" t="s">
+      <x:c r="M26" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="11" t="s">
+      <x:c r="B27" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C27" s="11" t="s">
+      <x:c r="C27" s="22" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="D27" s="12" t="s">
+      <x:c r="D27" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="s">
+      <x:c r="E27" s="22" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="s">
+      <x:c r="F27" s="22" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="G27" s="11" t="s">
+      <x:c r="G27" s="22" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="H27" s="13">
+      <x:c r="H27" s="24">
         <x:v>46073.1135069444</x:v>
       </x:c>
-      <x:c r="I27" s="22">
+      <x:c r="I27" s="27">
         <x:v>45751</x:v>
       </x:c>
-      <x:c r="J27" s="12" t="n">
+      <x:c r="J27" s="23" t="n">
         <x:v>1511213</x:v>
       </x:c>
-      <x:c r="K27" s="14" t="n">
+      <x:c r="K27" s="25" t="n">
         <x:v>7530</x:v>
       </x:c>
-      <x:c r="L27" s="15">
+      <x:c r="L27" s="26">
         <x:v>46097.2511342593</x:v>
       </x:c>
-      <x:c r="M27" s="11" t="s">
+      <x:c r="M27" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="11" t="s">
+      <x:c r="B28" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C28" s="11" t="s">
+      <x:c r="C28" s="22" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="D28" s="12" t="s">
+      <x:c r="D28" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E28" s="11" t="s">
+      <x:c r="E28" s="22" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="F28" s="11" t="s">
+      <x:c r="F28" s="22" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G28" s="11" t="s">
+      <x:c r="G28" s="22" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H28" s="13">
+      <x:c r="H28" s="24">
         <x:v>46084.3311921296</x:v>
       </x:c>
-      <x:c r="I28" s="22">
+      <x:c r="I28" s="27">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J28" s="12" t="n">
+      <x:c r="J28" s="23" t="n">
         <x:v>1511222</x:v>
       </x:c>
-      <x:c r="K28" s="14" t="n">
+      <x:c r="K28" s="25" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L28" s="15">
+      <x:c r="L28" s="26">
         <x:v>46093.366875</x:v>
       </x:c>
-      <x:c r="M28" s="11" t="s">
+      <x:c r="M28" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="11" t="s">
+      <x:c r="B29" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C29" s="11" t="s">
+      <x:c r="C29" s="22" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D29" s="12" t="s">
+      <x:c r="D29" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E29" s="11" t="s">
+      <x:c r="E29" s="22" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="F29" s="11" t="s">
+      <x:c r="F29" s="22" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G29" s="11" t="s">
+      <x:c r="G29" s="22" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="H29" s="13">
+      <x:c r="H29" s="24">
         <x:v>46092.1012731481</x:v>
       </x:c>
-      <x:c r="I29" s="22">
+      <x:c r="I29" s="27">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J29" s="12" t="n">
+      <x:c r="J29" s="23" t="n">
         <x:v>1511231</x:v>
       </x:c>
-      <x:c r="K29" s="14" t="n">
+      <x:c r="K29" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L29" s="15">
+      <x:c r="L29" s="26">
         <x:v>46097.1408217593</x:v>
       </x:c>
-      <x:c r="M29" s="11" t="s">
+      <x:c r="M29" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="11" t="s">
+      <x:c r="B30" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C30" s="11" t="s">
+      <x:c r="C30" s="22" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="D30" s="12" t="s">
+      <x:c r="D30" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E30" s="11" t="s">
+      <x:c r="E30" s="22" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="F30" s="11" t="s">
+      <x:c r="F30" s="22" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="G30" s="11" t="s">
+      <x:c r="G30" s="22" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="H30" s="13">
+      <x:c r="H30" s="24">
         <x:v>46086.1064814815</x:v>
       </x:c>
-      <x:c r="I30" s="22">
+      <x:c r="I30" s="27">
         <x:v>46095</x:v>
       </x:c>
-      <x:c r="J30" s="12" t="n">
+      <x:c r="J30" s="23" t="n">
         <x:v>1511761</x:v>
       </x:c>
-      <x:c r="K30" s="14" t="n">
+      <x:c r="K30" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L30" s="15">
+      <x:c r="L30" s="26">
         <x:v>46090.2765740741</x:v>
       </x:c>
-      <x:c r="M30" s="11" t="s">
+      <x:c r="M30" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="11" t="s">
+      <x:c r="B31" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C31" s="11" t="s">
+      <x:c r="C31" s="22" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D31" s="12" t="s">
+      <x:c r="D31" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E31" s="11" t="s">
+      <x:c r="E31" s="22" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="F31" s="11" t="s">
+      <x:c r="F31" s="22" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G31" s="11" t="s">
+      <x:c r="G31" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="H31" s="13">
+      <x:c r="H31" s="24">
         <x:v>46084.3419444444</x:v>
       </x:c>
-      <x:c r="I31" s="13">
+      <x:c r="I31" s="24">
         <x:v>46084.3419560185</x:v>
       </x:c>
-      <x:c r="J31" s="12" t="n">
+      <x:c r="J31" s="23" t="n">
         <x:v>1507967</x:v>
       </x:c>
-      <x:c r="K31" s="14" t="n">
+      <x:c r="K31" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L31" s="15">
+      <x:c r="L31" s="26">
         <x:v>46090.3480902778</x:v>
       </x:c>
-      <x:c r="M31" s="11" t="s">
+      <x:c r="M31" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="11" t="s">
+      <x:c r="B32" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C32" s="11" t="s">
+      <x:c r="C32" s="22" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D32" s="12" t="s">
+      <x:c r="D32" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E32" s="11" t="s">
+      <x:c r="E32" s="22" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="F32" s="11" t="s">
+      <x:c r="F32" s="22" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="G32" s="11" t="s">
+      <x:c r="G32" s="22" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="H32" s="13">
+      <x:c r="H32" s="24">
         <x:v>46085.1709143519</x:v>
       </x:c>
-      <x:c r="I32" s="13">
+      <x:c r="I32" s="24">
         <x:v>46085.1709375</x:v>
       </x:c>
-      <x:c r="J32" s="12" t="n">
+      <x:c r="J32" s="23" t="n">
         <x:v>1507965</x:v>
       </x:c>
-      <x:c r="K32" s="14" t="n">
+      <x:c r="K32" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L32" s="15">
+      <x:c r="L32" s="26">
         <x:v>46090.3336921296</x:v>
       </x:c>
-      <x:c r="M32" s="11" t="s">
+      <x:c r="M32" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="11" t="s">
+      <x:c r="B33" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C33" s="11" t="s">
+      <x:c r="C33" s="22" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D33" s="12" t="s">
+      <x:c r="D33" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E33" s="11" t="s">
+      <x:c r="E33" s="22" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="F33" s="11" t="s">
+      <x:c r="F33" s="22" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="G33" s="11" t="s">
+      <x:c r="G33" s="22" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H33" s="13">
+      <x:c r="H33" s="24">
         <x:v>46085.16625</x:v>
       </x:c>
-      <x:c r="I33" s="13">
+      <x:c r="I33" s="24">
         <x:v>46085.1662615741</x:v>
       </x:c>
-      <x:c r="J33" s="12" t="n">
+      <x:c r="J33" s="23" t="n">
         <x:v>1507966</x:v>
       </x:c>
-      <x:c r="K33" s="14" t="n">
+      <x:c r="K33" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L33" s="15">
+      <x:c r="L33" s="26">
         <x:v>46090.3437268519</x:v>
       </x:c>
-      <x:c r="M33" s="11" t="s">
+      <x:c r="M33" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="11" t="s">
+      <x:c r="B34" s="22" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C34" s="11" t="s">
+      <x:c r="C34" s="22" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D34" s="12" t="s">
+      <x:c r="D34" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E34" s="11" t="s">
+      <x:c r="E34" s="22" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="F34" s="11" t="s">
+      <x:c r="F34" s="22" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="G34" s="11" t="s">
+      <x:c r="G34" s="22" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="H34" s="13">
+      <x:c r="H34" s="24">
         <x:v>46085.1627430556</x:v>
       </x:c>
-      <x:c r="I34" s="13">
+      <x:c r="I34" s="24">
         <x:v>46085.1627546296</x:v>
       </x:c>
-      <x:c r="J34" s="12" t="n">
+      <x:c r="J34" s="23" t="n">
         <x:v>1507966</x:v>
       </x:c>
-      <x:c r="K34" s="14" t="n">
+      <x:c r="K34" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L34" s="15">
+      <x:c r="L34" s="26">
         <x:v>46090.3453472222</x:v>
       </x:c>
-      <x:c r="M34" s="11" t="s">
+      <x:c r="M34" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="11" t="s">
+      <x:c r="B35" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C35" s="11" t="s">
+      <x:c r="C35" s="22" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="D35" s="12" t="s">
+      <x:c r="D35" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E35" s="11" t="s">
+      <x:c r="E35" s="22" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="F35" s="11" t="s">
+      <x:c r="F35" s="22" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="G35" s="11" t="s">
+      <x:c r="G35" s="22" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="H35" s="13">
+      <x:c r="H35" s="24">
         <x:v>46084.1579513889</x:v>
       </x:c>
-      <x:c r="I35" s="22">
+      <x:c r="I35" s="27">
         <x:v>46145</x:v>
       </x:c>
-      <x:c r="J35" s="12" t="n">
+      <x:c r="J35" s="23" t="n">
         <x:v>1511226</x:v>
       </x:c>
-      <x:c r="K35" s="14" t="n">
+      <x:c r="K35" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L35" s="15">
+      <x:c r="L35" s="26">
         <x:v>46093.4169212963</x:v>
       </x:c>
-      <x:c r="M35" s="11" t="s">
+      <x:c r="M35" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="11" t="s">
+      <x:c r="B36" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C36" s="11" t="s">
+      <x:c r="C36" s="22" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="D36" s="12" t="s">
+      <x:c r="D36" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E36" s="11" t="s">
+      <x:c r="E36" s="22" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="F36" s="11" t="s">
+      <x:c r="F36" s="22" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="G36" s="11" t="s">
+      <x:c r="G36" s="22" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="H36" s="13">
+      <x:c r="H36" s="24">
         <x:v>46084.1080324074</x:v>
       </x:c>
-      <x:c r="I36" s="22">
+      <x:c r="I36" s="27">
         <x:v>46103</x:v>
       </x:c>
-      <x:c r="J36" s="12" t="n">
+      <x:c r="J36" s="23" t="n">
         <x:v>1511208</x:v>
       </x:c>
-      <x:c r="K36" s="14" t="n">
+      <x:c r="K36" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L36" s="15">
+      <x:c r="L36" s="26">
         <x:v>46097.2478125</x:v>
       </x:c>
-      <x:c r="M36" s="11" t="s">
+      <x:c r="M36" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="11" t="s">
+      <x:c r="B37" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C37" s="11" t="s">
+      <x:c r="C37" s="22" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="D37" s="12" t="s">
+      <x:c r="D37" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E37" s="11" t="s">
+      <x:c r="E37" s="22" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="F37" s="11" t="s">
+      <x:c r="F37" s="22" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="G37" s="11" t="s">
+      <x:c r="G37" s="22" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="H37" s="13">
+      <x:c r="H37" s="24">
         <x:v>46083.0787962963</x:v>
       </x:c>
-      <x:c r="I37" s="22">
+      <x:c r="I37" s="27">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J37" s="12" t="n">
+      <x:c r="J37" s="23" t="n">
         <x:v>1511639</x:v>
       </x:c>
-      <x:c r="K37" s="14" t="n">
+      <x:c r="K37" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L37" s="15">
+      <x:c r="L37" s="26">
         <x:v>46083.104224537</x:v>
       </x:c>
-      <x:c r="M37" s="11" t="s">
+      <x:c r="M37" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="11" t="s">
+      <x:c r="B38" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C38" s="11" t="s">
+      <x:c r="C38" s="22" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="D38" s="12" t="s">
+      <x:c r="D38" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E38" s="11" t="s">
+      <x:c r="E38" s="22" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="F38" s="11" t="s">
+      <x:c r="F38" s="22" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="G38" s="11" t="s">
+      <x:c r="G38" s="22" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="H38" s="13">
+      <x:c r="H38" s="24">
         <x:v>46086.1144444444</x:v>
       </x:c>
-      <x:c r="I38" s="22">
+      <x:c r="I38" s="27">
         <x:v>46097</x:v>
       </x:c>
-      <x:c r="J38" s="12" t="n">
+      <x:c r="J38" s="23" t="n">
         <x:v>1511759</x:v>
       </x:c>
-      <x:c r="K38" s="14" t="n">
+      <x:c r="K38" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L38" s="15">
+      <x:c r="L38" s="26">
         <x:v>46090.2703703704</x:v>
       </x:c>
-      <x:c r="M38" s="11" t="s">
+      <x:c r="M38" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="11" t="s">
+      <x:c r="B39" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C39" s="11" t="s">
+      <x:c r="C39" s="22" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="D39" s="12" t="s">
+      <x:c r="D39" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E39" s="11" t="s">
+      <x:c r="E39" s="22" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="F39" s="11" t="s">
+      <x:c r="F39" s="22" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="G39" s="11" t="s">
+      <x:c r="G39" s="22" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="H39" s="13">
+      <x:c r="H39" s="24">
         <x:v>46087.1643287037</x:v>
       </x:c>
-      <x:c r="I39" s="22">
+      <x:c r="I39" s="27">
         <x:v>46104</x:v>
       </x:c>
-      <x:c r="J39" s="12" t="n">
+      <x:c r="J39" s="23" t="n">
         <x:v>1511760</x:v>
       </x:c>
-      <x:c r="K39" s="14" t="n">
+      <x:c r="K39" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L39" s="15">
+      <x:c r="L39" s="26">
         <x:v>46090.2727777778</x:v>
       </x:c>
-      <x:c r="M39" s="11" t="s">
+      <x:c r="M39" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="11" t="s">
+      <x:c r="B40" s="22" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C40" s="11" t="s">
+      <x:c r="C40" s="22" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="D40" s="12" t="s">
+      <x:c r="D40" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E40" s="11" t="s">
+      <x:c r="E40" s="22" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="F40" s="11" t="s">
+      <x:c r="F40" s="22" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G40" s="11" t="s">
+      <x:c r="G40" s="22" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="H40" s="13">
+      <x:c r="H40" s="24">
         <x:v>46086.0997916667</x:v>
       </x:c>
-      <x:c r="I40" s="22">
+      <x:c r="I40" s="27">
         <x:v>46098</x:v>
       </x:c>
-      <x:c r="J40" s="12" t="n">
+      <x:c r="J40" s="23" t="n">
         <x:v>1511758</x:v>
       </x:c>
-      <x:c r="K40" s="14" t="n">
+      <x:c r="K40" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L40" s="15">
+      <x:c r="L40" s="26">
         <x:v>46090.2691087963</x:v>
       </x:c>
-      <x:c r="M40" s="11" t="s">
+      <x:c r="M40" s="22" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="11" t="s">
+      <x:c r="B41" s="22" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C41" s="11" t="s">
+      <x:c r="C41" s="22" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="D41" s="12" t="s">
+      <x:c r="D41" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E41" s="11" t="s">
+      <x:c r="E41" s="22" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="F41" s="11" t="s">
+      <x:c r="F41" s="22" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="G41" s="11" t="s">
+      <x:c r="G41" s="22" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="H41" s="13">
+      <x:c r="H41" s="24">
         <x:v>46092.9637847222</x:v>
       </x:c>
-      <x:c r="I41" s="22">
+      <x:c r="I41" s="27">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J41" s="12" t="n">
+      <x:c r="J41" s="23" t="n">
         <x:v>1511219</x:v>
       </x:c>
-      <x:c r="K41" s="14" t="n">
+      <x:c r="K41" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L41" s="15">
+      <x:c r="L41" s="26">
         <x:v>46093.3109375</x:v>
       </x:c>
-      <x:c r="M41" s="11" t="s">
+      <x:c r="M41" s="22" t="s">
         <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="11" t="s">
+      <x:c r="B42" s="22" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C42" s="11" t="s">
+      <x:c r="C42" s="22" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="D42" s="12" t="s">
+      <x:c r="D42" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E42" s="11" t="s">
+      <x:c r="E42" s="22" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="F42" s="11" t="s">
+      <x:c r="F42" s="22" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="G42" s="11" t="s">
+      <x:c r="G42" s="22" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="H42" s="13">
+      <x:c r="H42" s="24">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I42" s="22">
+      <x:c r="I42" s="27">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J42" s="12" t="n">
+      <x:c r="J42" s="23" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K42" s="14" t="n">
+      <x:c r="K42" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L42" s="15">
+      <x:c r="L42" s="26">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M42" s="11" t="s">
+      <x:c r="M42" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="23" t="s">
+    <x:row r="43" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B43" s="28" t="s"/>
+      <x:c r="C43" s="28" t="s"/>
+      <x:c r="D43" s="28" t="s"/>
+      <x:c r="E43" s="28" t="s"/>
+      <x:c r="F43" s="28" t="s"/>
+      <x:c r="G43" s="28" t="s"/>
+      <x:c r="H43" s="28" t="s"/>
+      <x:c r="I43" s="28" t="s"/>
+      <x:c r="J43" s="28" t="s"/>
+      <x:c r="K43" s="28" t="s"/>
+      <x:c r="L43" s="28" t="s"/>
+      <x:c r="M43" s="28" t="s"/>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B44" s="28" t="s"/>
+      <x:c r="C44" s="28" t="s"/>
+      <x:c r="D44" s="28" t="s"/>
+      <x:c r="E44" s="28" t="s"/>
+      <x:c r="F44" s="28" t="s"/>
+      <x:c r="G44" s="28" t="s"/>
+      <x:c r="H44" s="28" t="s"/>
+      <x:c r="I44" s="28" t="s"/>
+      <x:c r="J44" s="28" t="s"/>
+      <x:c r="K44" s="28" t="s"/>
+      <x:c r="L44" s="28" t="s"/>
+      <x:c r="M44" s="28" t="s"/>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B47" s="29" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="C45" s="24" t="s"/>
-      <x:c r="D45" s="24" t="s"/>
-      <x:c r="E45" s="25" t="s"/>
-      <x:c r="F45" s="25" t="s"/>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="26" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C46" s="27" t="s"/>
-      <x:c r="D46" s="27" t="s"/>
-      <x:c r="E46" s="27" t="s"/>
-      <x:c r="F46" s="28" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="29" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="C47" s="30" t="s"/>
       <x:c r="D47" s="30" t="s"/>
-      <x:c r="E47" s="30" t="s"/>
-      <x:c r="F47" s="31" t="n">
+      <x:c r="E47" s="31" t="s"/>
+      <x:c r="F47" s="31" t="s"/>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B48" s="32" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C48" s="33" t="s"/>
+      <x:c r="D48" s="33" t="s"/>
+      <x:c r="E48" s="33" t="s"/>
+      <x:c r="F48" s="34" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="35" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C49" s="36" t="s"/>
+      <x:c r="D49" s="36" t="s"/>
+      <x:c r="E49" s="36" t="s"/>
+      <x:c r="F49" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="29" t="s">
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="35" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C48" s="30" t="s"/>
-      <x:c r="D48" s="30" t="s"/>
-      <x:c r="E48" s="30" t="s"/>
-      <x:c r="F48" s="31" t="n">
+      <x:c r="C50" s="36" t="s"/>
+      <x:c r="D50" s="36" t="s"/>
+      <x:c r="E50" s="36" t="s"/>
+      <x:c r="F50" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="29" t="s">
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="35" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C49" s="30" t="s"/>
-      <x:c r="D49" s="30" t="s"/>
-      <x:c r="E49" s="30" t="s"/>
-      <x:c r="F49" s="31" t="n">
+      <x:c r="C51" s="36" t="s"/>
+      <x:c r="D51" s="36" t="s"/>
+      <x:c r="E51" s="36" t="s"/>
+      <x:c r="F51" s="37" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="29" t="s">
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="35" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C50" s="30" t="s"/>
-      <x:c r="D50" s="30" t="s"/>
-      <x:c r="E50" s="30" t="s"/>
-      <x:c r="F50" s="31" t="n">
+      <x:c r="C52" s="36" t="s"/>
+      <x:c r="D52" s="36" t="s"/>
+      <x:c r="E52" s="36" t="s"/>
+      <x:c r="F52" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="29" t="s">
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="35" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C51" s="30" t="s"/>
-      <x:c r="D51" s="30" t="s"/>
-      <x:c r="E51" s="30" t="s"/>
-      <x:c r="F51" s="31" t="n">
+      <x:c r="C53" s="36" t="s"/>
+      <x:c r="D53" s="36" t="s"/>
+      <x:c r="E53" s="36" t="s"/>
+      <x:c r="F53" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="29" t="s">
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="35" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C52" s="30" t="s"/>
-      <x:c r="D52" s="30" t="s"/>
-      <x:c r="E52" s="30" t="s"/>
-      <x:c r="F52" s="31" t="n">
+      <x:c r="C54" s="36" t="s"/>
+      <x:c r="D54" s="36" t="s"/>
+      <x:c r="E54" s="36" t="s"/>
+      <x:c r="F54" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B53" s="32" t="s">
+    <x:row r="55" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B55" s="38" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C53" s="33" t="s"/>
-      <x:c r="D53" s="33" t="s"/>
-      <x:c r="E53" s="33" t="s"/>
-      <x:c r="F53" s="34" t="n">
+      <x:c r="C55" s="39" t="s"/>
+      <x:c r="D55" s="39" t="s"/>
+      <x:c r="E55" s="39" t="s"/>
+      <x:c r="F55" s="40" t="n">
         <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6727,18 +6804,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B45:F45"/>
-    <x:mergeCell ref="B46:E46"/>
-    <x:mergeCell ref="B47:E47"/>
+  <x:mergeCells count="12">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B47:F47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B55:E55"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
   <x:si>
     <x:t>PERMIT SUMMARY</x:t>
   </x:si>
@@ -553,6 +553,24 @@
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
     <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
   </x:si>
   <x:si>
@@ -562,24 +580,6 @@
     <x:t>43A-2-2026-1144-933</x:t>
   </x:si>
   <x:si>
-    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1150-325</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0780 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1151-716</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -607,6 +607,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -616,15 +625,6 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
-    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-020R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1156-896</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -637,6 +637,24 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -646,24 +664,6 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -688,6 +688,18 @@
     <x:t>43A-3-2026-1152-831</x:t>
   </x:si>
   <x:si>
+    <x:t>MOBILECRAZE TELECOM INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-06-0809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1159-651</x:t>
+  </x:si>
+  <x:si>
     <x:t>ONE DOTCOM CELL INC.</x:t>
   </x:si>
   <x:si>
@@ -715,9 +727,6 @@
     <x:t>SYNCNETIC INC</x:t>
   </x:si>
   <x:si>
-    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-MP-24-468R</x:t>
   </x:si>
   <x:si>
@@ -727,6 +736,24 @@
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>LEVEL 3 0118, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-18-05-0718</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1083-282</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-02-25-0452R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
     <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -736,15 +763,6 @@
     <x:t>43A-2-2026-1108-762</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-02-25-0452R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1168-173</x:t>
-  </x:si>
-  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -754,6 +772,18 @@
     <x:t>43A-3-2026-1192-904</x:t>
   </x:si>
   <x:si>
+    <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3, 306A, BRGY. TEJERO, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-05-0452-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1084-395</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -769,6 +799,24 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
     <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
   </x:si>
   <x:si>
@@ -778,24 +826,6 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1171-081</x:t>
-  </x:si>
-  <x:si>
     <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
   </x:si>
   <x:si>
@@ -838,6 +868,15 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -854,15 +893,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1176-385</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-03-2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
@@ -1741,7 +1771,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1809,7 +1839,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>
@@ -4301,7 +4331,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -4369,7 +4399,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>
@@ -4542,19 +4572,19 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H11" s="24">
-        <x:v>46080.4532523148</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I11" s="27">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J11" s="23" t="n">
-        <x:v>1511232</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K11" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="26">
-        <x:v>46097.1461689815</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M11" s="22" t="s">
         <x:v>167</x:v>
@@ -4618,19 +4648,19 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="H13" s="24">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46080.4532523148</x:v>
       </x:c>
       <x:c r="I13" s="27">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J13" s="23" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511232</x:v>
       </x:c>
       <x:c r="K13" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="26">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M13" s="22" t="s">
         <x:v>167</x:v>
@@ -4732,19 +4762,19 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="H16" s="24">
-        <x:v>46084.0854513889</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I16" s="27">
-        <x:v>46144</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J16" s="23" t="n">
-        <x:v>1511225</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K16" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="26">
-        <x:v>46093.3956365741</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M16" s="22" t="s">
         <x:v>167</x:v>
@@ -4770,19 +4800,19 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="H17" s="24">
-        <x:v>46084.0996759259</x:v>
+        <x:v>46084.0854513889</x:v>
       </x:c>
       <x:c r="I17" s="27">
-        <x:v>46094</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J17" s="23" t="n">
-        <x:v>1511192</x:v>
+        <x:v>1511225</x:v>
       </x:c>
       <x:c r="K17" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="26">
-        <x:v>46097.2414583333</x:v>
+        <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M17" s="22" t="s">
         <x:v>167</x:v>
@@ -4846,19 +4876,19 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="H19" s="24">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I19" s="27">
-        <x:v>46133</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J19" s="23" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K19" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="26">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M19" s="22" t="s">
         <x:v>167</x:v>
@@ -4922,19 +4952,19 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H21" s="24">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I21" s="27">
-        <x:v>46035</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J21" s="23" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K21" s="25" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="26">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M21" s="22" t="s">
         <x:v>167</x:v>
@@ -5036,19 +5066,19 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="H24" s="24">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I24" s="27">
-        <x:v>46100</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J24" s="23" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K24" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="26">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M24" s="22" t="s">
         <x:v>167</x:v>
@@ -5074,19 +5104,19 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="H25" s="24">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I25" s="27">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J25" s="23" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K25" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="26">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M25" s="22" t="s">
         <x:v>167</x:v>
@@ -5112,19 +5142,19 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H26" s="24">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I26" s="27">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J26" s="23" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K26" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="26">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M26" s="22" t="s">
         <x:v>167</x:v>
@@ -5141,28 +5171,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E27" s="22" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F27" s="22" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="F27" s="22" t="s">
+      <x:c r="G27" s="22" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="G27" s="22" t="s">
-        <x:v>236</x:v>
-      </x:c>
       <x:c r="H27" s="24">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I27" s="27">
-        <x:v>45751</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J27" s="23" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K27" s="25" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="26">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M27" s="22" t="s">
         <x:v>167</x:v>
@@ -5173,7 +5203,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="22" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D28" s="23" t="s">
         <x:v>40</x:v>
@@ -5188,19 +5218,19 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="H28" s="24">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I28" s="27">
-        <x:v>46070</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J28" s="23" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K28" s="25" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="26">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M28" s="22" t="s">
         <x:v>167</x:v>
@@ -5211,7 +5241,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C29" s="22" t="s">
-        <x:v>56</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D29" s="23" t="s">
         <x:v>40</x:v>
@@ -5226,19 +5256,19 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="H29" s="24">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I29" s="27">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J29" s="23" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K29" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L29" s="26">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M29" s="22" t="s">
         <x:v>167</x:v>
@@ -5249,124 +5279,124 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C30" s="22" t="s">
-        <x:v>243</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D30" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E30" s="22" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F30" s="22" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="F30" s="22" t="s">
+      <x:c r="G30" s="22" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="G30" s="22" t="s">
-        <x:v>246</x:v>
-      </x:c>
       <x:c r="H30" s="24">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I30" s="27">
-        <x:v>46095</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J30" s="23" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K30" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L30" s="26">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M30" s="22" t="s">
-        <x:v>66</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B31" s="22" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C31" s="22" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D31" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E31" s="22" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="F31" s="22" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D31" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E31" s="22" t="s">
+      <x:c r="G31" s="22" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="F31" s="22" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G31" s="22" t="s">
-        <x:v>250</x:v>
-      </x:c>
       <x:c r="H31" s="24">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I31" s="24">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I31" s="27">
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J31" s="23" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K31" s="25" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="26">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M31" s="22" t="s">
-        <x:v>11</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B32" s="22" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C32" s="22" t="s">
-        <x:v>247</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="D32" s="23" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E32" s="22" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F32" s="22" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="F32" s="22" t="s">
+      <x:c r="G32" s="22" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="G32" s="22" t="s">
-        <x:v>253</x:v>
-      </x:c>
       <x:c r="H32" s="24">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I32" s="24">
-        <x:v>46085.1709375</x:v>
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I32" s="27">
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J32" s="23" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K32" s="25" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L32" s="26">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M32" s="22" t="s">
-        <x:v>11</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B33" s="22" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C33" s="22" t="s">
-        <x:v>247</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D33" s="23" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E33" s="22" t="s">
         <x:v>254</x:v>
@@ -5378,22 +5408,22 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="H33" s="24">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I33" s="24">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I33" s="27">
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J33" s="23" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K33" s="25" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="26">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M33" s="22" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5401,25 +5431,25 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C34" s="22" t="s">
-        <x:v>247</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D34" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E34" s="22" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="F34" s="22" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G34" s="22" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H34" s="24">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I34" s="24">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J34" s="23" t="n">
         <x:v>1507966</x:v>
@@ -5428,7 +5458,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L34" s="26">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M34" s="22" t="s">
         <x:v>11</x:v>
@@ -5436,13 +5466,13 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B35" s="22" t="s">
-        <x:v>75</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C35" s="22" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D35" s="23" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E35" s="22" t="s">
         <x:v>261</x:v>
@@ -5454,33 +5484,33 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="H35" s="24">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I35" s="27">
-        <x:v>46145</x:v>
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I35" s="24">
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J35" s="23" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K35" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L35" s="26">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M35" s="22" t="s">
-        <x:v>167</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B36" s="22" t="s">
-        <x:v>75</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C36" s="22" t="s">
-        <x:v>193</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D36" s="23" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E36" s="22" t="s">
         <x:v>264</x:v>
@@ -5492,60 +5522,60 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="H36" s="24">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I36" s="27">
-        <x:v>46103</x:v>
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I36" s="24">
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J36" s="23" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K36" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L36" s="26">
-        <x:v>46097.2478125</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M36" s="22" t="s">
-        <x:v>167</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B37" s="22" t="s">
-        <x:v>75</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="22" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D37" s="23" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E37" s="22" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="D37" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E37" s="22" t="s">
+      <x:c r="F37" s="22" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="F37" s="22" t="s">
+      <x:c r="G37" s="22" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="G37" s="22" t="s">
-        <x:v>270</x:v>
-      </x:c>
       <x:c r="H37" s="24">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I37" s="27">
-        <x:v>46084</x:v>
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I37" s="24">
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J37" s="23" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K37" s="25" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L37" s="26">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M37" s="22" t="s">
-        <x:v>66</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -5553,7 +5583,7 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="C38" s="22" t="s">
-        <x:v>243</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D38" s="23" t="s">
         <x:v>40</x:v>
@@ -5568,22 +5598,22 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="H38" s="24">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I38" s="27">
-        <x:v>46097</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J38" s="23" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K38" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="26">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M38" s="22" t="s">
-        <x:v>66</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -5591,7 +5621,7 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="C39" s="22" t="s">
-        <x:v>243</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D39" s="23" t="s">
         <x:v>40</x:v>
@@ -5606,22 +5636,22 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="H39" s="24">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I39" s="27">
-        <x:v>46104</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J39" s="23" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K39" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="26">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M39" s="22" t="s">
-        <x:v>66</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
@@ -5629,34 +5659,34 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="C40" s="22" t="s">
-        <x:v>243</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D40" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E40" s="22" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F40" s="22" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="G40" s="22" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="H40" s="24">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I40" s="27">
-        <x:v>46098</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J40" s="23" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K40" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L40" s="26">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M40" s="22" t="s">
         <x:v>66</x:v>
@@ -5664,10 +5694,10 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B41" s="22" t="s">
-        <x:v>125</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C41" s="22" t="s">
-        <x:v>280</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D41" s="23" t="s">
         <x:v>40</x:v>
@@ -5682,192 +5712,303 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="H41" s="24">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I41" s="27">
-        <x:v>46094</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J41" s="23" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K41" s="25" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L41" s="26">
-        <x:v>46093.3109375</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M41" s="22" t="s">
-        <x:v>167</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B42" s="22" t="s">
-        <x:v>125</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C42" s="22" t="s">
-        <x:v>284</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D42" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E42" s="22" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F42" s="22" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="F42" s="22" t="s">
+      <x:c r="G42" s="22" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="G42" s="22" t="s">
+      <x:c r="H42" s="24">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I42" s="27">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J42" s="23" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K42" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L42" s="26">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M42" s="22" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="22" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C43" s="22" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="D43" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E43" s="22" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="H42" s="24">
+      <x:c r="F43" s="22" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G43" s="22" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="H43" s="24">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I43" s="27">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J43" s="23" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K43" s="25" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="26">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M43" s="22" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="22" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C44" s="22" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D44" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E44" s="22" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="F44" s="22" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="G44" s="22" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H44" s="24">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I44" s="27">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J44" s="23" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K44" s="25" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L44" s="26">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M44" s="22" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="22" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C45" s="22" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="D45" s="23" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E45" s="22" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F45" s="22" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="G45" s="22" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H45" s="24">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I42" s="27">
+      <x:c r="I45" s="27">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J42" s="23" t="n">
+      <x:c r="J45" s="23" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K42" s="25" t="n">
+      <x:c r="K45" s="25" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L42" s="26">
+      <x:c r="L45" s="26">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M42" s="22" t="s">
+      <x:c r="M45" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B43" s="28" t="s"/>
-      <x:c r="C43" s="28" t="s"/>
-      <x:c r="D43" s="28" t="s"/>
-      <x:c r="E43" s="28" t="s"/>
-      <x:c r="F43" s="28" t="s"/>
-      <x:c r="G43" s="28" t="s"/>
-      <x:c r="H43" s="28" t="s"/>
-      <x:c r="I43" s="28" t="s"/>
-      <x:c r="J43" s="28" t="s"/>
-      <x:c r="K43" s="28" t="s"/>
-      <x:c r="L43" s="28" t="s"/>
-      <x:c r="M43" s="28" t="s"/>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B44" s="28" t="s"/>
-      <x:c r="C44" s="28" t="s"/>
-      <x:c r="D44" s="28" t="s"/>
-      <x:c r="E44" s="28" t="s"/>
-      <x:c r="F44" s="28" t="s"/>
-      <x:c r="G44" s="28" t="s"/>
-      <x:c r="H44" s="28" t="s"/>
-      <x:c r="I44" s="28" t="s"/>
-      <x:c r="J44" s="28" t="s"/>
-      <x:c r="K44" s="28" t="s"/>
-      <x:c r="L44" s="28" t="s"/>
-      <x:c r="M44" s="28" t="s"/>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B47" s="29" t="s">
+    <x:row r="46" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B46" s="28" t="s"/>
+      <x:c r="C46" s="28" t="s"/>
+      <x:c r="D46" s="28" t="s"/>
+      <x:c r="E46" s="28" t="s"/>
+      <x:c r="F46" s="28" t="s"/>
+      <x:c r="G46" s="28" t="s"/>
+      <x:c r="H46" s="28" t="s"/>
+      <x:c r="I46" s="28" t="s"/>
+      <x:c r="J46" s="28" t="s"/>
+      <x:c r="K46" s="28" t="s"/>
+      <x:c r="L46" s="28" t="s"/>
+      <x:c r="M46" s="28" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B47" s="28" t="s"/>
+      <x:c r="C47" s="28" t="s"/>
+      <x:c r="D47" s="28" t="s"/>
+      <x:c r="E47" s="28" t="s"/>
+      <x:c r="F47" s="28" t="s"/>
+      <x:c r="G47" s="28" t="s"/>
+      <x:c r="H47" s="28" t="s"/>
+      <x:c r="I47" s="28" t="s"/>
+      <x:c r="J47" s="28" t="s"/>
+      <x:c r="K47" s="28" t="s"/>
+      <x:c r="L47" s="28" t="s"/>
+      <x:c r="M47" s="28" t="s"/>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B50" s="29" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="C47" s="30" t="s"/>
-      <x:c r="D47" s="30" t="s"/>
-      <x:c r="E47" s="31" t="s"/>
-      <x:c r="F47" s="31" t="s"/>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B48" s="32" t="s">
+      <x:c r="C50" s="30" t="s"/>
+      <x:c r="D50" s="30" t="s"/>
+      <x:c r="E50" s="31" t="s"/>
+      <x:c r="F50" s="31" t="s"/>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B51" s="32" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="C48" s="33" t="s"/>
-      <x:c r="D48" s="33" t="s"/>
-      <x:c r="E48" s="33" t="s"/>
-      <x:c r="F48" s="34" t="s">
+      <x:c r="C51" s="33" t="s"/>
+      <x:c r="D51" s="33" t="s"/>
+      <x:c r="E51" s="33" t="s"/>
+      <x:c r="F51" s="34" t="s">
         <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="35" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C49" s="36" t="s"/>
-      <x:c r="D49" s="36" t="s"/>
-      <x:c r="E49" s="36" t="s"/>
-      <x:c r="F49" s="37" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="35" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C50" s="36" t="s"/>
-      <x:c r="D50" s="36" t="s"/>
-      <x:c r="E50" s="36" t="s"/>
-      <x:c r="F50" s="37" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="35" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C51" s="36" t="s"/>
-      <x:c r="D51" s="36" t="s"/>
-      <x:c r="E51" s="36" t="s"/>
-      <x:c r="F51" s="37" t="n">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
       <x:c r="B52" s="35" t="s">
-        <x:v>61</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C52" s="36" t="s"/>
       <x:c r="D52" s="36" t="s"/>
       <x:c r="E52" s="36" t="s"/>
       <x:c r="F52" s="37" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
       <x:c r="B53" s="35" t="s">
-        <x:v>75</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C53" s="36" t="s"/>
       <x:c r="D53" s="36" t="s"/>
       <x:c r="E53" s="36" t="s"/>
       <x:c r="F53" s="37" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
       <x:c r="B54" s="35" t="s">
-        <x:v>125</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C54" s="36" t="s"/>
       <x:c r="D54" s="36" t="s"/>
       <x:c r="E54" s="36" t="s"/>
       <x:c r="F54" s="37" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="35" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C55" s="36" t="s"/>
+      <x:c r="D55" s="36" t="s"/>
+      <x:c r="E55" s="36" t="s"/>
+      <x:c r="F55" s="37" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="35" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C56" s="36" t="s"/>
+      <x:c r="D56" s="36" t="s"/>
+      <x:c r="E56" s="36" t="s"/>
+      <x:c r="F56" s="37" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="35" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C57" s="36" t="s"/>
+      <x:c r="D57" s="36" t="s"/>
+      <x:c r="E57" s="36" t="s"/>
+      <x:c r="F57" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="38" t="s">
+    <x:row r="58" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B58" s="38" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C55" s="39" t="s"/>
-      <x:c r="D55" s="39" t="s"/>
-      <x:c r="E55" s="39" t="s"/>
-      <x:c r="F55" s="40" t="n">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C58" s="39" t="s"/>
+      <x:c r="D58" s="39" t="s"/>
+      <x:c r="E58" s="39" t="s"/>
+      <x:c r="F58" s="40" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
     <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6808,15 +6949,15 @@
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
     <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B47:F47"/>
-    <x:mergeCell ref="B48:E48"/>
-    <x:mergeCell ref="B49:E49"/>
-    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B50:F50"/>
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B57:E57"/>
+    <x:mergeCell ref="B58:E58"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,9 +23,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
   <x:si>
     <x:t>PERMIT SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -926,7 +962,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -971,21 +1007,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -995,6 +1016,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -1245,7 +1273,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1256,10 +1284,16 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1268,62 +1302,50 @@
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1354,56 +1376,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1418,63 +1392,75 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1773,18 +1759,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1802,1470 +1776,1482 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46069.1133333333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s"/>
-      <x:c r="E8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="F8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46069.0835185185</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46069.1006712963</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1506161</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46069.1133333333</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46069.0835648148</x:v>
       </x:c>
-      <x:c r="I8" s="20">
+      <x:c r="I10" s="16">
         <x:v>46069.1000231481</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1506159</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="18">
         <x:v>46069.1128587963</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s"/>
-      <x:c r="E9" s="19" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46072.1720833333</x:v>
       </x:c>
-      <x:c r="I9" s="20">
+      <x:c r="I11" s="16">
         <x:v>46072.235162037</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1507783</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="18">
         <x:v>46073.1890277778</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="22" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D10" s="23" t="s"/>
-      <x:c r="E10" s="22" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H10" s="24">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46063.2819560185</x:v>
       </x:c>
-      <x:c r="I10" s="24">
+      <x:c r="I12" s="16">
         <x:v>46063.2922685185</x:v>
       </x:c>
-      <x:c r="J10" s="23" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1507682</x:v>
       </x:c>
-      <x:c r="K10" s="25" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="26">
+      <x:c r="L12" s="18">
         <x:v>46063.2957638889</x:v>
       </x:c>
-      <x:c r="M10" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D11" s="23" t="s"/>
-      <x:c r="E11" s="22" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F11" s="22" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G11" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H11" s="24">
+      <x:c r="M12" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46058.4859837963</x:v>
       </x:c>
-      <x:c r="I11" s="24">
+      <x:c r="I13" s="16">
         <x:v>46062.157025463</x:v>
       </x:c>
-      <x:c r="J11" s="23" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1507672</x:v>
       </x:c>
-      <x:c r="K11" s="25" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="26">
+      <x:c r="L13" s="18">
         <x:v>46062.1881944444</x:v>
       </x:c>
-      <x:c r="M11" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D12" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E12" s="22" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F12" s="22" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G12" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H12" s="24">
+      <x:c r="M13" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>46067.3600231481</x:v>
       </x:c>
-      <x:c r="I12" s="24">
+      <x:c r="I14" s="16">
         <x:v>46067.3600462963</x:v>
       </x:c>
-      <x:c r="J12" s="23" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K12" s="25" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="26">
+      <x:c r="L14" s="18">
         <x:v>46079.2730092593</x:v>
       </x:c>
-      <x:c r="M12" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D13" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E13" s="22" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F13" s="22" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G13" s="22" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H13" s="24">
+      <x:c r="M14" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I13" s="24">
+      <x:c r="I15" s="16">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J13" s="23" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K13" s="25" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="26">
+      <x:c r="L15" s="18">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M13" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D14" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E14" s="22" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="M15" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G14" s="22" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H14" s="24">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I14" s="27">
+      <x:c r="E21" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J14" s="23" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K14" s="25" t="n">
+      <x:c r="J25" s="15" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="26">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M14" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D15" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E15" s="22" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F15" s="22" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G15" s="22" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H15" s="24">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I15" s="27">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J15" s="23" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K15" s="25" t="n">
+      <x:c r="L25" s="18">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="26">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M15" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D16" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E16" s="22" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F16" s="22" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G16" s="22" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H16" s="24">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I16" s="27">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J16" s="23" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K16" s="25" t="n">
+      <x:c r="L26" s="18">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="26">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M16" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s">
+      <x:c r="L27" s="18">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D17" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E17" s="22" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F17" s="22" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G17" s="22" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H17" s="24">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I17" s="27">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J17" s="23" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K17" s="25" t="n">
+      <x:c r="E28" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I28" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="26">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M17" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D18" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E18" s="22" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F18" s="22" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G18" s="22" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H18" s="24">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I18" s="27">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J18" s="23" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K18" s="25" t="n">
+      <x:c r="L28" s="18">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I29" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="26">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M18" s="22" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D19" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E19" s="22" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F19" s="22" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G19" s="22" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H19" s="24">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I19" s="24">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J19" s="23" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K19" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L19" s="26">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M19" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D20" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E20" s="22" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F20" s="22" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G20" s="22" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H20" s="24">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I20" s="24">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J20" s="23" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K20" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L20" s="26">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M20" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C21" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D21" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E21" s="22" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F21" s="22" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G21" s="22" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H21" s="24">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I21" s="24">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J21" s="23" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K21" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L21" s="26">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M21" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C22" s="22" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D22" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E22" s="22" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F22" s="22" t="s">
+      <x:c r="L29" s="18">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G22" s="22" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H22" s="24">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I22" s="27">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J22" s="23" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K22" s="25" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L22" s="26">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M22" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C23" s="22" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D23" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E23" s="22" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F23" s="22" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G23" s="22" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H23" s="24">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I23" s="27">
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I30" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J23" s="23" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K23" s="25" t="n">
+      <x:c r="J30" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="26">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M23" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C24" s="22" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D24" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E24" s="22" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F24" s="22" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G24" s="22" t="s">
+      <x:c r="L30" s="18">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="H24" s="24">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I24" s="27">
+      <x:c r="C31" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I31" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J24" s="23" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K24" s="25" t="n">
+      <x:c r="J31" s="15" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="26">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M24" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C25" s="22" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D25" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E25" s="22" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F25" s="22" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G25" s="22" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H25" s="24">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I25" s="27">
+      <x:c r="L31" s="18">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I32" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J25" s="23" t="n">
+      <x:c r="J32" s="15" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K25" s="25" t="n">
+      <x:c r="K32" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="26">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M25" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D26" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E26" s="22" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F26" s="22" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G26" s="22" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H26" s="24">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I26" s="27">
+      <x:c r="L32" s="18">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I33" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J26" s="23" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K26" s="25" t="n">
+      <x:c r="J33" s="15" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L26" s="26">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M26" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C27" s="22" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D27" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E27" s="22" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F27" s="22" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G27" s="22" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H27" s="24">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I27" s="27">
+      <x:c r="L33" s="18">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I34" s="19">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J27" s="23" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K27" s="25" t="n">
+      <x:c r="J34" s="15" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L27" s="26">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M27" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C28" s="22" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D28" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E28" s="22" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F28" s="22" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G28" s="22" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H28" s="24">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I28" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="23" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K28" s="25" t="n">
+      <x:c r="L34" s="18">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I35" s="19">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L28" s="26">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M28" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C29" s="22" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D29" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E29" s="22" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F29" s="22" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G29" s="22" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H29" s="24">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I29" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="23" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K29" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="26">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M29" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C30" s="22" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D30" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E30" s="22" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F30" s="22" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G30" s="22" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H30" s="24">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I30" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="23" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K30" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="26">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M30" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C31" s="22" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D31" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E31" s="22" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F31" s="22" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G31" s="22" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H31" s="24">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I31" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="23" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K31" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="26">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M31" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C32" s="22" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D32" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E32" s="22" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F32" s="22" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G32" s="22" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="H32" s="24">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I32" s="27">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="23" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K32" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="26">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M32" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C33" s="22" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D33" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E33" s="22" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F33" s="22" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G33" s="22" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H33" s="24">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I33" s="27">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J33" s="23" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K33" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="26">
+      <x:c r="L35" s="18">
         <x:v>46077.1078819444</x:v>
       </x:c>
-      <x:c r="M33" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="22" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C34" s="22" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D34" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E34" s="22" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F34" s="22" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G34" s="22" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H34" s="24">
+      <x:c r="M35" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
         <x:v>46062.1590162037</x:v>
       </x:c>
-      <x:c r="I34" s="24">
+      <x:c r="I36" s="16">
         <x:v>46062.1590277778</x:v>
       </x:c>
-      <x:c r="J34" s="23" t="n">
+      <x:c r="J36" s="15" t="n">
         <x:v>1510925</x:v>
       </x:c>
-      <x:c r="K34" s="25" t="n">
+      <x:c r="K36" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L34" s="26">
+      <x:c r="L36" s="18">
         <x:v>46062.1863194444</x:v>
       </x:c>
-      <x:c r="M34" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="22" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C35" s="22" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D35" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E35" s="22" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F35" s="22" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G35" s="22" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H35" s="24">
+      <x:c r="M36" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
         <x:v>46066.2180208333</x:v>
       </x:c>
-      <x:c r="I35" s="27">
+      <x:c r="I37" s="19">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J35" s="23" t="n">
+      <x:c r="J37" s="15" t="n">
         <x:v>1507743</x:v>
       </x:c>
-      <x:c r="K35" s="25" t="n">
+      <x:c r="K37" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L35" s="26">
+      <x:c r="L37" s="18">
         <x:v>46066.2724421296</x:v>
       </x:c>
-      <x:c r="M35" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="22" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C36" s="22" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D36" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E36" s="22" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F36" s="22" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G36" s="22" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H36" s="24">
+      <x:c r="M37" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
         <x:v>46071.0492476852</x:v>
       </x:c>
-      <x:c r="I36" s="27">
+      <x:c r="I38" s="19">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J36" s="23" t="n">
+      <x:c r="J38" s="15" t="n">
         <x:v>1511502</x:v>
       </x:c>
-      <x:c r="K36" s="25" t="n">
+      <x:c r="K38" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L36" s="26">
+      <x:c r="L38" s="18">
         <x:v>46071.0606134259</x:v>
       </x:c>
-      <x:c r="M36" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="22" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C37" s="22" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D37" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E37" s="22" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F37" s="22" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G37" s="22" t="s">
+      <x:c r="M38" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="14" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="H37" s="24">
+      <x:c r="C39" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
         <x:v>46066.2275347222</x:v>
       </x:c>
-      <x:c r="I37" s="27">
+      <x:c r="I39" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J37" s="23" t="n">
+      <x:c r="J39" s="15" t="n">
         <x:v>1507742</x:v>
       </x:c>
-      <x:c r="K37" s="25" t="n">
+      <x:c r="K39" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L37" s="26">
+      <x:c r="L39" s="18">
         <x:v>46066.2701736111</x:v>
       </x:c>
-      <x:c r="M37" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="22" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C38" s="22" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D38" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E38" s="22" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F38" s="22" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G38" s="22" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H38" s="24">
+      <x:c r="M39" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
         <x:v>46078.2436226852</x:v>
       </x:c>
-      <x:c r="I38" s="27">
+      <x:c r="I40" s="19">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J38" s="23" t="n">
+      <x:c r="J40" s="15" t="n">
         <x:v>1507839</x:v>
       </x:c>
-      <x:c r="K38" s="25" t="n">
+      <x:c r="K40" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L38" s="26">
+      <x:c r="L40" s="18">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M38" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="22" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C39" s="22" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D39" s="23" t="s"/>
-      <x:c r="E39" s="22" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F39" s="22" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G39" s="22" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H39" s="24">
+      <x:c r="M40" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="s"/>
+      <x:c r="E41" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I39" s="24">
+      <x:c r="I41" s="16">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J39" s="23" t="n">
+      <x:c r="J41" s="15" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K39" s="25" t="n">
+      <x:c r="K41" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L39" s="26">
+      <x:c r="L41" s="18">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M39" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="22" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C40" s="22" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D40" s="23" t="s"/>
-      <x:c r="E40" s="22" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F40" s="22" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G40" s="22" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H40" s="24">
+      <x:c r="M41" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s"/>
+      <x:c r="E42" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I40" s="24">
+      <x:c r="I42" s="16">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J40" s="23" t="n">
+      <x:c r="J42" s="15" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K40" s="25" t="n">
+      <x:c r="K42" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L40" s="26">
+      <x:c r="L42" s="18">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M40" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B41" s="28" t="s"/>
-      <x:c r="C41" s="28" t="s"/>
-      <x:c r="D41" s="28" t="s"/>
-      <x:c r="E41" s="28" t="s"/>
-      <x:c r="F41" s="28" t="s"/>
-      <x:c r="G41" s="28" t="s"/>
-      <x:c r="H41" s="28" t="s"/>
-      <x:c r="I41" s="28" t="s"/>
-      <x:c r="J41" s="28" t="s"/>
-      <x:c r="K41" s="28" t="s"/>
-      <x:c r="L41" s="28" t="s"/>
-      <x:c r="M41" s="28" t="s"/>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B42" s="28" t="s"/>
-      <x:c r="C42" s="28" t="s"/>
-      <x:c r="D42" s="28" t="s"/>
-      <x:c r="E42" s="28" t="s"/>
-      <x:c r="F42" s="28" t="s"/>
-      <x:c r="G42" s="28" t="s"/>
-      <x:c r="H42" s="28" t="s"/>
-      <x:c r="I42" s="28" t="s"/>
-      <x:c r="J42" s="28" t="s"/>
-      <x:c r="K42" s="28" t="s"/>
-      <x:c r="L42" s="28" t="s"/>
-      <x:c r="M42" s="28" t="s"/>
+      <x:c r="M42" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="29" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C45" s="30" t="s"/>
-      <x:c r="D45" s="30" t="s"/>
-      <x:c r="E45" s="31" t="s"/>
-      <x:c r="F45" s="31" t="s"/>
+      <x:c r="B45" s="20" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C45" s="21" t="s"/>
+      <x:c r="D45" s="21" t="s"/>
+      <x:c r="E45" s="22" t="s"/>
+      <x:c r="F45" s="22" t="s"/>
     </x:row>
     <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="32" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C46" s="33" t="s"/>
-      <x:c r="D46" s="33" t="s"/>
-      <x:c r="E46" s="33" t="s"/>
-      <x:c r="F46" s="34" t="s">
-        <x:v>153</x:v>
+      <x:c r="B46" s="23" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C46" s="24" t="s"/>
+      <x:c r="D46" s="24" t="s"/>
+      <x:c r="E46" s="24" t="s"/>
+      <x:c r="F46" s="25" t="s">
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="35" t="s">
+      <x:c r="B47" s="26" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C47" s="27" t="s"/>
+      <x:c r="D47" s="27" t="s"/>
+      <x:c r="E47" s="27" t="s"/>
+      <x:c r="F47" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C48" s="27" t="s"/>
+      <x:c r="D48" s="27" t="s"/>
+      <x:c r="E48" s="27" t="s"/>
+      <x:c r="F48" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="26" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C49" s="27" t="s"/>
+      <x:c r="D49" s="27" t="s"/>
+      <x:c r="E49" s="27" t="s"/>
+      <x:c r="F49" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="26" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C50" s="27" t="s"/>
+      <x:c r="D50" s="27" t="s"/>
+      <x:c r="E50" s="27" t="s"/>
+      <x:c r="F50" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="26" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C51" s="27" t="s"/>
+      <x:c r="D51" s="27" t="s"/>
+      <x:c r="E51" s="27" t="s"/>
+      <x:c r="F51" s="28" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="26" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C52" s="27" t="s"/>
+      <x:c r="D52" s="27" t="s"/>
+      <x:c r="E52" s="27" t="s"/>
+      <x:c r="F52" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C47" s="36" t="s"/>
-      <x:c r="D47" s="36" t="s"/>
-      <x:c r="E47" s="36" t="s"/>
-      <x:c r="F47" s="37" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="35" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C48" s="36" t="s"/>
-      <x:c r="D48" s="36" t="s"/>
-      <x:c r="E48" s="36" t="s"/>
-      <x:c r="F48" s="37" t="n">
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="26" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C53" s="27" t="s"/>
+      <x:c r="D53" s="27" t="s"/>
+      <x:c r="E53" s="27" t="s"/>
+      <x:c r="F53" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="26" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C54" s="27" t="s"/>
+      <x:c r="D54" s="27" t="s"/>
+      <x:c r="E54" s="27" t="s"/>
+      <x:c r="F54" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="35" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C49" s="36" t="s"/>
-      <x:c r="D49" s="36" t="s"/>
-      <x:c r="E49" s="36" t="s"/>
-      <x:c r="F49" s="37" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="35" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C50" s="36" t="s"/>
-      <x:c r="D50" s="36" t="s"/>
-      <x:c r="E50" s="36" t="s"/>
-      <x:c r="F50" s="37" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="35" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C51" s="36" t="s"/>
-      <x:c r="D51" s="36" t="s"/>
-      <x:c r="E51" s="36" t="s"/>
-      <x:c r="F51" s="37" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="35" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C52" s="36" t="s"/>
-      <x:c r="D52" s="36" t="s"/>
-      <x:c r="E52" s="36" t="s"/>
-      <x:c r="F52" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="35" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C53" s="36" t="s"/>
-      <x:c r="D53" s="36" t="s"/>
-      <x:c r="E53" s="36" t="s"/>
-      <x:c r="F53" s="37" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="35" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C54" s="36" t="s"/>
-      <x:c r="D54" s="36" t="s"/>
-      <x:c r="E54" s="36" t="s"/>
-      <x:c r="F54" s="37" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
     <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="38" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C55" s="39" t="s"/>
-      <x:c r="D55" s="39" t="s"/>
-      <x:c r="E55" s="39" t="s"/>
-      <x:c r="F55" s="40" t="n">
+      <x:c r="B55" s="29" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C55" s="30" t="s"/>
+      <x:c r="D55" s="30" t="s"/>
+      <x:c r="E55" s="30" t="s"/>
+      <x:c r="F55" s="31" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
@@ -4333,18 +4319,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4362,1650 +4336,1662 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>66</x:v>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46090.2558217593</x:v>
       </x:c>
-      <x:c r="I8" s="20">
+      <x:c r="I10" s="16">
         <x:v>46090.2558333333</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="18">
         <x:v>46097.2890740741</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46090.2418287037</x:v>
       </x:c>
-      <x:c r="I9" s="20">
+      <x:c r="I11" s="16">
         <x:v>46090.2418518519</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="18">
         <x:v>46093.3049884259</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D10" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E10" s="22" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H10" s="24">
+      <x:c r="M11" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46090.2109953704</x:v>
       </x:c>
-      <x:c r="I10" s="24">
+      <x:c r="I12" s="16">
         <x:v>46090.2110069444</x:v>
       </x:c>
-      <x:c r="J10" s="23" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1511204</x:v>
       </x:c>
-      <x:c r="K10" s="25" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="26">
+      <x:c r="L12" s="18">
         <x:v>46093.3080092593</x:v>
       </x:c>
-      <x:c r="M10" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D11" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E11" s="22" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F11" s="22" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G11" s="22" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H11" s="24">
+      <x:c r="M12" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46083.2380439815</x:v>
       </x:c>
-      <x:c r="I11" s="27">
+      <x:c r="I13" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J11" s="23" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1511234</x:v>
       </x:c>
-      <x:c r="K11" s="25" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="26">
+      <x:c r="L13" s="18">
         <x:v>46097.1564351852</x:v>
       </x:c>
-      <x:c r="M11" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D12" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E12" s="22" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="F12" s="22" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="G12" s="22" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H12" s="24">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>46083.2322337963</x:v>
       </x:c>
-      <x:c r="I12" s="27">
+      <x:c r="I14" s="19">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J12" s="23" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1511233</x:v>
       </x:c>
-      <x:c r="K12" s="25" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="26">
+      <x:c r="L14" s="18">
         <x:v>46097.149525463</x:v>
       </x:c>
-      <x:c r="M12" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D13" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E13" s="22" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F13" s="22" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G13" s="22" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H13" s="24">
+      <x:c r="M14" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>46080.4532523148</x:v>
       </x:c>
-      <x:c r="I13" s="27">
+      <x:c r="I15" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J13" s="23" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1511232</x:v>
       </x:c>
-      <x:c r="K13" s="25" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="26">
+      <x:c r="L15" s="18">
         <x:v>46097.1461689815</x:v>
       </x:c>
-      <x:c r="M13" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D14" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E14" s="22" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F14" s="22" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G14" s="22" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H14" s="24">
+      <x:c r="M15" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>46083.2599189815</x:v>
       </x:c>
-      <x:c r="I14" s="27">
+      <x:c r="I16" s="19">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J14" s="23" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1511237</x:v>
       </x:c>
-      <x:c r="K14" s="25" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="26">
+      <x:c r="L16" s="18">
         <x:v>46097.1652314815</x:v>
       </x:c>
-      <x:c r="M14" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="D15" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E15" s="22" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F15" s="22" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G15" s="22" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H15" s="24">
+      <x:c r="M16" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
         <x:v>46069.3514814815</x:v>
       </x:c>
-      <x:c r="I15" s="27">
+      <x:c r="I17" s="19">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J15" s="23" t="n">
+      <x:c r="J17" s="15" t="n">
         <x:v>1511194</x:v>
       </x:c>
-      <x:c r="K15" s="25" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="26">
+      <x:c r="L17" s="18">
         <x:v>46097.2437384259</x:v>
       </x:c>
-      <x:c r="M15" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D16" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E16" s="22" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F16" s="22" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G16" s="22" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H16" s="24">
+      <x:c r="M17" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
         <x:v>46084.0996759259</x:v>
       </x:c>
-      <x:c r="I16" s="27">
+      <x:c r="I18" s="19">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J16" s="23" t="n">
+      <x:c r="J18" s="15" t="n">
         <x:v>1511192</x:v>
       </x:c>
-      <x:c r="K16" s="25" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="26">
+      <x:c r="L18" s="18">
         <x:v>46097.2414583333</x:v>
       </x:c>
-      <x:c r="M16" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D17" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E17" s="22" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="F17" s="22" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="G17" s="22" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="H17" s="24">
+      <x:c r="M18" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
         <x:v>46084.0854513889</x:v>
       </x:c>
-      <x:c r="I17" s="27">
+      <x:c r="I19" s="19">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J17" s="23" t="n">
+      <x:c r="J19" s="15" t="n">
         <x:v>1511225</x:v>
       </x:c>
-      <x:c r="K17" s="25" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="26">
+      <x:c r="L19" s="18">
         <x:v>46093.3956365741</x:v>
       </x:c>
-      <x:c r="M17" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D18" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E18" s="22" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="F18" s="22" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="G18" s="22" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H18" s="24">
+      <x:c r="M19" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
         <x:v>46069.3573032407</x:v>
       </x:c>
-      <x:c r="I18" s="27">
+      <x:c r="I20" s="19">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J18" s="23" t="n">
+      <x:c r="J20" s="15" t="n">
         <x:v>1511193</x:v>
       </x:c>
-      <x:c r="K18" s="25" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="26">
+      <x:c r="L20" s="18">
         <x:v>46097.2426388889</x:v>
       </x:c>
-      <x:c r="M18" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D19" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E19" s="22" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F19" s="22" t="s">
+      <x:c r="M20" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I28" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I29" s="19">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I30" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I31" s="19">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L31" s="18">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I32" s="19">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K32" s="17" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L32" s="18">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I33" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="18">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I34" s="19">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="18">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I35" s="19">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="18">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I36" s="16">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L36" s="18">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L37" s="18">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I38" s="16">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J38" s="15" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="18">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I39" s="16">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="18">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I40" s="19">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J40" s="15" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L40" s="18">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G19" s="22" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="H19" s="24">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I19" s="27">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J19" s="23" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K19" s="25" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L19" s="26">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M19" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D20" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E20" s="22" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F20" s="22" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G20" s="22" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H20" s="24">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I20" s="27">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J20" s="23" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K20" s="25" t="n">
+      <x:c r="D41" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I41" s="19">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J41" s="15" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="26">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M20" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C21" s="22" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D21" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E21" s="22" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F21" s="22" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G21" s="22" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H21" s="24">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I21" s="27">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J21" s="23" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K21" s="25" t="n">
+      <x:c r="L41" s="18">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M41" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I42" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J42" s="15" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K42" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="26">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M21" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C22" s="22" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="D22" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E22" s="22" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F22" s="22" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G22" s="22" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H22" s="24">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I22" s="27">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J22" s="23" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K22" s="25" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L22" s="26">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M22" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C23" s="22" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D23" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E23" s="22" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F23" s="22" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G23" s="22" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H23" s="24">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I23" s="27">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J23" s="23" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K23" s="25" t="n">
+      <x:c r="L42" s="18">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D43" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H43" s="16">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I43" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J43" s="15" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K43" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="26">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M23" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C24" s="22" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D24" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E24" s="22" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F24" s="22" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G24" s="22" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H24" s="24">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I24" s="27">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J24" s="23" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K24" s="25" t="n">
+      <x:c r="L43" s="18">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D44" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E44" s="14" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G44" s="14" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="H44" s="16">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I44" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J44" s="15" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K44" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="26">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M24" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C25" s="22" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D25" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E25" s="22" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F25" s="22" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G25" s="22" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H25" s="24">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I25" s="27">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J25" s="23" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K25" s="25" t="n">
+      <x:c r="L44" s="18">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M44" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D45" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="G45" s="14" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="H45" s="16">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I45" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J45" s="15" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K45" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="26">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M25" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="D26" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E26" s="22" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F26" s="22" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G26" s="22" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H26" s="24">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I26" s="27">
+      <x:c r="L45" s="18">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M45" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="D46" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="G46" s="14" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="H46" s="16">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I46" s="19">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J26" s="23" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K26" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="26">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M26" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C27" s="22" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="D27" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E27" s="22" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F27" s="22" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G27" s="22" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H27" s="24">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I27" s="27">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J27" s="23" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K27" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="26">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M27" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C28" s="22" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D28" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E28" s="22" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="F28" s="22" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="G28" s="22" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="H28" s="24">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I28" s="27">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J28" s="23" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K28" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="26">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M28" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C29" s="22" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D29" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E29" s="22" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F29" s="22" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="G29" s="22" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="H29" s="24">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I29" s="27">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J29" s="23" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K29" s="25" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L29" s="26">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M29" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C30" s="22" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D30" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E30" s="22" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="F30" s="22" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="G30" s="22" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="H30" s="24">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I30" s="27">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J30" s="23" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K30" s="25" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L30" s="26">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M30" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C31" s="22" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D31" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E31" s="22" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="F31" s="22" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="G31" s="22" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="H31" s="24">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I31" s="27">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J31" s="23" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K31" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="26">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M31" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C32" s="22" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="D32" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E32" s="22" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="F32" s="22" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="G32" s="22" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="H32" s="24">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I32" s="27">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J32" s="23" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K32" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="26">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M32" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C33" s="22" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="D33" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E33" s="22" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="F33" s="22" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="G33" s="22" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="H33" s="24">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I33" s="27">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J33" s="23" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K33" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="26">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M33" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C34" s="22" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D34" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E34" s="22" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="F34" s="22" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="G34" s="22" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="H34" s="24">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I34" s="24">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J34" s="23" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K34" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L34" s="26">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M34" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C35" s="22" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D35" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E35" s="22" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="F35" s="22" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="G35" s="22" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="H35" s="24">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I35" s="24">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J35" s="23" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K35" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L35" s="26">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M35" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C36" s="22" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D36" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E36" s="22" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="F36" s="22" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="G36" s="22" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="H36" s="24">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I36" s="24">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J36" s="23" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K36" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L36" s="26">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M36" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C37" s="22" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="D37" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E37" s="22" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="F37" s="22" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="G37" s="22" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="H37" s="24">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I37" s="24">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J37" s="23" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K37" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L37" s="26">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M37" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C38" s="22" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D38" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E38" s="22" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F38" s="22" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="G38" s="22" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H38" s="24">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I38" s="27">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J38" s="23" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K38" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="26">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M38" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C39" s="22" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D39" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E39" s="22" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="F39" s="22" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G39" s="22" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H39" s="24">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I39" s="27">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J39" s="23" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K39" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L39" s="26">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M39" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C40" s="22" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="D40" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E40" s="22" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="F40" s="22" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="G40" s="22" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="H40" s="24">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I40" s="27">
+      <x:c r="J46" s="15" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K46" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L46" s="18">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M46" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D47" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="G47" s="14" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="H47" s="16">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I47" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J40" s="23" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K40" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L40" s="26">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M40" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C41" s="22" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="D41" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E41" s="22" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="F41" s="22" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="G41" s="22" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="H41" s="24">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I41" s="27">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J41" s="23" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K41" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="26">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M41" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C42" s="22" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="D42" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E42" s="22" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="F42" s="22" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="G42" s="22" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="H42" s="24">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I42" s="27">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J42" s="23" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K42" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L42" s="26">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M42" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="22" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C43" s="22" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="D43" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E43" s="22" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="F43" s="22" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="G43" s="22" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="H43" s="24">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I43" s="27">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J43" s="23" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K43" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="26">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M43" s="22" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="22" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C44" s="22" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="D44" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E44" s="22" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="F44" s="22" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="G44" s="22" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="H44" s="24">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I44" s="27">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J44" s="23" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K44" s="25" t="n">
+      <x:c r="J47" s="15" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K47" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L44" s="26">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M44" s="22" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="22" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C45" s="22" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="D45" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E45" s="22" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="F45" s="22" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="G45" s="22" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="H45" s="24">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I45" s="27">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J45" s="23" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K45" s="25" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L45" s="26">
+      <x:c r="L47" s="18">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M45" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B46" s="28" t="s"/>
-      <x:c r="C46" s="28" t="s"/>
-      <x:c r="D46" s="28" t="s"/>
-      <x:c r="E46" s="28" t="s"/>
-      <x:c r="F46" s="28" t="s"/>
-      <x:c r="G46" s="28" t="s"/>
-      <x:c r="H46" s="28" t="s"/>
-      <x:c r="I46" s="28" t="s"/>
-      <x:c r="J46" s="28" t="s"/>
-      <x:c r="K46" s="28" t="s"/>
-      <x:c r="L46" s="28" t="s"/>
-      <x:c r="M46" s="28" t="s"/>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B47" s="28" t="s"/>
-      <x:c r="C47" s="28" t="s"/>
-      <x:c r="D47" s="28" t="s"/>
-      <x:c r="E47" s="28" t="s"/>
-      <x:c r="F47" s="28" t="s"/>
-      <x:c r="G47" s="28" t="s"/>
-      <x:c r="H47" s="28" t="s"/>
-      <x:c r="I47" s="28" t="s"/>
-      <x:c r="J47" s="28" t="s"/>
-      <x:c r="K47" s="28" t="s"/>
-      <x:c r="L47" s="28" t="s"/>
-      <x:c r="M47" s="28" t="s"/>
+      <x:c r="M47" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="29" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C50" s="30" t="s"/>
-      <x:c r="D50" s="30" t="s"/>
-      <x:c r="E50" s="31" t="s"/>
-      <x:c r="F50" s="31" t="s"/>
+      <x:c r="B50" s="20" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C50" s="21" t="s"/>
+      <x:c r="D50" s="21" t="s"/>
+      <x:c r="E50" s="22" t="s"/>
+      <x:c r="F50" s="22" t="s"/>
     </x:row>
     <x:row r="51" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B51" s="32" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C51" s="33" t="s"/>
-      <x:c r="D51" s="33" t="s"/>
-      <x:c r="E51" s="33" t="s"/>
-      <x:c r="F51" s="34" t="s">
-        <x:v>153</x:v>
+      <x:c r="B51" s="23" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C51" s="24" t="s"/>
+      <x:c r="D51" s="24" t="s"/>
+      <x:c r="E51" s="24" t="s"/>
+      <x:c r="F51" s="25" t="s">
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="35" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C52" s="36" t="s"/>
-      <x:c r="D52" s="36" t="s"/>
-      <x:c r="E52" s="36" t="s"/>
-      <x:c r="F52" s="37" t="n">
+      <x:c r="B52" s="26" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C52" s="27" t="s"/>
+      <x:c r="D52" s="27" t="s"/>
+      <x:c r="E52" s="27" t="s"/>
+      <x:c r="F52" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="35" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C53" s="36" t="s"/>
-      <x:c r="D53" s="36" t="s"/>
-      <x:c r="E53" s="36" t="s"/>
-      <x:c r="F53" s="37" t="n">
+      <x:c r="B53" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C53" s="27" t="s"/>
+      <x:c r="D53" s="27" t="s"/>
+      <x:c r="E53" s="27" t="s"/>
+      <x:c r="F53" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="35" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C54" s="36" t="s"/>
-      <x:c r="D54" s="36" t="s"/>
-      <x:c r="E54" s="36" t="s"/>
-      <x:c r="F54" s="37" t="n">
+      <x:c r="B54" s="26" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C54" s="27" t="s"/>
+      <x:c r="D54" s="27" t="s"/>
+      <x:c r="E54" s="27" t="s"/>
+      <x:c r="F54" s="28" t="n">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="35" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C55" s="36" t="s"/>
-      <x:c r="D55" s="36" t="s"/>
-      <x:c r="E55" s="36" t="s"/>
-      <x:c r="F55" s="37" t="n">
+      <x:c r="B55" s="26" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C55" s="27" t="s"/>
+      <x:c r="D55" s="27" t="s"/>
+      <x:c r="E55" s="27" t="s"/>
+      <x:c r="F55" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="35" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C56" s="36" t="s"/>
-      <x:c r="D56" s="36" t="s"/>
-      <x:c r="E56" s="36" t="s"/>
-      <x:c r="F56" s="37" t="n">
+      <x:c r="B56" s="26" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C56" s="27" t="s"/>
+      <x:c r="D56" s="27" t="s"/>
+      <x:c r="E56" s="27" t="s"/>
+      <x:c r="F56" s="28" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="35" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C57" s="36" t="s"/>
-      <x:c r="D57" s="36" t="s"/>
-      <x:c r="E57" s="36" t="s"/>
-      <x:c r="F57" s="37" t="n">
+      <x:c r="B57" s="26" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C57" s="27" t="s"/>
+      <x:c r="D57" s="27" t="s"/>
+      <x:c r="E57" s="27" t="s"/>
+      <x:c r="F57" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B58" s="38" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C58" s="39" t="s"/>
-      <x:c r="D58" s="39" t="s"/>
-      <x:c r="E58" s="39" t="s"/>
-      <x:c r="F58" s="40" t="n">
+      <x:c r="B58" s="29" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C58" s="30" t="s"/>
+      <x:c r="D58" s="30" t="s"/>
+      <x:c r="E58" s="30" t="s"/>
+      <x:c r="F58" s="31" t="n">
         <x:v>40</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
   <x:si>
     <x:t>PERMIT SUMMARY</x:t>
   </x:si>
@@ -550,6 +550,18 @@
     <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
+    <x:t>RUBEN C. SESCON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Blk. 17, Lot 14, Phase 2 Aquino Street, Citihomes, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIV-A-07321-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1203-366</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
@@ -589,6 +601,24 @@
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0781 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1144-933</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -598,24 +628,6 @@
     <x:t>43A-3-2026-1151-716</x:t>
   </x:si>
   <x:si>
-    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1150-325</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0781 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1144-933</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -643,6 +655,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1155-834</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -652,18 +673,27 @@
     <x:t>43A-3-2026-1156-896</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0762</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1155-834</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -680,24 +710,6 @@
   </x:si>
   <x:si>
     <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
     <x:t>CLIXTEC INC.</x:t>
@@ -1273,9 +1285,12 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1345,7 +1360,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1375,6 +1390,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1709,7 +1728,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46054</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1781,1477 +1802,1477 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46069.0835185185</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46069.1006712963</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1506161</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46069.1133333333</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="12" t="s"/>
+      <x:c r="E9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46066.2950925926</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>46066.3145023148</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1507747</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46066.3194212963</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="H10" s="17">
         <x:v>46069.0835648148</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="17">
         <x:v>46069.1000231481</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1506159</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>46069.1128587963</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="C11" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="H11" s="17">
         <x:v>46072.1720833333</x:v>
       </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="I11" s="17">
         <x:v>46072.235162037</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1507783</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>46073.1890277778</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
+      <x:c r="M11" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="B12" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="C12" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="H12" s="17">
         <x:v>46063.2819560185</x:v>
       </x:c>
-      <x:c r="I12" s="16">
+      <x:c r="I12" s="17">
         <x:v>46063.2922685185</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1507682</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>46063.2957638889</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
+      <x:c r="M12" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="B13" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="C13" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s"/>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="H13" s="17">
         <x:v>46058.4859837963</x:v>
       </x:c>
-      <x:c r="I13" s="16">
+      <x:c r="I13" s="17">
         <x:v>46062.157025463</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1507672</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>46062.1881944444</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
+      <x:c r="M13" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
+      <x:c r="B14" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="C14" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
+      <x:c r="D14" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="E14" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="F14" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="G14" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="H14" s="17">
         <x:v>46067.3600231481</x:v>
       </x:c>
-      <x:c r="I14" s="16">
+      <x:c r="I14" s="17">
         <x:v>46067.3600462963</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="16" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="18">
+      <x:c r="L14" s="19">
         <x:v>46079.2730092593</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
+      <x:c r="M14" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
+      <x:c r="B15" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="C15" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
+      <x:c r="D15" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="E15" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="F15" s="15" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="G15" s="15" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="H15" s="17">
         <x:v>46072.3184259259</x:v>
       </x:c>
-      <x:c r="I15" s="16">
+      <x:c r="I15" s="17">
         <x:v>46072.3184375</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="16" t="n">
         <x:v>1505803</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="18">
+      <x:c r="L15" s="19">
         <x:v>46079.2696990741</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
+      <x:c r="M15" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
+      <x:c r="B16" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="C16" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
+      <x:c r="D16" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="E16" s="15" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="F16" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="G16" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H16" s="16">
+      <x:c r="H16" s="17">
         <x:v>46067.1596643518</x:v>
       </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="I16" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J16" s="16" t="n">
         <x:v>1505804</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="K16" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="18">
+      <x:c r="L16" s="19">
         <x:v>46079.2772569444</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
+      <x:c r="M16" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
+      <x:c r="B17" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="C17" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s">
+      <x:c r="D17" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E17" s="14" t="s">
+      <x:c r="E17" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="F17" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="G17" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H17" s="16">
+      <x:c r="H17" s="17">
         <x:v>46067.2222106481</x:v>
       </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="I17" s="20">
         <x:v>46089</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="n">
+      <x:c r="J17" s="16" t="n">
         <x:v>1505805</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="K17" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="18">
+      <x:c r="L17" s="19">
         <x:v>46079.2763078704</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="s">
+      <x:c r="M17" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
+      <x:c r="B18" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="C18" s="15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
+      <x:c r="D18" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="E18" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="F18" s="15" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="G18" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H18" s="16">
+      <x:c r="H18" s="17">
         <x:v>46072.3605555556</x:v>
       </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="I18" s="20">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="n">
+      <x:c r="J18" s="16" t="n">
         <x:v>1507784</x:v>
       </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="K18" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="18">
+      <x:c r="L18" s="19">
         <x:v>46073.2284953704</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
+      <x:c r="M18" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
+      <x:c r="B19" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C19" s="14" t="s">
+      <x:c r="C19" s="15" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="s">
+      <x:c r="D19" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E19" s="14" t="s">
+      <x:c r="E19" s="15" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="F19" s="15" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
+      <x:c r="G19" s="15" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H19" s="16">
+      <x:c r="H19" s="17">
         <x:v>46072.3529513889</x:v>
       </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="I19" s="20">
         <x:v>46073</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="n">
+      <x:c r="J19" s="16" t="n">
         <x:v>1507785</x:v>
       </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="K19" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="18">
+      <x:c r="L19" s="19">
         <x:v>46073.2314351852</x:v>
       </x:c>
-      <x:c r="M19" s="14" t="s">
+      <x:c r="M19" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
+      <x:c r="B20" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C20" s="14" t="s">
+      <x:c r="C20" s="15" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="s">
+      <x:c r="D20" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E20" s="14" t="s">
+      <x:c r="E20" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="F20" s="15" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
+      <x:c r="G20" s="15" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="H20" s="16">
+      <x:c r="H20" s="17">
         <x:v>46063.1352777778</x:v>
       </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="I20" s="20">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J20" s="15" t="n">
+      <x:c r="J20" s="16" t="n">
         <x:v>1511010</x:v>
       </x:c>
-      <x:c r="K20" s="17" t="n">
+      <x:c r="K20" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="18">
+      <x:c r="L20" s="19">
         <x:v>46063.2367708333</x:v>
       </x:c>
-      <x:c r="M20" s="14" t="s">
+      <x:c r="M20" s="15" t="s">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
+      <x:c r="B21" s="15" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C21" s="14" t="s">
+      <x:c r="C21" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="s">
+      <x:c r="D21" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E21" s="14" t="s">
+      <x:c r="E21" s="15" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="F21" s="15" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="G21" s="15" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H21" s="16">
+      <x:c r="H21" s="17">
         <x:v>46079.3584722222</x:v>
       </x:c>
-      <x:c r="I21" s="16">
+      <x:c r="I21" s="17">
         <x:v>46079.3584953704</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="n">
+      <x:c r="J21" s="16" t="n">
         <x:v>1511622</x:v>
       </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="K21" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L21" s="18">
+      <x:c r="L21" s="19">
         <x:v>46080.2311226852</x:v>
       </x:c>
-      <x:c r="M21" s="14" t="s">
+      <x:c r="M21" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
+      <x:c r="B22" s="15" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C22" s="14" t="s">
+      <x:c r="C22" s="15" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="s">
+      <x:c r="D22" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E22" s="14" t="s">
+      <x:c r="E22" s="15" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="F22" s="15" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
+      <x:c r="G22" s="15" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H22" s="16">
+      <x:c r="H22" s="17">
         <x:v>46079.3539699074</x:v>
       </x:c>
-      <x:c r="I22" s="16">
+      <x:c r="I22" s="17">
         <x:v>46079.3539814815</x:v>
       </x:c>
-      <x:c r="J22" s="15" t="n">
+      <x:c r="J22" s="16" t="n">
         <x:v>1511627</x:v>
       </x:c>
-      <x:c r="K22" s="17" t="n">
+      <x:c r="K22" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L22" s="18">
+      <x:c r="L22" s="19">
         <x:v>46080.2440856481</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="s">
+      <x:c r="M22" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
+      <x:c r="B23" s="15" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C23" s="14" t="s">
+      <x:c r="C23" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="s">
+      <x:c r="D23" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E23" s="14" t="s">
+      <x:c r="E23" s="15" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="s">
+      <x:c r="F23" s="15" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="G23" s="14" t="s">
+      <x:c r="G23" s="15" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="H23" s="16">
+      <x:c r="H23" s="17">
         <x:v>46058.1529282407</x:v>
       </x:c>
-      <x:c r="I23" s="16">
+      <x:c r="I23" s="17">
         <x:v>46058.1529398148</x:v>
       </x:c>
-      <x:c r="J23" s="15" t="n">
+      <x:c r="J23" s="16" t="n">
         <x:v>1507657</x:v>
       </x:c>
-      <x:c r="K23" s="17" t="n">
+      <x:c r="K23" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L23" s="18">
+      <x:c r="L23" s="19">
         <x:v>46058.2410648148</x:v>
       </x:c>
-      <x:c r="M23" s="14" t="s">
+      <x:c r="M23" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
+      <x:c r="B24" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C24" s="14" t="s">
+      <x:c r="C24" s="15" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="s">
+      <x:c r="D24" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E24" s="14" t="s">
+      <x:c r="E24" s="15" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="s">
+      <x:c r="F24" s="15" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G24" s="14" t="s">
+      <x:c r="G24" s="15" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H24" s="16">
+      <x:c r="H24" s="17">
         <x:v>46072.2635300926</x:v>
       </x:c>
-      <x:c r="I24" s="19">
+      <x:c r="I24" s="20">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J24" s="15" t="n">
+      <x:c r="J24" s="16" t="n">
         <x:v>1507790</x:v>
       </x:c>
-      <x:c r="K24" s="17" t="n">
+      <x:c r="K24" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L24" s="18">
+      <x:c r="L24" s="19">
         <x:v>46073.3091087963</x:v>
       </x:c>
-      <x:c r="M24" s="14" t="s">
+      <x:c r="M24" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
+      <x:c r="B25" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C25" s="14" t="s">
+      <x:c r="C25" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D25" s="15" t="s">
+      <x:c r="D25" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E25" s="14" t="s">
+      <x:c r="E25" s="15" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="s">
+      <x:c r="F25" s="15" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G25" s="14" t="s">
+      <x:c r="G25" s="15" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H25" s="16">
+      <x:c r="H25" s="17">
         <x:v>46079.3873148148</x:v>
       </x:c>
-      <x:c r="I25" s="19">
+      <x:c r="I25" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J25" s="15" t="n">
+      <x:c r="J25" s="16" t="n">
         <x:v>1511623</x:v>
       </x:c>
-      <x:c r="K25" s="17" t="n">
+      <x:c r="K25" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="18">
+      <x:c r="L25" s="19">
         <x:v>46080.2360763889</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="s">
+      <x:c r="M25" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
+      <x:c r="B26" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C26" s="14" t="s">
+      <x:c r="C26" s="15" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="s">
+      <x:c r="D26" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E26" s="14" t="s">
+      <x:c r="E26" s="15" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="s">
+      <x:c r="F26" s="15" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="s">
+      <x:c r="G26" s="15" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H26" s="16">
+      <x:c r="H26" s="17">
         <x:v>46079.2523032407</x:v>
       </x:c>
-      <x:c r="I26" s="19">
+      <x:c r="I26" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J26" s="15" t="n">
+      <x:c r="J26" s="16" t="n">
         <x:v>1511631</x:v>
       </x:c>
-      <x:c r="K26" s="17" t="n">
+      <x:c r="K26" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L26" s="18">
+      <x:c r="L26" s="19">
         <x:v>46080.2925810185</x:v>
       </x:c>
-      <x:c r="M26" s="14" t="s">
+      <x:c r="M26" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
+      <x:c r="B27" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C27" s="14" t="s">
+      <x:c r="C27" s="15" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="s">
+      <x:c r="D27" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E27" s="14" t="s">
+      <x:c r="E27" s="15" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="s">
+      <x:c r="F27" s="15" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="G27" s="14" t="s">
+      <x:c r="G27" s="15" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="H27" s="16">
+      <x:c r="H27" s="17">
         <x:v>46079.2430555556</x:v>
       </x:c>
-      <x:c r="I27" s="19">
+      <x:c r="I27" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J27" s="15" t="n">
+      <x:c r="J27" s="16" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K27" s="17" t="n">
+      <x:c r="K27" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L27" s="18">
+      <x:c r="L27" s="19">
         <x:v>46080.2801273148</x:v>
       </x:c>
-      <x:c r="M27" s="14" t="s">
+      <x:c r="M27" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
+      <x:c r="B28" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C28" s="14" t="s">
+      <x:c r="C28" s="15" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="D28" s="15" t="s">
+      <x:c r="D28" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E28" s="14" t="s">
+      <x:c r="E28" s="15" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="F28" s="14" t="s">
+      <x:c r="F28" s="15" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="G28" s="14" t="s">
+      <x:c r="G28" s="15" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="H28" s="16">
+      <x:c r="H28" s="17">
         <x:v>46079.3651967593</x:v>
       </x:c>
-      <x:c r="I28" s="19">
+      <x:c r="I28" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J28" s="15" t="n">
+      <x:c r="J28" s="16" t="n">
         <x:v>1511626</x:v>
       </x:c>
-      <x:c r="K28" s="17" t="n">
+      <x:c r="K28" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L28" s="18">
+      <x:c r="L28" s="19">
         <x:v>46080.2425462963</x:v>
       </x:c>
-      <x:c r="M28" s="14" t="s">
+      <x:c r="M28" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
+      <x:c r="B29" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C29" s="14" t="s">
+      <x:c r="C29" s="15" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="D29" s="15" t="s">
+      <x:c r="D29" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E29" s="14" t="s">
+      <x:c r="E29" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="F29" s="14" t="s">
+      <x:c r="F29" s="15" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="G29" s="14" t="s">
+      <x:c r="G29" s="15" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="H29" s="16">
+      <x:c r="H29" s="17">
         <x:v>46080.2923611111</x:v>
       </x:c>
-      <x:c r="I29" s="19">
+      <x:c r="I29" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J29" s="15" t="n">
+      <x:c r="J29" s="16" t="n">
         <x:v>1511635</x:v>
       </x:c>
-      <x:c r="K29" s="17" t="n">
+      <x:c r="K29" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L29" s="18">
+      <x:c r="L29" s="19">
         <x:v>46080.3208564815</x:v>
       </x:c>
-      <x:c r="M29" s="14" t="s">
+      <x:c r="M29" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
+      <x:c r="B30" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C30" s="14" t="s">
+      <x:c r="C30" s="15" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="D30" s="15" t="s">
+      <x:c r="D30" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E30" s="14" t="s">
+      <x:c r="E30" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="F30" s="14" t="s">
+      <x:c r="F30" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G30" s="14" t="s">
+      <x:c r="G30" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H30" s="16">
+      <x:c r="H30" s="17">
         <x:v>46079.31625</x:v>
       </x:c>
-      <x:c r="I30" s="19">
+      <x:c r="I30" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J30" s="15" t="n">
+      <x:c r="J30" s="16" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K30" s="17" t="n">
+      <x:c r="K30" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L30" s="18">
+      <x:c r="L30" s="19">
         <x:v>46080.2883680556</x:v>
       </x:c>
-      <x:c r="M30" s="14" t="s">
+      <x:c r="M30" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="14" t="s">
+      <x:c r="B31" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C31" s="14" t="s">
+      <x:c r="C31" s="15" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D31" s="15" t="s">
+      <x:c r="D31" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E31" s="14" t="s">
+      <x:c r="E31" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="F31" s="14" t="s">
+      <x:c r="F31" s="15" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G31" s="14" t="s">
+      <x:c r="G31" s="15" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H31" s="16">
+      <x:c r="H31" s="17">
         <x:v>46079.3059375</x:v>
       </x:c>
-      <x:c r="I31" s="19">
+      <x:c r="I31" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J31" s="15" t="n">
+      <x:c r="J31" s="16" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K31" s="17" t="n">
+      <x:c r="K31" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L31" s="18">
+      <x:c r="L31" s="19">
         <x:v>46080.2896875</x:v>
       </x:c>
-      <x:c r="M31" s="14" t="s">
+      <x:c r="M31" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="14" t="s">
+      <x:c r="B32" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C32" s="14" t="s">
+      <x:c r="C32" s="15" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="D32" s="15" t="s">
+      <x:c r="D32" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E32" s="14" t="s">
+      <x:c r="E32" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="F32" s="14" t="s">
+      <x:c r="F32" s="15" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G32" s="14" t="s">
+      <x:c r="G32" s="15" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H32" s="16">
+      <x:c r="H32" s="17">
         <x:v>46079.2943981482</x:v>
       </x:c>
-      <x:c r="I32" s="19">
+      <x:c r="I32" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J32" s="15" t="n">
+      <x:c r="J32" s="16" t="n">
         <x:v>1511630</x:v>
       </x:c>
-      <x:c r="K32" s="17" t="n">
+      <x:c r="K32" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L32" s="18">
+      <x:c r="L32" s="19">
         <x:v>46080.2916782407</x:v>
       </x:c>
-      <x:c r="M32" s="14" t="s">
+      <x:c r="M32" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="14" t="s">
+      <x:c r="B33" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C33" s="14" t="s">
+      <x:c r="C33" s="15" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D33" s="15" t="s">
+      <x:c r="D33" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E33" s="14" t="s">
+      <x:c r="E33" s="15" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F33" s="14" t="s">
+      <x:c r="F33" s="15" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G33" s="14" t="s">
+      <x:c r="G33" s="15" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="H33" s="16">
+      <x:c r="H33" s="17">
         <x:v>46079.378900463</x:v>
       </x:c>
-      <x:c r="I33" s="19">
+      <x:c r="I33" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J33" s="15" t="n">
+      <x:c r="J33" s="16" t="n">
         <x:v>1511624</x:v>
       </x:c>
-      <x:c r="K33" s="17" t="n">
+      <x:c r="K33" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L33" s="18">
+      <x:c r="L33" s="19">
         <x:v>46080.2376041667</x:v>
       </x:c>
-      <x:c r="M33" s="14" t="s">
+      <x:c r="M33" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="14" t="s">
+      <x:c r="B34" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C34" s="14" t="s">
+      <x:c r="C34" s="15" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D34" s="15" t="s">
+      <x:c r="D34" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E34" s="14" t="s">
+      <x:c r="E34" s="15" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F34" s="14" t="s">
+      <x:c r="F34" s="15" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="G34" s="14" t="s">
+      <x:c r="G34" s="15" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="H34" s="16">
+      <x:c r="H34" s="17">
         <x:v>46079.3728240741</x:v>
       </x:c>
-      <x:c r="I34" s="19">
+      <x:c r="I34" s="20">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J34" s="15" t="n">
+      <x:c r="J34" s="16" t="n">
         <x:v>1511625</x:v>
       </x:c>
-      <x:c r="K34" s="17" t="n">
+      <x:c r="K34" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L34" s="18">
+      <x:c r="L34" s="19">
         <x:v>46080.2394328704</x:v>
       </x:c>
-      <x:c r="M34" s="14" t="s">
+      <x:c r="M34" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="14" t="s">
+      <x:c r="B35" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C35" s="14" t="s">
+      <x:c r="C35" s="15" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="D35" s="15" t="s">
+      <x:c r="D35" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E35" s="14" t="s">
+      <x:c r="E35" s="15" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="F35" s="14" t="s">
+      <x:c r="F35" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="G35" s="14" t="s">
+      <x:c r="G35" s="15" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="H35" s="16">
+      <x:c r="H35" s="17">
         <x:v>46077.0697337963</x:v>
       </x:c>
-      <x:c r="I35" s="19">
+      <x:c r="I35" s="20">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J35" s="15" t="n">
+      <x:c r="J35" s="16" t="n">
         <x:v>1511576</x:v>
       </x:c>
-      <x:c r="K35" s="17" t="n">
+      <x:c r="K35" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L35" s="18">
+      <x:c r="L35" s="19">
         <x:v>46077.1078819444</x:v>
       </x:c>
-      <x:c r="M35" s="14" t="s">
+      <x:c r="M35" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="14" t="s">
+      <x:c r="B36" s="15" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="C36" s="14" t="s">
+      <x:c r="C36" s="15" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D36" s="15" t="s">
+      <x:c r="D36" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E36" s="14" t="s">
+      <x:c r="E36" s="15" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="F36" s="14" t="s">
+      <x:c r="F36" s="15" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="G36" s="14" t="s">
+      <x:c r="G36" s="15" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="H36" s="16">
+      <x:c r="H36" s="17">
         <x:v>46062.1590162037</x:v>
       </x:c>
-      <x:c r="I36" s="16">
+      <x:c r="I36" s="17">
         <x:v>46062.1590277778</x:v>
       </x:c>
-      <x:c r="J36" s="15" t="n">
+      <x:c r="J36" s="16" t="n">
         <x:v>1510925</x:v>
       </x:c>
-      <x:c r="K36" s="17" t="n">
+      <x:c r="K36" s="18" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L36" s="18">
+      <x:c r="L36" s="19">
         <x:v>46062.1863194444</x:v>
       </x:c>
-      <x:c r="M36" s="14" t="s">
+      <x:c r="M36" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="14" t="s">
+      <x:c r="B37" s="15" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C37" s="14" t="s">
+      <x:c r="C37" s="15" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D37" s="15" t="s">
+      <x:c r="D37" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E37" s="14" t="s">
+      <x:c r="E37" s="15" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="F37" s="14" t="s">
+      <x:c r="F37" s="15" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G37" s="14" t="s">
+      <x:c r="G37" s="15" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="H37" s="16">
+      <x:c r="H37" s="17">
         <x:v>46066.2180208333</x:v>
       </x:c>
-      <x:c r="I37" s="19">
+      <x:c r="I37" s="20">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J37" s="15" t="n">
+      <x:c r="J37" s="16" t="n">
         <x:v>1507743</x:v>
       </x:c>
-      <x:c r="K37" s="17" t="n">
+      <x:c r="K37" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L37" s="18">
+      <x:c r="L37" s="19">
         <x:v>46066.2724421296</x:v>
       </x:c>
-      <x:c r="M37" s="14" t="s">
+      <x:c r="M37" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="14" t="s">
+      <x:c r="B38" s="15" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C38" s="14" t="s">
+      <x:c r="C38" s="15" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="D38" s="15" t="s">
+      <x:c r="D38" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E38" s="14" t="s">
+      <x:c r="E38" s="15" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F38" s="14" t="s">
+      <x:c r="F38" s="15" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G38" s="14" t="s">
+      <x:c r="G38" s="15" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="H38" s="16">
+      <x:c r="H38" s="17">
         <x:v>46071.0492476852</x:v>
       </x:c>
-      <x:c r="I38" s="19">
+      <x:c r="I38" s="20">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J38" s="15" t="n">
+      <x:c r="J38" s="16" t="n">
         <x:v>1511502</x:v>
       </x:c>
-      <x:c r="K38" s="17" t="n">
+      <x:c r="K38" s="18" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L38" s="18">
+      <x:c r="L38" s="19">
         <x:v>46071.0606134259</x:v>
       </x:c>
-      <x:c r="M38" s="14" t="s">
+      <x:c r="M38" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="14" t="s">
+      <x:c r="B39" s="15" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C39" s="14" t="s">
+      <x:c r="C39" s="15" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="D39" s="15" t="s">
+      <x:c r="D39" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E39" s="14" t="s">
+      <x:c r="E39" s="15" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="F39" s="14" t="s">
+      <x:c r="F39" s="15" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G39" s="14" t="s">
+      <x:c r="G39" s="15" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="H39" s="16">
+      <x:c r="H39" s="17">
         <x:v>46066.2275347222</x:v>
       </x:c>
-      <x:c r="I39" s="19">
+      <x:c r="I39" s="20">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J39" s="15" t="n">
+      <x:c r="J39" s="16" t="n">
         <x:v>1507742</x:v>
       </x:c>
-      <x:c r="K39" s="17" t="n">
+      <x:c r="K39" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L39" s="18">
+      <x:c r="L39" s="19">
         <x:v>46066.2701736111</x:v>
       </x:c>
-      <x:c r="M39" s="14" t="s">
+      <x:c r="M39" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="14" t="s">
+      <x:c r="B40" s="15" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C40" s="14" t="s">
+      <x:c r="C40" s="15" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="D40" s="15" t="s">
+      <x:c r="D40" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E40" s="14" t="s">
+      <x:c r="E40" s="15" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="F40" s="14" t="s">
+      <x:c r="F40" s="15" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="G40" s="14" t="s">
+      <x:c r="G40" s="15" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="H40" s="16">
+      <x:c r="H40" s="17">
         <x:v>46078.2436226852</x:v>
       </x:c>
-      <x:c r="I40" s="19">
+      <x:c r="I40" s="20">
         <x:v>46085</x:v>
       </x:c>
-      <x:c r="J40" s="15" t="n">
+      <x:c r="J40" s="16" t="n">
         <x:v>1507839</x:v>
       </x:c>
-      <x:c r="K40" s="17" t="n">
+      <x:c r="K40" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L40" s="18">
+      <x:c r="L40" s="19">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M40" s="14" t="s">
+      <x:c r="M40" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="14" t="s">
+      <x:c r="B41" s="15" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C41" s="14" t="s">
+      <x:c r="C41" s="15" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D41" s="15" t="s"/>
-      <x:c r="E41" s="14" t="s">
+      <x:c r="D41" s="16" t="s"/>
+      <x:c r="E41" s="15" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F41" s="14" t="s">
+      <x:c r="F41" s="15" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G41" s="14" t="s">
+      <x:c r="G41" s="15" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H41" s="16">
+      <x:c r="H41" s="17">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I41" s="16">
+      <x:c r="I41" s="17">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J41" s="15" t="n">
+      <x:c r="J41" s="16" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K41" s="17" t="n">
+      <x:c r="K41" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L41" s="18">
+      <x:c r="L41" s="19">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M41" s="14" t="s">
+      <x:c r="M41" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="14" t="s">
+      <x:c r="B42" s="15" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C42" s="14" t="s">
+      <x:c r="C42" s="15" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="D42" s="15" t="s"/>
-      <x:c r="E42" s="14" t="s">
+      <x:c r="D42" s="16" t="s"/>
+      <x:c r="E42" s="15" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="F42" s="14" t="s">
+      <x:c r="F42" s="15" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G42" s="14" t="s">
+      <x:c r="G42" s="15" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="H42" s="16">
+      <x:c r="H42" s="17">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I42" s="16">
+      <x:c r="I42" s="17">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J42" s="15" t="n">
+      <x:c r="J42" s="16" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K42" s="17" t="n">
+      <x:c r="K42" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L42" s="18">
+      <x:c r="L42" s="19">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M42" s="14" t="s">
+      <x:c r="M42" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="20" t="s">
+      <x:c r="B45" s="21" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C45" s="21" t="s"/>
-      <x:c r="D45" s="21" t="s"/>
-      <x:c r="E45" s="22" t="s"/>
-      <x:c r="F45" s="22" t="s"/>
+      <x:c r="C45" s="22" t="s"/>
+      <x:c r="D45" s="22" t="s"/>
+      <x:c r="E45" s="23" t="s"/>
+      <x:c r="F45" s="23" t="s"/>
     </x:row>
     <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="23" t="s">
+      <x:c r="B46" s="24" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="C46" s="24" t="s"/>
-      <x:c r="D46" s="24" t="s"/>
-      <x:c r="E46" s="24" t="s"/>
-      <x:c r="F46" s="25" t="s">
+      <x:c r="C46" s="25" t="s"/>
+      <x:c r="D46" s="25" t="s"/>
+      <x:c r="E46" s="25" t="s"/>
+      <x:c r="F46" s="26" t="s">
         <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="26" t="s">
+      <x:c r="B47" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C47" s="27" t="s"/>
-      <x:c r="D47" s="27" t="s"/>
-      <x:c r="E47" s="27" t="s"/>
-      <x:c r="F47" s="28" t="n">
+      <x:c r="C47" s="28" t="s"/>
+      <x:c r="D47" s="28" t="s"/>
+      <x:c r="E47" s="28" t="s"/>
+      <x:c r="F47" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="26" t="s">
+      <x:c r="B48" s="27" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C48" s="27" t="s"/>
-      <x:c r="D48" s="27" t="s"/>
-      <x:c r="E48" s="27" t="s"/>
-      <x:c r="F48" s="28" t="n">
+      <x:c r="C48" s="28" t="s"/>
+      <x:c r="D48" s="28" t="s"/>
+      <x:c r="E48" s="28" t="s"/>
+      <x:c r="F48" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="26" t="s">
+      <x:c r="B49" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C49" s="27" t="s"/>
-      <x:c r="D49" s="27" t="s"/>
-      <x:c r="E49" s="27" t="s"/>
-      <x:c r="F49" s="28" t="n">
+      <x:c r="C49" s="28" t="s"/>
+      <x:c r="D49" s="28" t="s"/>
+      <x:c r="E49" s="28" t="s"/>
+      <x:c r="F49" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="26" t="s">
+      <x:c r="B50" s="27" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C50" s="27" t="s"/>
-      <x:c r="D50" s="27" t="s"/>
-      <x:c r="E50" s="27" t="s"/>
-      <x:c r="F50" s="28" t="n">
+      <x:c r="C50" s="28" t="s"/>
+      <x:c r="D50" s="28" t="s"/>
+      <x:c r="E50" s="28" t="s"/>
+      <x:c r="F50" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="26" t="s">
+      <x:c r="B51" s="27" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C51" s="27" t="s"/>
-      <x:c r="D51" s="27" t="s"/>
-      <x:c r="E51" s="27" t="s"/>
-      <x:c r="F51" s="28" t="n">
+      <x:c r="C51" s="28" t="s"/>
+      <x:c r="D51" s="28" t="s"/>
+      <x:c r="E51" s="28" t="s"/>
+      <x:c r="F51" s="29" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="26" t="s">
+      <x:c r="B52" s="27" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="C52" s="27" t="s"/>
-      <x:c r="D52" s="27" t="s"/>
-      <x:c r="E52" s="27" t="s"/>
-      <x:c r="F52" s="28" t="n">
+      <x:c r="C52" s="28" t="s"/>
+      <x:c r="D52" s="28" t="s"/>
+      <x:c r="E52" s="28" t="s"/>
+      <x:c r="F52" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="26" t="s">
+      <x:c r="B53" s="27" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C53" s="27" t="s"/>
-      <x:c r="D53" s="27" t="s"/>
-      <x:c r="E53" s="27" t="s"/>
-      <x:c r="F53" s="28" t="n">
+      <x:c r="C53" s="28" t="s"/>
+      <x:c r="D53" s="28" t="s"/>
+      <x:c r="E53" s="28" t="s"/>
+      <x:c r="F53" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="26" t="s">
+      <x:c r="B54" s="27" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C54" s="27" t="s"/>
-      <x:c r="D54" s="27" t="s"/>
-      <x:c r="E54" s="27" t="s"/>
-      <x:c r="F54" s="28" t="n">
+      <x:c r="C54" s="28" t="s"/>
+      <x:c r="D54" s="28" t="s"/>
+      <x:c r="E54" s="28" t="s"/>
+      <x:c r="F54" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="29" t="s">
+      <x:c r="B55" s="30" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C55" s="30" t="s"/>
-      <x:c r="D55" s="30" t="s"/>
-      <x:c r="E55" s="30" t="s"/>
-      <x:c r="F55" s="31" t="n">
+      <x:c r="C55" s="31" t="s"/>
+      <x:c r="D55" s="31" t="s"/>
+      <x:c r="E55" s="31" t="s"/>
+      <x:c r="F55" s="32" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
@@ -4269,7 +4290,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46082</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -4341,1661 +4364,1696 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46091.306099537</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46091.3107986111</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1511778</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46091.3131828704</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="12" t="s"/>
+      <x:c r="E9" s="12" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46093.1459375</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>46093.1585185185</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1511815</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46093.159537037</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46098.0792592593</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46098.0878935185</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1529776</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46098.0997569444</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="C11" s="15" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="E11" s="15" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46090.2558217593</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I11" s="17">
         <x:v>46090.2558333333</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L11" s="19">
         <x:v>46097.2890740741</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
+      <x:c r="M11" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
         <x:v>179</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="D12" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
+      <x:c r="C13" s="15" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="E13" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="L13" s="19">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I14" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I15" s="20">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I16" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I17" s="20">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I18" s="20">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I19" s="20">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I20" s="20">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I21" s="20">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I22" s="20">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I23" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I24" s="20">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I25" s="20">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="19">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="H26" s="17">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I26" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D27" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H27" s="17">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I27" s="20">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="19">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M27" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H28" s="17">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I28" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J28" s="16" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K28" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="19">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M28" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="H29" s="17">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I29" s="20">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="19">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M29" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H30" s="17">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I30" s="20">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J30" s="16" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K30" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="19">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M30" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D31" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G31" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H31" s="17">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I31" s="20">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J31" s="16" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K31" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="19">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M31" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D32" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H32" s="17">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I32" s="20">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J32" s="16" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K32" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L32" s="19">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M32" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D33" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H33" s="17">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I33" s="20">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J33" s="16" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K33" s="18" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L33" s="19">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M33" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G34" s="15" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H34" s="17">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I34" s="20">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J34" s="16" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K34" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="19">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M34" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G35" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H35" s="17">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I35" s="20">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K35" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="19">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M35" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="F36" s="15" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="G36" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="H36" s="17">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I36" s="20">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J36" s="16" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K36" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="19">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M36" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H37" s="17">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I37" s="17">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K37" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L37" s="19">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M37" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F38" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G38" s="15" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H38" s="17">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I38" s="17">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J38" s="16" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K38" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="19">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M38" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="F39" s="15" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G39" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="H39" s="17">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I39" s="17">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J39" s="16" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K39" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="19">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M39" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F40" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G40" s="15" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H40" s="17">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I40" s="17">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J40" s="16" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K40" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="19">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M40" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D41" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F41" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G41" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="H41" s="17">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I41" s="20">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J41" s="16" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K41" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L41" s="19">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M41" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C42" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E42" s="15" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F42" s="15" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G42" s="15" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H42" s="17">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I42" s="20">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J42" s="16" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K42" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L42" s="19">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M42" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C43" s="15" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D43" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E43" s="15" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="F43" s="15" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="G43" s="15" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="H43" s="17">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I43" s="20">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J43" s="16" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K43" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="19">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M43" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C44" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E44" s="15" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="F44" s="15" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="G44" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H44" s="17">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I44" s="20">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J44" s="16" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K44" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L44" s="19">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M44" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C45" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E45" s="15" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F45" s="15" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="G45" s="15" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="H45" s="17">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I45" s="20">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J45" s="16" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K45" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="19">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M45" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C46" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D46" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E46" s="15" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F46" s="15" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="G46" s="15" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="H46" s="17">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I46" s="20">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J46" s="16" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K46" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L46" s="19">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M46" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C47" s="15" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E47" s="15" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F47" s="15" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="G47" s="15" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="H47" s="17">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I47" s="20">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J47" s="16" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K47" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L47" s="19">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M47" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C48" s="15" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E48" s="15" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="F48" s="15" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="G48" s="15" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="H48" s="17">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I48" s="20">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J48" s="16" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K48" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L48" s="19">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M48" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B51" s="21" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C51" s="22" t="s"/>
+      <x:c r="D51" s="22" t="s"/>
+      <x:c r="E51" s="23" t="s"/>
+      <x:c r="F51" s="23" t="s"/>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B52" s="24" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C52" s="25" t="s"/>
+      <x:c r="D52" s="25" t="s"/>
+      <x:c r="E52" s="25" t="s"/>
+      <x:c r="F52" s="26" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C53" s="28" t="s"/>
+      <x:c r="D53" s="28" t="s"/>
+      <x:c r="E53" s="28" t="s"/>
+      <x:c r="F53" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="27" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="C54" s="28" t="s"/>
+      <x:c r="D54" s="28" t="s"/>
+      <x:c r="E54" s="28" t="s"/>
+      <x:c r="F54" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I28" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I29" s="19">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="18">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I30" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J30" s="15" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="18">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C31" s="14" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E31" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="G31" s="14" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="H31" s="16">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I31" s="19">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J31" s="15" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K31" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L31" s="18">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M31" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C32" s="14" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E32" s="14" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G32" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H32" s="16">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I32" s="19">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J32" s="15" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K32" s="17" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L32" s="18">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M32" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I33" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J33" s="15" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K33" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="18">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M33" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C34" s="14" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E34" s="14" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H34" s="16">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I34" s="19">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K34" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="18">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M34" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C35" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E35" s="14" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="G35" s="14" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="H35" s="16">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I35" s="19">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K35" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="18">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="14" t="s">
+      <x:c r="C55" s="28" t="s"/>
+      <x:c r="D55" s="28" t="s"/>
+      <x:c r="E55" s="28" t="s"/>
+      <x:c r="F55" s="29" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="27" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C36" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="G36" s="14" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="H36" s="16">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I36" s="16">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J36" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K36" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L36" s="18">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="G37" s="14" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="H37" s="16">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I37" s="16">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J37" s="15" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K37" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L37" s="18">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="H38" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I38" s="16">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J38" s="15" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K38" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L38" s="18">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D39" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E39" s="14" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="G39" s="14" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I39" s="16">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J39" s="15" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K39" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L39" s="18">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M39" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="14" t="s">
+      <x:c r="C56" s="28" t="s"/>
+      <x:c r="D56" s="28" t="s"/>
+      <x:c r="E56" s="28" t="s"/>
+      <x:c r="F56" s="29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="27" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C40" s="14" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="D40" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E40" s="14" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="G40" s="14" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="H40" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I40" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J40" s="15" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K40" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L40" s="18">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M40" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C41" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D41" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E41" s="14" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F41" s="14" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="G41" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H41" s="16">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I41" s="19">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J41" s="15" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K41" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="18">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M41" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C42" s="14" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="D42" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E42" s="14" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="F42" s="14" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="G42" s="14" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="H42" s="16">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I42" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J42" s="15" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K42" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L42" s="18">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M42" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C43" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="D43" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E43" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="F43" s="14" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="G43" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H43" s="16">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I43" s="19">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J43" s="15" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K43" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="18">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M43" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C44" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="D44" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E44" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="F44" s="14" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="G44" s="14" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="H44" s="16">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I44" s="19">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J44" s="15" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K44" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="18">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M44" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C45" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="D45" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E45" s="14" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="F45" s="14" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="G45" s="14" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="H45" s="16">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I45" s="19">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J45" s="15" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K45" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="18">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M45" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="14" t="s">
+      <x:c r="C57" s="28" t="s"/>
+      <x:c r="D57" s="28" t="s"/>
+      <x:c r="E57" s="28" t="s"/>
+      <x:c r="F57" s="29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B58" s="27" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C46" s="14" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="D46" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E46" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="F46" s="14" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="G46" s="14" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="H46" s="16">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I46" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J46" s="15" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K46" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L46" s="18">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M46" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C47" s="14" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="D47" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E47" s="14" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="F47" s="14" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="G47" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="H47" s="16">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I47" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J47" s="15" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K47" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L47" s="18">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M47" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="20" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="C50" s="21" t="s"/>
-      <x:c r="D50" s="21" t="s"/>
-      <x:c r="E50" s="22" t="s"/>
-      <x:c r="F50" s="22" t="s"/>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B51" s="23" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="C51" s="24" t="s"/>
-      <x:c r="D51" s="24" t="s"/>
-      <x:c r="E51" s="24" t="s"/>
-      <x:c r="F51" s="25" t="s">
-        <x:v>165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C52" s="27" t="s"/>
-      <x:c r="D52" s="27" t="s"/>
-      <x:c r="E52" s="27" t="s"/>
-      <x:c r="F52" s="28" t="n">
+      <x:c r="C58" s="28" t="s"/>
+      <x:c r="D58" s="28" t="s"/>
+      <x:c r="E58" s="28" t="s"/>
+      <x:c r="F58" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C53" s="27" t="s"/>
-      <x:c r="D53" s="27" t="s"/>
-      <x:c r="E53" s="27" t="s"/>
-      <x:c r="F53" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="26" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C54" s="27" t="s"/>
-      <x:c r="D54" s="27" t="s"/>
-      <x:c r="E54" s="27" t="s"/>
-      <x:c r="F54" s="28" t="n">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="26" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C55" s="27" t="s"/>
-      <x:c r="D55" s="27" t="s"/>
-      <x:c r="E55" s="27" t="s"/>
-      <x:c r="F55" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="26" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C56" s="27" t="s"/>
-      <x:c r="D56" s="27" t="s"/>
-      <x:c r="E56" s="27" t="s"/>
-      <x:c r="F56" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="26" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C57" s="27" t="s"/>
-      <x:c r="D57" s="27" t="s"/>
-      <x:c r="E57" s="27" t="s"/>
-      <x:c r="F57" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B58" s="29" t="s">
+    <x:row r="59" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B59" s="30" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C58" s="30" t="s"/>
-      <x:c r="D58" s="30" t="s"/>
-      <x:c r="E58" s="30" t="s"/>
-      <x:c r="F58" s="31" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C59" s="31" t="s"/>
+      <x:c r="D59" s="31" t="s"/>
+      <x:c r="E59" s="31" t="s"/>
+      <x:c r="F59" s="32" t="n">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6935,8 +6993,7 @@
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
     <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B50:F50"/>
-    <x:mergeCell ref="B51:E51"/>
+    <x:mergeCell ref="B51:F51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
@@ -6944,6 +7001,7 @@
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
+    <x:mergeCell ref="B59:E59"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,9 +23,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
-  <x:si>
-    <x:t>PERMIT SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
+  <x:si>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMITS SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IV-A | February 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -524,6 +530,9 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>HERALD BEBIS</x:t>
@@ -974,7 +983,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1014,6 +1023,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1285,15 +1318,21 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1308,59 +1347,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1391,95 +1430,103 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1708,58 +1755,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1802,1477 +1849,1477 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="F8" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46069.0835185185</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>46069.1006712963</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1506161</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46069.1133333333</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s"/>
-      <x:c r="E9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I9" s="13">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K9" s="14" t="n">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="L11" s="21">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="L12" s="21">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="L13" s="21">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46067.3600231481</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46067.3600462963</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46079.2730092593</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="21">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="21">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="21">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I19" s="22">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I20" s="22">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="21">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="21">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I24" s="22">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="21">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I25" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="21">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I26" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="21">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I27" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="21">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H28" s="19">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I28" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="18" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K28" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="21">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M28" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C29" s="17" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H29" s="19">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I29" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="18" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K29" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="21">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M29" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C30" s="17" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G30" s="17" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H30" s="19">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I30" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K30" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="21">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M30" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C31" s="17" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E31" s="17" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H31" s="19">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I31" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K31" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="21">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M31" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C32" s="17" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D32" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H32" s="19">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I32" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K32" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="21">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M32" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C33" s="17" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E33" s="17" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F33" s="17" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G33" s="17" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H33" s="19">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I33" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="18" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K33" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="21">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M33" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C34" s="17" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D34" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E34" s="17" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F34" s="17" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G34" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H34" s="19">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I34" s="22">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J34" s="18" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K34" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="21">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M34" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C35" s="17" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="D35" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E35" s="17" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F35" s="17" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G35" s="17" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H35" s="19">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I35" s="22">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J35" s="18" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K35" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="21">
+        <x:v>46077.1078819444</x:v>
+      </x:c>
+      <x:c r="M35" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="17" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C36" s="17" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D36" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="E36" s="17" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F36" s="17" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G36" s="17" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H36" s="19">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I36" s="19">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J36" s="18" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K36" s="20" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L36" s="21">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M36" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C37" s="17" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D37" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I16" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I17" s="20">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I18" s="20">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I19" s="20">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I20" s="20">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E37" s="17" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F37" s="17" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G37" s="17" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H37" s="19">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I37" s="22">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J37" s="18" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K37" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L37" s="21">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M37" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C38" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D38" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E38" s="17" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F38" s="17" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G38" s="17" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H38" s="19">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I38" s="22">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J38" s="18" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K38" s="20" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L38" s="21">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M38" s="17" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I24" s="20">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I25" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C26" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D26" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G26" s="15" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H26" s="17">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I26" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="16" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="19">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M26" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C27" s="15" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D27" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F27" s="15" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G27" s="15" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H27" s="17">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I27" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K27" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="19">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M27" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C28" s="15" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D28" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E28" s="15" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F28" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G28" s="15" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H28" s="17">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I28" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="16" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K28" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="19">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M28" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C29" s="15" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D29" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E29" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="G29" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="H29" s="17">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I29" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="16" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="19">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M29" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C30" s="15" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D30" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E30" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F30" s="15" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G30" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H30" s="17">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I30" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K30" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="19">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M30" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C31" s="15" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D31" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E31" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F31" s="15" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G31" s="15" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H31" s="17">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I31" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K31" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="19">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M31" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C32" s="15" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D32" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E32" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F32" s="15" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G32" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H32" s="17">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I32" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K32" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="19">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M32" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C33" s="15" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D33" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E33" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F33" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G33" s="15" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H33" s="17">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I33" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="16" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K33" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="19">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M33" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C34" s="15" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D34" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E34" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F34" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G34" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H34" s="17">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I34" s="20">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J34" s="16" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K34" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="19">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M34" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C35" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D35" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E35" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F35" s="15" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G35" s="15" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H35" s="17">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I35" s="20">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J35" s="16" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K35" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="19">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M35" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="15" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C36" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D36" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E36" s="15" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F36" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G36" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H36" s="17">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I36" s="17">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J36" s="16" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K36" s="18" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L36" s="19">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M36" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C37" s="15" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D37" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E37" s="15" t="s">
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="17" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G37" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H37" s="17">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I37" s="20">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J37" s="16" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K37" s="18" t="n">
+      <x:c r="C39" s="17" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D39" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E39" s="17" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G39" s="17" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H39" s="19">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I39" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J39" s="18" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K39" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L37" s="19">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M37" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C38" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D38" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E38" s="15" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F38" s="15" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G38" s="15" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H38" s="17">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I38" s="20">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J38" s="16" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K38" s="18" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L38" s="19">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M38" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C39" s="15" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D39" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E39" s="15" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="F39" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G39" s="15" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H39" s="17">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I39" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J39" s="16" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K39" s="18" t="n">
+      <x:c r="L39" s="21">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M39" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C40" s="17" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D40" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E40" s="17" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G40" s="17" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H40" s="19">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I40" s="22">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J40" s="18" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K40" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L39" s="19">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M39" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C40" s="15" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D40" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E40" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="F40" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G40" s="15" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H40" s="17">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I40" s="20">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J40" s="16" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K40" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L40" s="19">
+      <x:c r="L40" s="21">
         <x:v>46078.3266203704</x:v>
       </x:c>
-      <x:c r="M40" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M40" s="17" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="15" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C41" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D41" s="16" t="s"/>
-      <x:c r="E41" s="15" t="s">
+      <x:c r="B41" s="17" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F41" s="15" t="s">
+      <x:c r="C41" s="17" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G41" s="15" t="s">
+      <x:c r="D41" s="18" t="s"/>
+      <x:c r="E41" s="17" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H41" s="17">
+      <x:c r="F41" s="17" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G41" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H41" s="19">
         <x:v>46080.2342361111</x:v>
       </x:c>
-      <x:c r="I41" s="17">
+      <x:c r="I41" s="19">
         <x:v>46080.2342592593</x:v>
       </x:c>
-      <x:c r="J41" s="16" t="n">
+      <x:c r="J41" s="18" t="n">
         <x:v>1507884</x:v>
       </x:c>
-      <x:c r="K41" s="18" t="n">
+      <x:c r="K41" s="20" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L41" s="19">
+      <x:c r="L41" s="21">
         <x:v>46080.3353356481</x:v>
       </x:c>
-      <x:c r="M41" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M41" s="17" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="15" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C42" s="15" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D42" s="16" t="s"/>
-      <x:c r="E42" s="15" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F42" s="15" t="s">
+      <x:c r="B42" s="17" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C42" s="17" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G42" s="15" t="s">
+      <x:c r="D42" s="18" t="s"/>
+      <x:c r="E42" s="17" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="H42" s="17">
+      <x:c r="F42" s="17" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G42" s="17" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H42" s="19">
         <x:v>46080.2722685185</x:v>
       </x:c>
-      <x:c r="I42" s="17">
+      <x:c r="I42" s="19">
         <x:v>46080.2722800926</x:v>
       </x:c>
-      <x:c r="J42" s="16" t="n">
+      <x:c r="J42" s="18" t="n">
         <x:v>1507883</x:v>
       </x:c>
-      <x:c r="K42" s="18" t="n">
+      <x:c r="K42" s="20" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L42" s="19">
+      <x:c r="L42" s="21">
         <x:v>46080.3345717593</x:v>
       </x:c>
-      <x:c r="M42" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M42" s="17" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="21" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="C45" s="22" t="s"/>
-      <x:c r="D45" s="22" t="s"/>
-      <x:c r="E45" s="23" t="s"/>
-      <x:c r="F45" s="23" t="s"/>
+      <x:c r="B45" s="23" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C45" s="24" t="s"/>
+      <x:c r="D45" s="24" t="s"/>
+      <x:c r="E45" s="25" t="s"/>
+      <x:c r="F45" s="25" t="s"/>
     </x:row>
     <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="24" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="C46" s="25" t="s"/>
-      <x:c r="D46" s="25" t="s"/>
-      <x:c r="E46" s="25" t="s"/>
-      <x:c r="F46" s="26" t="s">
-        <x:v>165</x:v>
+      <x:c r="B46" s="26" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C46" s="27" t="s"/>
+      <x:c r="D46" s="27" t="s"/>
+      <x:c r="E46" s="27" t="s"/>
+      <x:c r="F46" s="28" t="s">
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C47" s="28" t="s"/>
-      <x:c r="D47" s="28" t="s"/>
-      <x:c r="E47" s="28" t="s"/>
-      <x:c r="F47" s="29" t="n">
+      <x:c r="B47" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C47" s="30" t="s"/>
+      <x:c r="D47" s="30" t="s"/>
+      <x:c r="E47" s="30" t="s"/>
+      <x:c r="F47" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="27" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C48" s="28" t="s"/>
-      <x:c r="D48" s="28" t="s"/>
-      <x:c r="E48" s="28" t="s"/>
-      <x:c r="F48" s="29" t="n">
+      <x:c r="B48" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C48" s="30" t="s"/>
+      <x:c r="D48" s="30" t="s"/>
+      <x:c r="E48" s="30" t="s"/>
+      <x:c r="F48" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="27" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C49" s="28" t="s"/>
-      <x:c r="D49" s="28" t="s"/>
-      <x:c r="E49" s="28" t="s"/>
-      <x:c r="F49" s="29" t="n">
+      <x:c r="B49" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C49" s="30" t="s"/>
+      <x:c r="D49" s="30" t="s"/>
+      <x:c r="E49" s="30" t="s"/>
+      <x:c r="F49" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="27" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C50" s="28" t="s"/>
-      <x:c r="D50" s="28" t="s"/>
-      <x:c r="E50" s="28" t="s"/>
-      <x:c r="F50" s="29" t="n">
+      <x:c r="B50" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C50" s="30" t="s"/>
+      <x:c r="D50" s="30" t="s"/>
+      <x:c r="E50" s="30" t="s"/>
+      <x:c r="F50" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="27" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C51" s="28" t="s"/>
-      <x:c r="D51" s="28" t="s"/>
-      <x:c r="E51" s="28" t="s"/>
-      <x:c r="F51" s="29" t="n">
+      <x:c r="B51" s="29" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C51" s="30" t="s"/>
+      <x:c r="D51" s="30" t="s"/>
+      <x:c r="E51" s="30" t="s"/>
+      <x:c r="F51" s="31" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="27" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C52" s="28" t="s"/>
-      <x:c r="D52" s="28" t="s"/>
-      <x:c r="E52" s="28" t="s"/>
-      <x:c r="F52" s="29" t="n">
+      <x:c r="B52" s="29" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="s"/>
+      <x:c r="D52" s="30" t="s"/>
+      <x:c r="E52" s="30" t="s"/>
+      <x:c r="F52" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="27" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C53" s="28" t="s"/>
-      <x:c r="D53" s="28" t="s"/>
-      <x:c r="E53" s="28" t="s"/>
-      <x:c r="F53" s="29" t="n">
+      <x:c r="B53" s="29" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C53" s="30" t="s"/>
+      <x:c r="D53" s="30" t="s"/>
+      <x:c r="E53" s="30" t="s"/>
+      <x:c r="F53" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="27" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C54" s="28" t="s"/>
-      <x:c r="D54" s="28" t="s"/>
-      <x:c r="E54" s="28" t="s"/>
-      <x:c r="F54" s="29" t="n">
+      <x:c r="B54" s="29" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C54" s="30" t="s"/>
+      <x:c r="D54" s="30" t="s"/>
+      <x:c r="E54" s="30" t="s"/>
+      <x:c r="F54" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="30" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C55" s="31" t="s"/>
-      <x:c r="D55" s="31" t="s"/>
-      <x:c r="E55" s="31" t="s"/>
-      <x:c r="F55" s="32" t="n">
+      <x:c r="B55" s="32" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C55" s="33" t="s"/>
+      <x:c r="D55" s="33" t="s"/>
+      <x:c r="E55" s="33" t="s"/>
+      <x:c r="F55" s="34" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
@@ -4218,7 +4265,7 @@
   <x:mergeCells count="14">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B45:F45"/>
     <x:mergeCell ref="B46:E46"/>
     <x:mergeCell ref="B47:E47"/>
@@ -4270,58 +4317,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -4364,1693 +4411,1693 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46091.306099537</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>46091.3107986111</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1511778</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46091.3131828704</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>78</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s"/>
-      <x:c r="E9" s="12" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46093.1459375</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="15">
         <x:v>46093.1585185185</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1511815</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>46093.159537037</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>78</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>46098.0792592593</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="19">
         <x:v>46098.0878935185</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1529776</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="21">
         <x:v>46098.0997569444</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="C11" s="17" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="D11" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
         <x:v>46090.2558217593</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="19">
         <x:v>46090.2558333333</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="21">
         <x:v>46097.2890740741</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>183</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="B12" s="17" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="C12" s="17" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="L13" s="21">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I14" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I15" s="22">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="21">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="21">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="21">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I19" s="22">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I20" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I21" s="22">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I22" s="22">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="21">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I23" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="21">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I24" s="22">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="21">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I25" s="22">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="21">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I26" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="21">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I27" s="22">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="21">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H28" s="19">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I28" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J28" s="18" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K28" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="21">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M28" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C29" s="17" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H29" s="19">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I29" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J29" s="18" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K29" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="21">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M29" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C30" s="17" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G30" s="17" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="H30" s="19">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I30" s="22">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J30" s="18" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K30" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="21">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M30" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C31" s="17" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E31" s="17" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H31" s="19">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I31" s="22">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J31" s="18" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K31" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="21">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M31" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C32" s="17" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D32" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H32" s="19">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I32" s="22">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J32" s="18" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K32" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L32" s="21">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M32" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C33" s="17" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E33" s="17" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F33" s="17" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G33" s="17" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H33" s="19">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I33" s="22">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J33" s="18" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K33" s="20" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L33" s="21">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M33" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C34" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D34" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E34" s="17" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F34" s="17" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G34" s="17" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H34" s="19">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I34" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J34" s="18" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K34" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="21">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M34" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C35" s="17" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D35" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E35" s="17" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F35" s="17" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G35" s="17" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H35" s="19">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I35" s="22">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J35" s="18" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K35" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="21">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M35" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C36" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D36" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E36" s="17" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F36" s="17" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G36" s="17" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H36" s="19">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I36" s="22">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J36" s="18" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K36" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="21">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M36" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C37" s="17" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D37" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E37" s="17" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F37" s="17" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G37" s="17" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H37" s="19">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I37" s="19">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J37" s="18" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K37" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I14" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="L37" s="21">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M37" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C38" s="17" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D38" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E38" s="17" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="F38" s="17" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G38" s="17" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="H38" s="19">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I38" s="19">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J38" s="18" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K38" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="21">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M38" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C39" s="17" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D39" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E39" s="17" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G39" s="17" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H39" s="19">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I39" s="19">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J39" s="18" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K39" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="21">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M39" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C40" s="17" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D40" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E40" s="17" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G40" s="17" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H40" s="19">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I40" s="19">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J40" s="18" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K40" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="21">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M40" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C41" s="17" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="D41" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E41" s="17" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F41" s="17" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G41" s="17" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H41" s="19">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I41" s="22">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J41" s="18" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K41" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I15" s="20">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="L41" s="21">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M41" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C42" s="17" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D42" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E42" s="17" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F42" s="17" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G42" s="17" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H42" s="19">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I42" s="22">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J42" s="18" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K42" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I16" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="L42" s="21">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M42" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C43" s="17" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="D43" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E43" s="17" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="F43" s="17" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="G43" s="17" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H43" s="19">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I43" s="22">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J43" s="18" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K43" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I17" s="20">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="L43" s="21">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M43" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C44" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D44" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E44" s="17" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F44" s="17" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="G44" s="17" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="H44" s="19">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I44" s="22">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J44" s="18" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K44" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I18" s="20">
+      <x:c r="L44" s="21">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M44" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C45" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D45" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E45" s="17" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F45" s="17" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="G45" s="17" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="H45" s="19">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I45" s="22">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J45" s="18" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K45" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="21">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M45" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C46" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D46" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E46" s="17" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="F46" s="17" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="G46" s="17" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="H46" s="19">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I46" s="22">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J46" s="18" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K46" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L46" s="21">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M46" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C47" s="17" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="D47" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E47" s="17" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="F47" s="17" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="G47" s="17" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="H47" s="19">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I47" s="22">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I19" s="20">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I20" s="20">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I21" s="20">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I22" s="20">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I23" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I24" s="20">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I25" s="20">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C26" s="15" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="D26" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="G26" s="15" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="H26" s="17">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I26" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J26" s="16" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="19">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M26" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C27" s="15" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="D27" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="F27" s="15" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="G27" s="15" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="H27" s="17">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I27" s="20">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J27" s="16" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K27" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="19">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M27" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C28" s="15" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="D28" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E28" s="15" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F28" s="15" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="G28" s="15" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="H28" s="17">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I28" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J28" s="16" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K28" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="19">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M28" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C29" s="15" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="D29" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E29" s="15" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="G29" s="15" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="H29" s="17">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I29" s="20">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J29" s="16" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="19">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M29" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C30" s="15" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="D30" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E30" s="15" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="F30" s="15" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G30" s="15" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="H30" s="17">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I30" s="20">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J30" s="16" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K30" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="19">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M30" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C31" s="15" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D31" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E31" s="15" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="F31" s="15" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="G31" s="15" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="H31" s="17">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I31" s="20">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J31" s="16" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K31" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="19">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M31" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C32" s="15" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D32" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E32" s="15" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F32" s="15" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="G32" s="15" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="H32" s="17">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I32" s="20">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J32" s="16" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K32" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L32" s="19">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M32" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C33" s="15" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D33" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E33" s="15" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F33" s="15" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G33" s="15" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H33" s="17">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I33" s="20">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J33" s="16" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K33" s="18" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L33" s="19">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M33" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C34" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D34" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E34" s="15" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F34" s="15" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G34" s="15" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H34" s="17">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I34" s="20">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J34" s="16" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K34" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="19">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M34" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C35" s="15" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="D35" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E35" s="15" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F35" s="15" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="G35" s="15" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="H35" s="17">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I35" s="20">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J35" s="16" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K35" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="19">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M35" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C36" s="15" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D36" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E36" s="15" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="F36" s="15" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="G36" s="15" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="H36" s="17">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I36" s="20">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J36" s="16" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K36" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="19">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M36" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C37" s="15" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="D37" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E37" s="15" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="F37" s="15" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G37" s="15" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H37" s="17">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I37" s="17">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J37" s="16" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K37" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L37" s="19">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M37" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C38" s="15" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="D38" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E38" s="15" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F38" s="15" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G38" s="15" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H38" s="17">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I38" s="17">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J38" s="16" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K38" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L38" s="19">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M38" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C39" s="15" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="D39" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E39" s="15" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="F39" s="15" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="G39" s="15" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="H39" s="17">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I39" s="17">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J39" s="16" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K39" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L39" s="19">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M39" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C40" s="15" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="D40" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E40" s="15" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="F40" s="15" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="G40" s="15" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="H40" s="17">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I40" s="17">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J40" s="16" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K40" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L40" s="19">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M40" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C41" s="15" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="D41" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E41" s="15" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="F41" s="15" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="G41" s="15" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="H41" s="17">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I41" s="20">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J41" s="16" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K41" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="19">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M41" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C42" s="15" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D42" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E42" s="15" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="F42" s="15" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="G42" s="15" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="H42" s="17">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I42" s="20">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J42" s="16" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K42" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L42" s="19">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M42" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C43" s="15" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="D43" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E43" s="15" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="F43" s="15" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="G43" s="15" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="H43" s="17">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I43" s="20">
+      <x:c r="J47" s="18" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K47" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L47" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M47" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C48" s="17" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D48" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E48" s="17" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F48" s="17" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="G48" s="17" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="H48" s="19">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I48" s="22">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J43" s="16" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K43" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="19">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M43" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C44" s="15" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D44" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E44" s="15" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="F44" s="15" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="G44" s="15" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="H44" s="17">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I44" s="20">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J44" s="16" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K44" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="19">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M44" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C45" s="15" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D45" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E45" s="15" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="F45" s="15" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="G45" s="15" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="H45" s="17">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I45" s="20">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J45" s="16" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K45" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="19">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M45" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C46" s="15" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D46" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E46" s="15" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="F46" s="15" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="G46" s="15" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="H46" s="17">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I46" s="20">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J46" s="16" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K46" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L46" s="19">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M46" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C47" s="15" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="D47" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E47" s="15" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="F47" s="15" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="G47" s="15" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="H47" s="17">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I47" s="20">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J47" s="16" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K47" s="18" t="n">
+      <x:c r="J48" s="18" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K48" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L47" s="19">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M47" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B48" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C48" s="15" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="D48" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E48" s="15" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="F48" s="15" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="G48" s="15" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="H48" s="17">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I48" s="20">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J48" s="16" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K48" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L48" s="19">
+      <x:c r="L48" s="21">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M48" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M48" s="17" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="21" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="C51" s="22" t="s"/>
-      <x:c r="D51" s="22" t="s"/>
-      <x:c r="E51" s="23" t="s"/>
-      <x:c r="F51" s="23" t="s"/>
+      <x:c r="B51" s="23" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C51" s="24" t="s"/>
+      <x:c r="D51" s="24" t="s"/>
+      <x:c r="E51" s="25" t="s"/>
+      <x:c r="F51" s="25" t="s"/>
     </x:row>
     <x:row r="52" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B52" s="24" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="C52" s="25" t="s"/>
-      <x:c r="D52" s="25" t="s"/>
-      <x:c r="E52" s="25" t="s"/>
-      <x:c r="F52" s="26" t="s">
-        <x:v>165</x:v>
+      <x:c r="B52" s="26" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C52" s="27" t="s"/>
+      <x:c r="D52" s="27" t="s"/>
+      <x:c r="E52" s="27" t="s"/>
+      <x:c r="F52" s="28" t="s">
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C53" s="28" t="s"/>
-      <x:c r="D53" s="28" t="s"/>
-      <x:c r="E53" s="28" t="s"/>
-      <x:c r="F53" s="29" t="n">
+      <x:c r="B53" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C53" s="30" t="s"/>
+      <x:c r="D53" s="30" t="s"/>
+      <x:c r="E53" s="30" t="s"/>
+      <x:c r="F53" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="27" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C54" s="28" t="s"/>
-      <x:c r="D54" s="28" t="s"/>
-      <x:c r="E54" s="28" t="s"/>
-      <x:c r="F54" s="29" t="n">
+      <x:c r="B54" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C54" s="30" t="s"/>
+      <x:c r="D54" s="30" t="s"/>
+      <x:c r="E54" s="30" t="s"/>
+      <x:c r="F54" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="27" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C55" s="28" t="s"/>
-      <x:c r="D55" s="28" t="s"/>
-      <x:c r="E55" s="28" t="s"/>
-      <x:c r="F55" s="29" t="n">
+      <x:c r="B55" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C55" s="30" t="s"/>
+      <x:c r="D55" s="30" t="s"/>
+      <x:c r="E55" s="30" t="s"/>
+      <x:c r="F55" s="31" t="n">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="27" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C56" s="28" t="s"/>
-      <x:c r="D56" s="28" t="s"/>
-      <x:c r="E56" s="28" t="s"/>
-      <x:c r="F56" s="29" t="n">
+      <x:c r="B56" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C56" s="30" t="s"/>
+      <x:c r="D56" s="30" t="s"/>
+      <x:c r="E56" s="30" t="s"/>
+      <x:c r="F56" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="27" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C57" s="28" t="s"/>
-      <x:c r="D57" s="28" t="s"/>
-      <x:c r="E57" s="28" t="s"/>
-      <x:c r="F57" s="29" t="n">
+      <x:c r="B57" s="29" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C57" s="30" t="s"/>
+      <x:c r="D57" s="30" t="s"/>
+      <x:c r="E57" s="30" t="s"/>
+      <x:c r="F57" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="27" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C58" s="28" t="s"/>
-      <x:c r="D58" s="28" t="s"/>
-      <x:c r="E58" s="28" t="s"/>
-      <x:c r="F58" s="29" t="n">
+      <x:c r="B58" s="29" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C58" s="30" t="s"/>
+      <x:c r="D58" s="30" t="s"/>
+      <x:c r="E58" s="30" t="s"/>
+      <x:c r="F58" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B59" s="30" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C59" s="31" t="s"/>
-      <x:c r="D59" s="31" t="s"/>
-      <x:c r="E59" s="31" t="s"/>
-      <x:c r="F59" s="32" t="n">
+      <x:c r="B59" s="32" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C59" s="33" t="s"/>
+      <x:c r="D59" s="33" t="s"/>
+      <x:c r="E59" s="33" t="s"/>
+      <x:c r="F59" s="34" t="n">
         <x:v>41</x:v>
       </x:c>
     </x:row>
@@ -6992,7 +7039,7 @@
   <x:mergeCells count="12">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B51:F51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -68,6 +68,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -980,10 +1016,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1028,15 +1066,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -1052,15 +1082,8 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -1323,19 +1346,19 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1347,59 +1370,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1430,103 +1453,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1755,78 +1766,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
-      <x:c r="N4" s="3" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28">
-      <x:c r="A5" s="4" t="s"/>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1847,7 +1870,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1887,1444 +1910,1494 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46069.0835185185</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46069.1006712963</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1506161</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46069.1133333333</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
+      <x:c r="M10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46066.2950925926</x:v>
       </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="I11" s="17">
         <x:v>46066.3145023148</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1507747</x:v>
       </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="15">
+      <x:c r="L11" s="19">
         <x:v>46066.3194212963</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
+      <x:c r="M11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
+      <x:c r="C12" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
         <x:v>46069.0835648148</x:v>
       </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="I12" s="17">
         <x:v>46069.1000231481</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1506159</x:v>
       </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="21">
+      <x:c r="L12" s="19">
         <x:v>46069.1128587963</x:v>
       </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
+      <x:c r="M12" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>46072.1720833333</x:v>
       </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="I13" s="17">
         <x:v>46072.235162037</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1507783</x:v>
       </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="21">
+      <x:c r="L13" s="19">
         <x:v>46073.1890277778</x:v>
       </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="17" t="s">
+      <x:c r="M13" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s"/>
+      <x:c r="E14" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s"/>
+      <x:c r="E15" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46067.3600231481</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46067.3600462963</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46079.2730092593</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I25" s="17">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L25" s="19">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H26" s="17">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I26" s="17">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D27" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H27" s="17">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I27" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="19">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M27" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H28" s="17">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I28" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="16" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K28" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="19">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M28" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H29" s="17">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I29" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="19">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M29" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H30" s="17">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I30" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="16" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K30" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="19">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M30" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D31" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G31" s="15" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H31" s="17">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I31" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="16" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K31" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="19">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M31" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D32" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="H32" s="17">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I32" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="16" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K32" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="19">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M32" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D33" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H33" s="17">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I33" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="16" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K33" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="19">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M33" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G34" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H34" s="17">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I34" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J34" s="16" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K34" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="19">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M34" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G35" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H35" s="17">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I35" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K35" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="19">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M35" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F36" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G36" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H36" s="17">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I36" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J36" s="16" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K36" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="19">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M36" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H37" s="17">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I37" s="17">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K37" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L37" s="19">
+        <x:v>46077.1078819444</x:v>
+      </x:c>
+      <x:c r="M37" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="15" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F38" s="15" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G38" s="15" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H38" s="17">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I38" s="17">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J38" s="16" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K38" s="18" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L38" s="19">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M38" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F39" s="15" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G39" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H39" s="17">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I39" s="17">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J39" s="16" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K39" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L39" s="19">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M39" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F40" s="15" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G40" s="15" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H40" s="17">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I40" s="17">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J40" s="16" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K40" s="18" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L40" s="19">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M40" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D41" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F41" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G41" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H41" s="17">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I41" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J41" s="16" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K41" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L41" s="19">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M41" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C42" s="15" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E42" s="15" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F42" s="15" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G42" s="15" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H42" s="17">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I42" s="17">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J42" s="16" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K42" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L42" s="19">
+        <x:v>46078.3266203704</x:v>
+      </x:c>
+      <x:c r="M42" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="15" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C43" s="15" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D43" s="16" t="s"/>
+      <x:c r="E43" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F43" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G43" s="15" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H43" s="17">
+        <x:v>46080.2342361111</x:v>
+      </x:c>
+      <x:c r="I43" s="17">
+        <x:v>46080.2342592593</x:v>
+      </x:c>
+      <x:c r="J43" s="16" t="n">
+        <x:v>1507884</x:v>
+      </x:c>
+      <x:c r="K43" s="18" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L43" s="19">
+        <x:v>46080.3353356481</x:v>
+      </x:c>
+      <x:c r="M43" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="15" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C44" s="15" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="s"/>
+      <x:c r="E44" s="15" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="F44" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G44" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H44" s="17">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I44" s="17">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J44" s="16" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K44" s="18" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L44" s="19">
+        <x:v>46080.3345717593</x:v>
+      </x:c>
+      <x:c r="M44" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B47" s="20" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C47" s="21" t="s"/>
+      <x:c r="D47" s="21" t="s"/>
+      <x:c r="E47" s="22" t="s"/>
+      <x:c r="F47" s="22" t="s"/>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B48" s="23" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C48" s="24" t="s"/>
+      <x:c r="D48" s="24" t="s"/>
+      <x:c r="E48" s="24" t="s"/>
+      <x:c r="F48" s="25" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C49" s="27" t="s"/>
+      <x:c r="D49" s="27" t="s"/>
+      <x:c r="E49" s="27" t="s"/>
+      <x:c r="F49" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="26" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C50" s="27" t="s"/>
+      <x:c r="D50" s="27" t="s"/>
+      <x:c r="E50" s="27" t="s"/>
+      <x:c r="F50" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="26" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C51" s="27" t="s"/>
+      <x:c r="D51" s="27" t="s"/>
+      <x:c r="E51" s="27" t="s"/>
+      <x:c r="F51" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="26" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C52" s="27" t="s"/>
+      <x:c r="D52" s="27" t="s"/>
+      <x:c r="E52" s="27" t="s"/>
+      <x:c r="F52" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="26" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C53" s="27" t="s"/>
+      <x:c r="D53" s="27" t="s"/>
+      <x:c r="E53" s="27" t="s"/>
+      <x:c r="F53" s="28" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="26" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C54" s="27" t="s"/>
+      <x:c r="D54" s="27" t="s"/>
+      <x:c r="E54" s="27" t="s"/>
+      <x:c r="F54" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="26" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C55" s="27" t="s"/>
+      <x:c r="D55" s="27" t="s"/>
+      <x:c r="E55" s="27" t="s"/>
+      <x:c r="F55" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="26" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C56" s="27" t="s"/>
+      <x:c r="D56" s="27" t="s"/>
+      <x:c r="E56" s="27" t="s"/>
+      <x:c r="F56" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B57" s="29" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C57" s="30" t="s"/>
+      <x:c r="D57" s="30" t="s"/>
+      <x:c r="E57" s="30" t="s"/>
+      <x:c r="F57" s="31" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I16" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I17" s="22">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I18" s="22">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I19" s="22">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I20" s="22">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I24" s="22">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F25" s="17" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H25" s="19">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I25" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K25" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="21">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M25" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D26" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E26" s="17" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F26" s="17" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G26" s="17" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H26" s="19">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I26" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="18" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K26" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="21">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M26" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C27" s="17" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D27" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E27" s="17" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F27" s="17" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H27" s="19">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I27" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K27" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="21">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M27" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C28" s="17" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D28" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E28" s="17" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F28" s="17" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G28" s="17" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H28" s="19">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I28" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="18" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K28" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="21">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M28" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C29" s="17" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D29" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E29" s="17" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F29" s="17" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G29" s="17" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H29" s="19">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I29" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="18" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K29" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="21">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M29" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C30" s="17" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D30" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E30" s="17" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F30" s="17" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="G30" s="17" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H30" s="19">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I30" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K30" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="21">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M30" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C31" s="17" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D31" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E31" s="17" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F31" s="17" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G31" s="17" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H31" s="19">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I31" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K31" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="21">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M31" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C32" s="17" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D32" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E32" s="17" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F32" s="17" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="G32" s="17" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H32" s="19">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I32" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K32" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="21">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M32" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C33" s="17" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D33" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E33" s="17" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="F33" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G33" s="17" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H33" s="19">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I33" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="18" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K33" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="21">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M33" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C34" s="17" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D34" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E34" s="17" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="F34" s="17" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G34" s="17" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H34" s="19">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I34" s="22">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J34" s="18" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K34" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="21">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M34" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C35" s="17" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D35" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E35" s="17" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F35" s="17" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G35" s="17" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H35" s="19">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I35" s="22">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J35" s="18" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K35" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="21">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M35" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="17" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C36" s="17" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D36" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E36" s="17" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F36" s="17" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G36" s="17" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H36" s="19">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I36" s="19">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J36" s="18" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K36" s="20" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L36" s="21">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M36" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C37" s="17" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D37" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E37" s="17" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F37" s="17" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G37" s="17" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H37" s="19">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I37" s="22">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J37" s="18" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K37" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L37" s="21">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M37" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C38" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D38" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E38" s="17" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F38" s="17" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G38" s="17" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H38" s="19">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I38" s="22">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J38" s="18" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K38" s="20" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L38" s="21">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M38" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C39" s="17" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D39" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E39" s="17" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F39" s="17" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G39" s="17" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H39" s="19">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I39" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J39" s="18" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K39" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L39" s="21">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M39" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C40" s="17" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D40" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E40" s="17" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F40" s="17" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G40" s="17" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H40" s="19">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I40" s="22">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J40" s="18" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K40" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L40" s="21">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M40" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="17" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C41" s="17" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D41" s="18" t="s"/>
-      <x:c r="E41" s="17" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F41" s="17" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G41" s="17" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="H41" s="19">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I41" s="19">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J41" s="18" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K41" s="20" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L41" s="21">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M41" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="17" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C42" s="17" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D42" s="18" t="s"/>
-      <x:c r="E42" s="17" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F42" s="17" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G42" s="17" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H42" s="19">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I42" s="19">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J42" s="18" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K42" s="20" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L42" s="21">
-        <x:v>46080.3345717593</x:v>
-      </x:c>
-      <x:c r="M42" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="23" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="C45" s="24" t="s"/>
-      <x:c r="D45" s="24" t="s"/>
-      <x:c r="E45" s="25" t="s"/>
-      <x:c r="F45" s="25" t="s"/>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="26" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C46" s="27" t="s"/>
-      <x:c r="D46" s="27" t="s"/>
-      <x:c r="E46" s="27" t="s"/>
-      <x:c r="F46" s="28" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C47" s="30" t="s"/>
-      <x:c r="D47" s="30" t="s"/>
-      <x:c r="E47" s="30" t="s"/>
-      <x:c r="F47" s="31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C48" s="30" t="s"/>
-      <x:c r="D48" s="30" t="s"/>
-      <x:c r="E48" s="30" t="s"/>
-      <x:c r="F48" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="29" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C49" s="30" t="s"/>
-      <x:c r="D49" s="30" t="s"/>
-      <x:c r="E49" s="30" t="s"/>
-      <x:c r="F49" s="31" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="29" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C50" s="30" t="s"/>
-      <x:c r="D50" s="30" t="s"/>
-      <x:c r="E50" s="30" t="s"/>
-      <x:c r="F50" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="29" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C51" s="30" t="s"/>
-      <x:c r="D51" s="30" t="s"/>
-      <x:c r="E51" s="30" t="s"/>
-      <x:c r="F51" s="31" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="29" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C52" s="30" t="s"/>
-      <x:c r="D52" s="30" t="s"/>
-      <x:c r="E52" s="30" t="s"/>
-      <x:c r="F52" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="29" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C53" s="30" t="s"/>
-      <x:c r="D53" s="30" t="s"/>
-      <x:c r="E53" s="30" t="s"/>
-      <x:c r="F53" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="29" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C54" s="30" t="s"/>
-      <x:c r="D54" s="30" t="s"/>
-      <x:c r="E54" s="30" t="s"/>
-      <x:c r="F54" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="32" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C55" s="33" t="s"/>
-      <x:c r="D55" s="33" t="s"/>
-      <x:c r="E55" s="33" t="s"/>
-      <x:c r="F55" s="34" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    </x:row>
     <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4262,13 +4335,12 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="14">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="15">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B45:F45"/>
-    <x:mergeCell ref="B46:E46"/>
-    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B47:F47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
@@ -4277,6 +4349,8 @@
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B57:E57"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -4317,78 +4391,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4409,7 +4495,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -4449,1660 +4535,1710 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="C8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46091.306099537</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46091.3107986111</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1511778</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46091.3131828704</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46098.0792592593</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46098.0878935185</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1529776</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46098.0997569444</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46097.2890740741</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I25" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="19">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H26" s="17">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I26" s="17">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D27" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H27" s="17">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I27" s="17">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L27" s="19">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M27" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H28" s="17">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I28" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J28" s="16" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K28" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="19">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M28" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H29" s="17">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I29" s="17">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="19">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M29" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H30" s="17">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I30" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J30" s="16" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K30" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="19">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M30" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="D31" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G31" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H31" s="17">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I31" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J31" s="16" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K31" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="19">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M31" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D32" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="H32" s="17">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I32" s="17">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J32" s="16" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K32" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="19">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M32" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D33" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H33" s="17">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I33" s="17">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J33" s="16" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K33" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="19">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M33" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G34" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H34" s="17">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I34" s="17">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J34" s="16" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K34" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L34" s="19">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M34" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G35" s="15" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H35" s="17">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I35" s="17">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K35" s="18" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L35" s="19">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M35" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F36" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G36" s="15" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H36" s="17">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I36" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J36" s="16" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K36" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="19">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M36" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H37" s="17">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I37" s="17">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K37" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L37" s="19">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M37" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F38" s="15" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="G38" s="15" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="H38" s="17">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I38" s="17">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J38" s="16" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K38" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L38" s="19">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M38" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="F39" s="15" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="G39" s="15" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="H39" s="17">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I39" s="17">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J39" s="16" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K39" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="19">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M39" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="F40" s="15" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G40" s="15" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H40" s="17">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I40" s="17">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J40" s="16" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K40" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="19">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M40" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D41" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F41" s="15" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="G41" s="15" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H41" s="17">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I41" s="17">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J41" s="16" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K41" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L41" s="19">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M41" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C42" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E42" s="15" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="F42" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G42" s="15" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H42" s="17">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I42" s="17">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J42" s="16" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K42" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L42" s="19">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M42" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C43" s="15" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="D43" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E43" s="15" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F43" s="15" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="G43" s="15" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="H43" s="17">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I43" s="17">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J43" s="16" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K43" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="19">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M43" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C44" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E44" s="15" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="F44" s="15" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="G44" s="15" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="H44" s="17">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I44" s="17">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J44" s="16" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K44" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L44" s="19">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M44" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C45" s="15" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E45" s="15" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F45" s="15" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="G45" s="15" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="H45" s="17">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I45" s="17">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J45" s="16" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K45" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="19">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M45" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C46" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D46" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E46" s="15" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="F46" s="15" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="G46" s="15" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="H46" s="17">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I46" s="17">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J46" s="16" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K46" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L46" s="19">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M46" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C47" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E47" s="15" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="F47" s="15" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="G47" s="15" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="H47" s="17">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I47" s="17">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J47" s="16" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K47" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L47" s="19">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M47" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C48" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E48" s="15" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="F48" s="15" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="G48" s="15" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H48" s="17">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I48" s="17">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J48" s="16" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K48" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L48" s="19">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M48" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B49" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C49" s="15" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="D49" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E49" s="15" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="F49" s="15" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="G49" s="15" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="H49" s="17">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I49" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J49" s="16" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K49" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L49" s="19">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M49" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B50" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C50" s="15" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="D50" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E50" s="15" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="F50" s="15" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="G50" s="15" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="H50" s="17">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I50" s="17">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J50" s="16" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K50" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L50" s="19">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M50" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B53" s="20" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
+      <x:c r="C53" s="21" t="s"/>
+      <x:c r="D53" s="21" t="s"/>
+      <x:c r="E53" s="22" t="s"/>
+      <x:c r="F53" s="22" t="s"/>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B54" s="23" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
+      <x:c r="C54" s="24" t="s"/>
+      <x:c r="D54" s="24" t="s"/>
+      <x:c r="E54" s="24" t="s"/>
+      <x:c r="F54" s="25" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C55" s="27" t="s"/>
+      <x:c r="D55" s="27" t="s"/>
+      <x:c r="E55" s="27" t="s"/>
+      <x:c r="F55" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="26" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C56" s="27" t="s"/>
+      <x:c r="D56" s="27" t="s"/>
+      <x:c r="E56" s="27" t="s"/>
+      <x:c r="F56" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="26" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C57" s="27" t="s"/>
+      <x:c r="D57" s="27" t="s"/>
+      <x:c r="E57" s="27" t="s"/>
+      <x:c r="F57" s="28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B58" s="26" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C58" s="27" t="s"/>
+      <x:c r="D58" s="27" t="s"/>
+      <x:c r="E58" s="27" t="s"/>
+      <x:c r="F58" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B59" s="26" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C59" s="27" t="s"/>
+      <x:c r="D59" s="27" t="s"/>
+      <x:c r="E59" s="27" t="s"/>
+      <x:c r="F59" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B60" s="26" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C60" s="27" t="s"/>
+      <x:c r="D60" s="27" t="s"/>
+      <x:c r="E60" s="27" t="s"/>
+      <x:c r="F60" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B61" s="29" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46098.0792592593</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46098.0878935185</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1529776</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46098.0997569444</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46097.2890740741</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I14" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I15" s="22">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I16" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I17" s="22">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I18" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I19" s="22">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I20" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I21" s="22">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I22" s="22">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I23" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I24" s="22">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="F25" s="17" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H25" s="19">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I25" s="22">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K25" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L25" s="21">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M25" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D26" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E26" s="17" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="F26" s="17" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="G26" s="17" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="H26" s="19">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I26" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J26" s="18" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K26" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="21">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M26" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C27" s="17" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="D27" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E27" s="17" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="F27" s="17" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="H27" s="19">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I27" s="22">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J27" s="18" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K27" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="21">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M27" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C28" s="17" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="D28" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E28" s="17" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F28" s="17" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G28" s="17" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H28" s="19">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I28" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J28" s="18" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K28" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="21">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M28" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C29" s="17" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D29" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E29" s="17" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="F29" s="17" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G29" s="17" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="H29" s="19">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I29" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J29" s="18" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K29" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="21">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M29" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C30" s="17" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D30" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E30" s="17" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="F30" s="17" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="G30" s="17" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="H30" s="19">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I30" s="22">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J30" s="18" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K30" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="21">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M30" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C31" s="17" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="D31" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E31" s="17" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="F31" s="17" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="G31" s="17" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="H31" s="19">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I31" s="22">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J31" s="18" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K31" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="21">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M31" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C32" s="17" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="D32" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E32" s="17" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F32" s="17" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G32" s="17" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H32" s="19">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I32" s="22">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J32" s="18" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K32" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L32" s="21">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M32" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C33" s="17" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="D33" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E33" s="17" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F33" s="17" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G33" s="17" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H33" s="19">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I33" s="22">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J33" s="18" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K33" s="20" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L33" s="21">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M33" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C34" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D34" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E34" s="17" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="F34" s="17" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="G34" s="17" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="H34" s="19">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I34" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J34" s="18" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K34" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="21">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M34" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C35" s="17" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D35" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E35" s="17" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="F35" s="17" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="G35" s="17" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H35" s="19">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I35" s="22">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J35" s="18" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K35" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="21">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M35" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C36" s="17" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="D36" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E36" s="17" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="F36" s="17" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="G36" s="17" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="H36" s="19">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I36" s="22">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J36" s="18" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K36" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="21">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M36" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C37" s="17" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D37" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E37" s="17" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F37" s="17" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G37" s="17" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H37" s="19">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I37" s="19">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J37" s="18" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K37" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L37" s="21">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M37" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C38" s="17" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D38" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E38" s="17" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="F38" s="17" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="G38" s="17" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="H38" s="19">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I38" s="19">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J38" s="18" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K38" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L38" s="21">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M38" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C39" s="17" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D39" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E39" s="17" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="F39" s="17" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="G39" s="17" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="H39" s="19">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I39" s="19">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J39" s="18" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K39" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L39" s="21">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M39" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C40" s="17" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D40" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E40" s="17" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F40" s="17" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="G40" s="17" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H40" s="19">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I40" s="19">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J40" s="18" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K40" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L40" s="21">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M40" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C41" s="17" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="D41" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E41" s="17" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="F41" s="17" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="G41" s="17" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="H41" s="19">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I41" s="22">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J41" s="18" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K41" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="21">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M41" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C42" s="17" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D42" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E42" s="17" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="F42" s="17" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="G42" s="17" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H42" s="19">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I42" s="22">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J42" s="18" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K42" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L42" s="21">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M42" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C43" s="17" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="D43" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E43" s="17" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="F43" s="17" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="G43" s="17" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="H43" s="19">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I43" s="22">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J43" s="18" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K43" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="21">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M43" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C44" s="17" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="D44" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E44" s="17" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="F44" s="17" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="G44" s="17" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="H44" s="19">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I44" s="22">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J44" s="18" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K44" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="21">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M44" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C45" s="17" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="D45" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E45" s="17" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="F45" s="17" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="G45" s="17" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="H45" s="19">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I45" s="22">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J45" s="18" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K45" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="21">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M45" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C46" s="17" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="D46" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E46" s="17" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="F46" s="17" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="G46" s="17" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="H46" s="19">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I46" s="22">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J46" s="18" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K46" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L46" s="21">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M46" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C47" s="17" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="D47" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E47" s="17" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="F47" s="17" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="G47" s="17" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="H47" s="19">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I47" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J47" s="18" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K47" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L47" s="21">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M47" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B48" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C48" s="17" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="D48" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E48" s="17" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="F48" s="17" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="G48" s="17" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="H48" s="19">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I48" s="22">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J48" s="18" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K48" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L48" s="21">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M48" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="23" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="C51" s="24" t="s"/>
-      <x:c r="D51" s="24" t="s"/>
-      <x:c r="E51" s="25" t="s"/>
-      <x:c r="F51" s="25" t="s"/>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B52" s="26" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C52" s="27" t="s"/>
-      <x:c r="D52" s="27" t="s"/>
-      <x:c r="E52" s="27" t="s"/>
-      <x:c r="F52" s="28" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C53" s="30" t="s"/>
-      <x:c r="D53" s="30" t="s"/>
-      <x:c r="E53" s="30" t="s"/>
-      <x:c r="F53" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C54" s="30" t="s"/>
-      <x:c r="D54" s="30" t="s"/>
-      <x:c r="E54" s="30" t="s"/>
-      <x:c r="F54" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="29" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C55" s="30" t="s"/>
-      <x:c r="D55" s="30" t="s"/>
-      <x:c r="E55" s="30" t="s"/>
-      <x:c r="F55" s="31" t="n">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="29" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C56" s="30" t="s"/>
-      <x:c r="D56" s="30" t="s"/>
-      <x:c r="E56" s="30" t="s"/>
-      <x:c r="F56" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="29" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C57" s="30" t="s"/>
-      <x:c r="D57" s="30" t="s"/>
-      <x:c r="E57" s="30" t="s"/>
-      <x:c r="F57" s="31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="29" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C58" s="30" t="s"/>
-      <x:c r="D58" s="30" t="s"/>
-      <x:c r="E58" s="30" t="s"/>
-      <x:c r="F58" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B59" s="32" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C59" s="33" t="s"/>
-      <x:c r="D59" s="33" t="s"/>
-      <x:c r="E59" s="33" t="s"/>
-      <x:c r="F59" s="34" t="n">
+      <x:c r="C61" s="30" t="s"/>
+      <x:c r="D61" s="30" t="s"/>
+      <x:c r="E61" s="30" t="s"/>
+      <x:c r="F61" s="31" t="n">
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7036,19 +7172,20 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="12">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="13">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B51:F51"/>
-    <x:mergeCell ref="B52:E52"/>
-    <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B53:F53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
+    <x:mergeCell ref="B60:E60"/>
+    <x:mergeCell ref="B61:E61"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -68,42 +68,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
@@ -1021,7 +985,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1065,14 +1029,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -1084,6 +1040,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -1341,7 +1312,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1349,16 +1320,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1370,13 +1341,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1388,41 +1353,50 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1453,28 +1427,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1489,55 +1455,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1870,7 +1852,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1910,1494 +1892,1444 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>46069.0835185185</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46069.1006712963</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1506161</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46069.1133333333</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="H9" s="15">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46066.3145023148</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1507747</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46066.3194212963</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="F10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="H10" s="19">
+        <x:v>46069.0835648148</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46069.1000231481</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1506159</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>46069.1128587963</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="F11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46072.1720833333</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46072.235162037</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1507783</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46069.1133333333</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="L11" s="21">
+        <x:v>46073.1890277778</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="17" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="F12" s="17" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="G12" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46063.2819560185</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46063.2922685185</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1507682</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="L12" s="21">
+        <x:v>46063.2957638889</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="17" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F13" s="17" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G13" s="17" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="H13" s="19">
+        <x:v>46058.4859837963</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46062.157025463</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1507672</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="L13" s="21">
+        <x:v>46062.1881944444</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="C14" s="17" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="D14" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="E14" s="17" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="F14" s="17" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46067.3600231481</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46067.3600462963</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46079.2730092593</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46072.3184259259</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46072.3184375</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1505803</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46079.2696990741</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46067.1596643518</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1505804</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="21">
+        <x:v>46079.2772569444</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46067.2222106481</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1505805</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="21">
+        <x:v>46079.2763078704</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46072.3605555556</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1507784</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="21">
+        <x:v>46073.2284953704</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46072.3529513889</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1507785</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46073.2314351852</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46063.1352777778</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511010</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46063.2367708333</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46079.3584722222</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46079.3584953704</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511622</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46080.2311226852</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46079.3539699074</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46079.3539814815</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1511627</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="21">
+        <x:v>46080.2440856481</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46058.1529282407</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46058.1529398148</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1507657</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="21">
+        <x:v>46058.2410648148</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46072.2635300926</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1507790</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="21">
+        <x:v>46073.3091087963</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46079.3873148148</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1511623</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="21">
+        <x:v>46080.2360763889</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
+        <x:v>46079.2523032407</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="n">
+        <x:v>1511631</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="21">
+        <x:v>46080.2925810185</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
+        <x:v>46079.2430555556</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="21">
+        <x:v>46080.2801273148</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H28" s="19">
+        <x:v>46079.3651967593</x:v>
+      </x:c>
+      <x:c r="I28" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="18" t="n">
+        <x:v>1511626</x:v>
+      </x:c>
+      <x:c r="K28" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="21">
+        <x:v>46080.2425462963</x:v>
+      </x:c>
+      <x:c r="M28" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C29" s="17" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H29" s="19">
+        <x:v>46080.2923611111</x:v>
+      </x:c>
+      <x:c r="I29" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="18" t="n">
+        <x:v>1511635</x:v>
+      </x:c>
+      <x:c r="K29" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="21">
+        <x:v>46080.3208564815</x:v>
+      </x:c>
+      <x:c r="M29" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C30" s="17" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G30" s="17" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H30" s="19">
+        <x:v>46079.31625</x:v>
+      </x:c>
+      <x:c r="I30" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K30" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="21">
+        <x:v>46080.2883680556</x:v>
+      </x:c>
+      <x:c r="M30" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C31" s="17" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E31" s="17" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H31" s="19">
+        <x:v>46079.3059375</x:v>
+      </x:c>
+      <x:c r="I31" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K31" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="21">
+        <x:v>46080.2896875</x:v>
+      </x:c>
+      <x:c r="M31" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C32" s="17" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D32" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H32" s="19">
+        <x:v>46079.2943981482</x:v>
+      </x:c>
+      <x:c r="I32" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="18" t="n">
+        <x:v>1511630</x:v>
+      </x:c>
+      <x:c r="K32" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="21">
+        <x:v>46080.2916782407</x:v>
+      </x:c>
+      <x:c r="M32" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C33" s="17" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E33" s="17" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F33" s="17" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G33" s="17" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H33" s="19">
+        <x:v>46079.378900463</x:v>
+      </x:c>
+      <x:c r="I33" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="18" t="n">
+        <x:v>1511624</x:v>
+      </x:c>
+      <x:c r="K33" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="21">
+        <x:v>46080.2376041667</x:v>
+      </x:c>
+      <x:c r="M33" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C34" s="17" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D34" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E34" s="17" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F34" s="17" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G34" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H34" s="19">
+        <x:v>46079.3728240741</x:v>
+      </x:c>
+      <x:c r="I34" s="19">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J34" s="18" t="n">
+        <x:v>1511625</x:v>
+      </x:c>
+      <x:c r="K34" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="21">
+        <x:v>46080.2394328704</x:v>
+      </x:c>
+      <x:c r="M34" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C35" s="17" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="D35" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E35" s="17" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F35" s="17" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G35" s="17" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H35" s="19">
+        <x:v>46077.0697337963</x:v>
+      </x:c>
+      <x:c r="I35" s="19">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J35" s="18" t="n">
+        <x:v>1511576</x:v>
+      </x:c>
+      <x:c r="K35" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="21">
+        <x:v>46077.1078819444</x:v>
+      </x:c>
+      <x:c r="M35" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="17" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C36" s="17" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D36" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E36" s="17" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F36" s="17" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G36" s="17" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H36" s="19">
+        <x:v>46062.1590162037</x:v>
+      </x:c>
+      <x:c r="I36" s="19">
+        <x:v>46062.1590277778</x:v>
+      </x:c>
+      <x:c r="J36" s="18" t="n">
+        <x:v>1510925</x:v>
+      </x:c>
+      <x:c r="K36" s="20" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L36" s="21">
+        <x:v>46062.1863194444</x:v>
+      </x:c>
+      <x:c r="M36" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C37" s="17" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D37" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E37" s="17" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F37" s="17" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G37" s="17" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H37" s="19">
+        <x:v>46066.2180208333</x:v>
+      </x:c>
+      <x:c r="I37" s="19">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J37" s="18" t="n">
+        <x:v>1507743</x:v>
+      </x:c>
+      <x:c r="K37" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L37" s="21">
+        <x:v>46066.2724421296</x:v>
+      </x:c>
+      <x:c r="M37" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C38" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D38" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E38" s="17" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F38" s="17" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G38" s="17" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H38" s="19">
+        <x:v>46071.0492476852</x:v>
+      </x:c>
+      <x:c r="I38" s="19">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J38" s="18" t="n">
+        <x:v>1511502</x:v>
+      </x:c>
+      <x:c r="K38" s="20" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L38" s="21">
+        <x:v>46071.0606134259</x:v>
+      </x:c>
+      <x:c r="M38" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C39" s="17" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D39" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E39" s="17" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G39" s="17" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H39" s="19">
+        <x:v>46066.2275347222</x:v>
+      </x:c>
+      <x:c r="I39" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J39" s="18" t="n">
+        <x:v>1507742</x:v>
+      </x:c>
+      <x:c r="K39" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L39" s="21">
+        <x:v>46066.2701736111</x:v>
+      </x:c>
+      <x:c r="M39" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C40" s="17" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D40" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E40" s="17" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G40" s="17" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H40" s="19">
+        <x:v>46078.2436226852</x:v>
+      </x:c>
+      <x:c r="I40" s="19">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J40" s="18" t="n">
+        <x:v>1507839</x:v>
+      </x:c>
+      <x:c r="K40" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L40" s="21">
+        <x:v>46078.3266203704</x:v>
+      </x:c>
+      <x:c r="M40" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="17" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C41" s="17" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D41" s="18" t="s"/>
+      <x:c r="E41" s="17" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F41" s="17" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G41" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H41" s="19">
+        <x:v>46080.2342361111</x:v>
+      </x:c>
+      <x:c r="I41" s="19">
+        <x:v>46080.2342592593</x:v>
+      </x:c>
+      <x:c r="J41" s="18" t="n">
+        <x:v>1507884</x:v>
+      </x:c>
+      <x:c r="K41" s="20" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L41" s="21">
+        <x:v>46080.3353356481</x:v>
+      </x:c>
+      <x:c r="M41" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="17" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C42" s="17" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D42" s="18" t="s"/>
+      <x:c r="E42" s="17" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F42" s="17" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G42" s="17" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H42" s="19">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I42" s="19">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J42" s="18" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K42" s="20" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L42" s="21">
+        <x:v>46080.3345717593</x:v>
+      </x:c>
+      <x:c r="M42" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="22" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C45" s="23" t="s"/>
+      <x:c r="D45" s="23" t="s"/>
+      <x:c r="E45" s="24" t="s"/>
+      <x:c r="F45" s="24" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B46" s="25" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C46" s="26" t="s"/>
+      <x:c r="D46" s="26" t="s"/>
+      <x:c r="E46" s="26" t="s"/>
+      <x:c r="F46" s="27" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C47" s="29" t="s"/>
+      <x:c r="D47" s="29" t="s"/>
+      <x:c r="E47" s="29" t="s"/>
+      <x:c r="F47" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="28" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C48" s="29" t="s"/>
+      <x:c r="D48" s="29" t="s"/>
+      <x:c r="E48" s="29" t="s"/>
+      <x:c r="F48" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="28" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I18" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I19" s="17">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="C49" s="29" t="s"/>
+      <x:c r="D49" s="29" t="s"/>
+      <x:c r="E49" s="29" t="s"/>
+      <x:c r="F49" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="28" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I20" s="17">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="C50" s="29" t="s"/>
+      <x:c r="D50" s="29" t="s"/>
+      <x:c r="E50" s="29" t="s"/>
+      <x:c r="F50" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="28" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I24" s="17">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I25" s="17">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C26" s="15" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D26" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G26" s="15" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H26" s="17">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I26" s="17">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J26" s="16" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L26" s="19">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M26" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C27" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D27" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F27" s="15" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G27" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H27" s="17">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I27" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="16" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K27" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="19">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M27" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C28" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D28" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E28" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F28" s="15" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G28" s="15" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H28" s="17">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I28" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="16" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K28" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="19">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M28" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C29" s="15" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D29" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E29" s="15" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G29" s="15" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H29" s="17">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I29" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="19">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M29" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C30" s="15" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D30" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E30" s="15" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F30" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G30" s="15" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H30" s="17">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I30" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="16" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K30" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="19">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M30" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C31" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D31" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E31" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F31" s="15" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G31" s="15" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H31" s="17">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I31" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="16" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K31" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="19">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M31" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C32" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D32" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E32" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F32" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="G32" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="H32" s="17">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I32" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K32" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="19">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M32" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C33" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D33" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E33" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F33" s="15" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G33" s="15" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H33" s="17">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I33" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K33" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="19">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M33" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C34" s="15" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D34" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E34" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F34" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G34" s="15" t="s">
+      <x:c r="C51" s="29" t="s"/>
+      <x:c r="D51" s="29" t="s"/>
+      <x:c r="E51" s="29" t="s"/>
+      <x:c r="F51" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="28" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="H34" s="17">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I34" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J34" s="16" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K34" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="19">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M34" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C35" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D35" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E35" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F35" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G35" s="15" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H35" s="17">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I35" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J35" s="16" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K35" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="19">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M35" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C36" s="15" t="s">
+      <x:c r="C52" s="29" t="s"/>
+      <x:c r="D52" s="29" t="s"/>
+      <x:c r="E52" s="29" t="s"/>
+      <x:c r="F52" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="28" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D36" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E36" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F36" s="15" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G36" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H36" s="17">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I36" s="17">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J36" s="16" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K36" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="19">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M36" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C37" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D37" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E37" s="15" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F37" s="15" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G37" s="15" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H37" s="17">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I37" s="17">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J37" s="16" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K37" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L37" s="19">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M37" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="15" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="C38" s="15" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D38" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E38" s="15" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F38" s="15" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G38" s="15" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H38" s="17">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I38" s="17">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J38" s="16" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K38" s="18" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L38" s="19">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M38" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C39" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D39" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E39" s="15" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F39" s="15" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G39" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H39" s="17">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I39" s="17">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J39" s="16" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K39" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L39" s="19">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M39" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C40" s="15" t="s">
+      <x:c r="C53" s="29" t="s"/>
+      <x:c r="D53" s="29" t="s"/>
+      <x:c r="E53" s="29" t="s"/>
+      <x:c r="F53" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="28" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="D40" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E40" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F40" s="15" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="G40" s="15" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="H40" s="17">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I40" s="17">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J40" s="16" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K40" s="18" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L40" s="19">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M40" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C41" s="15" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D41" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E41" s="15" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F41" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="G41" s="15" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H41" s="17">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I41" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J41" s="16" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K41" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L41" s="19">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M41" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C42" s="15" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D42" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E42" s="15" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F42" s="15" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G42" s="15" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H42" s="17">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I42" s="17">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J42" s="16" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K42" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L42" s="19">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M42" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="15" t="s">
+      <x:c r="C54" s="29" t="s"/>
+      <x:c r="D54" s="29" t="s"/>
+      <x:c r="E54" s="29" t="s"/>
+      <x:c r="F54" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B55" s="31" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C43" s="15" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D43" s="16" t="s"/>
-      <x:c r="E43" s="15" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F43" s="15" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G43" s="15" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H43" s="17">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I43" s="17">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J43" s="16" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K43" s="18" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L43" s="19">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M43" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="15" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C44" s="15" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D44" s="16" t="s"/>
-      <x:c r="E44" s="15" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="F44" s="15" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="G44" s="15" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H44" s="17">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I44" s="17">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J44" s="16" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K44" s="18" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L44" s="19">
-        <x:v>46080.3345717593</x:v>
-      </x:c>
-      <x:c r="M44" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B47" s="20" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="C47" s="21" t="s"/>
-      <x:c r="D47" s="21" t="s"/>
-      <x:c r="E47" s="22" t="s"/>
-      <x:c r="F47" s="22" t="s"/>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B48" s="23" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="C48" s="24" t="s"/>
-      <x:c r="D48" s="24" t="s"/>
-      <x:c r="E48" s="24" t="s"/>
-      <x:c r="F48" s="25" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C49" s="27" t="s"/>
-      <x:c r="D49" s="27" t="s"/>
-      <x:c r="E49" s="27" t="s"/>
-      <x:c r="F49" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C50" s="27" t="s"/>
-      <x:c r="D50" s="27" t="s"/>
-      <x:c r="E50" s="27" t="s"/>
-      <x:c r="F50" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="26" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C51" s="27" t="s"/>
-      <x:c r="D51" s="27" t="s"/>
-      <x:c r="E51" s="27" t="s"/>
-      <x:c r="F51" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="26" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C52" s="27" t="s"/>
-      <x:c r="D52" s="27" t="s"/>
-      <x:c r="E52" s="27" t="s"/>
-      <x:c r="F52" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C53" s="27" t="s"/>
-      <x:c r="D53" s="27" t="s"/>
-      <x:c r="E53" s="27" t="s"/>
-      <x:c r="F53" s="28" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="26" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="C54" s="27" t="s"/>
-      <x:c r="D54" s="27" t="s"/>
-      <x:c r="E54" s="27" t="s"/>
-      <x:c r="F54" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="26" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C55" s="27" t="s"/>
-      <x:c r="D55" s="27" t="s"/>
-      <x:c r="E55" s="27" t="s"/>
-      <x:c r="F55" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="26" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C56" s="27" t="s"/>
-      <x:c r="D56" s="27" t="s"/>
-      <x:c r="E56" s="27" t="s"/>
-      <x:c r="F56" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B57" s="29" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="C57" s="30" t="s"/>
-      <x:c r="D57" s="30" t="s"/>
-      <x:c r="E57" s="30" t="s"/>
-      <x:c r="F57" s="31" t="n">
+      <x:c r="C55" s="32" t="s"/>
+      <x:c r="D55" s="32" t="s"/>
+      <x:c r="E55" s="32" t="s"/>
+      <x:c r="F55" s="33" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4340,7 +4272,9 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B47:F47"/>
+    <x:mergeCell ref="B45:F45"/>
+    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B47:E47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
@@ -4349,8 +4283,6 @@
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
-    <x:mergeCell ref="B56:E56"/>
-    <x:mergeCell ref="B57:E57"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -4462,7 +4394,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>181</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -4495,7 +4427,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -4535,1710 +4467,1660 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46091.306099537</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46091.3107986111</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1511778</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46091.3131828704</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46093.1459375</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46093.1585185185</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1511815</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46093.159537037</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
+        <x:v>46098.0792592593</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46098.0878935185</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1529776</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>46098.0997569444</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46097.2890740741</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46080.4532523148</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1511232</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46097.1461689815</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46083.2380439815</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1511234</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="21">
+        <x:v>46097.1564351852</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46083.2599189815</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1511237</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="21">
+        <x:v>46097.1652314815</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="21">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46084.0854513889</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1511225</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46093.3956365741</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46084.0996759259</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511192</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46097.2414583333</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="21">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="21">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46069.1542013889</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1511206</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="21">
+        <x:v>46097.2466550926</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46069.2178703704</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1511196</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="21">
+        <x:v>46097.2456365741</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
+        <x:v>46083.2443865741</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="n">
+        <x:v>1511235</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="21">
+        <x:v>46097.1600115741</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
+        <x:v>46084.1225115741</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1511242</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="21">
+        <x:v>46097.3505092593</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H28" s="19">
+        <x:v>46083.2521064815</x:v>
+      </x:c>
+      <x:c r="I28" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J28" s="18" t="n">
+        <x:v>1511236</x:v>
+      </x:c>
+      <x:c r="K28" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="21">
+        <x:v>46097.1628935185</x:v>
+      </x:c>
+      <x:c r="M28" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C29" s="17" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="H29" s="19">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I29" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J29" s="18" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K29" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="21">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M29" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C30" s="17" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G30" s="17" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="H30" s="19">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I30" s="19">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J30" s="18" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K30" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="21">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M30" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C31" s="17" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E31" s="17" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H31" s="19">
+        <x:v>46069.115150463</x:v>
+      </x:c>
+      <x:c r="I31" s="19">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J31" s="18" t="n">
+        <x:v>1511241</x:v>
+      </x:c>
+      <x:c r="K31" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="21">
+        <x:v>46097.3433796296</x:v>
+      </x:c>
+      <x:c r="M31" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C32" s="17" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D32" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H32" s="19">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I32" s="19">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J32" s="18" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K32" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L32" s="21">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M32" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C33" s="17" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E33" s="17" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F33" s="17" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G33" s="17" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H33" s="19">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I33" s="19">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J33" s="18" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K33" s="20" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L33" s="21">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M33" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C34" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D34" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E34" s="17" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F34" s="17" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G34" s="17" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H34" s="19">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I34" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J34" s="18" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K34" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="21">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M34" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C35" s="17" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D35" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E35" s="17" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F35" s="17" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G35" s="17" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H35" s="19">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I35" s="19">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J35" s="18" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K35" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="21">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M35" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C36" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D36" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E36" s="17" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F36" s="17" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G36" s="17" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H36" s="19">
+        <x:v>46086.1064814815</x:v>
+      </x:c>
+      <x:c r="I36" s="19">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J36" s="18" t="n">
+        <x:v>1511761</x:v>
+      </x:c>
+      <x:c r="K36" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="21">
+        <x:v>46090.2765740741</x:v>
+      </x:c>
+      <x:c r="M36" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C37" s="17" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D37" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E37" s="17" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F37" s="17" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G37" s="17" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H37" s="19">
+        <x:v>46085.16625</x:v>
+      </x:c>
+      <x:c r="I37" s="19">
+        <x:v>46085.1662615741</x:v>
+      </x:c>
+      <x:c r="J37" s="18" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K37" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L37" s="21">
+        <x:v>46090.3437268519</x:v>
+      </x:c>
+      <x:c r="M37" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C38" s="17" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D38" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E38" s="17" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="F38" s="17" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G38" s="17" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="H38" s="19">
+        <x:v>46085.1709143519</x:v>
+      </x:c>
+      <x:c r="I38" s="19">
+        <x:v>46085.1709375</x:v>
+      </x:c>
+      <x:c r="J38" s="18" t="n">
+        <x:v>1507965</x:v>
+      </x:c>
+      <x:c r="K38" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="21">
+        <x:v>46090.3336921296</x:v>
+      </x:c>
+      <x:c r="M38" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C39" s="17" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D39" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E39" s="17" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G39" s="17" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H39" s="19">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I39" s="19">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J39" s="18" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K39" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="21">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M39" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C40" s="17" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D40" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E40" s="17" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G40" s="17" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H40" s="19">
+        <x:v>46085.1627430556</x:v>
+      </x:c>
+      <x:c r="I40" s="19">
+        <x:v>46085.1627546296</x:v>
+      </x:c>
+      <x:c r="J40" s="18" t="n">
+        <x:v>1507966</x:v>
+      </x:c>
+      <x:c r="K40" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="21">
+        <x:v>46090.3453472222</x:v>
+      </x:c>
+      <x:c r="M40" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C41" s="17" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="D41" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E41" s="17" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F41" s="17" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G41" s="17" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H41" s="19">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I41" s="19">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J41" s="18" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K41" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L41" s="21">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M41" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C42" s="17" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D42" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E42" s="17" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F42" s="17" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G42" s="17" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H42" s="19">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I42" s="19">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J42" s="18" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K42" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L42" s="21">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M42" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C43" s="17" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="D43" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E43" s="17" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="F43" s="17" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="G43" s="17" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H43" s="19">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I43" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J43" s="18" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K43" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="21">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M43" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C44" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D44" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E44" s="17" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F44" s="17" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="G44" s="17" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="H44" s="19">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I44" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J44" s="18" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K44" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L44" s="21">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M44" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C45" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D45" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E45" s="17" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F45" s="17" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="G45" s="17" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="H45" s="19">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I45" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J45" s="18" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K45" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="21">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M45" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C46" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D46" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E46" s="17" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="F46" s="17" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="G46" s="17" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="H46" s="19">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I46" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J46" s="18" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K46" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L46" s="21">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M46" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C47" s="17" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="D47" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E47" s="17" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="F47" s="17" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="G47" s="17" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="H47" s="19">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I47" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J47" s="18" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K47" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L47" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M47" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C48" s="17" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D48" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E48" s="17" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F48" s="17" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="G48" s="17" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="H48" s="19">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I48" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J48" s="18" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K48" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L48" s="21">
+        <x:v>46083.1543634259</x:v>
+      </x:c>
+      <x:c r="M48" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B51" s="22" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C51" s="23" t="s"/>
+      <x:c r="D51" s="23" t="s"/>
+      <x:c r="E51" s="24" t="s"/>
+      <x:c r="F51" s="24" t="s"/>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B52" s="25" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C52" s="26" t="s"/>
+      <x:c r="D52" s="26" t="s"/>
+      <x:c r="E52" s="26" t="s"/>
+      <x:c r="F52" s="27" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C53" s="29" t="s"/>
+      <x:c r="D53" s="29" t="s"/>
+      <x:c r="E53" s="29" t="s"/>
+      <x:c r="F53" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="28" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C54" s="29" t="s"/>
+      <x:c r="D54" s="29" t="s"/>
+      <x:c r="E54" s="29" t="s"/>
+      <x:c r="F54" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="28" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C55" s="29" t="s"/>
+      <x:c r="D55" s="29" t="s"/>
+      <x:c r="E55" s="29" t="s"/>
+      <x:c r="F55" s="30" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46098.0792592593</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46098.0878935185</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1529776</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46098.0997569444</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46097.2890740741</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I18" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I19" s="17">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I20" s="17">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I24" s="17">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I25" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C26" s="15" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="D26" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="G26" s="15" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="H26" s="17">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I26" s="17">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J26" s="16" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L26" s="19">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M26" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C27" s="15" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="D27" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F27" s="15" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G27" s="15" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H27" s="17">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I27" s="17">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J27" s="16" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K27" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L27" s="19">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M27" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C28" s="15" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D28" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E28" s="15" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="F28" s="15" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G28" s="15" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="H28" s="17">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I28" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J28" s="16" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K28" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="19">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M28" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C29" s="15" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D29" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E29" s="15" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="G29" s="15" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="H29" s="17">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I29" s="17">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J29" s="16" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="19">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M29" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C30" s="15" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D30" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E30" s="15" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F30" s="15" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="G30" s="15" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="H30" s="17">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I30" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J30" s="16" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K30" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="19">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M30" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C31" s="15" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="D31" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E31" s="15" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="F31" s="15" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="G31" s="15" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="H31" s="17">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I31" s="17">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J31" s="16" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K31" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="19">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M31" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C32" s="15" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="D32" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E32" s="15" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="F32" s="15" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="G32" s="15" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="H32" s="17">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I32" s="17">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J32" s="16" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K32" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="19">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M32" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C33" s="15" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="D33" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E33" s="15" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="F33" s="15" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="G33" s="15" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="H33" s="17">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I33" s="17">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J33" s="16" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K33" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="19">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M33" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C34" s="15" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="D34" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E34" s="15" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F34" s="15" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="G34" s="15" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H34" s="17">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I34" s="17">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J34" s="16" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K34" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L34" s="19">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M34" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C35" s="15" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="D35" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E35" s="15" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="F35" s="15" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G35" s="15" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H35" s="17">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I35" s="17">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J35" s="16" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K35" s="18" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L35" s="19">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M35" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C36" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D36" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E36" s="15" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F36" s="15" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G36" s="15" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H36" s="17">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I36" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J36" s="16" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K36" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="19">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M36" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C37" s="15" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D37" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E37" s="15" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="F37" s="15" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="G37" s="15" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="H37" s="17">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I37" s="17">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J37" s="16" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K37" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L37" s="19">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M37" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C38" s="15" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D38" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E38" s="15" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="F38" s="15" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="G38" s="15" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="H38" s="17">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I38" s="17">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J38" s="16" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K38" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="19">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M38" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C39" s="15" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D39" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E39" s="15" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="F39" s="15" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="G39" s="15" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="H39" s="17">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I39" s="17">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J39" s="16" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K39" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L39" s="19">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M39" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C40" s="15" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D40" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E40" s="15" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="F40" s="15" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="G40" s="15" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="H40" s="17">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I40" s="17">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J40" s="16" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K40" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L40" s="19">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M40" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C41" s="15" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D41" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E41" s="15" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="F41" s="15" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="G41" s="15" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="H41" s="17">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I41" s="17">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J41" s="16" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K41" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L41" s="19">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M41" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C42" s="15" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D42" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E42" s="15" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="F42" s="15" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="G42" s="15" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="H42" s="17">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I42" s="17">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J42" s="16" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K42" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L42" s="19">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M42" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C43" s="15" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="D43" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E43" s="15" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="F43" s="15" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="G43" s="15" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="H43" s="17">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I43" s="17">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J43" s="16" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K43" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="19">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M43" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C44" s="15" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D44" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E44" s="15" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="F44" s="15" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="G44" s="15" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="H44" s="17">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I44" s="17">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J44" s="16" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K44" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="19">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M44" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C45" s="15" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="D45" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E45" s="15" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="F45" s="15" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="G45" s="15" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="H45" s="17">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I45" s="17">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J45" s="16" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K45" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="19">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M45" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C46" s="15" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D46" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E46" s="15" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="F46" s="15" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="G46" s="15" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="H46" s="17">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I46" s="17">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J46" s="16" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K46" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L46" s="19">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M46" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C47" s="15" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D47" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E47" s="15" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="F47" s="15" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="G47" s="15" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="H47" s="17">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I47" s="17">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J47" s="16" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K47" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L47" s="19">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M47" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B48" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C48" s="15" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D48" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E48" s="15" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="F48" s="15" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="G48" s="15" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="H48" s="17">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I48" s="17">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J48" s="16" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K48" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L48" s="19">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M48" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B49" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C49" s="15" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="D49" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E49" s="15" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="F49" s="15" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="G49" s="15" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="H49" s="17">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I49" s="17">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J49" s="16" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K49" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L49" s="19">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M49" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B50" s="15" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C50" s="15" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="D50" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E50" s="15" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="F50" s="15" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="G50" s="15" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="H50" s="17">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I50" s="17">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J50" s="16" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K50" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L50" s="19">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M50" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="20" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="C53" s="21" t="s"/>
-      <x:c r="D53" s="21" t="s"/>
-      <x:c r="E53" s="22" t="s"/>
-      <x:c r="F53" s="22" t="s"/>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B54" s="23" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="C54" s="24" t="s"/>
-      <x:c r="D54" s="24" t="s"/>
-      <x:c r="E54" s="24" t="s"/>
-      <x:c r="F54" s="25" t="s">
-        <x:v>179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C55" s="27" t="s"/>
-      <x:c r="D55" s="27" t="s"/>
-      <x:c r="E55" s="27" t="s"/>
-      <x:c r="F55" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C56" s="27" t="s"/>
-      <x:c r="D56" s="27" t="s"/>
-      <x:c r="E56" s="27" t="s"/>
-      <x:c r="F56" s="28" t="n">
-        <x:v>3</x:v>
+      <x:c r="B56" s="28" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C56" s="29" t="s"/>
+      <x:c r="D56" s="29" t="s"/>
+      <x:c r="E56" s="29" t="s"/>
+      <x:c r="F56" s="30" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="26" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C57" s="27" t="s"/>
-      <x:c r="D57" s="27" t="s"/>
-      <x:c r="E57" s="27" t="s"/>
-      <x:c r="F57" s="28" t="n">
-        <x:v>23</x:v>
+      <x:c r="B57" s="28" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C57" s="29" t="s"/>
+      <x:c r="D57" s="29" t="s"/>
+      <x:c r="E57" s="29" t="s"/>
+      <x:c r="F57" s="30" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="26" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C58" s="27" t="s"/>
-      <x:c r="D58" s="27" t="s"/>
-      <x:c r="E58" s="27" t="s"/>
-      <x:c r="F58" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B59" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C59" s="27" t="s"/>
-      <x:c r="D59" s="27" t="s"/>
-      <x:c r="E59" s="27" t="s"/>
-      <x:c r="F59" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B60" s="26" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C60" s="27" t="s"/>
-      <x:c r="D60" s="27" t="s"/>
-      <x:c r="E60" s="27" t="s"/>
-      <x:c r="F60" s="28" t="n">
+      <x:c r="B58" s="28" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C58" s="29" t="s"/>
+      <x:c r="D58" s="29" t="s"/>
+      <x:c r="E58" s="29" t="s"/>
+      <x:c r="F58" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B61" s="29" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="C61" s="30" t="s"/>
-      <x:c r="D61" s="30" t="s"/>
-      <x:c r="E61" s="30" t="s"/>
-      <x:c r="F61" s="31" t="n">
+    <x:row r="59" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B59" s="31" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C59" s="32" t="s"/>
+      <x:c r="D59" s="32" t="s"/>
+      <x:c r="E59" s="32" t="s"/>
+      <x:c r="F59" s="33" t="n">
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7177,15 +7059,15 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B53:F53"/>
+    <x:mergeCell ref="B51:F51"/>
+    <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
-    <x:mergeCell ref="B60:E60"/>
-    <x:mergeCell ref="B61:E61"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -574,6 +574,18 @@
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06915-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1178-478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -583,18 +595,6 @@
     <x:t>43A-3-2026-1179-857</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-06915-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1178-478</x:t>
-  </x:si>
-  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -619,6 +619,15 @@
     <x:t>43A-2-2026-1144-933</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -628,15 +637,6 @@
     <x:t>43A-3-2026-1150-325</x:t>
   </x:si>
   <x:si>
-    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0780 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1151-716</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -685,6 +685,24 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -694,15 +712,6 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -712,15 +721,6 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -856,6 +856,15 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
     <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
   </x:si>
   <x:si>
@@ -883,15 +892,6 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
-    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-0002C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1170-469</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -950,6 +950,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLBOY INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLOOR CYBERZONE SM CALAMBA NATIONAL HIGHWAY, REAL, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-16-12-0951</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1205-403</x:t>
   </x:si>
   <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
@@ -4596,10 +4608,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H11" s="19">
-        <x:v>46090.2558217593</x:v>
+        <x:v>46090.2418287037</x:v>
       </x:c>
       <x:c r="I11" s="19">
-        <x:v>46090.2558333333</x:v>
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
         <x:v>1511203</x:v>
@@ -4608,7 +4620,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="21">
-        <x:v>46097.2890740741</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M11" s="17" t="s">
         <x:v>186</x:v>
@@ -4634,10 +4646,10 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="H12" s="19">
-        <x:v>46090.2418287037</x:v>
+        <x:v>46090.2558217593</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46090.2418518519</x:v>
+        <x:v>46090.2558333333</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
         <x:v>1511203</x:v>
@@ -4646,7 +4658,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="21">
-        <x:v>46093.3049884259</x:v>
+        <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M12" s="17" t="s">
         <x:v>186</x:v>
@@ -4748,19 +4760,19 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H15" s="19">
-        <x:v>46083.2322337963</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>1511233</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="21">
-        <x:v>46097.149525463</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M15" s="17" t="s">
         <x:v>186</x:v>
@@ -4786,19 +4798,19 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="H16" s="19">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46083.2322337963</x:v>
       </x:c>
       <x:c r="I16" s="19">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511233</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="21">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46097.149525463</x:v>
       </x:c>
       <x:c r="M16" s="17" t="s">
         <x:v>186</x:v>
@@ -4976,19 +4988,19 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46133</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
         <x:v>186</x:v>
@@ -5052,19 +5064,19 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
         <x:v>186</x:v>
@@ -5090,19 +5102,19 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="H24" s="19">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46035</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
         <x:v>186</x:v>
@@ -5584,10 +5596,10 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="H37" s="19">
-        <x:v>46085.16625</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I37" s="19">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J37" s="18" t="n">
         <x:v>1507966</x:v>
@@ -5596,7 +5608,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L37" s="21">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M37" s="17" t="s">
         <x:v>25</x:v>
@@ -5622,19 +5634,19 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="H38" s="19">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I38" s="19">
-        <x:v>46085.1709375</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J38" s="18" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K38" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L38" s="21">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M38" s="17" t="s">
         <x:v>25</x:v>
@@ -5660,19 +5672,19 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="H39" s="19">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I39" s="19">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J39" s="18" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K39" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="21">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M39" s="17" t="s">
         <x:v>25</x:v>
@@ -5698,19 +5710,19 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="H40" s="19">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I40" s="19">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J40" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K40" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="21">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M40" s="17" t="s">
         <x:v>25</x:v>
@@ -5964,22 +5976,22 @@
         <x:v>312</x:v>
       </x:c>
       <x:c r="H47" s="19">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46098.2908796296</x:v>
       </x:c>
       <x:c r="I47" s="19">
-        <x:v>46094</x:v>
+        <x:v>45997</x:v>
       </x:c>
       <x:c r="J47" s="18" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511858</x:v>
       </x:c>
       <x:c r="K47" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L47" s="21">
-        <x:v>46093.3109375</x:v>
+        <x:v>46098.3188657407</x:v>
       </x:c>
       <x:c r="M47" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
@@ -6002,60 +6014,87 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="H48" s="19">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46092.9637847222</x:v>
       </x:c>
       <x:c r="I48" s="19">
-        <x:v>46084</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J48" s="18" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1511219</x:v>
       </x:c>
       <x:c r="K48" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L48" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M48" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B49" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C49" s="17" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="D49" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E49" s="17" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="F49" s="17" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="G49" s="17" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H49" s="19">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I49" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J49" s="18" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K49" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L49" s="21">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M48" s="17" t="s">
+      <x:c r="M49" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="22" t="s">
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B52" s="22" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="C51" s="23" t="s"/>
-      <x:c r="D51" s="23" t="s"/>
-      <x:c r="E51" s="24" t="s"/>
-      <x:c r="F51" s="24" t="s"/>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B52" s="25" t="s">
+      <x:c r="C52" s="23" t="s"/>
+      <x:c r="D52" s="23" t="s"/>
+      <x:c r="E52" s="24" t="s"/>
+      <x:c r="F52" s="24" t="s"/>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B53" s="25" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C52" s="26" t="s"/>
-      <x:c r="D52" s="26" t="s"/>
-      <x:c r="E52" s="26" t="s"/>
-      <x:c r="F52" s="27" t="s">
+      <x:c r="C53" s="26" t="s"/>
+      <x:c r="D53" s="26" t="s"/>
+      <x:c r="E53" s="26" t="s"/>
+      <x:c r="F53" s="27" t="s">
         <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C53" s="29" t="s"/>
-      <x:c r="D53" s="29" t="s"/>
-      <x:c r="E53" s="29" t="s"/>
-      <x:c r="F53" s="30" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
       <x:c r="B54" s="28" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C54" s="29" t="s"/>
       <x:c r="D54" s="29" t="s"/>
@@ -6066,60 +6105,70 @@
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
       <x:c r="B55" s="28" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C55" s="29" t="s"/>
       <x:c r="D55" s="29" t="s"/>
       <x:c r="E55" s="29" t="s"/>
       <x:c r="F55" s="30" t="n">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
       <x:c r="B56" s="28" t="s">
-        <x:v>75</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C56" s="29" t="s"/>
       <x:c r="D56" s="29" t="s"/>
       <x:c r="E56" s="29" t="s"/>
       <x:c r="F56" s="30" t="n">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
       <x:c r="B57" s="28" t="s">
-        <x:v>89</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C57" s="29" t="s"/>
       <x:c r="D57" s="29" t="s"/>
       <x:c r="E57" s="29" t="s"/>
       <x:c r="F57" s="30" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
       <x:c r="B58" s="28" t="s">
-        <x:v>139</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C58" s="29" t="s"/>
       <x:c r="D58" s="29" t="s"/>
       <x:c r="E58" s="29" t="s"/>
       <x:c r="F58" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B59" s="31" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B59" s="28" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C59" s="29" t="s"/>
+      <x:c r="D59" s="29" t="s"/>
+      <x:c r="E59" s="29" t="s"/>
+      <x:c r="F59" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B60" s="31" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C59" s="32" t="s"/>
-      <x:c r="D59" s="32" t="s"/>
-      <x:c r="E59" s="32" t="s"/>
-      <x:c r="F59" s="33" t="n">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C60" s="32" t="s"/>
+      <x:c r="D60" s="32" t="s"/>
+      <x:c r="E60" s="32" t="s"/>
+      <x:c r="F60" s="33" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7059,8 +7108,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B51:F51"/>
-    <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B52:F52"/>
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
@@ -7068,6 +7116,7 @@
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
+    <x:mergeCell ref="B60:E60"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="330">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -250,6 +250,21 @@
     <x:t>Ceasar Allen Centeno</x:t>
   </x:si>
   <x:si>
+    <x:t>Duplicate Copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGA PIXEL MARKETING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2F E205 SM CITY, SAMPALOC I, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-07-0003C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1114-391</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -574,6 +589,18 @@
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06919-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1179-857</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -583,18 +610,6 @@
     <x:t>43A-3-2026-1178-478</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-06919-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1179-857</x:t>
-  </x:si>
-  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -610,6 +625,24 @@
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0780 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1151-716</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
     <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
   </x:si>
   <x:si>
@@ -619,24 +652,6 @@
     <x:t>43A-2-2026-1144-933</x:t>
   </x:si>
   <x:si>
-    <x:t>CZ 248-3 SM City San Pablo, Brgy. San Rafael, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0780 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1151-716</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1150-325</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -664,6 +679,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -673,18 +697,36 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
-    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-020R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1156-896</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
     <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
   </x:si>
   <x:si>
@@ -694,33 +736,6 @@
     <x:t>43A-2-2026-1085-453</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467-24R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1096-022</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -733,6 +748,18 @@
     <x:t>43A-2-2026-1086-471</x:t>
   </x:si>
   <x:si>
+    <x:t>HLH GENTECH INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-17-11-0683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1109-317</x:t>
+  </x:si>
+  <x:si>
     <x:t>INTO GADGETS TOO INC.</x:t>
   </x:si>
   <x:si>
@@ -793,6 +820,15 @@
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 24-471R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1108-762</x:t>
+  </x:si>
+  <x:si>
     <x:t>LEVEL 3 0118, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -811,15 +847,6 @@
     <x:t>43A-3-2026-1168-173</x:t>
   </x:si>
   <x:si>
-    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 24-471R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1108-762</x:t>
-  </x:si>
-  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -856,6 +883,24 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1171-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
     <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
   </x:si>
   <x:si>
@@ -863,24 +908,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1170-469</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1171-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
   </x:si>
   <x:si>
     <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
@@ -2394,9 +2421,7 @@
       <x:c r="C21" s="17" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D21" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
+      <x:c r="D21" s="18" t="s"/>
       <x:c r="E21" s="17" t="s">
         <x:v>77</x:v>
       </x:c>
@@ -2407,27 +2432,27 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46079.3584722222</x:v>
+        <x:v>46073.2761689815</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46079.3584953704</x:v>
+        <x:v>46073.2761689815</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511622</x:v>
+        <x:v>1507791</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46080.2311226852</x:v>
+        <x:v>46073.3142476852</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B22" s="17" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C22" s="17" t="s">
         <x:v>81</x:v>
@@ -2445,71 +2470,71 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H22" s="19">
-        <x:v>46079.3539699074</x:v>
+        <x:v>46079.3584722222</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46079.3539814815</x:v>
+        <x:v>46079.3584953704</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1511627</x:v>
+        <x:v>1511622</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46080.2440856481</x:v>
+        <x:v>46080.2311226852</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B23" s="17" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C23" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E23" s="17" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F23" s="17" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G23" s="17" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46058.1529282407</x:v>
+        <x:v>46079.3539699074</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46058.1529398148</x:v>
+        <x:v>46079.3539814815</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1507657</x:v>
+        <x:v>1511627</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46058.2410648148</x:v>
+        <x:v>46080.2440856481</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C24" s="17" t="s">
         <x:v>90</x:v>
       </x:c>
       <x:c r="D24" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E24" s="17" t="s">
         <x:v>91</x:v>
@@ -2521,19 +2546,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H24" s="19">
-        <x:v>46072.2635300926</x:v>
+        <x:v>46058.1529282407</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46055</x:v>
+        <x:v>46058.1529398148</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1507790</x:v>
+        <x:v>1507657</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46073.3091087963</x:v>
+        <x:v>46058.2410648148</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
         <x:v>25</x:v>
@@ -2541,253 +2566,253 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C25" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D25" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E25" s="17" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F25" s="17" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G25" s="17" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H25" s="19">
-        <x:v>46079.3873148148</x:v>
+        <x:v>46072.2635300926</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46092</x:v>
+        <x:v>46055</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>1511623</x:v>
+        <x:v>1507790</x:v>
       </x:c>
       <x:c r="K25" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L25" s="21">
-        <x:v>46080.2360763889</x:v>
+        <x:v>46073.3091087963</x:v>
       </x:c>
       <x:c r="M25" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C26" s="17" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D26" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E26" s="17" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F26" s="17" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G26" s="17" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H26" s="19">
-        <x:v>46079.2523032407</x:v>
+        <x:v>46079.3873148148</x:v>
       </x:c>
       <x:c r="I26" s="19">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1511631</x:v>
+        <x:v>1511623</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46080.2925810185</x:v>
+        <x:v>46080.2360763889</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B27" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C27" s="17" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D27" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E27" s="17" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F27" s="17" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G27" s="17" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H27" s="19">
-        <x:v>46079.2430555556</x:v>
+        <x:v>46079.2523032407</x:v>
       </x:c>
       <x:c r="I27" s="19">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>1511630</x:v>
+        <x:v>1511631</x:v>
       </x:c>
       <x:c r="K27" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="21">
-        <x:v>46080.2801273148</x:v>
+        <x:v>46080.2925810185</x:v>
       </x:c>
       <x:c r="M27" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B28" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C28" s="17" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D28" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E28" s="17" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F28" s="17" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G28" s="17" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H28" s="19">
-        <x:v>46079.3651967593</x:v>
+        <x:v>46079.2430555556</x:v>
       </x:c>
       <x:c r="I28" s="19">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>1511626</x:v>
+        <x:v>1511630</x:v>
       </x:c>
       <x:c r="K28" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="21">
-        <x:v>46080.2425462963</x:v>
+        <x:v>46080.2801273148</x:v>
       </x:c>
       <x:c r="M28" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B29" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C29" s="17" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D29" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E29" s="17" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F29" s="17" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G29" s="17" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H29" s="19">
-        <x:v>46080.2923611111</x:v>
+        <x:v>46079.3651967593</x:v>
       </x:c>
       <x:c r="I29" s="19">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>1511635</x:v>
+        <x:v>1511626</x:v>
       </x:c>
       <x:c r="K29" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="21">
-        <x:v>46080.3208564815</x:v>
+        <x:v>46080.2425462963</x:v>
       </x:c>
       <x:c r="M29" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B30" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C30" s="17" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D30" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E30" s="17" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F30" s="17" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G30" s="17" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H30" s="19">
-        <x:v>46079.31625</x:v>
+        <x:v>46080.2923611111</x:v>
       </x:c>
       <x:c r="I30" s="19">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>1511630</x:v>
+        <x:v>1511635</x:v>
       </x:c>
       <x:c r="K30" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L30" s="21">
-        <x:v>46080.2883680556</x:v>
+        <x:v>46080.3208564815</x:v>
       </x:c>
       <x:c r="M30" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B31" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C31" s="17" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D31" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E31" s="17" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F31" s="17" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G31" s="17" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H31" s="19">
-        <x:v>46079.3059375</x:v>
+        <x:v>46079.31625</x:v>
       </x:c>
       <x:c r="I31" s="19">
         <x:v>46092</x:v>
@@ -2799,33 +2824,33 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="21">
-        <x:v>46080.2896875</x:v>
+        <x:v>46080.2883680556</x:v>
       </x:c>
       <x:c r="M31" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B32" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C32" s="17" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D32" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E32" s="17" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F32" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G32" s="17" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H32" s="19">
-        <x:v>46079.2943981482</x:v>
+        <x:v>46079.3059375</x:v>
       </x:c>
       <x:c r="I32" s="19">
         <x:v>46092</x:v>
@@ -2837,135 +2862,135 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L32" s="21">
-        <x:v>46080.2916782407</x:v>
+        <x:v>46080.2896875</x:v>
       </x:c>
       <x:c r="M32" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B33" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C33" s="17" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D33" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E33" s="17" t="s">
-        <x:v>124</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F33" s="17" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G33" s="17" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H33" s="19">
-        <x:v>46079.378900463</x:v>
+        <x:v>46079.2943981482</x:v>
       </x:c>
       <x:c r="I33" s="19">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J33" s="18" t="n">
-        <x:v>1511624</x:v>
+        <x:v>1511630</x:v>
       </x:c>
       <x:c r="K33" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="21">
-        <x:v>46080.2376041667</x:v>
+        <x:v>46080.2916782407</x:v>
       </x:c>
       <x:c r="M33" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B34" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C34" s="17" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D34" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E34" s="17" t="s">
-        <x:v>124</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F34" s="17" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G34" s="17" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H34" s="19">
-        <x:v>46079.3728240741</x:v>
+        <x:v>46079.378900463</x:v>
       </x:c>
       <x:c r="I34" s="19">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="J34" s="18" t="n">
-        <x:v>1511625</x:v>
+        <x:v>1511624</x:v>
       </x:c>
       <x:c r="K34" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L34" s="21">
-        <x:v>46080.2394328704</x:v>
+        <x:v>46080.2376041667</x:v>
       </x:c>
       <x:c r="M34" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B35" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="17" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D35" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E35" s="17" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F35" s="17" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G35" s="17" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H35" s="19">
-        <x:v>46077.0697337963</x:v>
+        <x:v>46079.3728240741</x:v>
       </x:c>
       <x:c r="I35" s="19">
-        <x:v>46081</x:v>
+        <x:v>46092</x:v>
       </x:c>
       <x:c r="J35" s="18" t="n">
-        <x:v>1511576</x:v>
+        <x:v>1511625</x:v>
       </x:c>
       <x:c r="K35" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L35" s="21">
-        <x:v>46077.1078819444</x:v>
+        <x:v>46080.2394328704</x:v>
       </x:c>
       <x:c r="M35" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B36" s="17" t="s">
-        <x:v>134</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C36" s="17" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="D36" s="18" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E36" s="17" t="s">
         <x:v>136</x:v>
@@ -2977,22 +3002,22 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="H36" s="19">
-        <x:v>46062.1590162037</x:v>
+        <x:v>46077.0697337963</x:v>
       </x:c>
       <x:c r="I36" s="19">
-        <x:v>46062.1590277778</x:v>
+        <x:v>46081</x:v>
       </x:c>
       <x:c r="J36" s="18" t="n">
-        <x:v>1510925</x:v>
+        <x:v>1511576</x:v>
       </x:c>
       <x:c r="K36" s="20" t="n">
-        <x:v>2130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L36" s="21">
-        <x:v>46062.1863194444</x:v>
+        <x:v>46077.1078819444</x:v>
       </x:c>
       <x:c r="M36" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
@@ -3003,7 +3028,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="D37" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E37" s="17" t="s">
         <x:v>141</x:v>
@@ -3015,133 +3040,133 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="H37" s="19">
-        <x:v>46066.2180208333</x:v>
+        <x:v>46062.1590162037</x:v>
       </x:c>
       <x:c r="I37" s="19">
-        <x:v>46083</x:v>
+        <x:v>46062.1590277778</x:v>
       </x:c>
       <x:c r="J37" s="18" t="n">
-        <x:v>1507743</x:v>
+        <x:v>1510925</x:v>
       </x:c>
       <x:c r="K37" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L37" s="21">
-        <x:v>46066.2724421296</x:v>
+        <x:v>46062.1863194444</x:v>
       </x:c>
       <x:c r="M37" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B38" s="17" t="s">
-        <x:v>139</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C38" s="17" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D38" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E38" s="17" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F38" s="17" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G38" s="17" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H38" s="19">
-        <x:v>46071.0492476852</x:v>
+        <x:v>46066.2180208333</x:v>
       </x:c>
       <x:c r="I38" s="19">
-        <x:v>46052</x:v>
+        <x:v>46083</x:v>
       </x:c>
       <x:c r="J38" s="18" t="n">
-        <x:v>1511502</x:v>
+        <x:v>1507743</x:v>
       </x:c>
       <x:c r="K38" s="20" t="n">
-        <x:v>2550</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L38" s="21">
-        <x:v>46071.0606134259</x:v>
+        <x:v>46066.2724421296</x:v>
       </x:c>
       <x:c r="M38" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B39" s="17" t="s">
-        <x:v>139</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C39" s="17" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D39" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E39" s="17" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F39" s="17" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G39" s="17" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H39" s="19">
-        <x:v>46066.2275347222</x:v>
+        <x:v>46071.0492476852</x:v>
       </x:c>
       <x:c r="I39" s="19">
-        <x:v>46100</x:v>
+        <x:v>46052</x:v>
       </x:c>
       <x:c r="J39" s="18" t="n">
-        <x:v>1507742</x:v>
+        <x:v>1511502</x:v>
       </x:c>
       <x:c r="K39" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L39" s="21">
-        <x:v>46066.2701736111</x:v>
+        <x:v>46071.0606134259</x:v>
       </x:c>
       <x:c r="M39" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B40" s="17" t="s">
-        <x:v>139</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C40" s="17" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D40" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E40" s="17" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F40" s="17" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G40" s="17" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H40" s="19">
-        <x:v>46078.2436226852</x:v>
+        <x:v>46066.2275347222</x:v>
       </x:c>
       <x:c r="I40" s="19">
-        <x:v>46085</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J40" s="18" t="n">
-        <x:v>1507839</x:v>
+        <x:v>1507742</x:v>
       </x:c>
       <x:c r="K40" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L40" s="21">
-        <x:v>46078.3266203704</x:v>
+        <x:v>46066.2701736111</x:v>
       </x:c>
       <x:c r="M40" s="17" t="s">
         <x:v>25</x:v>
@@ -3149,12 +3174,14 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B41" s="17" t="s">
-        <x:v>156</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C41" s="17" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="D41" s="18" t="s"/>
+      <x:c r="D41" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
       <x:c r="E41" s="17" t="s">
         <x:v>158</x:v>
       </x:c>
@@ -3165,19 +3192,19 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="H41" s="19">
-        <x:v>46080.2342361111</x:v>
+        <x:v>46078.2436226852</x:v>
       </x:c>
       <x:c r="I41" s="19">
-        <x:v>46080.2342592593</x:v>
+        <x:v>46085</x:v>
       </x:c>
       <x:c r="J41" s="18" t="n">
-        <x:v>1507884</x:v>
+        <x:v>1507839</x:v>
       </x:c>
       <x:c r="K41" s="20" t="n">
-        <x:v>426</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L41" s="21">
-        <x:v>46080.3353356481</x:v>
+        <x:v>46078.3266203704</x:v>
       </x:c>
       <x:c r="M41" s="17" t="s">
         <x:v>25</x:v>
@@ -3185,163 +3212,208 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B42" s="17" t="s">
-        <x:v>156</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C42" s="17" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D42" s="18" t="s"/>
       <x:c r="E42" s="17" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F42" s="17" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G42" s="17" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H42" s="19">
-        <x:v>46080.2722685185</x:v>
+        <x:v>46080.2342361111</x:v>
       </x:c>
       <x:c r="I42" s="19">
-        <x:v>46080.2722800926</x:v>
+        <x:v>46080.2342592593</x:v>
       </x:c>
       <x:c r="J42" s="18" t="n">
-        <x:v>1507883</x:v>
+        <x:v>1507884</x:v>
       </x:c>
       <x:c r="K42" s="20" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L42" s="21">
-        <x:v>46080.3345717593</x:v>
+        <x:v>46080.3353356481</x:v>
       </x:c>
       <x:c r="M42" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="17" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C43" s="17" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D43" s="18" t="s"/>
+      <x:c r="E43" s="17" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F43" s="17" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G43" s="17" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H43" s="19">
+        <x:v>46080.2722685185</x:v>
+      </x:c>
+      <x:c r="I43" s="19">
+        <x:v>46080.2722800926</x:v>
+      </x:c>
+      <x:c r="J43" s="18" t="n">
+        <x:v>1507883</x:v>
+      </x:c>
+      <x:c r="K43" s="20" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L43" s="21">
+        <x:v>46080.3345717593</x:v>
+      </x:c>
+      <x:c r="M43" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="22" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="C45" s="23" t="s"/>
-      <x:c r="D45" s="23" t="s"/>
-      <x:c r="E45" s="24" t="s"/>
-      <x:c r="F45" s="24" t="s"/>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="25" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C46" s="26" t="s"/>
-      <x:c r="D46" s="26" t="s"/>
-      <x:c r="E46" s="26" t="s"/>
-      <x:c r="F46" s="27" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C47" s="29" t="s"/>
-      <x:c r="D47" s="29" t="s"/>
-      <x:c r="E47" s="29" t="s"/>
-      <x:c r="F47" s="30" t="n">
-        <x:v>6</x:v>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="22" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C46" s="23" t="s"/>
+      <x:c r="D46" s="23" t="s"/>
+      <x:c r="E46" s="24" t="s"/>
+      <x:c r="F46" s="24" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B47" s="25" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C47" s="26" t="s"/>
+      <x:c r="D47" s="26" t="s"/>
+      <x:c r="E47" s="26" t="s"/>
+      <x:c r="F47" s="27" t="s">
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="28" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C48" s="29" t="s"/>
       <x:c r="D48" s="29" t="s"/>
       <x:c r="E48" s="29" t="s"/>
       <x:c r="F48" s="30" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
       <x:c r="B49" s="28" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C49" s="29" t="s"/>
       <x:c r="D49" s="29" t="s"/>
       <x:c r="E49" s="29" t="s"/>
       <x:c r="F49" s="30" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="28" t="s">
-        <x:v>75</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C50" s="29" t="s"/>
       <x:c r="D50" s="29" t="s"/>
       <x:c r="E50" s="29" t="s"/>
       <x:c r="F50" s="30" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
       <x:c r="B51" s="28" t="s">
-        <x:v>89</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C51" s="29" t="s"/>
       <x:c r="D51" s="29" t="s"/>
       <x:c r="E51" s="29" t="s"/>
       <x:c r="F51" s="30" t="n">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
       <x:c r="B52" s="28" t="s">
-        <x:v>134</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C52" s="29" t="s"/>
       <x:c r="D52" s="29" t="s"/>
       <x:c r="E52" s="29" t="s"/>
       <x:c r="F52" s="30" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
       <x:c r="B53" s="28" t="s">
-        <x:v>139</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C53" s="29" t="s"/>
       <x:c r="D53" s="29" t="s"/>
       <x:c r="E53" s="29" t="s"/>
       <x:c r="F53" s="30" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
       <x:c r="B54" s="28" t="s">
-        <x:v>156</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C54" s="29" t="s"/>
       <x:c r="D54" s="29" t="s"/>
       <x:c r="E54" s="29" t="s"/>
       <x:c r="F54" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="28" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C55" s="29" t="s"/>
+      <x:c r="D55" s="29" t="s"/>
+      <x:c r="E55" s="29" t="s"/>
+      <x:c r="F55" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="28" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C56" s="29" t="s"/>
+      <x:c r="D56" s="29" t="s"/>
+      <x:c r="E56" s="29" t="s"/>
+      <x:c r="F56" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="31" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C55" s="32" t="s"/>
-      <x:c r="D55" s="32" t="s"/>
-      <x:c r="E55" s="32" t="s"/>
-      <x:c r="F55" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B57" s="31" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C57" s="32" t="s"/>
+      <x:c r="D57" s="32" t="s"/>
+      <x:c r="E57" s="32" t="s"/>
+      <x:c r="F57" s="33" t="n">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
     <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4279,13 +4351,12 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="15">
+  <x:mergeCells count="16">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B45:F45"/>
-    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B46:F46"/>
     <x:mergeCell ref="B47:E47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
@@ -4295,6 +4366,8 @@
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B57:E57"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -4406,7 +4479,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>169</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -4485,17 +4558,17 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>170</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>172</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>173</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H8" s="15">
         <x:v>46091.306099537</x:v>
@@ -4513,7 +4586,7 @@
         <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -4521,17 +4594,17 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>174</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>177</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>46093.1459375</x:v>
@@ -4549,7 +4622,7 @@
         <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
@@ -4557,17 +4630,17 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="17" t="s">
-        <x:v>178</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D10" s="18" t="s"/>
       <x:c r="E10" s="17" t="s">
-        <x:v>179</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F10" s="17" t="s">
-        <x:v>180</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G10" s="17" t="s">
-        <x:v>181</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H10" s="19">
         <x:v>46098.0792592593</x:v>
@@ -4593,25 +4666,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s">
-        <x:v>182</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E11" s="17" t="s">
-        <x:v>183</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F11" s="17" t="s">
-        <x:v>184</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G11" s="17" t="s">
-        <x:v>185</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H11" s="19">
-        <x:v>46090.2418287037</x:v>
+        <x:v>46090.2558217593</x:v>
       </x:c>
       <x:c r="I11" s="19">
-        <x:v>46090.2418518519</x:v>
+        <x:v>46090.2558333333</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
         <x:v>1511203</x:v>
@@ -4620,10 +4693,10 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="21">
-        <x:v>46093.3049884259</x:v>
+        <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M11" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -4631,25 +4704,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C12" s="17" t="s">
-        <x:v>182</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D12" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E12" s="17" t="s">
-        <x:v>187</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F12" s="17" t="s">
-        <x:v>188</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G12" s="17" t="s">
-        <x:v>189</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H12" s="19">
-        <x:v>46090.2558217593</x:v>
+        <x:v>46090.2418287037</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46090.2558333333</x:v>
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
         <x:v>1511203</x:v>
@@ -4658,10 +4731,10 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="21">
-        <x:v>46097.2890740741</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M12" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
@@ -4669,19 +4742,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C13" s="17" t="s">
-        <x:v>190</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D13" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F13" s="17" t="s">
-        <x:v>192</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G13" s="17" t="s">
-        <x:v>193</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H13" s="19">
         <x:v>46090.2109953704</x:v>
@@ -4699,7 +4772,7 @@
         <x:v>46093.3080092593</x:v>
       </x:c>
       <x:c r="M13" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
@@ -4707,37 +4780,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="17" t="s">
-        <x:v>194</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D14" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E14" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F14" s="17" t="s">
-        <x:v>196</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G14" s="17" t="s">
-        <x:v>197</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H14" s="19">
-        <x:v>46080.4532523148</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I14" s="19">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J14" s="18" t="n">
-        <x:v>1511232</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K14" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="21">
-        <x:v>46097.1461689815</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M14" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -4745,37 +4818,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C15" s="17" t="s">
-        <x:v>194</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E15" s="17" t="s">
-        <x:v>198</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F15" s="17" t="s">
-        <x:v>199</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G15" s="17" t="s">
-        <x:v>200</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H15" s="19">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46083.2322337963</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511233</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="21">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46097.149525463</x:v>
       </x:c>
       <x:c r="M15" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -4783,37 +4856,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C16" s="17" t="s">
-        <x:v>194</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D16" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E16" s="17" t="s">
-        <x:v>201</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F16" s="17" t="s">
-        <x:v>202</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="G16" s="17" t="s">
-        <x:v>203</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H16" s="19">
-        <x:v>46083.2322337963</x:v>
+        <x:v>46080.4532523148</x:v>
       </x:c>
       <x:c r="I16" s="19">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>1511233</x:v>
+        <x:v>1511232</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="21">
-        <x:v>46097.149525463</x:v>
+        <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M16" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
@@ -4821,19 +4894,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="17" t="s">
-        <x:v>204</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D17" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E17" s="17" t="s">
-        <x:v>205</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F17" s="17" t="s">
-        <x:v>206</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G17" s="17" t="s">
-        <x:v>207</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H17" s="19">
         <x:v>46083.2599189815</x:v>
@@ -4851,7 +4924,7 @@
         <x:v>46097.1652314815</x:v>
       </x:c>
       <x:c r="M17" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
@@ -4859,19 +4932,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="17" t="s">
-        <x:v>208</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D18" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E18" s="17" t="s">
-        <x:v>209</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F18" s="17" t="s">
-        <x:v>210</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G18" s="17" t="s">
-        <x:v>211</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="H18" s="19">
         <x:v>46069.3514814815</x:v>
@@ -4889,7 +4962,7 @@
         <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M18" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -4897,37 +4970,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="17" t="s">
-        <x:v>212</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D19" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E19" s="17" t="s">
-        <x:v>213</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F19" s="17" t="s">
-        <x:v>214</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G19" s="17" t="s">
-        <x:v>215</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H19" s="19">
-        <x:v>46084.0854513889</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I19" s="19">
-        <x:v>46144</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>1511225</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="21">
-        <x:v>46093.3956365741</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M19" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -4935,37 +5008,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>212</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D20" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E20" s="17" t="s">
-        <x:v>216</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F20" s="17" t="s">
-        <x:v>217</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G20" s="17" t="s">
-        <x:v>218</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H20" s="19">
-        <x:v>46084.0996759259</x:v>
+        <x:v>46084.0854513889</x:v>
       </x:c>
       <x:c r="I20" s="19">
-        <x:v>46094</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>1511192</x:v>
+        <x:v>1511225</x:v>
       </x:c>
       <x:c r="K20" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="21">
-        <x:v>46097.2414583333</x:v>
+        <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M20" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -4973,37 +5046,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C21" s="17" t="s">
-        <x:v>219</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D21" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E21" s="17" t="s">
-        <x:v>220</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F21" s="17" t="s">
-        <x:v>221</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G21" s="17" t="s">
-        <x:v>222</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46035</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -5011,19 +5084,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C22" s="17" t="s">
-        <x:v>219</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D22" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="17" t="s">
-        <x:v>223</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F22" s="17" t="s">
-        <x:v>224</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G22" s="17" t="s">
-        <x:v>225</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H22" s="19">
         <x:v>46084.2250115741</x:v>
@@ -5041,7 +5114,7 @@
         <x:v>46093.3804398148</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -5049,37 +5122,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="17" t="s">
-        <x:v>219</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E23" s="17" t="s">
-        <x:v>226</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F23" s="17" t="s">
-        <x:v>227</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G23" s="17" t="s">
-        <x:v>228</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46133</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
@@ -5087,37 +5160,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="17" t="s">
-        <x:v>219</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D24" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E24" s="17" t="s">
-        <x:v>229</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F24" s="17" t="s">
-        <x:v>230</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G24" s="17" t="s">
-        <x:v>231</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H24" s="19">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46100</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -5125,19 +5198,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C25" s="17" t="s">
-        <x:v>232</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D25" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E25" s="17" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F25" s="17" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="G25" s="17" t="s">
-        <x:v>235</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H25" s="19">
         <x:v>46069.2178703704</x:v>
@@ -5155,7 +5228,7 @@
         <x:v>46097.2456365741</x:v>
       </x:c>
       <x:c r="M25" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
@@ -5163,37 +5236,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C26" s="17" t="s">
-        <x:v>236</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D26" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E26" s="17" t="s">
-        <x:v>237</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="F26" s="17" t="s">
-        <x:v>238</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="G26" s="17" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="H26" s="19">
-        <x:v>46083.2443865741</x:v>
+        <x:v>46073.125162037</x:v>
       </x:c>
       <x:c r="I26" s="19">
-        <x:v>46100</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1511235</x:v>
+        <x:v>1511246</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46097.1600115741</x:v>
+        <x:v>46099.1200231481</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
@@ -5201,37 +5274,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C27" s="17" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="D27" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E27" s="17" t="s">
-        <x:v>241</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="F27" s="17" t="s">
-        <x:v>242</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G27" s="17" t="s">
-        <x:v>243</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H27" s="19">
-        <x:v>46084.1225115741</x:v>
+        <x:v>46083.2443865741</x:v>
       </x:c>
       <x:c r="I27" s="19">
-        <x:v>46172</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>1511242</x:v>
+        <x:v>1511235</x:v>
       </x:c>
       <x:c r="K27" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="21">
-        <x:v>46097.3505092593</x:v>
+        <x:v>46097.1600115741</x:v>
       </x:c>
       <x:c r="M27" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
@@ -5239,37 +5312,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C28" s="17" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="D28" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E28" s="17" t="s">
-        <x:v>245</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="F28" s="17" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G28" s="17" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H28" s="19">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I28" s="19">
-        <x:v>46100</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K28" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="21">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M28" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
@@ -5277,37 +5350,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C29" s="17" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D29" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E29" s="17" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F29" s="17" t="s">
-        <x:v>250</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G29" s="17" t="s">
-        <x:v>251</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="H29" s="19">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I29" s="19">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K29" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="21">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M29" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
@@ -5315,37 +5388,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C30" s="17" t="s">
-        <x:v>252</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D30" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E30" s="17" t="s">
-        <x:v>241</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="F30" s="17" t="s">
-        <x:v>253</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G30" s="17" t="s">
-        <x:v>254</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H30" s="19">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I30" s="19">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K30" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L30" s="21">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M30" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
@@ -5353,37 +5426,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C31" s="17" t="s">
-        <x:v>255</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D31" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E31" s="17" t="s">
-        <x:v>256</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="F31" s="17" t="s">
-        <x:v>257</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G31" s="17" t="s">
-        <x:v>258</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="H31" s="19">
-        <x:v>46069.115150463</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I31" s="19">
-        <x:v>46172</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J31" s="18" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K31" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="21">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M31" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
@@ -5391,37 +5464,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C32" s="17" t="s">
-        <x:v>255</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D32" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E32" s="17" t="s">
-        <x:v>259</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F32" s="17" t="s">
-        <x:v>260</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="G32" s="17" t="s">
-        <x:v>261</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="H32" s="19">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I32" s="19">
-        <x:v>46070</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K32" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L32" s="21">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M32" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
@@ -5429,37 +5502,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C33" s="17" t="s">
-        <x:v>255</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D33" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E33" s="17" t="s">
-        <x:v>262</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="F33" s="17" t="s">
-        <x:v>263</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G33" s="17" t="s">
-        <x:v>264</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="H33" s="19">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I33" s="19">
-        <x:v>45751</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J33" s="18" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K33" s="20" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="21">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M33" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5467,37 +5540,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C34" s="17" t="s">
-        <x:v>70</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D34" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E34" s="17" t="s">
-        <x:v>265</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="F34" s="17" t="s">
-        <x:v>266</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="G34" s="17" t="s">
-        <x:v>267</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H34" s="19">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I34" s="19">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J34" s="18" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K34" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L34" s="21">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M34" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
@@ -5505,37 +5578,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C35" s="17" t="s">
-        <x:v>268</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D35" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E35" s="17" t="s">
-        <x:v>269</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="F35" s="17" t="s">
-        <x:v>270</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="G35" s="17" t="s">
-        <x:v>271</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="H35" s="19">
-        <x:v>46069.121724537</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I35" s="19">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J35" s="18" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K35" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L35" s="21">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M35" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
@@ -5543,95 +5616,95 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C36" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D36" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E36" s="17" t="s">
-        <x:v>273</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F36" s="17" t="s">
-        <x:v>274</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="G36" s="17" t="s">
-        <x:v>275</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="H36" s="19">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I36" s="19">
-        <x:v>46095</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J36" s="18" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K36" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L36" s="21">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M36" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B37" s="17" t="s">
-        <x:v>75</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C37" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D37" s="18" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E37" s="17" t="s">
-        <x:v>277</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="F37" s="17" t="s">
-        <x:v>278</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="G37" s="17" t="s">
-        <x:v>279</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="H37" s="19">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I37" s="19">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J37" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K37" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="21">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M37" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B38" s="17" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C38" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D38" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E38" s="17" t="s">
-        <x:v>280</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="F38" s="17" t="s">
-        <x:v>281</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="G38" s="17" t="s">
-        <x:v>282</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H38" s="19">
         <x:v>46085.16625</x:v>
@@ -5654,22 +5727,22 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B39" s="17" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C39" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D39" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E39" s="17" t="s">
-        <x:v>283</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="F39" s="17" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="G39" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="H39" s="19">
         <x:v>46085.1709143519</x:v>
@@ -5692,37 +5765,37 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B40" s="17" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C40" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D40" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E40" s="17" t="s">
-        <x:v>286</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F40" s="17" t="s">
-        <x:v>287</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G40" s="17" t="s">
-        <x:v>288</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="H40" s="19">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I40" s="19">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J40" s="18" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K40" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="21">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M40" s="17" t="s">
         <x:v>25</x:v>
@@ -5730,382 +5803,409 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B41" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C41" s="17" t="s">
-        <x:v>289</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D41" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E41" s="17" t="s">
-        <x:v>290</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F41" s="17" t="s">
-        <x:v>291</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="G41" s="17" t="s">
-        <x:v>292</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="H41" s="19">
-        <x:v>46084.1579513889</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I41" s="19">
-        <x:v>46145</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J41" s="18" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K41" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="21">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M41" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B42" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C42" s="17" t="s">
-        <x:v>212</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D42" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E42" s="17" t="s">
-        <x:v>293</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F42" s="17" t="s">
-        <x:v>294</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="G42" s="17" t="s">
-        <x:v>295</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H42" s="19">
-        <x:v>46084.1080324074</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I42" s="19">
-        <x:v>46103</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J42" s="18" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K42" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L42" s="21">
-        <x:v>46097.2478125</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M42" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B43" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C43" s="17" t="s">
-        <x:v>296</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D43" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E43" s="17" t="s">
-        <x:v>297</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F43" s="17" t="s">
-        <x:v>298</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="G43" s="17" t="s">
-        <x:v>299</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H43" s="19">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I43" s="19">
-        <x:v>46084</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J43" s="18" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K43" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L43" s="21">
-        <x:v>46083.104224537</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M43" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B44" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C44" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="D44" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E44" s="17" t="s">
-        <x:v>300</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="F44" s="17" t="s">
-        <x:v>301</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="G44" s="17" t="s">
-        <x:v>302</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="H44" s="19">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I44" s="19">
-        <x:v>46098</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J44" s="18" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K44" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="21">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M44" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B45" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C45" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D45" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E45" s="17" t="s">
-        <x:v>303</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F45" s="17" t="s">
-        <x:v>304</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="G45" s="17" t="s">
-        <x:v>305</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="H45" s="19">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I45" s="19">
-        <x:v>46097</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J45" s="18" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K45" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="21">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M45" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B46" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C46" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D46" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E46" s="17" t="s">
-        <x:v>306</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F46" s="17" t="s">
-        <x:v>307</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="G46" s="17" t="s">
-        <x:v>308</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="H46" s="19">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I46" s="19">
-        <x:v>46104</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J46" s="18" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K46" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L46" s="21">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M46" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B47" s="17" t="s">
-        <x:v>139</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C47" s="17" t="s">
-        <x:v>309</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D47" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E47" s="17" t="s">
-        <x:v>310</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F47" s="17" t="s">
-        <x:v>311</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="G47" s="17" t="s">
-        <x:v>312</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="H47" s="19">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I47" s="19">
-        <x:v>45997</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J47" s="18" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K47" s="20" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="21">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M47" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B48" s="17" t="s">
-        <x:v>139</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C48" s="17" t="s">
-        <x:v>313</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E48" s="17" t="s">
-        <x:v>314</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="F48" s="17" t="s">
-        <x:v>315</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="G48" s="17" t="s">
-        <x:v>316</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="H48" s="19">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46098.2908796296</x:v>
       </x:c>
       <x:c r="I48" s="19">
-        <x:v>46094</x:v>
+        <x:v>45997</x:v>
       </x:c>
       <x:c r="J48" s="18" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511858</x:v>
       </x:c>
       <x:c r="K48" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L48" s="21">
-        <x:v>46093.3109375</x:v>
+        <x:v>46098.3188657407</x:v>
       </x:c>
       <x:c r="M48" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B49" s="17" t="s">
-        <x:v>139</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C49" s="17" t="s">
-        <x:v>317</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D49" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E49" s="17" t="s">
-        <x:v>318</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="F49" s="17" t="s">
-        <x:v>319</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="G49" s="17" t="s">
-        <x:v>320</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="H49" s="19">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46092.9637847222</x:v>
       </x:c>
       <x:c r="I49" s="19">
-        <x:v>46084</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J49" s="18" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1511219</x:v>
       </x:c>
       <x:c r="K49" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L49" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M49" s="17" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B50" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C50" s="17" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="D50" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E50" s="17" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="F50" s="17" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="G50" s="17" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="H50" s="19">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I50" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J50" s="18" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K50" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L50" s="21">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M49" s="17" t="s">
+      <x:c r="M50" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B52" s="22" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="C52" s="23" t="s"/>
-      <x:c r="D52" s="23" t="s"/>
-      <x:c r="E52" s="24" t="s"/>
-      <x:c r="F52" s="24" t="s"/>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B53" s="25" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C53" s="26" t="s"/>
-      <x:c r="D53" s="26" t="s"/>
-      <x:c r="E53" s="26" t="s"/>
-      <x:c r="F53" s="27" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C54" s="29" t="s"/>
-      <x:c r="D54" s="29" t="s"/>
-      <x:c r="E54" s="29" t="s"/>
-      <x:c r="F54" s="30" t="n">
-        <x:v>3</x:v>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B53" s="22" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C53" s="23" t="s"/>
+      <x:c r="D53" s="23" t="s"/>
+      <x:c r="E53" s="24" t="s"/>
+      <x:c r="F53" s="24" t="s"/>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B54" s="25" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C54" s="26" t="s"/>
+      <x:c r="D54" s="26" t="s"/>
+      <x:c r="E54" s="26" t="s"/>
+      <x:c r="F54" s="27" t="s">
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
       <x:c r="B55" s="28" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C55" s="29" t="s"/>
       <x:c r="D55" s="29" t="s"/>
@@ -6116,60 +6216,70 @@
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
       <x:c r="B56" s="28" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C56" s="29" t="s"/>
       <x:c r="D56" s="29" t="s"/>
       <x:c r="E56" s="29" t="s"/>
       <x:c r="F56" s="30" t="n">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
       <x:c r="B57" s="28" t="s">
-        <x:v>75</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C57" s="29" t="s"/>
       <x:c r="D57" s="29" t="s"/>
       <x:c r="E57" s="29" t="s"/>
       <x:c r="F57" s="30" t="n">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
       <x:c r="B58" s="28" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C58" s="29" t="s"/>
       <x:c r="D58" s="29" t="s"/>
       <x:c r="E58" s="29" t="s"/>
       <x:c r="F58" s="30" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="18" customHeight="1">
       <x:c r="B59" s="28" t="s">
-        <x:v>139</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C59" s="29" t="s"/>
       <x:c r="D59" s="29" t="s"/>
       <x:c r="E59" s="29" t="s"/>
       <x:c r="F59" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B60" s="28" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C60" s="29" t="s"/>
+      <x:c r="D60" s="29" t="s"/>
+      <x:c r="E60" s="29" t="s"/>
+      <x:c r="F60" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B60" s="31" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C60" s="32" t="s"/>
-      <x:c r="D60" s="32" t="s"/>
-      <x:c r="E60" s="32" t="s"/>
-      <x:c r="F60" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B61" s="31" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C61" s="32" t="s"/>
+      <x:c r="D61" s="32" t="s"/>
+      <x:c r="E61" s="32" t="s"/>
+      <x:c r="F61" s="33" t="n">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7108,8 +7218,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B52:F52"/>
-    <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B53:F53"/>
     <x:mergeCell ref="B54:E54"/>
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
@@ -7117,6 +7226,7 @@
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
     <x:mergeCell ref="B60:E60"/>
+    <x:mergeCell ref="B61:E61"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="330">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="334">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -700,6 +700,24 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -709,15 +727,6 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -727,15 +736,6 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -784,6 +784,18 @@
     <x:t>43A-3-2026-1159-651</x:t>
   </x:si>
   <x:si>
+    <x:t>MOBILECRAZE TELECOM INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NO. 6 PUREGOLD BLDG. SAN PABLO COLAGO AVE, SAN ROQUE, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1113-757</x:t>
+  </x:si>
+  <x:si>
     <x:t>ONE DOTCOM CELL INC.</x:t>
   </x:si>
   <x:si>
@@ -892,6 +904,15 @@
     <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
     <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -899,15 +920,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-0002C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1170-469</x:t>
   </x:si>
   <x:si>
     <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
@@ -5061,19 +5073,19 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46133</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
         <x:v>191</x:v>
@@ -5137,19 +5149,19 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
         <x:v>191</x:v>
@@ -5175,19 +5187,19 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="H24" s="19">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46035</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
         <x:v>191</x:v>
@@ -5365,19 +5377,19 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="H29" s="19">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46073.1541087963</x:v>
       </x:c>
       <x:c r="I29" s="19">
-        <x:v>46100</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511248</x:v>
       </x:c>
       <x:c r="K29" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L29" s="21">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46099.1583912037</x:v>
       </x:c>
       <x:c r="M29" s="17" t="s">
         <x:v>191</x:v>
@@ -5403,19 +5415,19 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="H30" s="19">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I30" s="19">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K30" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L30" s="21">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M30" s="17" t="s">
         <x:v>191</x:v>
@@ -5432,28 +5444,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E31" s="17" t="s">
-        <x:v>250</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F31" s="17" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G31" s="17" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H31" s="19">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I31" s="19">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J31" s="18" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K31" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="21">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M31" s="17" t="s">
         <x:v>191</x:v>
@@ -5464,13 +5476,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C32" s="17" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D32" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E32" s="17" t="s">
-        <x:v>265</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="F32" s="17" t="s">
         <x:v>266</x:v>
@@ -5479,19 +5491,19 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="H32" s="19">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I32" s="19">
-        <x:v>45751</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K32" s="20" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L32" s="21">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M32" s="17" t="s">
         <x:v>191</x:v>
@@ -5502,34 +5514,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C33" s="17" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D33" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E33" s="17" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F33" s="17" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="G33" s="17" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="H33" s="19">
-        <x:v>46069.115150463</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I33" s="19">
-        <x:v>46172</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J33" s="18" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K33" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L33" s="21">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M33" s="17" t="s">
         <x:v>191</x:v>
@@ -5540,34 +5552,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C34" s="17" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D34" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E34" s="17" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F34" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G34" s="17" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="H34" s="19">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I34" s="19">
-        <x:v>46070</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J34" s="18" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K34" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L34" s="21">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M34" s="17" t="s">
         <x:v>191</x:v>
@@ -5578,34 +5590,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C35" s="17" t="s">
-        <x:v>70</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D35" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E35" s="17" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F35" s="17" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="G35" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="H35" s="19">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I35" s="19">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J35" s="18" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K35" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L35" s="21">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M35" s="17" t="s">
         <x:v>191</x:v>
@@ -5616,7 +5628,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C36" s="17" t="s">
-        <x:v>277</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D36" s="18" t="s">
         <x:v>54</x:v>
@@ -5631,19 +5643,19 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="H36" s="19">
-        <x:v>46069.121724537</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I36" s="19">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J36" s="18" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K36" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L36" s="21">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M36" s="17" t="s">
         <x:v>191</x:v>
@@ -5669,33 +5681,33 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="H37" s="19">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I37" s="19">
-        <x:v>46095</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J37" s="18" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K37" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="21">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M37" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B38" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C38" s="17" t="s">
         <x:v>285</x:v>
       </x:c>
       <x:c r="D38" s="18" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E38" s="17" t="s">
         <x:v>286</x:v>
@@ -5707,22 +5719,22 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="H38" s="19">
-        <x:v>46085.16625</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I38" s="19">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J38" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K38" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="21">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M38" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -5730,34 +5742,34 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C39" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D39" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E39" s="17" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F39" s="17" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="G39" s="17" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="H39" s="19">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I39" s="19">
-        <x:v>46085.1709375</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J39" s="18" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K39" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="21">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M39" s="17" t="s">
         <x:v>25</x:v>
@@ -5768,19 +5780,19 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C40" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D40" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E40" s="17" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F40" s="17" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="G40" s="17" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="H40" s="19">
         <x:v>46085.1627430556</x:v>
@@ -5806,34 +5818,34 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C41" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D41" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E41" s="17" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="F41" s="17" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G41" s="17" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="H41" s="19">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I41" s="19">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J41" s="18" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K41" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="21">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M41" s="17" t="s">
         <x:v>25</x:v>
@@ -5841,13 +5853,13 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B42" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C42" s="17" t="s">
-        <x:v>298</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D42" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E42" s="17" t="s">
         <x:v>299</x:v>
@@ -5859,22 +5871,22 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="H42" s="19">
-        <x:v>46084.1579513889</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I42" s="19">
-        <x:v>46145</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J42" s="18" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K42" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L42" s="21">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M42" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
@@ -5882,34 +5894,34 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C43" s="17" t="s">
-        <x:v>217</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="D43" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E43" s="17" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F43" s="17" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="G43" s="17" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="H43" s="19">
-        <x:v>46084.1080324074</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I43" s="19">
-        <x:v>46103</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J43" s="18" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K43" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L43" s="21">
-        <x:v>46097.2478125</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M43" s="17" t="s">
         <x:v>191</x:v>
@@ -5920,7 +5932,7 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C44" s="17" t="s">
-        <x:v>305</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D44" s="18" t="s">
         <x:v>54</x:v>
@@ -5935,22 +5947,22 @@
         <x:v>308</x:v>
       </x:c>
       <x:c r="H44" s="19">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I44" s="19">
-        <x:v>46084</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J44" s="18" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K44" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="21">
-        <x:v>46083.104224537</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M44" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
@@ -5958,34 +5970,34 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C45" s="17" t="s">
-        <x:v>281</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="D45" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E45" s="17" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F45" s="17" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="G45" s="17" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="H45" s="19">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I45" s="19">
-        <x:v>46098</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J45" s="18" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K45" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="21">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M45" s="17" t="s">
         <x:v>85</x:v>
@@ -5996,34 +6008,34 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C46" s="17" t="s">
-        <x:v>281</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D46" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E46" s="17" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="F46" s="17" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="G46" s="17" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="H46" s="19">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I46" s="19">
-        <x:v>46097</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J46" s="18" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K46" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L46" s="21">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M46" s="17" t="s">
         <x:v>85</x:v>
@@ -6034,34 +6046,34 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C47" s="17" t="s">
-        <x:v>281</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D47" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E47" s="17" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="F47" s="17" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="G47" s="17" t="s">
-        <x:v>317</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="H47" s="19">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I47" s="19">
-        <x:v>46104</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J47" s="18" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K47" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="21">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M47" s="17" t="s">
         <x:v>85</x:v>
@@ -6069,10 +6081,10 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B48" s="17" t="s">
-        <x:v>144</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C48" s="17" t="s">
-        <x:v>318</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
         <x:v>54</x:v>
@@ -6087,19 +6099,19 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="H48" s="19">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I48" s="19">
-        <x:v>45997</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J48" s="18" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K48" s="20" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L48" s="21">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M48" s="17" t="s">
         <x:v>85</x:v>
@@ -6125,22 +6137,22 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="H49" s="19">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46098.2908796296</x:v>
       </x:c>
       <x:c r="I49" s="19">
-        <x:v>46094</x:v>
+        <x:v>45997</x:v>
       </x:c>
       <x:c r="J49" s="18" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511858</x:v>
       </x:c>
       <x:c r="K49" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L49" s="21">
-        <x:v>46093.3109375</x:v>
+        <x:v>46098.3188657407</x:v>
       </x:c>
       <x:c r="M49" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
@@ -6163,60 +6175,87 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="H50" s="19">
-        <x:v>46083.0936111111</x:v>
+        <x:v>46092.9637847222</x:v>
       </x:c>
       <x:c r="I50" s="19">
-        <x:v>46084</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J50" s="18" t="n">
-        <x:v>1507892</x:v>
+        <x:v>1511219</x:v>
       </x:c>
       <x:c r="K50" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L50" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M50" s="17" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B51" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C51" s="17" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="D51" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E51" s="17" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="F51" s="17" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="G51" s="17" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="H51" s="19">
+        <x:v>46083.0936111111</x:v>
+      </x:c>
+      <x:c r="I51" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J51" s="18" t="n">
+        <x:v>1507892</x:v>
+      </x:c>
+      <x:c r="K51" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L51" s="21">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M50" s="17" t="s">
+      <x:c r="M51" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="22" t="s">
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B54" s="22" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C53" s="23" t="s"/>
-      <x:c r="D53" s="23" t="s"/>
-      <x:c r="E53" s="24" t="s"/>
-      <x:c r="F53" s="24" t="s"/>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B54" s="25" t="s">
+      <x:c r="C54" s="23" t="s"/>
+      <x:c r="D54" s="23" t="s"/>
+      <x:c r="E54" s="24" t="s"/>
+      <x:c r="F54" s="24" t="s"/>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B55" s="25" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C54" s="26" t="s"/>
-      <x:c r="D54" s="26" t="s"/>
-      <x:c r="E54" s="26" t="s"/>
-      <x:c r="F54" s="27" t="s">
+      <x:c r="C55" s="26" t="s"/>
+      <x:c r="D55" s="26" t="s"/>
+      <x:c r="E55" s="26" t="s"/>
+      <x:c r="F55" s="27" t="s">
         <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C55" s="29" t="s"/>
-      <x:c r="D55" s="29" t="s"/>
-      <x:c r="E55" s="29" t="s"/>
-      <x:c r="F55" s="30" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="18" customHeight="1">
       <x:c r="B56" s="28" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C56" s="29" t="s"/>
       <x:c r="D56" s="29" t="s"/>
@@ -6227,60 +6266,70 @@
     </x:row>
     <x:row r="57" spans="1:28" ht="18" customHeight="1">
       <x:c r="B57" s="28" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C57" s="29" t="s"/>
       <x:c r="D57" s="29" t="s"/>
       <x:c r="E57" s="29" t="s"/>
       <x:c r="F57" s="30" t="n">
-        <x:v>24</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
       <x:c r="B58" s="28" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C58" s="29" t="s"/>
       <x:c r="D58" s="29" t="s"/>
       <x:c r="E58" s="29" t="s"/>
       <x:c r="F58" s="30" t="n">
-        <x:v>4</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="18" customHeight="1">
       <x:c r="B59" s="28" t="s">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C59" s="29" t="s"/>
       <x:c r="D59" s="29" t="s"/>
       <x:c r="E59" s="29" t="s"/>
       <x:c r="F59" s="30" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="18" customHeight="1">
       <x:c r="B60" s="28" t="s">
-        <x:v>144</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C60" s="29" t="s"/>
       <x:c r="D60" s="29" t="s"/>
       <x:c r="E60" s="29" t="s"/>
       <x:c r="F60" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B61" s="28" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C61" s="29" t="s"/>
+      <x:c r="D61" s="29" t="s"/>
+      <x:c r="E61" s="29" t="s"/>
+      <x:c r="F61" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B61" s="31" t="s">
+    <x:row r="62" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B62" s="31" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="C61" s="32" t="s"/>
-      <x:c r="D61" s="32" t="s"/>
-      <x:c r="E61" s="32" t="s"/>
-      <x:c r="F61" s="33" t="n">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C62" s="32" t="s"/>
+      <x:c r="D62" s="32" t="s"/>
+      <x:c r="E62" s="32" t="s"/>
+      <x:c r="F62" s="33" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7218,8 +7267,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B53:F53"/>
-    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B54:F54"/>
     <x:mergeCell ref="B55:E55"/>
     <x:mergeCell ref="B56:E56"/>
     <x:mergeCell ref="B57:E57"/>
@@ -7227,6 +7275,7 @@
     <x:mergeCell ref="B59:E59"/>
     <x:mergeCell ref="B60:E60"/>
     <x:mergeCell ref="B61:E61"/>
+    <x:mergeCell ref="B62:E62"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="334">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="342">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -550,6 +550,18 @@
     <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
+    <x:t>ALCALA, GLENN GUIBAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Block 2 Lot 9 Sunridge Ville Phase 1 Isarog Street, Barangay Isabang, City Of Tayabas, Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03011-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1207-652</x:t>
+  </x:si>
+  <x:si>
     <x:t>HERALD BEBIS</x:t>
   </x:si>
   <x:si>
@@ -679,6 +691,15 @@
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1155-834</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -688,18 +709,36 @@
     <x:t>43A-3-2026-1156-896</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0762</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1155-834</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
     <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
   </x:si>
   <x:si>
@@ -709,33 +748,6 @@
     <x:t>43A-2-2026-1085-453</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467-24R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1096-022</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -859,6 +871,18 @@
     <x:t>43A-3-2026-1168-173</x:t>
   </x:si>
   <x:si>
+    <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-03-0776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1201-204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -895,6 +919,24 @@
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06698-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1169-102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-0002C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1170-469</x:t>
+  </x:si>
+  <x:si>
     <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
   </x:si>
   <x:si>
@@ -904,15 +946,6 @@
     <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
-    <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-0002C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1170-469</x:t>
-  </x:si>
-  <x:si>
     <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -922,15 +955,6 @@
     <x:t>43A-3-2026-1172-434</x:t>
   </x:si>
   <x:si>
-    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRRP-ROIV-A-06698-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1169-102</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -964,6 +988,24 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1175-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
     <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -971,24 +1013,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1173-016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1175-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1176-385</x:t>
   </x:si>
   <x:si>
     <x:t>CELLBOY INC.</x:t>
@@ -4583,19 +4607,19 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46091.306099537</x:v>
+        <x:v>46100.1144675926</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46091.3107986111</x:v>
+        <x:v>46100.1505092593</x:v>
       </x:c>
       <x:c r="J8" s="14" t="n">
-        <x:v>1511778</x:v>
+        <x:v>1511906</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46091.3131828704</x:v>
+        <x:v>46100.1652777778</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>85</x:v>
@@ -4619,19 +4643,19 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H9" s="15">
-        <x:v>46093.1459375</x:v>
+        <x:v>46091.306099537</x:v>
       </x:c>
       <x:c r="I9" s="15">
-        <x:v>46093.1585185185</x:v>
+        <x:v>46091.3107986111</x:v>
       </x:c>
       <x:c r="J9" s="14" t="n">
-        <x:v>1511815</x:v>
+        <x:v>1511778</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="L9" s="15">
-        <x:v>46093.159537037</x:v>
+        <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>85</x:v>
@@ -4655,34 +4679,32 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H10" s="19">
-        <x:v>46098.0792592593</x:v>
+        <x:v>46093.1459375</x:v>
       </x:c>
       <x:c r="I10" s="19">
-        <x:v>46098.0878935185</x:v>
+        <x:v>46093.1585185185</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>1529776</x:v>
+        <x:v>1511815</x:v>
       </x:c>
       <x:c r="K10" s="20" t="n">
-        <x:v>130</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L10" s="21">
-        <x:v>46098.0997569444</x:v>
+        <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M10" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="17" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
+      <x:c r="D11" s="18" t="s"/>
       <x:c r="E11" s="17" t="s">
         <x:v>188</x:v>
       </x:c>
@@ -4693,22 +4715,22 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="H11" s="19">
-        <x:v>46090.2558217593</x:v>
+        <x:v>46098.0792592593</x:v>
       </x:c>
       <x:c r="I11" s="19">
-        <x:v>46090.2558333333</x:v>
+        <x:v>46098.0878935185</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
-        <x:v>1511203</x:v>
+        <x:v>1529776</x:v>
       </x:c>
       <x:c r="K11" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L11" s="21">
-        <x:v>46097.2890740741</x:v>
+        <x:v>46098.0997569444</x:v>
       </x:c>
       <x:c r="M11" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -4716,7 +4738,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C12" s="17" t="s">
-        <x:v>187</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D12" s="18" t="s">
         <x:v>44</x:v>
@@ -4731,10 +4753,10 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H12" s="19">
-        <x:v>46090.2418287037</x:v>
+        <x:v>46090.2558217593</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46090.2418518519</x:v>
+        <x:v>46090.2558333333</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
         <x:v>1511203</x:v>
@@ -4743,10 +4765,10 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="21">
-        <x:v>46093.3049884259</x:v>
+        <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M12" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
@@ -4754,7 +4776,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C13" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D13" s="18" t="s">
         <x:v>44</x:v>
@@ -4769,33 +4791,33 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="H13" s="19">
-        <x:v>46090.2109953704</x:v>
+        <x:v>46090.2418287037</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46090.2110069444</x:v>
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>1511204</x:v>
+        <x:v>1511203</x:v>
       </x:c>
       <x:c r="K13" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="21">
-        <x:v>46093.3080092593</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M13" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="17" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C14" s="17" t="s">
         <x:v>199</x:v>
       </x:c>
       <x:c r="D14" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E14" s="17" t="s">
         <x:v>200</x:v>
@@ -4807,22 +4829,22 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="H14" s="19">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46090.2109953704</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46100</x:v>
+        <x:v>46090.2110069444</x:v>
       </x:c>
       <x:c r="J14" s="18" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511204</x:v>
       </x:c>
       <x:c r="K14" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L14" s="21">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46093.3080092593</x:v>
       </x:c>
       <x:c r="M14" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -4830,37 +4852,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C15" s="17" t="s">
-        <x:v>199</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E15" s="17" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F15" s="17" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G15" s="17" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H15" s="19">
-        <x:v>46083.2322337963</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>1511233</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="21">
-        <x:v>46097.149525463</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M15" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -4868,37 +4890,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C16" s="17" t="s">
-        <x:v>199</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D16" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E16" s="17" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F16" s="17" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G16" s="17" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H16" s="19">
-        <x:v>46080.4532523148</x:v>
+        <x:v>46083.2322337963</x:v>
       </x:c>
       <x:c r="I16" s="19">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>1511232</x:v>
+        <x:v>1511233</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="21">
-        <x:v>46097.1461689815</x:v>
+        <x:v>46097.149525463</x:v>
       </x:c>
       <x:c r="M16" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
@@ -4906,7 +4928,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="17" t="s">
-        <x:v>209</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D17" s="18" t="s">
         <x:v>54</x:v>
@@ -4921,22 +4943,22 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H17" s="19">
-        <x:v>46083.2599189815</x:v>
+        <x:v>46080.4532523148</x:v>
       </x:c>
       <x:c r="I17" s="19">
-        <x:v>46101</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>1511237</x:v>
+        <x:v>1511232</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="21">
-        <x:v>46097.1652314815</x:v>
+        <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M17" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
@@ -4959,22 +4981,22 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="H18" s="19">
-        <x:v>46069.3514814815</x:v>
+        <x:v>46083.2599189815</x:v>
       </x:c>
       <x:c r="I18" s="19">
-        <x:v>46094</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J18" s="18" t="n">
-        <x:v>1511194</x:v>
+        <x:v>1511237</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="21">
-        <x:v>46097.2437384259</x:v>
+        <x:v>46097.1652314815</x:v>
       </x:c>
       <x:c r="M18" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -4997,22 +5019,22 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="H19" s="19">
-        <x:v>46084.0996759259</x:v>
+        <x:v>46069.3514814815</x:v>
       </x:c>
       <x:c r="I19" s="19">
         <x:v>46094</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>1511192</x:v>
+        <x:v>1511194</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="21">
-        <x:v>46097.2414583333</x:v>
+        <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M19" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -5020,19 +5042,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D20" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E20" s="17" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F20" s="17" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G20" s="17" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H20" s="19">
         <x:v>46084.0854513889</x:v>
@@ -5050,7 +5072,7 @@
         <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M20" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -5058,7 +5080,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C21" s="17" t="s">
-        <x:v>224</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D21" s="18" t="s">
         <x:v>54</x:v>
@@ -5073,22 +5095,22 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46035</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -5096,37 +5118,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C22" s="17" t="s">
-        <x:v>224</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D22" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="17" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F22" s="17" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="G22" s="17" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H22" s="19">
-        <x:v>46084.2250115741</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46144</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1511224</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46093.3804398148</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -5134,37 +5156,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="17" t="s">
-        <x:v>224</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E23" s="17" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="F23" s="17" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="G23" s="17" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46084.2250115741</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46133</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511224</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46093.3804398148</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
@@ -5172,37 +5194,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="17" t="s">
-        <x:v>224</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D24" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E24" s="17" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="F24" s="17" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G24" s="17" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="H24" s="19">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -5210,7 +5232,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C25" s="17" t="s">
-        <x:v>237</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D25" s="18" t="s">
         <x:v>54</x:v>
@@ -5225,22 +5247,22 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="H25" s="19">
-        <x:v>46069.2178703704</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46051</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>1511196</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K25" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L25" s="21">
-        <x:v>46097.2456365741</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M25" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
@@ -5263,22 +5285,22 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="H26" s="19">
-        <x:v>46073.125162037</x:v>
+        <x:v>46069.2178703704</x:v>
       </x:c>
       <x:c r="I26" s="19">
-        <x:v>45619</x:v>
+        <x:v>46051</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1511246</x:v>
+        <x:v>1511196</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
-        <x:v>11280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46099.1200231481</x:v>
+        <x:v>46097.2456365741</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
@@ -5301,22 +5323,22 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="H27" s="19">
-        <x:v>46083.2443865741</x:v>
+        <x:v>46073.125162037</x:v>
       </x:c>
       <x:c r="I27" s="19">
-        <x:v>46100</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>1511235</x:v>
+        <x:v>1511246</x:v>
       </x:c>
       <x:c r="K27" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L27" s="21">
-        <x:v>46097.1600115741</x:v>
+        <x:v>46099.1200231481</x:v>
       </x:c>
       <x:c r="M27" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
@@ -5339,22 +5361,22 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="H28" s="19">
-        <x:v>46084.1225115741</x:v>
+        <x:v>46083.2443865741</x:v>
       </x:c>
       <x:c r="I28" s="19">
-        <x:v>46172</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>1511242</x:v>
+        <x:v>1511235</x:v>
       </x:c>
       <x:c r="K28" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="21">
-        <x:v>46097.3505092593</x:v>
+        <x:v>46097.1600115741</x:v>
       </x:c>
       <x:c r="M28" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
@@ -5377,22 +5399,22 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="H29" s="19">
-        <x:v>46073.1541087963</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I29" s="19">
-        <x:v>46030</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>1511248</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K29" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="21">
-        <x:v>46099.1583912037</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M29" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
@@ -5415,22 +5437,22 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="H30" s="19">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46073.1541087963</x:v>
       </x:c>
       <x:c r="I30" s="19">
-        <x:v>46100</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511248</x:v>
       </x:c>
       <x:c r="K30" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L30" s="21">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46099.1583912037</x:v>
       </x:c>
       <x:c r="M30" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
@@ -5453,22 +5475,22 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="H31" s="19">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I31" s="19">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J31" s="18" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K31" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="21">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M31" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
@@ -5482,31 +5504,31 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E32" s="17" t="s">
-        <x:v>250</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F32" s="17" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="G32" s="17" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="H32" s="19">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I32" s="19">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K32" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L32" s="21">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M32" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
@@ -5514,13 +5536,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C33" s="17" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D33" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E33" s="17" t="s">
-        <x:v>269</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F33" s="17" t="s">
         <x:v>270</x:v>
@@ -5529,22 +5551,22 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="H33" s="19">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I33" s="19">
-        <x:v>45751</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J33" s="18" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K33" s="20" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="21">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M33" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5552,37 +5574,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C34" s="17" t="s">
-        <x:v>268</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D34" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E34" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="F34" s="17" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="G34" s="17" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="H34" s="19">
-        <x:v>46069.115150463</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I34" s="19">
-        <x:v>46172</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J34" s="18" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K34" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L34" s="21">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M34" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
@@ -5590,37 +5612,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C35" s="17" t="s">
-        <x:v>268</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D35" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E35" s="17" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="F35" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="G35" s="17" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="H35" s="19">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I35" s="19">
-        <x:v>46070</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J35" s="18" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K35" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L35" s="21">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M35" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
@@ -5628,37 +5650,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C36" s="17" t="s">
-        <x:v>70</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D36" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E36" s="17" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="F36" s="17" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="G36" s="17" t="s">
-        <x:v>280</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="H36" s="19">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I36" s="19">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J36" s="18" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K36" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L36" s="21">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M36" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
@@ -5666,7 +5688,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C37" s="17" t="s">
-        <x:v>281</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D37" s="18" t="s">
         <x:v>54</x:v>
@@ -5681,22 +5703,22 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="H37" s="19">
-        <x:v>46069.121724537</x:v>
+        <x:v>46097.4214930556</x:v>
       </x:c>
       <x:c r="I37" s="19">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J37" s="18" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511270</x:v>
       </x:c>
       <x:c r="K37" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="21">
-        <x:v>46097.3375</x:v>
+        <x:v>46100.2966666667</x:v>
       </x:c>
       <x:c r="M37" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -5704,7 +5726,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C38" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D38" s="18" t="s">
         <x:v>54</x:v>
@@ -5719,33 +5741,33 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="H38" s="19">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I38" s="19">
-        <x:v>46095</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J38" s="18" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K38" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="21">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M38" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B39" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C39" s="17" t="s">
         <x:v>289</x:v>
       </x:c>
       <x:c r="D39" s="18" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E39" s="17" t="s">
         <x:v>290</x:v>
@@ -5757,60 +5779,60 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="H39" s="19">
-        <x:v>46085.16625</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I39" s="19">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J39" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K39" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="21">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M39" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B40" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C40" s="17" t="s">
-        <x:v>289</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D40" s="18" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E40" s="17" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="F40" s="17" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="G40" s="17" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="H40" s="19">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I40" s="19">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J40" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K40" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L40" s="21">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M40" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
@@ -5818,34 +5840,34 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C41" s="17" t="s">
-        <x:v>289</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D41" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E41" s="17" t="s">
-        <x:v>296</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="F41" s="17" t="s">
-        <x:v>297</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="G41" s="17" t="s">
-        <x:v>298</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="H41" s="19">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I41" s="19">
-        <x:v>46085.1709375</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J41" s="18" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K41" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="21">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M41" s="17" t="s">
         <x:v>25</x:v>
@@ -5856,34 +5878,34 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C42" s="17" t="s">
-        <x:v>289</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D42" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E42" s="17" t="s">
-        <x:v>299</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F42" s="17" t="s">
-        <x:v>300</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="G42" s="17" t="s">
-        <x:v>301</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="H42" s="19">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I42" s="19">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J42" s="18" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K42" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L42" s="21">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M42" s="17" t="s">
         <x:v>25</x:v>
@@ -5891,78 +5913,78 @@
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B43" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C43" s="17" t="s">
-        <x:v>302</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D43" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E43" s="17" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F43" s="17" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="G43" s="17" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H43" s="19">
-        <x:v>46084.1579513889</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I43" s="19">
-        <x:v>46145</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J43" s="18" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K43" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L43" s="21">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M43" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B44" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C44" s="17" t="s">
-        <x:v>217</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D44" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E44" s="17" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F44" s="17" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="G44" s="17" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="H44" s="19">
-        <x:v>46084.1080324074</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I44" s="19">
-        <x:v>46103</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J44" s="18" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K44" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L44" s="21">
-        <x:v>46097.2478125</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M44" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
@@ -5970,37 +5992,37 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C45" s="17" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D45" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E45" s="17" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="F45" s="17" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="G45" s="17" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="H45" s="19">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I45" s="19">
-        <x:v>46084</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J45" s="18" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K45" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="21">
-        <x:v>46083.104224537</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M45" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
@@ -6008,37 +6030,37 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C46" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D46" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E46" s="17" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F46" s="17" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="G46" s="17" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="H46" s="19">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46084.1080324074</x:v>
       </x:c>
       <x:c r="I46" s="19">
-        <x:v>46098</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J46" s="18" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1511208</x:v>
       </x:c>
       <x:c r="K46" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L46" s="21">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46097.2478125</x:v>
       </x:c>
       <x:c r="M46" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
@@ -6046,34 +6068,34 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C47" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D47" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E47" s="17" t="s">
-        <x:v>316</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="F47" s="17" t="s">
-        <x:v>317</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="G47" s="17" t="s">
-        <x:v>318</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="H47" s="19">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46083.0787962963</x:v>
       </x:c>
       <x:c r="I47" s="19">
-        <x:v>46097</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J47" s="18" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1511639</x:v>
       </x:c>
       <x:c r="K47" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="21">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46083.104224537</x:v>
       </x:c>
       <x:c r="M47" s="17" t="s">
         <x:v>85</x:v>
@@ -6084,34 +6106,34 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C48" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E48" s="17" t="s">
-        <x:v>319</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F48" s="17" t="s">
-        <x:v>320</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="G48" s="17" t="s">
-        <x:v>321</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="H48" s="19">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46086.1144444444</x:v>
       </x:c>
       <x:c r="I48" s="19">
-        <x:v>46104</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J48" s="18" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1511759</x:v>
       </x:c>
       <x:c r="K48" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L48" s="21">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.2703703704</x:v>
       </x:c>
       <x:c r="M48" s="17" t="s">
         <x:v>85</x:v>
@@ -6119,37 +6141,37 @@
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B49" s="17" t="s">
-        <x:v>144</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C49" s="17" t="s">
-        <x:v>322</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D49" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E49" s="17" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F49" s="17" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="G49" s="17" t="s">
-        <x:v>325</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="H49" s="19">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46087.1643287037</x:v>
       </x:c>
       <x:c r="I49" s="19">
-        <x:v>45997</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J49" s="18" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1511760</x:v>
       </x:c>
       <x:c r="K49" s="20" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L49" s="21">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.2727777778</x:v>
       </x:c>
       <x:c r="M49" s="17" t="s">
         <x:v>85</x:v>
@@ -6157,10 +6179,10 @@
     </x:row>
     <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B50" s="17" t="s">
-        <x:v>144</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C50" s="17" t="s">
-        <x:v>326</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D50" s="18" t="s">
         <x:v>54</x:v>
@@ -6175,22 +6197,22 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="H50" s="19">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46086.0997916667</x:v>
       </x:c>
       <x:c r="I50" s="19">
-        <x:v>46094</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J50" s="18" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511758</x:v>
       </x:c>
       <x:c r="K50" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L50" s="21">
-        <x:v>46093.3109375</x:v>
+        <x:v>46090.2691087963</x:v>
       </x:c>
       <x:c r="M50" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
@@ -6213,125 +6235,199 @@
         <x:v>333</x:v>
       </x:c>
       <x:c r="H51" s="19">
+        <x:v>46098.2908796296</x:v>
+      </x:c>
+      <x:c r="I51" s="19">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J51" s="18" t="n">
+        <x:v>1511858</x:v>
+      </x:c>
+      <x:c r="K51" s="20" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L51" s="21">
+        <x:v>46098.3188657407</x:v>
+      </x:c>
+      <x:c r="M51" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B52" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C52" s="17" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="D52" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E52" s="17" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="F52" s="17" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="G52" s="17" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="H52" s="19">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I52" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J52" s="18" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K52" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L52" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M52" s="17" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B53" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C53" s="17" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D53" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E53" s="17" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="F53" s="17" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="G53" s="17" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="H53" s="19">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I51" s="19">
+      <x:c r="I53" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J51" s="18" t="n">
+      <x:c r="J53" s="18" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K51" s="20" t="n">
+      <x:c r="K53" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L51" s="21">
+      <x:c r="L53" s="21">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M51" s="17" t="s">
+      <x:c r="M53" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B54" s="22" t="s">
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B56" s="22" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C54" s="23" t="s"/>
-      <x:c r="D54" s="23" t="s"/>
-      <x:c r="E54" s="24" t="s"/>
-      <x:c r="F54" s="24" t="s"/>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B55" s="25" t="s">
+      <x:c r="C56" s="23" t="s"/>
+      <x:c r="D56" s="23" t="s"/>
+      <x:c r="E56" s="24" t="s"/>
+      <x:c r="F56" s="24" t="s"/>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B57" s="25" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C55" s="26" t="s"/>
-      <x:c r="D55" s="26" t="s"/>
-      <x:c r="E55" s="26" t="s"/>
-      <x:c r="F55" s="27" t="s">
+      <x:c r="C57" s="26" t="s"/>
+      <x:c r="D57" s="26" t="s"/>
+      <x:c r="E57" s="26" t="s"/>
+      <x:c r="F57" s="27" t="s">
         <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C56" s="29" t="s"/>
-      <x:c r="D56" s="29" t="s"/>
-      <x:c r="E56" s="29" t="s"/>
-      <x:c r="F56" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="28" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C57" s="29" t="s"/>
-      <x:c r="D57" s="29" t="s"/>
-      <x:c r="E57" s="29" t="s"/>
-      <x:c r="F57" s="30" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="18" customHeight="1">
       <x:c r="B58" s="28" t="s">
-        <x:v>52</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C58" s="29" t="s"/>
       <x:c r="D58" s="29" t="s"/>
       <x:c r="E58" s="29" t="s"/>
       <x:c r="F58" s="30" t="n">
-        <x:v>25</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="18" customHeight="1">
       <x:c r="B59" s="28" t="s">
-        <x:v>80</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C59" s="29" t="s"/>
       <x:c r="D59" s="29" t="s"/>
       <x:c r="E59" s="29" t="s"/>
       <x:c r="F59" s="30" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="18" customHeight="1">
       <x:c r="B60" s="28" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C60" s="29" t="s"/>
       <x:c r="D60" s="29" t="s"/>
       <x:c r="E60" s="29" t="s"/>
       <x:c r="F60" s="30" t="n">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:28" ht="18" customHeight="1">
       <x:c r="B61" s="28" t="s">
-        <x:v>144</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C61" s="29" t="s"/>
       <x:c r="D61" s="29" t="s"/>
       <x:c r="E61" s="29" t="s"/>
       <x:c r="F61" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B62" s="28" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C62" s="29" t="s"/>
+      <x:c r="D62" s="29" t="s"/>
+      <x:c r="E62" s="29" t="s"/>
+      <x:c r="F62" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B63" s="28" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C63" s="29" t="s"/>
+      <x:c r="D63" s="29" t="s"/>
+      <x:c r="E63" s="29" t="s"/>
+      <x:c r="F63" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B62" s="31" t="s">
+    <x:row r="64" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B64" s="31" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="C62" s="32" t="s"/>
-      <x:c r="D62" s="32" t="s"/>
-      <x:c r="E62" s="32" t="s"/>
-      <x:c r="F62" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C64" s="32" t="s"/>
+      <x:c r="D64" s="32" t="s"/>
+      <x:c r="E64" s="32" t="s"/>
+      <x:c r="F64" s="33" t="n">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
     <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7267,15 +7363,15 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B54:F54"/>
-    <x:mergeCell ref="B55:E55"/>
-    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B56:F56"/>
     <x:mergeCell ref="B57:E57"/>
     <x:mergeCell ref="B58:E58"/>
     <x:mergeCell ref="B59:E59"/>
     <x:mergeCell ref="B60:E60"/>
     <x:mergeCell ref="B61:E61"/>
     <x:mergeCell ref="B62:E62"/>
+    <x:mergeCell ref="B63:E63"/>
+    <x:mergeCell ref="B64:E64"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="342">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -562,6 +562,24 @@
     <x:t>43A-3-2026-1207-652</x:t>
   </x:si>
   <x:si>
+    <x:t>CHRISTOPHER I. PALLESCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Block 3 Lot 12 Phase 1 Lavanya Subdivision, Bacao 2, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03055C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1210-786</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-02054C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1209-851</x:t>
+  </x:si>
+  <x:si>
     <x:t>HERALD BEBIS</x:t>
   </x:si>
   <x:si>
@@ -601,6 +619,18 @@
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06915-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1178-478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -610,18 +640,6 @@
     <x:t>43A-3-2026-1179-857</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-06915-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1178-478</x:t>
-  </x:si>
-  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -679,6 +697,18 @@
     <x:t>CELLBLITZ MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>LG05 SM MARKETMALL, BUROL I, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-010R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1089-192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY BATANGAS, PALLOCAN KANLURAN, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -721,6 +751,33 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1111-408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -730,24 +787,6 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -763,6 +802,15 @@
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>SM CENTER ILLUSTRE AVE, DISTRICT IV, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1097-702</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -820,6 +868,18 @@
     <x:t>43A-3-2026-1153-796</x:t>
   </x:si>
   <x:si>
+    <x:t>PHONEVILLE MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sm City Taytay Manila East Road Sm City Taytay Manila East Road, Dolores, Taytay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-03-0774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1202-217</x:t>
+  </x:si>
+  <x:si>
     <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -880,9 +940,6 @@
     <x:t>43A-3-2026-1201-204</x:t>
   </x:si>
   <x:si>
-    <x:t>Caesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -904,6 +961,15 @@
     <x:t>43A-2-2026-1084-395</x:t>
   </x:si>
   <x:si>
+    <x:t>AYALA MALLS SERIN JUNCTION EAST, SILANG, Tagaytay City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-20-01-0883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1087-228</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -986,6 +1052,15 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1146-031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#95 CZ13 SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-02-2011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1163-392</x:t>
   </x:si>
   <x:si>
     <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
@@ -4643,22 +4718,22 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H9" s="15">
-        <x:v>46091.306099537</x:v>
+        <x:v>46100.3734490741</x:v>
       </x:c>
       <x:c r="I9" s="15">
-        <x:v>46091.3107986111</x:v>
+        <x:v>46100.388599537</x:v>
       </x:c>
       <x:c r="J9" s="14" t="n">
-        <x:v>1511778</x:v>
+        <x:v>1529812</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
-        <x:v>230</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="15">
-        <x:v>46091.3131828704</x:v>
+        <x:v>46100.3957175926</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
@@ -4666,35 +4741,35 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="17" t="s">
-        <x:v>183</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D10" s="18" t="s"/>
       <x:c r="E10" s="17" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
       <x:c r="H10" s="19">
-        <x:v>46093.1459375</x:v>
+        <x:v>46100.365787037</x:v>
       </x:c>
       <x:c r="I10" s="19">
-        <x:v>46093.1585185185</x:v>
+        <x:v>46100.3731712963</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>1511815</x:v>
+        <x:v>1529809</x:v>
       </x:c>
       <x:c r="K10" s="20" t="n">
-        <x:v>230</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="21">
-        <x:v>46093.159537037</x:v>
+        <x:v>46100.3868981482</x:v>
       </x:c>
       <x:c r="M10" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -4702,111 +4777,107 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s"/>
       <x:c r="E11" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>190</x:v>
-      </x:c>
       <x:c r="H11" s="19">
-        <x:v>46098.0792592593</x:v>
+        <x:v>46091.306099537</x:v>
       </x:c>
       <x:c r="I11" s="19">
-        <x:v>46098.0878935185</x:v>
+        <x:v>46091.3107986111</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
-        <x:v>1529776</x:v>
+        <x:v>1511778</x:v>
       </x:c>
       <x:c r="K11" s="20" t="n">
-        <x:v>130</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L11" s="21">
-        <x:v>46098.0997569444</x:v>
+        <x:v>46091.3131828704</x:v>
       </x:c>
       <x:c r="M11" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="17" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="17" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="17" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
+      <x:c r="G12" s="17" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>194</x:v>
-      </x:c>
       <x:c r="H12" s="19">
-        <x:v>46090.2558217593</x:v>
+        <x:v>46093.1459375</x:v>
       </x:c>
       <x:c r="I12" s="19">
-        <x:v>46090.2558333333</x:v>
+        <x:v>46093.1585185185</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
-        <x:v>1511203</x:v>
+        <x:v>1511815</x:v>
       </x:c>
       <x:c r="K12" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L12" s="21">
-        <x:v>46097.2890740741</x:v>
+        <x:v>46093.159537037</x:v>
       </x:c>
       <x:c r="M12" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="17" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="17" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s"/>
       <x:c r="E13" s="17" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>198</x:v>
-      </x:c>
       <x:c r="H13" s="19">
-        <x:v>46090.2418287037</x:v>
+        <x:v>46098.0792592593</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46090.2418518519</x:v>
+        <x:v>46098.0878935185</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>1511203</x:v>
+        <x:v>1529776</x:v>
       </x:c>
       <x:c r="K13" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L13" s="21">
-        <x:v>46093.3049884259</x:v>
+        <x:v>46098.0997569444</x:v>
       </x:c>
       <x:c r="M13" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
@@ -4814,113 +4885,113 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C14" s="17" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D14" s="18" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E14" s="17" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>202</x:v>
-      </x:c>
       <x:c r="H14" s="19">
-        <x:v>46090.2109953704</x:v>
+        <x:v>46090.2418287037</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46090.2110069444</x:v>
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J14" s="18" t="n">
-        <x:v>1511204</x:v>
+        <x:v>1511203</x:v>
       </x:c>
       <x:c r="K14" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L14" s="21">
-        <x:v>46093.3080092593</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M14" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="17" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="17" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
+      <x:c r="G15" s="17" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>206</x:v>
-      </x:c>
       <x:c r="H15" s="19">
-        <x:v>46083.2380439815</x:v>
+        <x:v>46090.2558217593</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46100</x:v>
+        <x:v>46090.2558333333</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>1511234</x:v>
+        <x:v>1511203</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="21">
-        <x:v>46097.1564351852</x:v>
+        <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M15" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="17" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="17" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D16" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E16" s="17" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="F16" s="17" t="s">
+      <x:c r="G16" s="17" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>209</x:v>
-      </x:c>
       <x:c r="H16" s="19">
-        <x:v>46083.2322337963</x:v>
+        <x:v>46090.2109953704</x:v>
       </x:c>
       <x:c r="I16" s="19">
-        <x:v>46112</x:v>
+        <x:v>46090.2110069444</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>1511233</x:v>
+        <x:v>1511204</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="21">
-        <x:v>46097.149525463</x:v>
+        <x:v>46093.3080092593</x:v>
       </x:c>
       <x:c r="M16" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
@@ -4928,7 +4999,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="17" t="s">
-        <x:v>203</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D17" s="18" t="s">
         <x:v>54</x:v>
@@ -4943,22 +5014,22 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H17" s="19">
-        <x:v>46080.4532523148</x:v>
+        <x:v>46083.2380439815</x:v>
       </x:c>
       <x:c r="I17" s="19">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>1511232</x:v>
+        <x:v>1511234</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="21">
-        <x:v>46097.1461689815</x:v>
+        <x:v>46097.1564351852</x:v>
       </x:c>
       <x:c r="M17" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
@@ -4966,37 +5037,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="17" t="s">
-        <x:v>213</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D18" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E18" s="17" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="F18" s="17" t="s">
+      <x:c r="G18" s="17" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>216</x:v>
-      </x:c>
       <x:c r="H18" s="19">
-        <x:v>46083.2599189815</x:v>
+        <x:v>46083.2322337963</x:v>
       </x:c>
       <x:c r="I18" s="19">
-        <x:v>46101</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J18" s="18" t="n">
-        <x:v>1511237</x:v>
+        <x:v>1511233</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="21">
-        <x:v>46097.1652314815</x:v>
+        <x:v>46097.149525463</x:v>
       </x:c>
       <x:c r="M18" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -5004,37 +5075,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="17" t="s">
-        <x:v>217</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D19" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E19" s="17" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>220</x:v>
-      </x:c>
       <x:c r="H19" s="19">
-        <x:v>46069.3514814815</x:v>
+        <x:v>46080.4532523148</x:v>
       </x:c>
       <x:c r="I19" s="19">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>1511194</x:v>
+        <x:v>1511232</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="21">
-        <x:v>46097.2437384259</x:v>
+        <x:v>46097.1461689815</x:v>
       </x:c>
       <x:c r="M19" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -5042,37 +5113,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="D20" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E20" s="17" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>224</x:v>
-      </x:c>
       <x:c r="H20" s="19">
-        <x:v>46084.0854513889</x:v>
+        <x:v>46083.2599189815</x:v>
       </x:c>
       <x:c r="I20" s="19">
-        <x:v>46144</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>1511225</x:v>
+        <x:v>1511237</x:v>
       </x:c>
       <x:c r="K20" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="21">
-        <x:v>46093.3956365741</x:v>
+        <x:v>46097.1652314815</x:v>
       </x:c>
       <x:c r="M20" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -5080,37 +5151,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C21" s="17" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D21" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E21" s="17" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="F21" s="17" t="s">
+      <x:c r="G21" s="17" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G21" s="17" t="s">
+      <x:c r="H21" s="19">
+        <x:v>46069.2785648148</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511276</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46100.3884027778</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -5118,37 +5189,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C22" s="17" t="s">
-        <x:v>228</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D22" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="17" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="F22" s="17" t="s">
+      <x:c r="G22" s="17" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>231</x:v>
-      </x:c>
       <x:c r="H22" s="19">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46069.3514814815</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46100</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511194</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -5156,7 +5227,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="17" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
         <x:v>54</x:v>
@@ -5171,22 +5242,22 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46084.2250115741</x:v>
+        <x:v>46084.0854513889</x:v>
       </x:c>
       <x:c r="I23" s="19">
         <x:v>46144</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1511224</x:v>
+        <x:v>1511225</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46093.3804398148</x:v>
+        <x:v>46093.3956365741</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
@@ -5194,7 +5265,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="17" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D24" s="18" t="s">
         <x:v>54</x:v>
@@ -5209,22 +5280,22 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="H24" s="19">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46084.0996759259</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46133</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511192</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2414583333</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -5232,37 +5303,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C25" s="17" t="s">
-        <x:v>228</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D25" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E25" s="17" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="F25" s="17" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G25" s="17" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="H25" s="19">
-        <x:v>46069.1542013889</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46035</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>1511206</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K25" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="21">
-        <x:v>46097.2466550926</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M25" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
@@ -5270,7 +5341,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C26" s="17" t="s">
-        <x:v>241</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D26" s="18" t="s">
         <x:v>54</x:v>
@@ -5285,22 +5356,22 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="H26" s="19">
-        <x:v>46069.2178703704</x:v>
+        <x:v>46069.1542013889</x:v>
       </x:c>
       <x:c r="I26" s="19">
-        <x:v>46051</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1511196</x:v>
+        <x:v>1511206</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46097.2456365741</x:v>
+        <x:v>46097.2466550926</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
@@ -5308,37 +5379,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C27" s="17" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D27" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E27" s="17" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="F27" s="17" t="s">
+      <x:c r="G27" s="17" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="G27" s="17" t="s">
-        <x:v>248</x:v>
-      </x:c>
       <x:c r="H27" s="19">
-        <x:v>46073.125162037</x:v>
+        <x:v>46073.1441087963</x:v>
       </x:c>
       <x:c r="I27" s="19">
-        <x:v>45619</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>1511246</x:v>
+        <x:v>1511278</x:v>
       </x:c>
       <x:c r="K27" s="20" t="n">
-        <x:v>11280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L27" s="21">
-        <x:v>46099.1200231481</x:v>
+        <x:v>46100.4005439815</x:v>
       </x:c>
       <x:c r="M27" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
@@ -5346,37 +5417,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C28" s="17" t="s">
-        <x:v>249</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D28" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E28" s="17" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="F28" s="17" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="G28" s="17" t="s">
-        <x:v>252</x:v>
-      </x:c>
       <x:c r="H28" s="19">
-        <x:v>46083.2443865741</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I28" s="19">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>1511235</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K28" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="21">
-        <x:v>46097.1600115741</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M28" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
@@ -5384,37 +5455,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C29" s="17" t="s">
-        <x:v>253</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D29" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E29" s="17" t="s">
-        <x:v>254</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F29" s="17" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G29" s="17" t="s">
-        <x:v>256</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="H29" s="19">
-        <x:v>46084.1225115741</x:v>
+        <x:v>46084.2250115741</x:v>
       </x:c>
       <x:c r="I29" s="19">
-        <x:v>46172</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>1511242</x:v>
+        <x:v>1511224</x:v>
       </x:c>
       <x:c r="K29" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="21">
-        <x:v>46097.3505092593</x:v>
+        <x:v>46093.3804398148</x:v>
       </x:c>
       <x:c r="M29" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
@@ -5422,37 +5493,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C30" s="17" t="s">
-        <x:v>257</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D30" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E30" s="17" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F30" s="17" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G30" s="17" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H30" s="19">
-        <x:v>46073.1541087963</x:v>
+        <x:v>46069.2178703704</x:v>
       </x:c>
       <x:c r="I30" s="19">
-        <x:v>46030</x:v>
+        <x:v>46051</x:v>
       </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>1511248</x:v>
+        <x:v>1511196</x:v>
       </x:c>
       <x:c r="K30" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L30" s="21">
-        <x:v>46099.1583912037</x:v>
+        <x:v>46097.2456365741</x:v>
       </x:c>
       <x:c r="M30" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
@@ -5460,37 +5531,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C31" s="17" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D31" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E31" s="17" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F31" s="17" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="G31" s="17" t="s">
-        <x:v>264</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="H31" s="19">
-        <x:v>46083.2521064815</x:v>
+        <x:v>46069.3717592593</x:v>
       </x:c>
       <x:c r="I31" s="19">
-        <x:v>46100</x:v>
+        <x:v>46066</x:v>
       </x:c>
       <x:c r="J31" s="18" t="n">
-        <x:v>1511236</x:v>
+        <x:v>1511274</x:v>
       </x:c>
       <x:c r="K31" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L31" s="21">
-        <x:v>46097.1628935185</x:v>
+        <x:v>46100.3754861111</x:v>
       </x:c>
       <x:c r="M31" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
@@ -5498,37 +5569,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C32" s="17" t="s">
-        <x:v>265</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D32" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E32" s="17" t="s">
-        <x:v>266</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F32" s="17" t="s">
-        <x:v>267</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G32" s="17" t="s">
-        <x:v>268</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H32" s="19">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46073.125162037</x:v>
       </x:c>
       <x:c r="I32" s="19">
-        <x:v>46094</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511246</x:v>
       </x:c>
       <x:c r="K32" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L32" s="21">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46099.1200231481</x:v>
       </x:c>
       <x:c r="M32" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
@@ -5536,37 +5607,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C33" s="17" t="s">
-        <x:v>269</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D33" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E33" s="17" t="s">
-        <x:v>254</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F33" s="17" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="G33" s="17" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="H33" s="19">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46083.2443865741</x:v>
       </x:c>
       <x:c r="I33" s="19">
-        <x:v>46102</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J33" s="18" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511235</x:v>
       </x:c>
       <x:c r="K33" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="21">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.1600115741</x:v>
       </x:c>
       <x:c r="M33" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5574,37 +5645,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C34" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D34" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E34" s="17" t="s">
-        <x:v>273</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="F34" s="17" t="s">
-        <x:v>274</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="G34" s="17" t="s">
-        <x:v>275</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="H34" s="19">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46084.1225115741</x:v>
       </x:c>
       <x:c r="I34" s="19">
-        <x:v>45751</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J34" s="18" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511242</x:v>
       </x:c>
       <x:c r="K34" s="20" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L34" s="21">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.3505092593</x:v>
       </x:c>
       <x:c r="M34" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
@@ -5612,37 +5683,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C35" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D35" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E35" s="17" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F35" s="17" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G35" s="17" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="F35" s="17" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="G35" s="17" t="s">
-        <x:v>278</x:v>
-      </x:c>
       <x:c r="H35" s="19">
-        <x:v>46069.115150463</x:v>
+        <x:v>46073.1541087963</x:v>
       </x:c>
       <x:c r="I35" s="19">
-        <x:v>46172</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J35" s="18" t="n">
-        <x:v>1511241</x:v>
+        <x:v>1511248</x:v>
       </x:c>
       <x:c r="K35" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L35" s="21">
-        <x:v>46097.3433796296</x:v>
+        <x:v>46099.1583912037</x:v>
       </x:c>
       <x:c r="M35" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
@@ -5650,37 +5721,37 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C36" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D36" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E36" s="17" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="F36" s="17" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="F36" s="17" t="s">
+      <x:c r="G36" s="17" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="G36" s="17" t="s">
-        <x:v>281</x:v>
-      </x:c>
       <x:c r="H36" s="19">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46083.2521064815</x:v>
       </x:c>
       <x:c r="I36" s="19">
-        <x:v>46070</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J36" s="18" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511236</x:v>
       </x:c>
       <x:c r="K36" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L36" s="21">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.1628935185</x:v>
       </x:c>
       <x:c r="M36" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
@@ -5688,7 +5759,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C37" s="17" t="s">
-        <x:v>70</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D37" s="18" t="s">
         <x:v>54</x:v>
@@ -5703,22 +5774,22 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="H37" s="19">
-        <x:v>46097.4214930556</x:v>
+        <x:v>46097.4788425926</x:v>
       </x:c>
       <x:c r="I37" s="19">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J37" s="18" t="n">
-        <x:v>1511270</x:v>
+        <x:v>1511271</x:v>
       </x:c>
       <x:c r="K37" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="21">
-        <x:v>46100.2966666667</x:v>
+        <x:v>46100.29875</x:v>
       </x:c>
       <x:c r="M37" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -5726,7 +5797,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C38" s="17" t="s">
-        <x:v>70</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D38" s="18" t="s">
         <x:v>54</x:v>
@@ -5741,22 +5812,22 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="H38" s="19">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I38" s="19">
-        <x:v>46100</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J38" s="18" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K38" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="21">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M38" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -5770,31 +5841,31 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E39" s="17" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="F39" s="17" t="s">
+      <x:c r="G39" s="17" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="G39" s="17" t="s">
-        <x:v>292</x:v>
-      </x:c>
       <x:c r="H39" s="19">
-        <x:v>46069.121724537</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I39" s="19">
-        <x:v>46157</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J39" s="18" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K39" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="21">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M39" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
@@ -5802,300 +5873,300 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C40" s="17" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D40" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E40" s="17" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="F40" s="17" t="s">
+      <x:c r="G40" s="17" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="G40" s="17" t="s">
-        <x:v>296</x:v>
-      </x:c>
       <x:c r="H40" s="19">
-        <x:v>46086.1064814815</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I40" s="19">
-        <x:v>46095</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J40" s="18" t="n">
-        <x:v>1511761</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K40" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L40" s="21">
-        <x:v>46090.2765740741</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M40" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B41" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C41" s="17" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D41" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E41" s="17" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F41" s="17" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="D41" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E41" s="17" t="s">
+      <x:c r="G41" s="17" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="F41" s="17" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="G41" s="17" t="s">
-        <x:v>300</x:v>
-      </x:c>
       <x:c r="H41" s="19">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46069.115150463</x:v>
       </x:c>
       <x:c r="I41" s="19">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J41" s="18" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511241</x:v>
       </x:c>
       <x:c r="K41" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L41" s="21">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46097.3433796296</x:v>
       </x:c>
       <x:c r="M41" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B42" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C42" s="17" t="s">
-        <x:v>297</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D42" s="18" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E42" s="17" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F42" s="17" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="G42" s="17" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="F42" s="17" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="G42" s="17" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="H42" s="19">
-        <x:v>46085.1627430556</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I42" s="19">
-        <x:v>46085.1627546296</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J42" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K42" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L42" s="21">
-        <x:v>46090.3453472222</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M42" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B43" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C43" s="17" t="s">
-        <x:v>297</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D43" s="18" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E43" s="17" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F43" s="17" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="G43" s="17" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="F43" s="17" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G43" s="17" t="s">
-        <x:v>306</x:v>
-      </x:c>
       <x:c r="H43" s="19">
-        <x:v>46085.16625</x:v>
+        <x:v>46097.4214930556</x:v>
       </x:c>
       <x:c r="I43" s="19">
-        <x:v>46085.1662615741</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J43" s="18" t="n">
-        <x:v>1507966</x:v>
+        <x:v>1511270</x:v>
       </x:c>
       <x:c r="K43" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L43" s="21">
-        <x:v>46090.3437268519</x:v>
+        <x:v>46100.2966666667</x:v>
       </x:c>
       <x:c r="M43" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B44" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C44" s="17" t="s">
-        <x:v>297</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D44" s="18" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E44" s="17" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="F44" s="17" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="G44" s="17" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="F44" s="17" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="G44" s="17" t="s">
-        <x:v>309</x:v>
-      </x:c>
       <x:c r="H44" s="19">
-        <x:v>46085.1709143519</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I44" s="19">
-        <x:v>46085.1709375</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J44" s="18" t="n">
-        <x:v>1507965</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K44" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="21">
-        <x:v>46090.3336921296</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M44" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B45" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C45" s="17" t="s">
-        <x:v>310</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="D45" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E45" s="17" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F45" s="17" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="G45" s="17" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="F45" s="17" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="G45" s="17" t="s">
-        <x:v>313</x:v>
-      </x:c>
       <x:c r="H45" s="19">
-        <x:v>46084.1579513889</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I45" s="19">
-        <x:v>46145</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J45" s="18" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K45" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="21">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M45" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B46" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C46" s="17" t="s">
-        <x:v>221</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="D46" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E46" s="17" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="F46" s="17" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="G46" s="17" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="F46" s="17" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="G46" s="17" t="s">
-        <x:v>316</x:v>
-      </x:c>
       <x:c r="H46" s="19">
-        <x:v>46084.1080324074</x:v>
+        <x:v>46069.2327893519</x:v>
       </x:c>
       <x:c r="I46" s="19">
-        <x:v>46103</x:v>
+        <x:v>46049</x:v>
       </x:c>
       <x:c r="J46" s="18" t="n">
-        <x:v>1511208</x:v>
+        <x:v>1511275</x:v>
       </x:c>
       <x:c r="K46" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L46" s="21">
-        <x:v>46097.2478125</x:v>
+        <x:v>46100.3816782407</x:v>
       </x:c>
       <x:c r="M46" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B47" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C47" s="17" t="s">
-        <x:v>317</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="D47" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E47" s="17" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F47" s="17" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="G47" s="17" t="s">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="F47" s="17" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="G47" s="17" t="s">
-        <x:v>320</x:v>
-      </x:c>
       <x:c r="H47" s="19">
-        <x:v>46083.0787962963</x:v>
+        <x:v>46086.1064814815</x:v>
       </x:c>
       <x:c r="I47" s="19">
-        <x:v>46084</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J47" s="18" t="n">
-        <x:v>1511639</x:v>
+        <x:v>1511761</x:v>
       </x:c>
       <x:c r="K47" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="21">
-        <x:v>46083.104224537</x:v>
+        <x:v>46090.2765740741</x:v>
       </x:c>
       <x:c r="M47" s="17" t="s">
         <x:v>85</x:v>
@@ -6103,339 +6174,635 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B48" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C48" s="17" t="s">
-        <x:v>293</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="D48" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E48" s="17" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="F48" s="17" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="F48" s="17" t="s">
+      <x:c r="G48" s="17" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="G48" s="17" t="s">
-        <x:v>323</x:v>
-      </x:c>
       <x:c r="H48" s="19">
-        <x:v>46086.1144444444</x:v>
+        <x:v>46084.3419444444</x:v>
       </x:c>
       <x:c r="I48" s="19">
-        <x:v>46097</x:v>
+        <x:v>46084.3419560185</x:v>
       </x:c>
       <x:c r="J48" s="18" t="n">
-        <x:v>1511759</x:v>
+        <x:v>1507967</x:v>
       </x:c>
       <x:c r="K48" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L48" s="21">
-        <x:v>46090.2703703704</x:v>
+        <x:v>46090.3480902778</x:v>
       </x:c>
       <x:c r="M48" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B49" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C49" s="17" t="s">
-        <x:v>293</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="D49" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E49" s="17" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="F49" s="17" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="F49" s="17" t="s">
+      <x:c r="G49" s="17" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="G49" s="17" t="s">
-        <x:v>326</x:v>
-      </x:c>
       <x:c r="H49" s="19">
-        <x:v>46087.1643287037</x:v>
+        <x:v>46085.1627430556</x:v>
       </x:c>
       <x:c r="I49" s="19">
-        <x:v>46104</x:v>
+        <x:v>46085.1627546296</x:v>
       </x:c>
       <x:c r="J49" s="18" t="n">
-        <x:v>1511760</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K49" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L49" s="21">
-        <x:v>46090.2727777778</x:v>
+        <x:v>46090.3453472222</x:v>
       </x:c>
       <x:c r="M49" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B50" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C50" s="17" t="s">
-        <x:v>293</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="D50" s="18" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E50" s="17" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="F50" s="17" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="F50" s="17" t="s">
+      <x:c r="G50" s="17" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="G50" s="17" t="s">
-        <x:v>329</x:v>
-      </x:c>
       <x:c r="H50" s="19">
-        <x:v>46086.0997916667</x:v>
+        <x:v>46085.16625</x:v>
       </x:c>
       <x:c r="I50" s="19">
-        <x:v>46098</x:v>
+        <x:v>46085.1662615741</x:v>
       </x:c>
       <x:c r="J50" s="18" t="n">
-        <x:v>1511758</x:v>
+        <x:v>1507966</x:v>
       </x:c>
       <x:c r="K50" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L50" s="21">
-        <x:v>46090.2691087963</x:v>
+        <x:v>46090.3437268519</x:v>
       </x:c>
       <x:c r="M50" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B51" s="17" t="s">
-        <x:v>144</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C51" s="17" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="D51" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E51" s="17" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F51" s="17" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="D51" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E51" s="17" t="s">
+      <x:c r="G51" s="17" t="s">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="F51" s="17" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="G51" s="17" t="s">
-        <x:v>333</x:v>
-      </x:c>
       <x:c r="H51" s="19">
-        <x:v>46098.2908796296</x:v>
+        <x:v>46085.1709143519</x:v>
       </x:c>
       <x:c r="I51" s="19">
-        <x:v>45997</x:v>
+        <x:v>46085.1709375</x:v>
       </x:c>
       <x:c r="J51" s="18" t="n">
-        <x:v>1511858</x:v>
+        <x:v>1507965</x:v>
       </x:c>
       <x:c r="K51" s="20" t="n">
-        <x:v>2550</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L51" s="21">
-        <x:v>46098.3188657407</x:v>
+        <x:v>46090.3336921296</x:v>
       </x:c>
       <x:c r="M51" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B52" s="17" t="s">
-        <x:v>144</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C52" s="17" t="s">
-        <x:v>334</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="D52" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E52" s="17" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="F52" s="17" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="G52" s="17" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="F52" s="17" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="G52" s="17" t="s">
-        <x:v>337</x:v>
-      </x:c>
       <x:c r="H52" s="19">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I52" s="19">
-        <x:v>46094</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J52" s="18" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K52" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L52" s="21">
-        <x:v>46093.3109375</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M52" s="17" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B53" s="17" t="s">
-        <x:v>144</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C53" s="17" t="s">
-        <x:v>338</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D53" s="18" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E53" s="17" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="F53" s="17" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="G53" s="17" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="H53" s="19">
+        <x:v>46084.1080324074</x:v>
+      </x:c>
+      <x:c r="I53" s="19">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J53" s="18" t="n">
+        <x:v>1511208</x:v>
+      </x:c>
+      <x:c r="K53" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L53" s="21">
+        <x:v>46097.2478125</x:v>
+      </x:c>
+      <x:c r="M53" s="17" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B54" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C54" s="17" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="F53" s="17" t="s">
+      <x:c r="D54" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E54" s="17" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="G53" s="17" t="s">
+      <x:c r="F54" s="17" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="H53" s="19">
+      <x:c r="G54" s="17" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="H54" s="19">
+        <x:v>46083.0787962963</x:v>
+      </x:c>
+      <x:c r="I54" s="19">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J54" s="18" t="n">
+        <x:v>1511639</x:v>
+      </x:c>
+      <x:c r="K54" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L54" s="21">
+        <x:v>46083.104224537</x:v>
+      </x:c>
+      <x:c r="M54" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B55" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C55" s="17" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="D55" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E55" s="17" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="F55" s="17" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="G55" s="17" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="H55" s="19">
+        <x:v>46084.1627430556</x:v>
+      </x:c>
+      <x:c r="I55" s="19">
+        <x:v>46060</x:v>
+      </x:c>
+      <x:c r="J55" s="18" t="n">
+        <x:v>1511277</x:v>
+      </x:c>
+      <x:c r="K55" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L55" s="21">
+        <x:v>46100.3929282407</x:v>
+      </x:c>
+      <x:c r="M55" s="17" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B56" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C56" s="17" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D56" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E56" s="17" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="F56" s="17" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="G56" s="17" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="H56" s="19">
+        <x:v>46086.1144444444</x:v>
+      </x:c>
+      <x:c r="I56" s="19">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J56" s="18" t="n">
+        <x:v>1511759</x:v>
+      </x:c>
+      <x:c r="K56" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L56" s="21">
+        <x:v>46090.2703703704</x:v>
+      </x:c>
+      <x:c r="M56" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B57" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C57" s="17" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D57" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E57" s="17" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="F57" s="17" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="G57" s="17" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="H57" s="19">
+        <x:v>46087.1643287037</x:v>
+      </x:c>
+      <x:c r="I57" s="19">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J57" s="18" t="n">
+        <x:v>1511760</x:v>
+      </x:c>
+      <x:c r="K57" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L57" s="21">
+        <x:v>46090.2727777778</x:v>
+      </x:c>
+      <x:c r="M57" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B58" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C58" s="17" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D58" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E58" s="17" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="F58" s="17" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="G58" s="17" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="H58" s="19">
+        <x:v>46086.0997916667</x:v>
+      </x:c>
+      <x:c r="I58" s="19">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J58" s="18" t="n">
+        <x:v>1511758</x:v>
+      </x:c>
+      <x:c r="K58" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L58" s="21">
+        <x:v>46090.2691087963</x:v>
+      </x:c>
+      <x:c r="M58" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B59" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C59" s="17" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="D59" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E59" s="17" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="F59" s="17" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="G59" s="17" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="H59" s="19">
+        <x:v>46098.2908796296</x:v>
+      </x:c>
+      <x:c r="I59" s="19">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J59" s="18" t="n">
+        <x:v>1511858</x:v>
+      </x:c>
+      <x:c r="K59" s="20" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L59" s="21">
+        <x:v>46098.3188657407</x:v>
+      </x:c>
+      <x:c r="M59" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B60" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C60" s="17" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="D60" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E60" s="17" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="F60" s="17" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="G60" s="17" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="H60" s="19">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I60" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J60" s="18" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K60" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L60" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M60" s="17" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B61" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C61" s="17" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="D61" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E61" s="17" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="F61" s="17" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="G61" s="17" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="H61" s="19">
         <x:v>46083.0936111111</x:v>
       </x:c>
-      <x:c r="I53" s="19">
+      <x:c r="I61" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J53" s="18" t="n">
+      <x:c r="J61" s="18" t="n">
         <x:v>1507892</x:v>
       </x:c>
-      <x:c r="K53" s="20" t="n">
+      <x:c r="K61" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L53" s="21">
+      <x:c r="L61" s="21">
         <x:v>46083.1543634259</x:v>
       </x:c>
-      <x:c r="M53" s="17" t="s">
+      <x:c r="M61" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B56" s="22" t="s">
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B64" s="22" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C56" s="23" t="s"/>
-      <x:c r="D56" s="23" t="s"/>
-      <x:c r="E56" s="24" t="s"/>
-      <x:c r="F56" s="24" t="s"/>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B57" s="25" t="s">
+      <x:c r="C64" s="23" t="s"/>
+      <x:c r="D64" s="23" t="s"/>
+      <x:c r="E64" s="24" t="s"/>
+      <x:c r="F64" s="24" t="s"/>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B65" s="25" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C57" s="26" t="s"/>
-      <x:c r="D57" s="26" t="s"/>
-      <x:c r="E57" s="26" t="s"/>
-      <x:c r="F57" s="27" t="s">
+      <x:c r="C65" s="26" t="s"/>
+      <x:c r="D65" s="26" t="s"/>
+      <x:c r="E65" s="26" t="s"/>
+      <x:c r="F65" s="27" t="s">
         <x:v>172</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="28" t="s">
+    <x:row r="66" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B66" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C58" s="29" t="s"/>
-      <x:c r="D58" s="29" t="s"/>
-      <x:c r="E58" s="29" t="s"/>
-      <x:c r="F58" s="30" t="n">
+      <x:c r="C66" s="29" t="s"/>
+      <x:c r="D66" s="29" t="s"/>
+      <x:c r="E66" s="29" t="s"/>
+      <x:c r="F66" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B67" s="28" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C67" s="29" t="s"/>
+      <x:c r="D67" s="29" t="s"/>
+      <x:c r="E67" s="29" t="s"/>
+      <x:c r="F67" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B68" s="28" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C68" s="29" t="s"/>
+      <x:c r="D68" s="29" t="s"/>
+      <x:c r="E68" s="29" t="s"/>
+      <x:c r="F68" s="30" t="n">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B69" s="28" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C69" s="29" t="s"/>
+      <x:c r="D69" s="29" t="s"/>
+      <x:c r="E69" s="29" t="s"/>
+      <x:c r="F69" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B59" s="28" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C59" s="29" t="s"/>
-      <x:c r="D59" s="29" t="s"/>
-      <x:c r="E59" s="29" t="s"/>
-      <x:c r="F59" s="30" t="n">
+    <x:row r="70" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B70" s="28" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C70" s="29" t="s"/>
+      <x:c r="D70" s="29" t="s"/>
+      <x:c r="E70" s="29" t="s"/>
+      <x:c r="F70" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B71" s="28" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C71" s="29" t="s"/>
+      <x:c r="D71" s="29" t="s"/>
+      <x:c r="E71" s="29" t="s"/>
+      <x:c r="F71" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B60" s="28" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C60" s="29" t="s"/>
-      <x:c r="D60" s="29" t="s"/>
-      <x:c r="E60" s="29" t="s"/>
-      <x:c r="F60" s="30" t="n">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B61" s="28" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C61" s="29" t="s"/>
-      <x:c r="D61" s="29" t="s"/>
-      <x:c r="E61" s="29" t="s"/>
-      <x:c r="F61" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B62" s="28" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C62" s="29" t="s"/>
-      <x:c r="D62" s="29" t="s"/>
-      <x:c r="E62" s="29" t="s"/>
-      <x:c r="F62" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B63" s="28" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C63" s="29" t="s"/>
-      <x:c r="D63" s="29" t="s"/>
-      <x:c r="E63" s="29" t="s"/>
-      <x:c r="F63" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B64" s="31" t="s">
+    <x:row r="72" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B72" s="31" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="C64" s="32" t="s"/>
-      <x:c r="D64" s="32" t="s"/>
-      <x:c r="E64" s="32" t="s"/>
-      <x:c r="F64" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C72" s="32" t="s"/>
+      <x:c r="D72" s="32" t="s"/>
+      <x:c r="E72" s="32" t="s"/>
+      <x:c r="F72" s="33" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
     <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7363,15 +7730,15 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B56:F56"/>
-    <x:mergeCell ref="B57:E57"/>
-    <x:mergeCell ref="B58:E58"/>
-    <x:mergeCell ref="B59:E59"/>
-    <x:mergeCell ref="B60:E60"/>
-    <x:mergeCell ref="B61:E61"/>
-    <x:mergeCell ref="B62:E62"/>
-    <x:mergeCell ref="B63:E63"/>
-    <x:mergeCell ref="B64:E64"/>
+    <x:mergeCell ref="B64:F64"/>
+    <x:mergeCell ref="B65:E65"/>
+    <x:mergeCell ref="B66:E66"/>
+    <x:mergeCell ref="B67:E67"/>
+    <x:mergeCell ref="B68:E68"/>
+    <x:mergeCell ref="B69:E69"/>
+    <x:mergeCell ref="B70:E70"/>
+    <x:mergeCell ref="B71:E71"/>
+    <x:mergeCell ref="B72:E72"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -85,6 +85,9 @@
     <x:t>43A-2-2026-1081-190</x:t>
   </x:si>
   <x:si>
+    <x:t>1506161</x:t>
+  </x:si>
+  <x:si>
     <x:t>Nerrisa Manalo</x:t>
   </x:si>
   <x:si>
@@ -100,6 +103,9 @@
     <x:t>43A-2-2026-1076-698</x:t>
   </x:si>
   <x:si>
+    <x:t>1507747</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ricardo Natividad</x:t>
   </x:si>
   <x:si>
@@ -115,6 +121,9 @@
     <x:t>43A-2-2026-1082-997</x:t>
   </x:si>
   <x:si>
+    <x:t>1506159</x:t>
+  </x:si>
+  <x:si>
     <x:t>JORETO S. GABAT</x:t>
   </x:si>
   <x:si>
@@ -127,6 +136,9 @@
     <x:t>43A-2-2026-1103-424</x:t>
   </x:si>
   <x:si>
+    <x:t>1507783</x:t>
+  </x:si>
+  <x:si>
     <x:t>RASEL C. FERRER</x:t>
   </x:si>
   <x:si>
@@ -139,6 +151,9 @@
     <x:t>43A-2-2026-1072-268</x:t>
   </x:si>
   <x:si>
+    <x:t>1507682</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROFIEN F. NUÑEZ</x:t>
   </x:si>
   <x:si>
@@ -151,6 +166,9 @@
     <x:t>43A-2-2026-1061-611</x:t>
   </x:si>
   <x:si>
+    <x:t>1507672</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -169,6 +187,9 @@
     <x:t>43A-2-2026-1080-857</x:t>
   </x:si>
   <x:si>
+    <x:t>1505803</x:t>
+  </x:si>
+  <x:si>
     <x:t>Deniel Puyo</x:t>
   </x:si>
   <x:si>
@@ -199,6 +220,9 @@
     <x:t>43A-2-2026-1078-427</x:t>
   </x:si>
   <x:si>
+    <x:t>1505804</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILETOOLS VENTURE INC</x:t>
   </x:si>
   <x:si>
@@ -211,6 +235,9 @@
     <x:t>43A-2-2026-1079-778</x:t>
   </x:si>
   <x:si>
+    <x:t>1505805</x:t>
+  </x:si>
+  <x:si>
     <x:t>STAR APPLIANCE CENTER, INC.</x:t>
   </x:si>
   <x:si>
@@ -223,6 +250,9 @@
     <x:t>43A-2-2026-1107-513</x:t>
   </x:si>
   <x:si>
+    <x:t>1507784</x:t>
+  </x:si>
+  <x:si>
     <x:t>STAR APPLIANCE CENTER, INC. - (BRANCH)</x:t>
   </x:si>
   <x:si>
@@ -235,6 +265,9 @@
     <x:t>43A-2-2026-1106-738</x:t>
   </x:si>
   <x:si>
+    <x:t>1507785</x:t>
+  </x:si>
+  <x:si>
     <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
   </x:si>
   <x:si>
@@ -247,6 +280,9 @@
     <x:t>43A-2-2026-1070-812</x:t>
   </x:si>
   <x:si>
+    <x:t>1511010</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ceasar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -265,6 +301,9 @@
     <x:t>43A-2-2026-1114-391</x:t>
   </x:si>
   <x:si>
+    <x:t>1507791</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -280,6 +319,9 @@
     <x:t>43A-2-2026-1135-273</x:t>
   </x:si>
   <x:si>
+    <x:t>1511622</x:t>
+  </x:si>
+  <x:si>
     <x:t>Adora Mercado</x:t>
   </x:si>
   <x:si>
@@ -295,6 +337,9 @@
     <x:t>43A-2-2026-1134-784</x:t>
   </x:si>
   <x:si>
+    <x:t>1511627</x:t>
+  </x:si>
+  <x:si>
     <x:t>STAY YOUNG ONLINE TRADING OPC</x:t>
   </x:si>
   <x:si>
@@ -307,6 +352,9 @@
     <x:t>43A-2-2026-1059-113</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve"> 1507657</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -322,6 +370,9 @@
     <x:t>43A-2-2026-1104-763</x:t>
   </x:si>
   <x:si>
+    <x:t>1507790</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOM CELLPHONE &amp; ACCESSORIES CENTER</x:t>
   </x:si>
   <x:si>
@@ -334,6 +385,9 @@
     <x:t>43A-2-2026-1139-014</x:t>
   </x:si>
   <x:si>
+    <x:t>1511623</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOM CELLPHONE &amp; ACCESSORIES CENTER  (TECNO STORE)</x:t>
   </x:si>
   <x:si>
@@ -346,6 +400,9 @@
     <x:t>43A-2-2026-1129-801</x:t>
   </x:si>
   <x:si>
+    <x:t>1511631</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOM CELLPHONE AND ACCESSORIES CENTER (HONOR STORE )</x:t>
   </x:si>
   <x:si>
@@ -358,6 +415,9 @@
     <x:t>43A-2-2026-1128-999</x:t>
   </x:si>
   <x:si>
+    <x:t>1511630</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC.</x:t>
   </x:si>
   <x:si>
@@ -370,6 +430,9 @@
     <x:t>43A-2-2026-1136-850</x:t>
   </x:si>
   <x:si>
+    <x:t>1511626</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC. (GREENTELCOM STORE)</x:t>
   </x:si>
   <x:si>
@@ -382,6 +445,9 @@
     <x:t>43A-2-2026-1142-741</x:t>
   </x:si>
   <x:si>
+    <x:t>1511635</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC. (HONOR STORE )</x:t>
   </x:si>
   <x:si>
@@ -421,6 +487,9 @@
     <x:t>43A-2-2026-1138-367</x:t>
   </x:si>
   <x:si>
+    <x:t>1511624</x:t>
+  </x:si>
+  <x:si>
     <x:t>GREENTELCOMMUNICATIONS TRADING INC.(GREENTELCOM STORE)</x:t>
   </x:si>
   <x:si>
@@ -430,6 +499,9 @@
     <x:t>43A-2-2026-1137-243</x:t>
   </x:si>
   <x:si>
+    <x:t>1511625</x:t>
+  </x:si>
+  <x:si>
     <x:t>IT AVENUE GENERAL MERCHANDISE</x:t>
   </x:si>
   <x:si>
@@ -442,6 +514,9 @@
     <x:t>43A-2-2026-1121-512</x:t>
   </x:si>
   <x:si>
+    <x:t>1511576</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -457,6 +532,9 @@
     <x:t>43A-2-2026-1067-112</x:t>
   </x:si>
   <x:si>
+    <x:t>1510925</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -472,6 +550,9 @@
     <x:t>43A-2-2026-1074-021</x:t>
   </x:si>
   <x:si>
+    <x:t>1507743</x:t>
+  </x:si>
+  <x:si>
     <x:t>GIZMOTECH CORPORATION</x:t>
   </x:si>
   <x:si>
@@ -484,6 +565,9 @@
     <x:t>43A-2-2026-1099-127</x:t>
   </x:si>
   <x:si>
+    <x:t>1511502</x:t>
+  </x:si>
+  <x:si>
     <x:t>GIZMOTECH CORPORATION - GAMES AND GADGETS</x:t>
   </x:si>
   <x:si>
@@ -496,6 +580,9 @@
     <x:t>43A-2-2026-1075-295</x:t>
   </x:si>
   <x:si>
+    <x:t>1507742</x:t>
+  </x:si>
+  <x:si>
     <x:t>MUNERIS INCORPORATED (SST LAPTOP)</x:t>
   </x:si>
   <x:si>
@@ -508,6 +595,9 @@
     <x:t>43A-2-2026-1123-290</x:t>
   </x:si>
   <x:si>
+    <x:t>1507839</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station Permit to PURCHASE/POSSESS (DOMESTIC Trade)</x:t>
   </x:si>
   <x:si>
@@ -523,6 +613,9 @@
     <x:t>43A-2-2026-1140-568</x:t>
   </x:si>
   <x:si>
+    <x:t>1507884</x:t>
+  </x:si>
+  <x:si>
     <x:t>RODOLFO C. ABAD JR.</x:t>
   </x:si>
   <x:si>
@@ -535,6 +628,9 @@
     <x:t>43A-2-2026-1141-720</x:t>
   </x:si>
   <x:si>
+    <x:t>1507883</x:t>
+  </x:si>
+  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -562,6 +658,9 @@
     <x:t>43A-3-2026-1207-652</x:t>
   </x:si>
   <x:si>
+    <x:t>1511906</x:t>
+  </x:si>
+  <x:si>
     <x:t>CHRISTOPHER I. PALLESCO</x:t>
   </x:si>
   <x:si>
@@ -574,12 +673,18 @@
     <x:t>43A-3-2026-1210-786</x:t>
   </x:si>
   <x:si>
+    <x:t>1529812</x:t>
+  </x:si>
+  <x:si>
     <x:t>DD-AT-02054C-2026</x:t>
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1209-851</x:t>
   </x:si>
   <x:si>
+    <x:t>1529809</x:t>
+  </x:si>
+  <x:si>
     <x:t>HERALD BEBIS</x:t>
   </x:si>
   <x:si>
@@ -592,6 +697,9 @@
     <x:t>43A-3-2026-1189-403</x:t>
   </x:si>
   <x:si>
+    <x:t>1511778</x:t>
+  </x:si>
+  <x:si>
     <x:t>JAKE C. PASILAN</x:t>
   </x:si>
   <x:si>
@@ -604,6 +712,9 @@
     <x:t>43A-3-2026-1198-002</x:t>
   </x:si>
   <x:si>
+    <x:t>1511815</x:t>
+  </x:si>
+  <x:si>
     <x:t>RUBEN C. SESCON</x:t>
   </x:si>
   <x:si>
@@ -616,6 +727,9 @@
     <x:t>43A-3-2026-1203-366</x:t>
   </x:si>
   <x:si>
+    <x:t>1529776</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
@@ -628,6 +742,9 @@
     <x:t>43A-3-2026-1178-478</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve"> 1511203</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cesar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -640,6 +757,9 @@
     <x:t>43A-3-2026-1179-857</x:t>
   </x:si>
   <x:si>
+    <x:t>1511203</x:t>
+  </x:si>
+  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -652,6 +772,9 @@
     <x:t>43A-3-2026-1177-099</x:t>
   </x:si>
   <x:si>
+    <x:t>1511204</x:t>
+  </x:si>
+  <x:si>
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -664,6 +787,9 @@
     <x:t>43A-3-2026-1151-716</x:t>
   </x:si>
   <x:si>
+    <x:t>1511234</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -673,6 +799,9 @@
     <x:t>43A-3-2026-1150-325</x:t>
   </x:si>
   <x:si>
+    <x:t>1511233</x:t>
+  </x:si>
+  <x:si>
     <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
   </x:si>
   <x:si>
@@ -682,6 +811,9 @@
     <x:t>43A-2-2026-1144-933</x:t>
   </x:si>
   <x:si>
+    <x:t>1511232</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -694,6 +826,9 @@
     <x:t>43A-3-2026-1154-964</x:t>
   </x:si>
   <x:si>
+    <x:t>1511237</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLBLITZ MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -706,6 +841,9 @@
     <x:t>43A-2-2026-1089-192</x:t>
   </x:si>
   <x:si>
+    <x:t>1511276</x:t>
+  </x:si>
+  <x:si>
     <x:t>Caesar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -718,6 +856,9 @@
     <x:t>43A-2-2026-1095-163</x:t>
   </x:si>
   <x:si>
+    <x:t>1511194</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
@@ -730,6 +871,9 @@
     <x:t>43A-3-2026-1155-834</x:t>
   </x:si>
   <x:si>
+    <x:t>1511225</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -739,6 +883,9 @@
     <x:t>43A-3-2026-1156-896</x:t>
   </x:si>
   <x:si>
+    <x:t>1511192</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -751,6 +898,9 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
+    <x:t>1511193</x:t>
+  </x:si>
+  <x:si>
     <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
   </x:si>
   <x:si>
@@ -760,6 +910,9 @@
     <x:t>43A-2-2026-1085-453</x:t>
   </x:si>
   <x:si>
+    <x:t>1511206</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
   </x:si>
   <x:si>
@@ -769,6 +922,9 @@
     <x:t>43A-2-2026-1111-408</x:t>
   </x:si>
   <x:si>
+    <x:t>1511278</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -778,6 +934,9 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
+    <x:t>1511223</x:t>
+  </x:si>
+  <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -787,6 +946,9 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
+    <x:t>1511224</x:t>
+  </x:si>
+  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -799,6 +961,9 @@
     <x:t>43A-2-2026-1086-471</x:t>
   </x:si>
   <x:si>
+    <x:t>1511196</x:t>
+  </x:si>
+  <x:si>
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
@@ -811,6 +976,9 @@
     <x:t>43A-2-2026-1097-702</x:t>
   </x:si>
   <x:si>
+    <x:t>1511274</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -820,6 +988,9 @@
     <x:t>43A-2-2026-1109-317</x:t>
   </x:si>
   <x:si>
+    <x:t>1511246</x:t>
+  </x:si>
+  <x:si>
     <x:t>INTO GADGETS TOO INC.</x:t>
   </x:si>
   <x:si>
@@ -832,6 +1003,9 @@
     <x:t>43A-3-2026-1152-831</x:t>
   </x:si>
   <x:si>
+    <x:t>1511235</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILECRAZE TELECOM INC</x:t>
   </x:si>
   <x:si>
@@ -844,6 +1018,9 @@
     <x:t>43A-3-2026-1159-651</x:t>
   </x:si>
   <x:si>
+    <x:t>1511242</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILECRAZE TELECOM INC.</x:t>
   </x:si>
   <x:si>
@@ -856,6 +1033,9 @@
     <x:t>43A-2-2026-1113-757</x:t>
   </x:si>
   <x:si>
+    <x:t>1511248</x:t>
+  </x:si>
+  <x:si>
     <x:t>ONE DOTCOM CELL INC.</x:t>
   </x:si>
   <x:si>
@@ -868,6 +1048,9 @@
     <x:t>43A-3-2026-1153-796</x:t>
   </x:si>
   <x:si>
+    <x:t>1511236</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHONEVILLE MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -880,6 +1063,9 @@
     <x:t>43A-3-2026-1202-217</x:t>
   </x:si>
   <x:si>
+    <x:t>1511271</x:t>
+  </x:si>
+  <x:si>
     <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -892,6 +1078,9 @@
     <x:t>43A-2-2026-1094-777</x:t>
   </x:si>
   <x:si>
+    <x:t>1511195</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC</x:t>
   </x:si>
   <x:si>
@@ -901,6 +1090,9 @@
     <x:t>43A-3-2026-1161-717</x:t>
   </x:si>
   <x:si>
+    <x:t>1511211</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
@@ -913,6 +1105,9 @@
     <x:t>43A-2-2026-1108-762</x:t>
   </x:si>
   <x:si>
+    <x:t>1511213</x:t>
+  </x:si>
+  <x:si>
     <x:t>LEVEL 3 0118, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -922,6 +1117,9 @@
     <x:t>43A-2-2026-1083-282</x:t>
   </x:si>
   <x:si>
+    <x:t>1511241</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -931,6 +1129,9 @@
     <x:t>43A-3-2026-1168-173</x:t>
   </x:si>
   <x:si>
+    <x:t>1511222</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
   </x:si>
   <x:si>
@@ -940,6 +1141,9 @@
     <x:t>43A-3-2026-1201-204</x:t>
   </x:si>
   <x:si>
+    <x:t>1511270</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -949,6 +1153,9 @@
     <x:t>43A-3-2026-1192-904</x:t>
   </x:si>
   <x:si>
+    <x:t>1511231</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -961,6 +1168,9 @@
     <x:t>43A-2-2026-1084-395</x:t>
   </x:si>
   <x:si>
+    <x:t>1511240</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYALA MALLS SERIN JUNCTION EAST, SILANG, Tagaytay City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -970,6 +1180,9 @@
     <x:t>43A-2-2026-1087-228</x:t>
   </x:si>
   <x:si>
+    <x:t>1511275</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -982,6 +1195,9 @@
     <x:t>43A-3-2026-1174-419</x:t>
   </x:si>
   <x:si>
+    <x:t>1511761</x:t>
+  </x:si>
+  <x:si>
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -994,6 +1210,9 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
+    <x:t>1507967</x:t>
+  </x:si>
+  <x:si>
     <x:t>STADIUM SHOPPING STRIP ANTERO SORIANO HIGHWAY, MUNTING MAPINO, Naic, Cavite</x:t>
   </x:si>
   <x:si>
@@ -1003,6 +1222,9 @@
     <x:t>43A-3-2026-1170-469</x:t>
   </x:si>
   <x:si>
+    <x:t>1507966</x:t>
+  </x:si>
+  <x:si>
     <x:t>VISTAMALL TANZA TANZA-TRECE, PUNTA II, Tanza, Cavite</x:t>
   </x:si>
   <x:si>
@@ -1021,6 +1243,9 @@
     <x:t>43A-3-2026-1172-434</x:t>
   </x:si>
   <x:si>
+    <x:t>1507965</x:t>
+  </x:si>
+  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -1033,6 +1258,9 @@
     <x:t>43A-3-2026-1162-745</x:t>
   </x:si>
   <x:si>
+    <x:t>1511226</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART TANAUAN 225 WALTERMART JPL-HWAY, DARASA, City Of Tanauan, Batangas</x:t>
   </x:si>
   <x:si>
@@ -1042,6 +1270,9 @@
     <x:t>43A-3-2026-1157-256</x:t>
   </x:si>
   <x:si>
+    <x:t>1511208</x:t>
+  </x:si>
+  <x:si>
     <x:t>INNOVASIA MARKETING</x:t>
   </x:si>
   <x:si>
@@ -1054,6 +1285,9 @@
     <x:t>43A-3-2026-1146-031</x:t>
   </x:si>
   <x:si>
+    <x:t>1511639</x:t>
+  </x:si>
+  <x:si>
     <x:t>#95 CZ13 SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -1063,6 +1297,9 @@
     <x:t>43A-3-2026-1163-392</x:t>
   </x:si>
   <x:si>
+    <x:t>1511277</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -1072,6 +1309,9 @@
     <x:t>43A-3-2026-1175-710</x:t>
   </x:si>
   <x:si>
+    <x:t>1511759</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -1081,6 +1321,9 @@
     <x:t>43A-3-2026-1176-385</x:t>
   </x:si>
   <x:si>
+    <x:t>1511760</x:t>
+  </x:si>
+  <x:si>
     <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -1090,6 +1333,9 @@
     <x:t>43A-3-2026-1173-016</x:t>
   </x:si>
   <x:si>
+    <x:t>1511758</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLBOY INC.</x:t>
   </x:si>
   <x:si>
@@ -1102,6 +1348,9 @@
     <x:t>43A-3-2026-1205-403</x:t>
   </x:si>
   <x:si>
+    <x:t>1511858</x:t>
+  </x:si>
+  <x:si>
     <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
@@ -1114,6 +1363,9 @@
     <x:t>43A-3-2026-1194-347</x:t>
   </x:si>
   <x:si>
+    <x:t>1511219</x:t>
+  </x:si>
+  <x:si>
     <x:t>MILLENNIAL ZEAL TECHNOLOGY CORPORATION</x:t>
   </x:si>
   <x:si>
@@ -1124,6 +1376,9 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1147-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507892</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1135,7 +1390,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1197,13 +1452,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -1462,7 +1710,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1503,50 +1751,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1594,6 +1833,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1605,71 +1848,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -2050,7 +2277,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -2060,23 +2287,23 @@
       <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46069.0835185185</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46069.1006712963</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1506161</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>46069.0835222569</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46069.1006819792</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46069.1133333333</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46069.1133347338</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -2084,1444 +2311,1444 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46066.2950925926</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46066.3145039236</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46066.3194256134</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46069.0835757523</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46069.1000300231</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>46069.1128697454</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46066.2950925926</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46066.3145023148</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1507747</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46072.1720853819</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46072.2351628009</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46066.3194212963</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="L11" s="18">
+        <x:v>46073.1890290625</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
+      <x:c r="C12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46063.2819612616</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46063.2922791319</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46063.2957673958</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46069.0835648148</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46069.1000231481</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1506159</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46058.4859935069</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46062.1570258102</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46069.1128587963</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46072.1720833333</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46072.235162037</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1507783</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="L13" s="18">
+        <x:v>46062.1882026968</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46067.3600302778</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46067.3600485417</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46079.273015787</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46072.3184291551</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46072.3184479745</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46079.269710081</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46067.1596693866</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46079.277259919</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46067.222213287</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46089</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46079.2763165278</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46072.3605633333</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46073.2285051968</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46072.352960787</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46073</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46073.2314433796</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46063.1352781944</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46063.2367775347</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s"/>
+      <x:c r="E21" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46073.2761712037</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46073.3142477315</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46079.3584810995</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46079.3584983796</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46080.2311256134</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46079.3539738194</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46079.3539910417</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46080.244091956</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46058.1529325347</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46058.1529476968</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46058.2410705671</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46072.2635348032</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46073.3091133681</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46079.3873177662</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46080.2360791898</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46079.2523059375</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46080.2925916204</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46079.2430618866</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46073.1890277778</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46063.2819560185</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46063.2922685185</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1507682</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="K28" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46080.2801283218</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46079.3652018403</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46080.2425555208</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46080.2923673264</x:v>
+      </x:c>
+      <x:c r="I30" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46080.3208568171</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46079.3162545833</x:v>
+      </x:c>
+      <x:c r="I31" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46063.2957638889</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46058.4859837963</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46062.157025463</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1507672</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="K31" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="18">
+        <x:v>46080.2883729977</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46079.3059443634</x:v>
+      </x:c>
+      <x:c r="I32" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46062.1881944444</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46067.3600231481</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46067.3600462963</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46079.2730092593</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
+      <x:c r="K32" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="18">
+        <x:v>46080.2896890278</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46079.2943998843</x:v>
+      </x:c>
+      <x:c r="I33" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="18">
+        <x:v>46080.2916823611</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46079.3789042361</x:v>
+      </x:c>
+      <x:c r="I34" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="18">
+        <x:v>46080.2376106713</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46079.3728295139</x:v>
+      </x:c>
+      <x:c r="I35" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L35" s="18">
+        <x:v>46080.2394384722</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
+        <x:v>46077.0697396412</x:v>
+      </x:c>
+      <x:c r="I36" s="16">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="18">
+        <x:v>46077.1078903704</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46072.3184259259</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46072.3184375</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1505803</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46079.2696990741</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46067.1596643518</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1505804</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46079.2772569444</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
+      <x:c r="E37" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
+        <x:v>46062.159017581</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46062.1590321875</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L37" s="18">
+        <x:v>46062.1863264931</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46067.2222106481</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46089</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1505805</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46079.2763078704</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46072.3605555556</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1507784</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46073.2284953704</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46072.3529513889</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>46073</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1507785</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46073.2314351852</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46063.1352777778</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1511010</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46063.2367708333</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s"/>
-      <x:c r="E21" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46073.2761689815</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1507791</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46073.3142476852</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46079.3584722222</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46079.3584953704</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1511622</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46080.2311226852</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46079.3539699074</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46079.3539814815</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1511627</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46080.2440856481</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46058.1529282407</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46058.1529398148</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1507657</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46058.2410648148</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F25" s="17" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H25" s="19">
-        <x:v>46072.2635300926</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="n">
-        <x:v>1507790</x:v>
-      </x:c>
-      <x:c r="K25" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L25" s="21">
-        <x:v>46073.3091087963</x:v>
-      </x:c>
-      <x:c r="M25" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="s">
+      <x:c r="E38" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
+        <x:v>46066.2180240509</x:v>
+      </x:c>
+      <x:c r="I38" s="16">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J38" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L38" s="18">
+        <x:v>46066.2724449537</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
+        <x:v>46071.0492490046</x:v>
+      </x:c>
+      <x:c r="I39" s="16">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L39" s="18">
+        <x:v>46071.0606162616</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D26" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E26" s="17" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F26" s="17" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G26" s="17" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H26" s="19">
-        <x:v>46079.3873148148</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J26" s="18" t="n">
-        <x:v>1511623</x:v>
-      </x:c>
-      <x:c r="K26" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="21">
-        <x:v>46080.2360763889</x:v>
-      </x:c>
-      <x:c r="M26" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C27" s="17" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D27" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E27" s="17" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="F27" s="17" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="H27" s="19">
-        <x:v>46079.2523032407</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J27" s="18" t="n">
-        <x:v>1511631</x:v>
-      </x:c>
-      <x:c r="K27" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L27" s="21">
-        <x:v>46080.2925810185</x:v>
-      </x:c>
-      <x:c r="M27" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C28" s="17" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D28" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E28" s="17" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F28" s="17" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G28" s="17" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H28" s="19">
-        <x:v>46079.2430555556</x:v>
-      </x:c>
-      <x:c r="I28" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J28" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K28" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="21">
-        <x:v>46080.2801273148</x:v>
-      </x:c>
-      <x:c r="M28" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C29" s="17" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D29" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E29" s="17" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F29" s="17" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G29" s="17" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H29" s="19">
-        <x:v>46079.3651967593</x:v>
-      </x:c>
-      <x:c r="I29" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J29" s="18" t="n">
-        <x:v>1511626</x:v>
-      </x:c>
-      <x:c r="K29" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L29" s="21">
-        <x:v>46080.2425462963</x:v>
-      </x:c>
-      <x:c r="M29" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C30" s="17" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D30" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E30" s="17" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F30" s="17" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="G30" s="17" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H30" s="19">
-        <x:v>46080.2923611111</x:v>
-      </x:c>
-      <x:c r="I30" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J30" s="18" t="n">
-        <x:v>1511635</x:v>
-      </x:c>
-      <x:c r="K30" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L30" s="21">
-        <x:v>46080.3208564815</x:v>
-      </x:c>
-      <x:c r="M30" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C31" s="17" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D31" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E31" s="17" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F31" s="17" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G31" s="17" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H31" s="19">
-        <x:v>46079.31625</x:v>
-      </x:c>
-      <x:c r="I31" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J31" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K31" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="21">
-        <x:v>46080.2883680556</x:v>
-      </x:c>
-      <x:c r="M31" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C32" s="17" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D32" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E32" s="17" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F32" s="17" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G32" s="17" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H32" s="19">
-        <x:v>46079.3059375</x:v>
-      </x:c>
-      <x:c r="I32" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J32" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K32" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="21">
-        <x:v>46080.2896875</x:v>
-      </x:c>
-      <x:c r="M32" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C33" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D33" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E33" s="17" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F33" s="17" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G33" s="17" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H33" s="19">
-        <x:v>46079.2943981482</x:v>
-      </x:c>
-      <x:c r="I33" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J33" s="18" t="n">
-        <x:v>1511630</x:v>
-      </x:c>
-      <x:c r="K33" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="21">
-        <x:v>46080.2916782407</x:v>
-      </x:c>
-      <x:c r="M33" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C34" s="17" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D34" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E34" s="17" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F34" s="17" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G34" s="17" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H34" s="19">
-        <x:v>46079.378900463</x:v>
-      </x:c>
-      <x:c r="I34" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J34" s="18" t="n">
-        <x:v>1511624</x:v>
-      </x:c>
-      <x:c r="K34" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="21">
-        <x:v>46080.2376041667</x:v>
-      </x:c>
-      <x:c r="M34" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C35" s="17" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D35" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E35" s="17" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F35" s="17" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G35" s="17" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H35" s="19">
-        <x:v>46079.3728240741</x:v>
-      </x:c>
-      <x:c r="I35" s="19">
-        <x:v>46092</x:v>
-      </x:c>
-      <x:c r="J35" s="18" t="n">
-        <x:v>1511625</x:v>
-      </x:c>
-      <x:c r="K35" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L35" s="21">
-        <x:v>46080.2394328704</x:v>
-      </x:c>
-      <x:c r="M35" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C36" s="17" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D36" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E36" s="17" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F36" s="17" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G36" s="17" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H36" s="19">
-        <x:v>46077.0697337963</x:v>
-      </x:c>
-      <x:c r="I36" s="19">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J36" s="18" t="n">
-        <x:v>1511576</x:v>
-      </x:c>
-      <x:c r="K36" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L36" s="21">
-        <x:v>46077.1078819444</x:v>
-      </x:c>
-      <x:c r="M36" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C37" s="17" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D37" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E37" s="17" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F37" s="17" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G37" s="17" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H37" s="19">
-        <x:v>46062.1590162037</x:v>
-      </x:c>
-      <x:c r="I37" s="19">
-        <x:v>46062.1590277778</x:v>
-      </x:c>
-      <x:c r="J37" s="18" t="n">
-        <x:v>1510925</x:v>
-      </x:c>
-      <x:c r="K37" s="20" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L37" s="21">
-        <x:v>46062.1863194444</x:v>
-      </x:c>
-      <x:c r="M37" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C38" s="17" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D38" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E38" s="17" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F38" s="17" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="G38" s="17" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H38" s="19">
-        <x:v>46066.2180208333</x:v>
-      </x:c>
-      <x:c r="I38" s="19">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J38" s="18" t="n">
-        <x:v>1507743</x:v>
-      </x:c>
-      <x:c r="K38" s="20" t="n">
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
+        <x:v>46066.2275385417</x:v>
+      </x:c>
+      <x:c r="I40" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J40" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L38" s="21">
-        <x:v>46066.2724421296</x:v>
-      </x:c>
-      <x:c r="M38" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C39" s="17" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D39" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E39" s="17" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F39" s="17" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="G39" s="17" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="H39" s="19">
-        <x:v>46071.0492476852</x:v>
-      </x:c>
-      <x:c r="I39" s="19">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J39" s="18" t="n">
-        <x:v>1511502</x:v>
-      </x:c>
-      <x:c r="K39" s="20" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L39" s="21">
-        <x:v>46071.0606134259</x:v>
-      </x:c>
-      <x:c r="M39" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C40" s="17" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D40" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E40" s="17" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="F40" s="17" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G40" s="17" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H40" s="19">
-        <x:v>46066.2275347222</x:v>
-      </x:c>
-      <x:c r="I40" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J40" s="18" t="n">
-        <x:v>1507742</x:v>
-      </x:c>
-      <x:c r="K40" s="20" t="n">
+      <x:c r="L40" s="18">
+        <x:v>46066.2701807986</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
+        <x:v>46078.2436305208</x:v>
+      </x:c>
+      <x:c r="I41" s="16">
+        <x:v>46085</x:v>
+      </x:c>
+      <x:c r="J41" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L40" s="21">
-        <x:v>46066.2701736111</x:v>
-      </x:c>
-      <x:c r="M40" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C41" s="17" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D41" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E41" s="17" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F41" s="17" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G41" s="17" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="H41" s="19">
-        <x:v>46078.2436226852</x:v>
-      </x:c>
-      <x:c r="I41" s="19">
-        <x:v>46085</x:v>
-      </x:c>
-      <x:c r="J41" s="18" t="n">
-        <x:v>1507839</x:v>
-      </x:c>
-      <x:c r="K41" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L41" s="21">
-        <x:v>46078.3266203704</x:v>
-      </x:c>
-      <x:c r="M41" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="L41" s="18">
+        <x:v>46078.3266231366</x:v>
+      </x:c>
+      <x:c r="M41" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="17" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C42" s="17" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D42" s="18" t="s"/>
-      <x:c r="E42" s="17" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="F42" s="17" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="G42" s="17" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="H42" s="19">
-        <x:v>46080.2342361111</x:v>
-      </x:c>
-      <x:c r="I42" s="19">
-        <x:v>46080.2342592593</x:v>
-      </x:c>
-      <x:c r="J42" s="18" t="n">
-        <x:v>1507884</x:v>
-      </x:c>
-      <x:c r="K42" s="20" t="n">
+      <x:c r="B42" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s"/>
+      <x:c r="E42" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
+        <x:v>46080.2342400116</x:v>
+      </x:c>
+      <x:c r="I42" s="16">
+        <x:v>46080.2342615972</x:v>
+      </x:c>
+      <x:c r="J42" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K42" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L42" s="21">
-        <x:v>46080.3353356481</x:v>
-      </x:c>
-      <x:c r="M42" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="L42" s="18">
+        <x:v>46080.3353454745</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="17" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C43" s="17" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="D43" s="18" t="s"/>
-      <x:c r="E43" s="17" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="F43" s="17" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="G43" s="17" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H43" s="19">
-        <x:v>46080.2722685185</x:v>
-      </x:c>
-      <x:c r="I43" s="19">
-        <x:v>46080.2722800926</x:v>
-      </x:c>
-      <x:c r="J43" s="18" t="n">
-        <x:v>1507883</x:v>
-      </x:c>
-      <x:c r="K43" s="20" t="n">
+      <x:c r="B43" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D43" s="15" t="s"/>
+      <x:c r="E43" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H43" s="16">
+        <x:v>46080.272270544</x:v>
+      </x:c>
+      <x:c r="I43" s="16">
+        <x:v>46080.2722898495</x:v>
+      </x:c>
+      <x:c r="J43" s="15" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="K43" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L43" s="21">
-        <x:v>46080.3345717593</x:v>
-      </x:c>
-      <x:c r="M43" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="L43" s="18">
+        <x:v>46080.3345804745</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="22" t="s">
+      <x:c r="B46" s="19" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C46" s="20" t="s"/>
+      <x:c r="D46" s="20" t="s"/>
+      <x:c r="E46" s="21" t="s"/>
+      <x:c r="F46" s="21" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B47" s="22" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C47" s="23" t="s"/>
+      <x:c r="D47" s="23" t="s"/>
+      <x:c r="E47" s="23" t="s"/>
+      <x:c r="F47" s="24" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C48" s="26" t="s"/>
+      <x:c r="D48" s="26" t="s"/>
+      <x:c r="E48" s="26" t="s"/>
+      <x:c r="F48" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="25" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C49" s="26" t="s"/>
+      <x:c r="D49" s="26" t="s"/>
+      <x:c r="E49" s="26" t="s"/>
+      <x:c r="F49" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="25" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C50" s="26" t="s"/>
+      <x:c r="D50" s="26" t="s"/>
+      <x:c r="E50" s="26" t="s"/>
+      <x:c r="F50" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="25" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C51" s="26" t="s"/>
+      <x:c r="D51" s="26" t="s"/>
+      <x:c r="E51" s="26" t="s"/>
+      <x:c r="F51" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="25" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C52" s="26" t="s"/>
+      <x:c r="D52" s="26" t="s"/>
+      <x:c r="E52" s="26" t="s"/>
+      <x:c r="F52" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="25" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C53" s="26" t="s"/>
+      <x:c r="D53" s="26" t="s"/>
+      <x:c r="E53" s="26" t="s"/>
+      <x:c r="F53" s="27" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="25" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C54" s="26" t="s"/>
+      <x:c r="D54" s="26" t="s"/>
+      <x:c r="E54" s="26" t="s"/>
+      <x:c r="F54" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="25" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C46" s="23" t="s"/>
-      <x:c r="D46" s="23" t="s"/>
-      <x:c r="E46" s="24" t="s"/>
-      <x:c r="F46" s="24" t="s"/>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B47" s="25" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C47" s="26" t="s"/>
-      <x:c r="D47" s="26" t="s"/>
-      <x:c r="E47" s="26" t="s"/>
-      <x:c r="F47" s="27" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C48" s="29" t="s"/>
-      <x:c r="D48" s="29" t="s"/>
-      <x:c r="E48" s="29" t="s"/>
-      <x:c r="F48" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="28" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C49" s="29" t="s"/>
-      <x:c r="D49" s="29" t="s"/>
-      <x:c r="E49" s="29" t="s"/>
-      <x:c r="F49" s="30" t="n">
+      <x:c r="C55" s="26" t="s"/>
+      <x:c r="D55" s="26" t="s"/>
+      <x:c r="E55" s="26" t="s"/>
+      <x:c r="F55" s="27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="25" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C56" s="26" t="s"/>
+      <x:c r="D56" s="26" t="s"/>
+      <x:c r="E56" s="26" t="s"/>
+      <x:c r="F56" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="28" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C50" s="29" t="s"/>
-      <x:c r="D50" s="29" t="s"/>
-      <x:c r="E50" s="29" t="s"/>
-      <x:c r="F50" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="28" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C51" s="29" t="s"/>
-      <x:c r="D51" s="29" t="s"/>
-      <x:c r="E51" s="29" t="s"/>
-      <x:c r="F51" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="28" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C52" s="29" t="s"/>
-      <x:c r="D52" s="29" t="s"/>
-      <x:c r="E52" s="29" t="s"/>
-      <x:c r="F52" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="28" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C53" s="29" t="s"/>
-      <x:c r="D53" s="29" t="s"/>
-      <x:c r="E53" s="29" t="s"/>
-      <x:c r="F53" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="28" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C54" s="29" t="s"/>
-      <x:c r="D54" s="29" t="s"/>
-      <x:c r="E54" s="29" t="s"/>
-      <x:c r="F54" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="28" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C55" s="29" t="s"/>
-      <x:c r="D55" s="29" t="s"/>
-      <x:c r="E55" s="29" t="s"/>
-      <x:c r="F55" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="28" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C56" s="29" t="s"/>
-      <x:c r="D56" s="29" t="s"/>
-      <x:c r="E56" s="29" t="s"/>
-      <x:c r="F56" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
     <x:row r="57" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B57" s="31" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="C57" s="32" t="s"/>
-      <x:c r="D57" s="32" t="s"/>
-      <x:c r="E57" s="32" t="s"/>
-      <x:c r="F57" s="33" t="n">
+      <x:c r="B57" s="28" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C57" s="29" t="s"/>
+      <x:c r="D57" s="29" t="s"/>
+      <x:c r="E57" s="29" t="s"/>
+      <x:c r="F57" s="30" t="n">
         <x:v>36</x:v>
       </x:c>
     </x:row>
@@ -4590,7 +4817,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>174</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -4669,35 +4896,35 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>177</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46100.1144675926</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46100.1505092593</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1511906</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46100.1144765394</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46100.1505107292</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46100.1652777778</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46100.1652817245</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -4705,2101 +4932,2101 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46100.3734490741</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46100.388599537</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1529812</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46100.3734511921</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46100.3886071759</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46100.3957175926</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46100.3957177662</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46100.365787037</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46100.3731712963</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1529809</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="C10" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46100.3657890856</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46100.3731746412</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46100.3868981482</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46100.3869012616</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46091.306099537</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46091.3107986111</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1511778</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="C11" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46091.3061033796</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46091.3108077083</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46091.3131828704</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>85</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46091.3131892477</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="17" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46093.1459375</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>46093.1585185185</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1511815</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="C12" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46093.1459465972</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46093.1585187731</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46093.159537037</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>85</x:v>
+      <x:c r="L12" s="18">
+        <x:v>46093.1595409143</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="17" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46098.0792592593</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46098.0878935185</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1529776</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="C13" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46098.0792632986</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46098.0878978819</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46098.0997569444</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="L13" s="18">
+        <x:v>46098.0997679745</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="B14" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46090.2418365857</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46090.2418534606</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="L14" s="18">
+        <x:v>46093.3049920255</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="B15" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46090.2558238542</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46090.2558400116</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46097.2890740741</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="L15" s="18">
+        <x:v>46097.2890797917</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
+      <x:c r="B16" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46090.210999456</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46090.211015162</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="L16" s="18">
+        <x:v>46093.3080127546</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46083.2380439815</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="B17" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46083.2380494329</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1511234</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
+      <x:c r="J17" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46097.1564351852</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="L17" s="18">
+        <x:v>46097.1564439468</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="B18" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46083.2322339931</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
+      <x:c r="J18" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="L18" s="18">
+        <x:v>46097.1495293519</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46080.4532523148</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="B19" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46080.4532551852</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1511232</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
+      <x:c r="J19" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46097.1461689815</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="L19" s="18">
+        <x:v>46097.1461728357</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46083.2599189815</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="B20" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46083.2599218056</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1511237</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
+      <x:c r="J20" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46097.1652314815</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="L20" s="18">
+        <x:v>46097.1652390856</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46069.2785648148</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
+      <x:c r="B21" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46069.278571956</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
         <x:v>46067</x:v>
       </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1511276</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
+      <x:c r="J21" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46100.3884027778</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>227</x:v>
+      <x:c r="L21" s="18">
+        <x:v>46100.3884108912</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
+      <x:c r="B22" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46069.3514850347</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
+      <x:c r="J22" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L22" s="21">
+      <x:c r="L22" s="18">
         <x:v>46097.2437384259</x:v>
       </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="M22" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46084.0854513889</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
+      <x:c r="B23" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46084.0854516898</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1511225</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
+      <x:c r="J23" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46093.3956365741</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="L23" s="18">
+        <x:v>46093.3956400694</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46084.0996759259</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
+      <x:c r="B24" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46084.0996762384</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1511192</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
+      <x:c r="J24" s="15" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46097.2414583333</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>201</x:v>
+      <x:c r="L24" s="18">
+        <x:v>46097.241468588</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="F25" s="17" t="s">
+      <x:c r="B25" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46069.3573124306</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46097.2426396643</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="H25" s="19">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46069.1542109954</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46035</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46097.2466610301</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46073.1441202083</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46100.4005466667</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46084.2189288542</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46093.3723926852</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46084.2250188542</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46093.3804507639</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46069.2178798032</x:v>
+      </x:c>
+      <x:c r="I30" s="16">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46097.2456397685</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46069.3717699074</x:v>
+      </x:c>
+      <x:c r="I31" s="16">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L31" s="18">
+        <x:v>46100.3754893056</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46073.1251625463</x:v>
+      </x:c>
+      <x:c r="I32" s="16">
+        <x:v>45619</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="K32" s="17" t="n">
+        <x:v>11280</x:v>
+      </x:c>
+      <x:c r="L32" s="18">
+        <x:v>46099.1200232986</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46083.2443981019</x:v>
+      </x:c>
+      <x:c r="I33" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J25" s="18" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K25" s="20" t="n">
+      <x:c r="J33" s="15" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="21">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M25" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D26" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E26" s="17" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F26" s="17" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="G26" s="17" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="H26" s="19">
-        <x:v>46069.1542013889</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46035</x:v>
-      </x:c>
-      <x:c r="J26" s="18" t="n">
-        <x:v>1511206</x:v>
-      </x:c>
-      <x:c r="K26" s="20" t="n">
+      <x:c r="L33" s="18">
+        <x:v>46097.1600206018</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46084.1225139699</x:v>
+      </x:c>
+      <x:c r="I34" s="16">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="18">
+        <x:v>46097.3505144329</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46073.1541139005</x:v>
+      </x:c>
+      <x:c r="I35" s="16">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L26" s="21">
-        <x:v>46097.2466550926</x:v>
-      </x:c>
-      <x:c r="M26" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C27" s="17" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D27" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E27" s="17" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F27" s="17" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H27" s="19">
-        <x:v>46073.1441087963</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J27" s="18" t="n">
-        <x:v>1511278</x:v>
-      </x:c>
-      <x:c r="K27" s="20" t="n">
+      <x:c r="L35" s="18">
+        <x:v>46099.1584012616</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
+        <x:v>46083.252116412</x:v>
+      </x:c>
+      <x:c r="I36" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L36" s="18">
+        <x:v>46097.1628986343</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
+        <x:v>46097.4788515162</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L37" s="18">
+        <x:v>46100.2987549074</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
+        <x:v>46069.3341180556</x:v>
+      </x:c>
+      <x:c r="I38" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J38" s="15" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L38" s="18">
+        <x:v>46097.244735544</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
+        <x:v>46084.1513040509</x:v>
+      </x:c>
+      <x:c r="I39" s="16">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L39" s="18">
+        <x:v>46097.2494578472</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
+        <x:v>46073.1135088426</x:v>
+      </x:c>
+      <x:c r="I40" s="16">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J40" s="15" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L40" s="18">
+        <x:v>46097.2511403241</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B41" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
+        <x:v>46069.1151616435</x:v>
+      </x:c>
+      <x:c r="I41" s="16">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J41" s="15" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L41" s="18">
+        <x:v>46097.343386956</x:v>
+      </x:c>
+      <x:c r="M41" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
+        <x:v>46084.3311976389</x:v>
+      </x:c>
+      <x:c r="I42" s="16">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J42" s="15" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="K42" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L27" s="21">
-        <x:v>46100.4005439815</x:v>
-      </x:c>
-      <x:c r="M27" s="17" t="s">
-        <x:v>227</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C28" s="17" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D28" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E28" s="17" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="F28" s="17" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G28" s="17" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H28" s="19">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I28" s="19">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J28" s="18" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K28" s="20" t="n">
+      <x:c r="L42" s="18">
+        <x:v>46093.3668852546</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B43" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D43" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="H43" s="16">
+        <x:v>46097.4214954398</x:v>
+      </x:c>
+      <x:c r="I43" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J43" s="15" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="K43" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L28" s="21">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M28" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C29" s="17" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="D29" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E29" s="17" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="F29" s="17" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="G29" s="17" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="H29" s="19">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I29" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J29" s="18" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K29" s="20" t="n">
+      <x:c r="L43" s="18">
+        <x:v>46100.2966699421</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B44" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D44" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E44" s="14" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="G44" s="14" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="H44" s="16">
+        <x:v>46092.1012814815</x:v>
+      </x:c>
+      <x:c r="I44" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J44" s="15" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="K44" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L29" s="21">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M29" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C30" s="17" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="D30" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E30" s="17" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="F30" s="17" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G30" s="17" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H30" s="19">
-        <x:v>46069.2178703704</x:v>
-      </x:c>
-      <x:c r="I30" s="19">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J30" s="18" t="n">
-        <x:v>1511196</x:v>
-      </x:c>
-      <x:c r="K30" s="20" t="n">
+      <x:c r="L44" s="18">
+        <x:v>46097.1408234491</x:v>
+      </x:c>
+      <x:c r="M44" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B45" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D45" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="G45" s="14" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="H45" s="16">
+        <x:v>46069.1217257292</x:v>
+      </x:c>
+      <x:c r="I45" s="16">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J45" s="15" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="K45" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L45" s="18">
+        <x:v>46097.3375062153</x:v>
+      </x:c>
+      <x:c r="M45" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B46" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D46" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="G46" s="14" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H46" s="16">
+        <x:v>46069.2327997454</x:v>
+      </x:c>
+      <x:c r="I46" s="16">
+        <x:v>46049</x:v>
+      </x:c>
+      <x:c r="J46" s="15" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="K46" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L30" s="21">
-        <x:v>46097.2456365741</x:v>
-      </x:c>
-      <x:c r="M30" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C31" s="17" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D31" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E31" s="17" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F31" s="17" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G31" s="17" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H31" s="19">
-        <x:v>46069.3717592593</x:v>
-      </x:c>
-      <x:c r="I31" s="19">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J31" s="18" t="n">
-        <x:v>1511274</x:v>
-      </x:c>
-      <x:c r="K31" s="20" t="n">
+      <x:c r="L46" s="18">
+        <x:v>46100.3816829514</x:v>
+      </x:c>
+      <x:c r="M46" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B47" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="D47" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="G47" s="14" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="H47" s="16">
+        <x:v>46086.106481875</x:v>
+      </x:c>
+      <x:c r="I47" s="16">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="J47" s="15" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="K47" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L47" s="18">
+        <x:v>46090.2765830324</x:v>
+      </x:c>
+      <x:c r="M47" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B48" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C48" s="14" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D48" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="G48" s="14" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H48" s="16">
+        <x:v>46084.3419451968</x:v>
+      </x:c>
+      <x:c r="I48" s="16">
+        <x:v>46084.3419617014</x:v>
+      </x:c>
+      <x:c r="J48" s="15" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="K48" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L48" s="18">
+        <x:v>46090.3480933681</x:v>
+      </x:c>
+      <x:c r="M48" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B49" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D49" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="G49" s="14" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="H49" s="16">
+        <x:v>46085.1627479398</x:v>
+      </x:c>
+      <x:c r="I49" s="16">
+        <x:v>46085.1627651505</x:v>
+      </x:c>
+      <x:c r="J49" s="15" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="K49" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L49" s="18">
+        <x:v>46090.3453534259</x:v>
+      </x:c>
+      <x:c r="M49" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B50" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D50" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="G50" s="14" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="H50" s="16">
+        <x:v>46085.1662527662</x:v>
+      </x:c>
+      <x:c r="I50" s="16">
+        <x:v>46085.1662689699</x:v>
+      </x:c>
+      <x:c r="J50" s="15" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="K50" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L50" s="18">
+        <x:v>46090.3437343634</x:v>
+      </x:c>
+      <x:c r="M50" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B51" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C51" s="14" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D51" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E51" s="14" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="G51" s="14" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="H51" s="16">
+        <x:v>46085.1709247338</x:v>
+      </x:c>
+      <x:c r="I51" s="16">
+        <x:v>46085.1709419676</x:v>
+      </x:c>
+      <x:c r="J51" s="15" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="K51" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L51" s="18">
+        <x:v>46090.3337014815</x:v>
+      </x:c>
+      <x:c r="M51" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B52" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C52" s="14" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="D52" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="G52" s="14" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="H52" s="16">
+        <x:v>46084.1579541898</x:v>
+      </x:c>
+      <x:c r="I52" s="16">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J52" s="15" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="K52" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L52" s="18">
+        <x:v>46093.4169326042</x:v>
+      </x:c>
+      <x:c r="M52" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B53" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C53" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D53" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E53" s="14" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="G53" s="14" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="H53" s="16">
+        <x:v>46084.1080380324</x:v>
+      </x:c>
+      <x:c r="I53" s="16">
+        <x:v>46103</x:v>
+      </x:c>
+      <x:c r="J53" s="15" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="K53" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L53" s="18">
+        <x:v>46097.2478153472</x:v>
+      </x:c>
+      <x:c r="M53" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B54" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="D54" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="G54" s="14" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="H54" s="16">
+        <x:v>46083.0788057755</x:v>
+      </x:c>
+      <x:c r="I54" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J54" s="15" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="K54" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L54" s="18">
+        <x:v>46083.1042250116</x:v>
+      </x:c>
+      <x:c r="M54" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B55" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C55" s="14" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="D55" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E55" s="14" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="G55" s="14" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="H55" s="16">
+        <x:v>46084.1627466204</x:v>
+      </x:c>
+      <x:c r="I55" s="16">
+        <x:v>46060</x:v>
+      </x:c>
+      <x:c r="J55" s="15" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="K55" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L31" s="21">
-        <x:v>46100.3754861111</x:v>
-      </x:c>
-      <x:c r="M31" s="17" t="s">
-        <x:v>227</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C32" s="17" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D32" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E32" s="17" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F32" s="17" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G32" s="17" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H32" s="19">
-        <x:v>46073.125162037</x:v>
-      </x:c>
-      <x:c r="I32" s="19">
-        <x:v>45619</x:v>
-      </x:c>
-      <x:c r="J32" s="18" t="n">
-        <x:v>1511246</x:v>
-      </x:c>
-      <x:c r="K32" s="20" t="n">
-        <x:v>11280</x:v>
-      </x:c>
-      <x:c r="L32" s="21">
-        <x:v>46099.1200231481</x:v>
-      </x:c>
-      <x:c r="M32" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C33" s="17" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="D33" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E33" s="17" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F33" s="17" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="G33" s="17" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="H33" s="19">
-        <x:v>46083.2443865741</x:v>
-      </x:c>
-      <x:c r="I33" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J33" s="18" t="n">
-        <x:v>1511235</x:v>
-      </x:c>
-      <x:c r="K33" s="20" t="n">
+      <x:c r="L55" s="18">
+        <x:v>46100.392939537</x:v>
+      </x:c>
+      <x:c r="M55" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B56" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C56" s="14" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="D56" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="G56" s="14" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="H56" s="16">
+        <x:v>46086.1144463079</x:v>
+      </x:c>
+      <x:c r="I56" s="16">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J56" s="15" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="K56" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L33" s="21">
-        <x:v>46097.1600115741</x:v>
-      </x:c>
-      <x:c r="M33" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C34" s="17" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D34" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E34" s="17" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="F34" s="17" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="G34" s="17" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="H34" s="19">
-        <x:v>46084.1225115741</x:v>
-      </x:c>
-      <x:c r="I34" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J34" s="18" t="n">
-        <x:v>1511242</x:v>
-      </x:c>
-      <x:c r="K34" s="20" t="n">
+      <x:c r="L56" s="18">
+        <x:v>46090.2703739352</x:v>
+      </x:c>
+      <x:c r="M56" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B57" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C57" s="14" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="D57" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="G57" s="14" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="H57" s="16">
+        <x:v>46087.1643336806</x:v>
+      </x:c>
+      <x:c r="I57" s="16">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="J57" s="15" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="K57" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L34" s="21">
-        <x:v>46097.3505092593</x:v>
-      </x:c>
-      <x:c r="M34" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C35" s="17" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="D35" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E35" s="17" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="F35" s="17" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G35" s="17" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H35" s="19">
-        <x:v>46073.1541087963</x:v>
-      </x:c>
-      <x:c r="I35" s="19">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J35" s="18" t="n">
-        <x:v>1511248</x:v>
-      </x:c>
-      <x:c r="K35" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L35" s="21">
-        <x:v>46099.1583912037</x:v>
-      </x:c>
-      <x:c r="M35" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C36" s="17" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="D36" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E36" s="17" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="F36" s="17" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="G36" s="17" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="H36" s="19">
-        <x:v>46083.2521064815</x:v>
-      </x:c>
-      <x:c r="I36" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J36" s="18" t="n">
-        <x:v>1511236</x:v>
-      </x:c>
-      <x:c r="K36" s="20" t="n">
+      <x:c r="L57" s="18">
+        <x:v>46090.2727784143</x:v>
+      </x:c>
+      <x:c r="M57" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B58" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C58" s="14" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="D58" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="G58" s="14" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="H58" s="16">
+        <x:v>46086.099798588</x:v>
+      </x:c>
+      <x:c r="I58" s="16">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="J58" s="15" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="K58" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L36" s="21">
-        <x:v>46097.1628935185</x:v>
-      </x:c>
-      <x:c r="M36" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C37" s="17" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="D37" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E37" s="17" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="F37" s="17" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="G37" s="17" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="H37" s="19">
-        <x:v>46097.4788425926</x:v>
-      </x:c>
-      <x:c r="I37" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J37" s="18" t="n">
-        <x:v>1511271</x:v>
-      </x:c>
-      <x:c r="K37" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L37" s="21">
-        <x:v>46100.29875</x:v>
-      </x:c>
-      <x:c r="M37" s="17" t="s">
-        <x:v>227</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C38" s="17" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="D38" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E38" s="17" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F38" s="17" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="G38" s="17" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H38" s="19">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I38" s="19">
+      <x:c r="L58" s="18">
+        <x:v>46090.2691152778</x:v>
+      </x:c>
+      <x:c r="M58" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B59" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="D59" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="G59" s="14" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="H59" s="16">
+        <x:v>46098.290884375</x:v>
+      </x:c>
+      <x:c r="I59" s="16">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J59" s="15" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="K59" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L59" s="18">
+        <x:v>46098.3188767824</x:v>
+      </x:c>
+      <x:c r="M59" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B60" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C60" s="14" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="D60" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E60" s="14" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="G60" s="14" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="H60" s="16">
+        <x:v>46092.9637875116</x:v>
+      </x:c>
+      <x:c r="I60" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J38" s="18" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K38" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="21">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M38" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C39" s="17" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="D39" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E39" s="17" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="F39" s="17" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="G39" s="17" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="H39" s="19">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I39" s="19">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J39" s="18" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K39" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L39" s="21">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M39" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B40" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C40" s="17" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D40" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E40" s="17" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="F40" s="17" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="G40" s="17" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H40" s="19">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I40" s="19">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J40" s="18" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K40" s="20" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L40" s="21">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M40" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B41" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C41" s="17" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D41" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E41" s="17" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="F41" s="17" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="G41" s="17" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="H41" s="19">
-        <x:v>46069.115150463</x:v>
-      </x:c>
-      <x:c r="I41" s="19">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J41" s="18" t="n">
-        <x:v>1511241</x:v>
-      </x:c>
-      <x:c r="K41" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="21">
-        <x:v>46097.3433796296</x:v>
-      </x:c>
-      <x:c r="M41" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B42" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C42" s="17" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D42" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E42" s="17" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="F42" s="17" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="G42" s="17" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="H42" s="19">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I42" s="19">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J42" s="18" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K42" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L42" s="21">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M42" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B43" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C43" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D43" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E43" s="17" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="F43" s="17" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="G43" s="17" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="H43" s="19">
-        <x:v>46097.4214930556</x:v>
-      </x:c>
-      <x:c r="I43" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J43" s="18" t="n">
-        <x:v>1511270</x:v>
-      </x:c>
-      <x:c r="K43" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="21">
-        <x:v>46100.2966666667</x:v>
-      </x:c>
-      <x:c r="M43" s="17" t="s">
-        <x:v>227</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B44" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C44" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D44" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E44" s="17" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="F44" s="17" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="G44" s="17" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="H44" s="19">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I44" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J44" s="18" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K44" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="21">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M44" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B45" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C45" s="17" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="D45" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E45" s="17" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="F45" s="17" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="G45" s="17" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="H45" s="19">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I45" s="19">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J45" s="18" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K45" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L45" s="21">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M45" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B46" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C46" s="17" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="D46" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E46" s="17" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="F46" s="17" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="G46" s="17" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="H46" s="19">
-        <x:v>46069.2327893519</x:v>
-      </x:c>
-      <x:c r="I46" s="19">
-        <x:v>46049</x:v>
-      </x:c>
-      <x:c r="J46" s="18" t="n">
-        <x:v>1511275</x:v>
-      </x:c>
-      <x:c r="K46" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L46" s="21">
-        <x:v>46100.3816782407</x:v>
-      </x:c>
-      <x:c r="M46" s="17" t="s">
-        <x:v>227</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B47" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C47" s="17" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="D47" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E47" s="17" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="F47" s="17" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="G47" s="17" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="H47" s="19">
-        <x:v>46086.1064814815</x:v>
-      </x:c>
-      <x:c r="I47" s="19">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="J47" s="18" t="n">
-        <x:v>1511761</x:v>
-      </x:c>
-      <x:c r="K47" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L47" s="21">
-        <x:v>46090.2765740741</x:v>
-      </x:c>
-      <x:c r="M47" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B48" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C48" s="17" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="D48" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E48" s="17" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="F48" s="17" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="G48" s="17" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="H48" s="19">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I48" s="19">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J48" s="18" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K48" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L48" s="21">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M48" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B49" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C49" s="17" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="D49" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E49" s="17" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="F49" s="17" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="G49" s="17" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="H49" s="19">
-        <x:v>46085.1627430556</x:v>
-      </x:c>
-      <x:c r="I49" s="19">
-        <x:v>46085.1627546296</x:v>
-      </x:c>
-      <x:c r="J49" s="18" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K49" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L49" s="21">
-        <x:v>46090.3453472222</x:v>
-      </x:c>
-      <x:c r="M49" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B50" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C50" s="17" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="D50" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E50" s="17" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="F50" s="17" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="G50" s="17" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="H50" s="19">
-        <x:v>46085.16625</x:v>
-      </x:c>
-      <x:c r="I50" s="19">
-        <x:v>46085.1662615741</x:v>
-      </x:c>
-      <x:c r="J50" s="18" t="n">
-        <x:v>1507966</x:v>
-      </x:c>
-      <x:c r="K50" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L50" s="21">
-        <x:v>46090.3437268519</x:v>
-      </x:c>
-      <x:c r="M50" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B51" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C51" s="17" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="D51" s="18" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E51" s="17" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="F51" s="17" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="G51" s="17" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="H51" s="19">
-        <x:v>46085.1709143519</x:v>
-      </x:c>
-      <x:c r="I51" s="19">
-        <x:v>46085.1709375</x:v>
-      </x:c>
-      <x:c r="J51" s="18" t="n">
-        <x:v>1507965</x:v>
-      </x:c>
-      <x:c r="K51" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L51" s="21">
-        <x:v>46090.3336921296</x:v>
-      </x:c>
-      <x:c r="M51" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B52" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C52" s="17" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="D52" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E52" s="17" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="F52" s="17" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="G52" s="17" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="H52" s="19">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I52" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J52" s="18" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K52" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L52" s="21">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M52" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B53" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C53" s="17" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="D53" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E53" s="17" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="F53" s="17" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="G53" s="17" t="s">
-        <x:v>338</x:v>
-      </x:c>
-      <x:c r="H53" s="19">
-        <x:v>46084.1080324074</x:v>
-      </x:c>
-      <x:c r="I53" s="19">
-        <x:v>46103</x:v>
-      </x:c>
-      <x:c r="J53" s="18" t="n">
-        <x:v>1511208</x:v>
-      </x:c>
-      <x:c r="K53" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L53" s="21">
-        <x:v>46097.2478125</x:v>
-      </x:c>
-      <x:c r="M53" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B54" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C54" s="17" t="s">
-        <x:v>339</x:v>
-      </x:c>
-      <x:c r="D54" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E54" s="17" t="s">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="F54" s="17" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="G54" s="17" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="H54" s="19">
-        <x:v>46083.0787962963</x:v>
-      </x:c>
-      <x:c r="I54" s="19">
+      <x:c r="J60" s="15" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="K60" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L60" s="18">
+        <x:v>46093.3109466551</x:v>
+      </x:c>
+      <x:c r="M60" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B61" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C61" s="14" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="D61" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E61" s="14" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="G61" s="14" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="H61" s="16">
+        <x:v>46083.0936215278</x:v>
+      </x:c>
+      <x:c r="I61" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J54" s="18" t="n">
-        <x:v>1511639</x:v>
-      </x:c>
-      <x:c r="K54" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L54" s="21">
-        <x:v>46083.104224537</x:v>
-      </x:c>
-      <x:c r="M54" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B55" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C55" s="17" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="D55" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E55" s="17" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="F55" s="17" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="G55" s="17" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="H55" s="19">
-        <x:v>46084.1627430556</x:v>
-      </x:c>
-      <x:c r="I55" s="19">
-        <x:v>46060</x:v>
-      </x:c>
-      <x:c r="J55" s="18" t="n">
-        <x:v>1511277</x:v>
-      </x:c>
-      <x:c r="K55" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L55" s="21">
-        <x:v>46100.3929282407</x:v>
-      </x:c>
-      <x:c r="M55" s="17" t="s">
-        <x:v>227</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B56" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C56" s="17" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="D56" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E56" s="17" t="s">
-        <x:v>346</x:v>
-      </x:c>
-      <x:c r="F56" s="17" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="G56" s="17" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="H56" s="19">
-        <x:v>46086.1144444444</x:v>
-      </x:c>
-      <x:c r="I56" s="19">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J56" s="18" t="n">
-        <x:v>1511759</x:v>
-      </x:c>
-      <x:c r="K56" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L56" s="21">
-        <x:v>46090.2703703704</x:v>
-      </x:c>
-      <x:c r="M56" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B57" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C57" s="17" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="D57" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E57" s="17" t="s">
-        <x:v>349</x:v>
-      </x:c>
-      <x:c r="F57" s="17" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="G57" s="17" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="H57" s="19">
-        <x:v>46087.1643287037</x:v>
-      </x:c>
-      <x:c r="I57" s="19">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="J57" s="18" t="n">
-        <x:v>1511760</x:v>
-      </x:c>
-      <x:c r="K57" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L57" s="21">
-        <x:v>46090.2727777778</x:v>
-      </x:c>
-      <x:c r="M57" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B58" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C58" s="17" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="D58" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E58" s="17" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="F58" s="17" t="s">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="G58" s="17" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="H58" s="19">
-        <x:v>46086.0997916667</x:v>
-      </x:c>
-      <x:c r="I58" s="19">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="J58" s="18" t="n">
-        <x:v>1511758</x:v>
-      </x:c>
-      <x:c r="K58" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L58" s="21">
-        <x:v>46090.2691087963</x:v>
-      </x:c>
-      <x:c r="M58" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B59" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C59" s="17" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="D59" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E59" s="17" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="F59" s="17" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="G59" s="17" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="H59" s="19">
-        <x:v>46098.2908796296</x:v>
-      </x:c>
-      <x:c r="I59" s="19">
-        <x:v>45997</x:v>
-      </x:c>
-      <x:c r="J59" s="18" t="n">
-        <x:v>1511858</x:v>
-      </x:c>
-      <x:c r="K59" s="20" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L59" s="21">
-        <x:v>46098.3188657407</x:v>
-      </x:c>
-      <x:c r="M59" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B60" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C60" s="17" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="D60" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E60" s="17" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="F60" s="17" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="G60" s="17" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="H60" s="19">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I60" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J60" s="18" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K60" s="20" t="n">
+      <x:c r="J61" s="15" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="K61" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L60" s="21">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M60" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B61" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C61" s="17" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="D61" s="18" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E61" s="17" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="F61" s="17" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="G61" s="17" t="s">
-        <x:v>366</x:v>
-      </x:c>
-      <x:c r="H61" s="19">
-        <x:v>46083.0936111111</x:v>
-      </x:c>
-      <x:c r="I61" s="19">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J61" s="18" t="n">
-        <x:v>1507892</x:v>
-      </x:c>
-      <x:c r="K61" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L61" s="21">
-        <x:v>46083.1543634259</x:v>
-      </x:c>
-      <x:c r="M61" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="L61" s="18">
+        <x:v>46083.1543707755</x:v>
+      </x:c>
+      <x:c r="M61" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B64" s="22" t="s">
+      <x:c r="B64" s="19" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C64" s="20" t="s"/>
+      <x:c r="D64" s="20" t="s"/>
+      <x:c r="E64" s="21" t="s"/>
+      <x:c r="F64" s="21" t="s"/>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B65" s="22" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C65" s="23" t="s"/>
+      <x:c r="D65" s="23" t="s"/>
+      <x:c r="E65" s="23" t="s"/>
+      <x:c r="F65" s="24" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B66" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C66" s="26" t="s"/>
+      <x:c r="D66" s="26" t="s"/>
+      <x:c r="E66" s="26" t="s"/>
+      <x:c r="F66" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B67" s="25" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C67" s="26" t="s"/>
+      <x:c r="D67" s="26" t="s"/>
+      <x:c r="E67" s="26" t="s"/>
+      <x:c r="F67" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B68" s="25" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C68" s="26" t="s"/>
+      <x:c r="D68" s="26" t="s"/>
+      <x:c r="E68" s="26" t="s"/>
+      <x:c r="F68" s="27" t="n">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B69" s="25" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C69" s="26" t="s"/>
+      <x:c r="D69" s="26" t="s"/>
+      <x:c r="E69" s="26" t="s"/>
+      <x:c r="F69" s="27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B70" s="25" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C70" s="26" t="s"/>
+      <x:c r="D70" s="26" t="s"/>
+      <x:c r="E70" s="26" t="s"/>
+      <x:c r="F70" s="27" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B71" s="25" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C64" s="23" t="s"/>
-      <x:c r="D64" s="23" t="s"/>
-      <x:c r="E64" s="24" t="s"/>
-      <x:c r="F64" s="24" t="s"/>
-    </x:row>
-    <x:row r="65" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B65" s="25" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C65" s="26" t="s"/>
-      <x:c r="D65" s="26" t="s"/>
-      <x:c r="E65" s="26" t="s"/>
-      <x:c r="F65" s="27" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B66" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C66" s="29" t="s"/>
-      <x:c r="D66" s="29" t="s"/>
-      <x:c r="E66" s="29" t="s"/>
-      <x:c r="F66" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B67" s="28" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C67" s="29" t="s"/>
-      <x:c r="D67" s="29" t="s"/>
-      <x:c r="E67" s="29" t="s"/>
-      <x:c r="F67" s="30" t="n">
+      <x:c r="C71" s="26" t="s"/>
+      <x:c r="D71" s="26" t="s"/>
+      <x:c r="E71" s="26" t="s"/>
+      <x:c r="F71" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B68" s="28" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C68" s="29" t="s"/>
-      <x:c r="D68" s="29" t="s"/>
-      <x:c r="E68" s="29" t="s"/>
-      <x:c r="F68" s="30" t="n">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B69" s="28" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C69" s="29" t="s"/>
-      <x:c r="D69" s="29" t="s"/>
-      <x:c r="E69" s="29" t="s"/>
-      <x:c r="F69" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B70" s="28" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C70" s="29" t="s"/>
-      <x:c r="D70" s="29" t="s"/>
-      <x:c r="E70" s="29" t="s"/>
-      <x:c r="F70" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B71" s="28" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C71" s="29" t="s"/>
-      <x:c r="D71" s="29" t="s"/>
-      <x:c r="E71" s="29" t="s"/>
-      <x:c r="F71" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
     <x:row r="72" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B72" s="31" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="C72" s="32" t="s"/>
-      <x:c r="D72" s="32" t="s"/>
-      <x:c r="E72" s="32" t="s"/>
-      <x:c r="F72" s="33" t="n">
+      <x:c r="B72" s="28" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C72" s="29" t="s"/>
+      <x:c r="D72" s="29" t="s"/>
+      <x:c r="E72" s="29" t="s"/>
+      <x:c r="F72" s="30" t="n">
         <x:v>54</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="457">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -715,6 +715,21 @@
     <x:t>1511815</x:t>
   </x:si>
   <x:si>
+    <x:t>ROBERT O. DELA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phase 1A Blk 3 Lot 3 RCD Royale Homes, Kalubkob, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03514-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1220-726</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1506181</x:t>
+  </x:si>
+  <x:si>
     <x:t>RUBEN C. SESCON</x:t>
   </x:si>
   <x:si>
@@ -889,6 +904,42 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1085-453</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511224</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -901,18 +952,6 @@
     <x:t>1511193</x:t>
   </x:si>
   <x:si>
-    <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1085-453</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511206</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
   </x:si>
   <x:si>
@@ -925,30 +964,6 @@
     <x:t>1511278</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511224</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -967,6 +982,18 @@
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-17-11-0683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1109-317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511246</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CENTER ILLUSTRE AVE, DISTRICT IV, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -977,18 +1004,6 @@
   </x:si>
   <x:si>
     <x:t>1511274</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-17-11-0683</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1109-317</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511246</x:t>
   </x:si>
   <x:si>
     <x:t>INTO GADGETS TOO INC.</x:t>
@@ -5089,10 +5104,10 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46098.0792632986</x:v>
+        <x:v>46104.2283957986</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46098.0878978819</x:v>
+        <x:v>46104.2427159028</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>234</x:v>
@@ -5101,22 +5116,20 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46098.0997679745</x:v>
+        <x:v>46104.2658305093</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
+      <x:c r="D14" s="15" t="s"/>
       <x:c r="E14" s="14" t="s">
         <x:v>236</x:v>
       </x:c>
@@ -5127,22 +5140,22 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46090.2418365857</x:v>
+        <x:v>46098.0792632986</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46090.2418534606</x:v>
+        <x:v>46098.0878978819</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46093.3049920255</x:v>
+        <x:v>46098.0997679745</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -5150,7 +5163,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>235</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>50</x:v>
@@ -5165,10 +5178,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46090.2558238542</x:v>
+        <x:v>46090.2418365857</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46090.2558400116</x:v>
+        <x:v>46090.2418534606</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
         <x:v>244</x:v>
@@ -5177,10 +5190,10 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46097.2890797917</x:v>
+        <x:v>46093.3049920255</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -5188,7 +5201,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>50</x:v>
@@ -5203,10 +5216,10 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46090.210999456</x:v>
+        <x:v>46090.2558238542</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46090.211015162</x:v>
+        <x:v>46090.2558400116</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
         <x:v>249</x:v>
@@ -5215,21 +5228,21 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46093.3080127546</x:v>
+        <x:v>46097.2890797917</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
         <x:v>250</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
         <x:v>251</x:v>
@@ -5241,22 +5254,22 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46083.2380494329</x:v>
+        <x:v>46090.210999456</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46100</x:v>
+        <x:v>46090.211015162</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
         <x:v>254</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46097.1564439468</x:v>
+        <x:v>46093.3080127546</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
@@ -5264,37 +5277,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46083.2322339931</x:v>
+        <x:v>46083.2380494329</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46097.1495293519</x:v>
+        <x:v>46097.1564439468</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -5302,37 +5315,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46080.4532551852</x:v>
+        <x:v>46083.2322339931</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46097.1461728357</x:v>
+        <x:v>46097.1495293519</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -5340,7 +5353,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>263</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>61</x:v>
@@ -5355,10 +5368,10 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46083.2599218056</x:v>
+        <x:v>46080.4532551852</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46101</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>267</x:v>
@@ -5367,10 +5380,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46097.1652390856</x:v>
+        <x:v>46097.1461728357</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -5393,22 +5406,22 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46069.278571956</x:v>
+        <x:v>46083.2599218056</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46067</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
         <x:v>272</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46100.3884108912</x:v>
+        <x:v>46097.1652390856</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -5416,7 +5429,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>268</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>61</x:v>
@@ -5431,22 +5444,22 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46069.3514850347</x:v>
+        <x:v>46069.278571956</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46094</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
         <x:v>277</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46097.2437384259</x:v>
+        <x:v>46100.3884108912</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -5454,7 +5467,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>61</x:v>
@@ -5469,10 +5482,10 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46084.0854516898</x:v>
+        <x:v>46069.3514850347</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46144</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
         <x:v>282</x:v>
@@ -5481,10 +5494,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46093.3956400694</x:v>
+        <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
@@ -5492,37 +5505,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46084.0996762384</x:v>
+        <x:v>46084.0854516898</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46094</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46097.241468588</x:v>
+        <x:v>46093.3956400694</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -5530,7 +5543,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>287</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
         <x:v>61</x:v>
@@ -5545,10 +5558,10 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46069.3573124306</x:v>
+        <x:v>46084.0996762384</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46100</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
         <x:v>291</x:v>
@@ -5557,10 +5570,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46097.2426396643</x:v>
+        <x:v>46097.241468588</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
@@ -5568,19 +5581,19 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>287</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="G26" s="14" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="H26" s="16">
         <x:v>46069.1542109954</x:v>
@@ -5589,7 +5602,7 @@
         <x:v>46035</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="K26" s="17" t="n">
         <x:v>3780</x:v>
@@ -5598,7 +5611,7 @@
         <x:v>46097.2466610301</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
@@ -5606,37 +5619,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>287</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E27" s="14" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="G27" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46073.1441202083</x:v>
+        <x:v>46084.2189288542</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46030</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46100.4005466667</x:v>
+        <x:v>46093.3723926852</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
@@ -5644,37 +5657,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>287</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E28" s="14" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="G28" s="14" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46084.2189288542</x:v>
+        <x:v>46084.2250188542</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46133</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="18">
-        <x:v>46093.3723926852</x:v>
+        <x:v>46093.3804507639</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
@@ -5682,37 +5695,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C29" s="14" t="s">
-        <x:v>287</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D29" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E29" s="14" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F29" s="14" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="G29" s="14" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46084.2250188542</x:v>
+        <x:v>46069.3573124306</x:v>
       </x:c>
       <x:c r="I29" s="16">
-        <x:v>46144</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J29" s="15" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="K29" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="18">
-        <x:v>46093.3804507639</x:v>
+        <x:v>46097.2426396643</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
@@ -5720,7 +5733,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C30" s="14" t="s">
-        <x:v>308</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D30" s="15" t="s">
         <x:v>61</x:v>
@@ -5735,10 +5748,10 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="H30" s="16">
-        <x:v>46069.2178798032</x:v>
+        <x:v>46073.1441202083</x:v>
       </x:c>
       <x:c r="I30" s="16">
-        <x:v>46051</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J30" s="15" t="s">
         <x:v>312</x:v>
@@ -5747,10 +5760,10 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L30" s="18">
-        <x:v>46097.2456397685</x:v>
+        <x:v>46100.4005466667</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
@@ -5773,10 +5786,10 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="H31" s="16">
-        <x:v>46069.3717699074</x:v>
+        <x:v>46069.2178798032</x:v>
       </x:c>
       <x:c r="I31" s="16">
-        <x:v>46066</x:v>
+        <x:v>46051</x:v>
       </x:c>
       <x:c r="J31" s="15" t="s">
         <x:v>317</x:v>
@@ -5785,10 +5798,10 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L31" s="18">
-        <x:v>46100.3754893056</x:v>
+        <x:v>46097.2456397685</x:v>
       </x:c>
       <x:c r="M31" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
@@ -5796,19 +5809,19 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C32" s="14" t="s">
-        <x:v>313</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D32" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E32" s="14" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="F32" s="14" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="G32" s="14" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="H32" s="16">
         <x:v>46073.1251625463</x:v>
@@ -5817,7 +5830,7 @@
         <x:v>45619</x:v>
       </x:c>
       <x:c r="J32" s="15" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="K32" s="17" t="n">
         <x:v>11280</x:v>
@@ -5826,7 +5839,7 @@
         <x:v>46099.1200232986</x:v>
       </x:c>
       <x:c r="M32" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
@@ -5834,7 +5847,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C33" s="14" t="s">
-        <x:v>322</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D33" s="15" t="s">
         <x:v>61</x:v>
@@ -5849,22 +5862,22 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="H33" s="16">
-        <x:v>46083.2443981019</x:v>
+        <x:v>46069.3717699074</x:v>
       </x:c>
       <x:c r="I33" s="16">
-        <x:v>46100</x:v>
+        <x:v>46066</x:v>
       </x:c>
       <x:c r="J33" s="15" t="s">
         <x:v>326</x:v>
       </x:c>
       <x:c r="K33" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L33" s="18">
-        <x:v>46097.1600206018</x:v>
+        <x:v>46100.3754893056</x:v>
       </x:c>
       <x:c r="M33" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5887,10 +5900,10 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="H34" s="16">
-        <x:v>46084.1225139699</x:v>
+        <x:v>46083.2443981019</x:v>
       </x:c>
       <x:c r="I34" s="16">
-        <x:v>46172</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J34" s="15" t="s">
         <x:v>331</x:v>
@@ -5899,10 +5912,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L34" s="18">
-        <x:v>46097.3505144329</x:v>
+        <x:v>46097.1600206018</x:v>
       </x:c>
       <x:c r="M34" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
@@ -5925,22 +5938,22 @@
         <x:v>335</x:v>
       </x:c>
       <x:c r="H35" s="16">
-        <x:v>46073.1541139005</x:v>
+        <x:v>46084.1225139699</x:v>
       </x:c>
       <x:c r="I35" s="16">
-        <x:v>46030</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J35" s="15" t="s">
         <x:v>336</x:v>
       </x:c>
       <x:c r="K35" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L35" s="18">
-        <x:v>46099.1584012616</x:v>
+        <x:v>46097.3505144329</x:v>
       </x:c>
       <x:c r="M35" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
@@ -5963,22 +5976,22 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="H36" s="16">
-        <x:v>46083.252116412</x:v>
+        <x:v>46073.1541139005</x:v>
       </x:c>
       <x:c r="I36" s="16">
-        <x:v>46100</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J36" s="15" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="K36" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L36" s="18">
-        <x:v>46097.1628986343</x:v>
+        <x:v>46099.1584012616</x:v>
       </x:c>
       <x:c r="M36" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
@@ -6001,7 +6014,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="H37" s="16">
-        <x:v>46097.4788515162</x:v>
+        <x:v>46083.252116412</x:v>
       </x:c>
       <x:c r="I37" s="16">
         <x:v>46100</x:v>
@@ -6013,10 +6026,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="18">
-        <x:v>46100.2987549074</x:v>
+        <x:v>46097.1628986343</x:v>
       </x:c>
       <x:c r="M37" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -6039,10 +6052,10 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="H38" s="16">
-        <x:v>46069.3341180556</x:v>
+        <x:v>46097.4788515162</x:v>
       </x:c>
       <x:c r="I38" s="16">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J38" s="15" t="s">
         <x:v>351</x:v>
@@ -6051,10 +6064,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="18">
-        <x:v>46097.244735544</x:v>
+        <x:v>46100.2987549074</x:v>
       </x:c>
       <x:c r="M38" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -6068,31 +6081,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E39" s="14" t="s">
-        <x:v>328</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F39" s="14" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="G39" s="14" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="H39" s="16">
-        <x:v>46084.1513040509</x:v>
+        <x:v>46069.3341180556</x:v>
       </x:c>
       <x:c r="I39" s="16">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J39" s="15" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="K39" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="18">
-        <x:v>46097.2494578472</x:v>
+        <x:v>46097.244735544</x:v>
       </x:c>
       <x:c r="M39" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
@@ -6100,13 +6113,13 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C40" s="14" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="D40" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E40" s="14" t="s">
-        <x:v>357</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="F40" s="14" t="s">
         <x:v>358</x:v>
@@ -6115,22 +6128,22 @@
         <x:v>359</x:v>
       </x:c>
       <x:c r="H40" s="16">
-        <x:v>46073.1135088426</x:v>
+        <x:v>46084.1513040509</x:v>
       </x:c>
       <x:c r="I40" s="16">
-        <x:v>45751</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J40" s="15" t="s">
         <x:v>360</x:v>
       </x:c>
       <x:c r="K40" s="17" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L40" s="18">
-        <x:v>46097.2511403241</x:v>
+        <x:v>46097.2494578472</x:v>
       </x:c>
       <x:c r="M40" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
@@ -6138,37 +6151,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C41" s="14" t="s">
-        <x:v>356</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="D41" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E41" s="14" t="s">
-        <x:v>361</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F41" s="14" t="s">
-        <x:v>362</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="G41" s="14" t="s">
-        <x:v>363</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="H41" s="16">
-        <x:v>46069.1151616435</x:v>
+        <x:v>46073.1135088426</x:v>
       </x:c>
       <x:c r="I41" s="16">
-        <x:v>46172</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J41" s="15" t="s">
-        <x:v>364</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="K41" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L41" s="18">
-        <x:v>46097.343386956</x:v>
+        <x:v>46097.2511403241</x:v>
       </x:c>
       <x:c r="M41" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
@@ -6176,37 +6189,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C42" s="14" t="s">
-        <x:v>356</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="D42" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E42" s="14" t="s">
-        <x:v>365</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="F42" s="14" t="s">
-        <x:v>366</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="G42" s="14" t="s">
-        <x:v>367</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="H42" s="16">
-        <x:v>46084.3311976389</x:v>
+        <x:v>46069.1151616435</x:v>
       </x:c>
       <x:c r="I42" s="16">
-        <x:v>46070</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J42" s="15" t="s">
-        <x:v>368</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K42" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L42" s="18">
-        <x:v>46093.3668852546</x:v>
+        <x:v>46097.343386956</x:v>
       </x:c>
       <x:c r="M42" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
@@ -6214,37 +6227,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C43" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="D43" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E43" s="14" t="s">
-        <x:v>369</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F43" s="14" t="s">
-        <x:v>370</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="G43" s="14" t="s">
-        <x:v>371</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="H43" s="16">
-        <x:v>46097.4214954398</x:v>
+        <x:v>46084.3311976389</x:v>
       </x:c>
       <x:c r="I43" s="16">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J43" s="15" t="s">
-        <x:v>372</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="K43" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L43" s="18">
-        <x:v>46100.2966699421</x:v>
+        <x:v>46093.3668852546</x:v>
       </x:c>
       <x:c r="M43" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
@@ -6258,31 +6271,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E44" s="14" t="s">
-        <x:v>373</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F44" s="14" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="G44" s="14" t="s">
-        <x:v>375</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="H44" s="16">
-        <x:v>46092.1012814815</x:v>
+        <x:v>46097.4214954398</x:v>
       </x:c>
       <x:c r="I44" s="16">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J44" s="15" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="K44" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="18">
-        <x:v>46097.1408234491</x:v>
+        <x:v>46100.2966699421</x:v>
       </x:c>
       <x:c r="M44" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
@@ -6290,7 +6303,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C45" s="14" t="s">
-        <x:v>377</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D45" s="15" t="s">
         <x:v>61</x:v>
@@ -6305,10 +6318,10 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="H45" s="16">
-        <x:v>46069.1217257292</x:v>
+        <x:v>46092.1012814815</x:v>
       </x:c>
       <x:c r="I45" s="16">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J45" s="15" t="s">
         <x:v>381</x:v>
@@ -6317,10 +6330,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="18">
-        <x:v>46097.3375062153</x:v>
+        <x:v>46097.1408234491</x:v>
       </x:c>
       <x:c r="M45" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
@@ -6328,37 +6341,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C46" s="14" t="s">
-        <x:v>377</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D46" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E46" s="14" t="s">
-        <x:v>382</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F46" s="14" t="s">
-        <x:v>383</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="G46" s="14" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="H46" s="16">
-        <x:v>46069.2327997454</x:v>
+        <x:v>46069.1217257292</x:v>
       </x:c>
       <x:c r="I46" s="16">
-        <x:v>46049</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J46" s="15" t="s">
-        <x:v>385</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="K46" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L46" s="18">
-        <x:v>46100.3816829514</x:v>
+        <x:v>46097.3375062153</x:v>
       </x:c>
       <x:c r="M46" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
@@ -6366,7 +6379,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C47" s="14" t="s">
-        <x:v>386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D47" s="15" t="s">
         <x:v>61</x:v>
@@ -6381,33 +6394,33 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="H47" s="16">
-        <x:v>46086.106481875</x:v>
+        <x:v>46069.2327997454</x:v>
       </x:c>
       <x:c r="I47" s="16">
-        <x:v>46095</x:v>
+        <x:v>46049</x:v>
       </x:c>
       <x:c r="J47" s="15" t="s">
         <x:v>390</x:v>
       </x:c>
       <x:c r="K47" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L47" s="18">
-        <x:v>46090.2765830324</x:v>
+        <x:v>46100.3816829514</x:v>
       </x:c>
       <x:c r="M47" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B48" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C48" s="14" t="s">
         <x:v>391</x:v>
       </x:c>
       <x:c r="D48" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E48" s="14" t="s">
         <x:v>392</x:v>
@@ -6419,22 +6432,22 @@
         <x:v>394</x:v>
       </x:c>
       <x:c r="H48" s="16">
-        <x:v>46084.3419451968</x:v>
+        <x:v>46086.106481875</x:v>
       </x:c>
       <x:c r="I48" s="16">
-        <x:v>46084.3419617014</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="J48" s="15" t="s">
         <x:v>395</x:v>
       </x:c>
       <x:c r="K48" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L48" s="18">
-        <x:v>46090.3480933681</x:v>
+        <x:v>46090.2765830324</x:v>
       </x:c>
       <x:c r="M48" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="16.798828" customHeight="1">
@@ -6442,34 +6455,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C49" s="14" t="s">
-        <x:v>391</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="D49" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E49" s="14" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="F49" s="14" t="s">
-        <x:v>397</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="G49" s="14" t="s">
-        <x:v>398</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="H49" s="16">
-        <x:v>46085.1627479398</x:v>
+        <x:v>46084.3419451968</x:v>
       </x:c>
       <x:c r="I49" s="16">
-        <x:v>46085.1627651505</x:v>
+        <x:v>46084.3419617014</x:v>
       </x:c>
       <x:c r="J49" s="15" t="s">
-        <x:v>399</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="K49" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L49" s="18">
-        <x:v>46090.3453534259</x:v>
+        <x:v>46090.3480933681</x:v>
       </x:c>
       <x:c r="M49" s="14" t="s">
         <x:v>27</x:v>
@@ -6480,34 +6493,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C50" s="14" t="s">
-        <x:v>391</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="D50" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E50" s="14" t="s">
-        <x:v>400</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="F50" s="14" t="s">
-        <x:v>401</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="G50" s="14" t="s">
-        <x:v>402</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="H50" s="16">
-        <x:v>46085.1662527662</x:v>
+        <x:v>46085.1627479398</x:v>
       </x:c>
       <x:c r="I50" s="16">
-        <x:v>46085.1662689699</x:v>
+        <x:v>46085.1627651505</x:v>
       </x:c>
       <x:c r="J50" s="15" t="s">
-        <x:v>399</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="K50" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L50" s="18">
-        <x:v>46090.3437343634</x:v>
+        <x:v>46090.3453534259</x:v>
       </x:c>
       <x:c r="M50" s="14" t="s">
         <x:v>27</x:v>
@@ -6518,34 +6531,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C51" s="14" t="s">
-        <x:v>391</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="D51" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E51" s="14" t="s">
-        <x:v>403</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F51" s="14" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="G51" s="14" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="H51" s="16">
+        <x:v>46085.1662527662</x:v>
+      </x:c>
+      <x:c r="I51" s="16">
+        <x:v>46085.1662689699</x:v>
+      </x:c>
+      <x:c r="J51" s="15" t="s">
         <x:v>404</x:v>
-      </x:c>
-      <x:c r="G51" s="14" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="H51" s="16">
-        <x:v>46085.1709247338</x:v>
-      </x:c>
-      <x:c r="I51" s="16">
-        <x:v>46085.1709419676</x:v>
-      </x:c>
-      <x:c r="J51" s="15" t="s">
-        <x:v>406</x:v>
       </x:c>
       <x:c r="K51" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L51" s="18">
-        <x:v>46090.3337014815</x:v>
+        <x:v>46090.3437343634</x:v>
       </x:c>
       <x:c r="M51" s="14" t="s">
         <x:v>27</x:v>
@@ -6553,13 +6566,13 @@
     </x:row>
     <x:row r="52" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B52" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C52" s="14" t="s">
-        <x:v>407</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="D52" s="15" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E52" s="14" t="s">
         <x:v>408</x:v>
@@ -6571,22 +6584,22 @@
         <x:v>410</x:v>
       </x:c>
       <x:c r="H52" s="16">
-        <x:v>46084.1579541898</x:v>
+        <x:v>46085.1709247338</x:v>
       </x:c>
       <x:c r="I52" s="16">
-        <x:v>46145</x:v>
+        <x:v>46085.1709419676</x:v>
       </x:c>
       <x:c r="J52" s="15" t="s">
         <x:v>411</x:v>
       </x:c>
       <x:c r="K52" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L52" s="18">
-        <x:v>46093.4169326042</x:v>
+        <x:v>46090.3337014815</x:v>
       </x:c>
       <x:c r="M52" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
@@ -6594,37 +6607,37 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C53" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="D53" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E53" s="14" t="s">
-        <x:v>412</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F53" s="14" t="s">
-        <x:v>413</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="G53" s="14" t="s">
-        <x:v>414</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="H53" s="16">
-        <x:v>46084.1080380324</x:v>
+        <x:v>46084.1579541898</x:v>
       </x:c>
       <x:c r="I53" s="16">
-        <x:v>46103</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J53" s="15" t="s">
-        <x:v>415</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="K53" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L53" s="18">
-        <x:v>46097.2478153472</x:v>
+        <x:v>46093.4169326042</x:v>
       </x:c>
       <x:c r="M53" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
@@ -6632,7 +6645,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C54" s="14" t="s">
-        <x:v>416</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D54" s="15" t="s">
         <x:v>61</x:v>
@@ -6647,10 +6660,10 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="H54" s="16">
-        <x:v>46083.0788057755</x:v>
+        <x:v>46084.1080380324</x:v>
       </x:c>
       <x:c r="I54" s="16">
-        <x:v>46084</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J54" s="15" t="s">
         <x:v>420</x:v>
@@ -6659,10 +6672,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L54" s="18">
-        <x:v>46083.1042250116</x:v>
+        <x:v>46097.2478153472</x:v>
       </x:c>
       <x:c r="M54" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="16.798828" customHeight="1">
@@ -6670,37 +6683,37 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C55" s="14" t="s">
-        <x:v>352</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="D55" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E55" s="14" t="s">
-        <x:v>421</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="F55" s="14" t="s">
-        <x:v>422</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="G55" s="14" t="s">
-        <x:v>423</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="H55" s="16">
-        <x:v>46084.1627466204</x:v>
+        <x:v>46083.0788057755</x:v>
       </x:c>
       <x:c r="I55" s="16">
-        <x:v>46060</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J55" s="15" t="s">
-        <x:v>424</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="K55" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L55" s="18">
-        <x:v>46100.392939537</x:v>
+        <x:v>46083.1042250116</x:v>
       </x:c>
       <x:c r="M55" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="16.798828" customHeight="1">
@@ -6708,37 +6721,37 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C56" s="14" t="s">
-        <x:v>386</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="D56" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E56" s="14" t="s">
-        <x:v>425</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="F56" s="14" t="s">
-        <x:v>426</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="G56" s="14" t="s">
-        <x:v>427</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H56" s="16">
-        <x:v>46086.1144463079</x:v>
+        <x:v>46084.1627466204</x:v>
       </x:c>
       <x:c r="I56" s="16">
-        <x:v>46097</x:v>
+        <x:v>46060</x:v>
       </x:c>
       <x:c r="J56" s="15" t="s">
-        <x:v>428</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="K56" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L56" s="18">
-        <x:v>46090.2703739352</x:v>
+        <x:v>46100.392939537</x:v>
       </x:c>
       <x:c r="M56" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="16.798828" customHeight="1">
@@ -6746,34 +6759,34 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C57" s="14" t="s">
-        <x:v>386</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D57" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E57" s="14" t="s">
-        <x:v>429</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F57" s="14" t="s">
-        <x:v>430</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="G57" s="14" t="s">
-        <x:v>431</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="H57" s="16">
-        <x:v>46087.1643336806</x:v>
+        <x:v>46086.1144463079</x:v>
       </x:c>
       <x:c r="I57" s="16">
-        <x:v>46104</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J57" s="15" t="s">
-        <x:v>432</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="K57" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L57" s="18">
-        <x:v>46090.2727784143</x:v>
+        <x:v>46090.2703739352</x:v>
       </x:c>
       <x:c r="M57" s="14" t="s">
         <x:v>99</x:v>
@@ -6784,34 +6797,34 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C58" s="14" t="s">
-        <x:v>386</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D58" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E58" s="14" t="s">
-        <x:v>433</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="F58" s="14" t="s">
-        <x:v>434</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="G58" s="14" t="s">
-        <x:v>435</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H58" s="16">
-        <x:v>46086.099798588</x:v>
+        <x:v>46087.1643336806</x:v>
       </x:c>
       <x:c r="I58" s="16">
-        <x:v>46098</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J58" s="15" t="s">
-        <x:v>436</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="K58" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L58" s="18">
-        <x:v>46090.2691152778</x:v>
+        <x:v>46090.2727784143</x:v>
       </x:c>
       <x:c r="M58" s="14" t="s">
         <x:v>99</x:v>
@@ -6819,10 +6832,10 @@
     </x:row>
     <x:row r="59" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B59" s="14" t="s">
-        <x:v>170</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C59" s="14" t="s">
-        <x:v>437</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D59" s="15" t="s">
         <x:v>61</x:v>
@@ -6837,19 +6850,19 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="H59" s="16">
-        <x:v>46098.290884375</x:v>
+        <x:v>46086.099798588</x:v>
       </x:c>
       <x:c r="I59" s="16">
-        <x:v>45997</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J59" s="15" t="s">
         <x:v>441</x:v>
       </x:c>
       <x:c r="K59" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L59" s="18">
-        <x:v>46098.3188767824</x:v>
+        <x:v>46090.2691152778</x:v>
       </x:c>
       <x:c r="M59" s="14" t="s">
         <x:v>99</x:v>
@@ -6875,22 +6888,22 @@
         <x:v>445</x:v>
       </x:c>
       <x:c r="H60" s="16">
-        <x:v>46092.9637875116</x:v>
+        <x:v>46098.290884375</x:v>
       </x:c>
       <x:c r="I60" s="16">
-        <x:v>46094</x:v>
+        <x:v>45997</x:v>
       </x:c>
       <x:c r="J60" s="15" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="K60" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L60" s="18">
-        <x:v>46093.3109466551</x:v>
+        <x:v>46098.3188767824</x:v>
       </x:c>
       <x:c r="M60" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
@@ -6913,10 +6926,10 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="H61" s="16">
-        <x:v>46083.0936215278</x:v>
+        <x:v>46092.9637875116</x:v>
       </x:c>
       <x:c r="I61" s="16">
-        <x:v>46084</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J61" s="15" t="s">
         <x:v>451</x:v>
@@ -6925,112 +6938,149 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L61" s="18">
+        <x:v>46093.3109466551</x:v>
+      </x:c>
+      <x:c r="M61" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B62" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C62" s="14" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="D62" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E62" s="14" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="G62" s="14" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="H62" s="16">
+        <x:v>46083.0936215278</x:v>
+      </x:c>
+      <x:c r="I62" s="16">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J62" s="15" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="K62" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L62" s="18">
         <x:v>46083.1543707755</x:v>
       </x:c>
-      <x:c r="M61" s="14" t="s">
+      <x:c r="M62" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B64" s="19" t="s">
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B65" s="19" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="C64" s="20" t="s"/>
-      <x:c r="D64" s="20" t="s"/>
-      <x:c r="E64" s="21" t="s"/>
-      <x:c r="F64" s="21" t="s"/>
-    </x:row>
-    <x:row r="65" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B65" s="22" t="s">
+      <x:c r="C65" s="20" t="s"/>
+      <x:c r="D65" s="20" t="s"/>
+      <x:c r="E65" s="21" t="s"/>
+      <x:c r="F65" s="21" t="s"/>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B66" s="22" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C65" s="23" t="s"/>
-      <x:c r="D65" s="23" t="s"/>
-      <x:c r="E65" s="23" t="s"/>
-      <x:c r="F65" s="24" t="s">
+      <x:c r="C66" s="23" t="s"/>
+      <x:c r="D66" s="23" t="s"/>
+      <x:c r="E66" s="23" t="s"/>
+      <x:c r="F66" s="24" t="s">
         <x:v>204</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B66" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C66" s="26" t="s"/>
-      <x:c r="D66" s="26" t="s"/>
-      <x:c r="E66" s="26" t="s"/>
-      <x:c r="F66" s="27" t="n">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:28" ht="18" customHeight="1">
       <x:c r="B67" s="25" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C67" s="26" t="s"/>
       <x:c r="D67" s="26" t="s"/>
       <x:c r="E67" s="26" t="s"/>
       <x:c r="F67" s="27" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:28" ht="18" customHeight="1">
       <x:c r="B68" s="25" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C68" s="26" t="s"/>
       <x:c r="D68" s="26" t="s"/>
       <x:c r="E68" s="26" t="s"/>
       <x:c r="F68" s="27" t="n">
-        <x:v>31</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:28" ht="18" customHeight="1">
       <x:c r="B69" s="25" t="s">
-        <x:v>93</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C69" s="26" t="s"/>
       <x:c r="D69" s="26" t="s"/>
       <x:c r="E69" s="26" t="s"/>
       <x:c r="F69" s="27" t="n">
-        <x:v>4</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:28" ht="18" customHeight="1">
       <x:c r="B70" s="25" t="s">
-        <x:v>110</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C70" s="26" t="s"/>
       <x:c r="D70" s="26" t="s"/>
       <x:c r="E70" s="26" t="s"/>
       <x:c r="F70" s="27" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:28" ht="18" customHeight="1">
       <x:c r="B71" s="25" t="s">
-        <x:v>170</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C71" s="26" t="s"/>
       <x:c r="D71" s="26" t="s"/>
       <x:c r="E71" s="26" t="s"/>
       <x:c r="F71" s="27" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B72" s="25" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C72" s="26" t="s"/>
+      <x:c r="D72" s="26" t="s"/>
+      <x:c r="E72" s="26" t="s"/>
+      <x:c r="F72" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B72" s="28" t="s">
+    <x:row r="73" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B73" s="28" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="C72" s="29" t="s"/>
-      <x:c r="D72" s="29" t="s"/>
-      <x:c r="E72" s="29" t="s"/>
-      <x:c r="F72" s="30" t="n">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C73" s="29" t="s"/>
+      <x:c r="D73" s="29" t="s"/>
+      <x:c r="E73" s="29" t="s"/>
+      <x:c r="F73" s="30" t="n">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
     <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7957,8 +8007,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B64:F64"/>
-    <x:mergeCell ref="B65:E65"/>
+    <x:mergeCell ref="B65:F65"/>
     <x:mergeCell ref="B66:E66"/>
     <x:mergeCell ref="B67:E67"/>
     <x:mergeCell ref="B68:E68"/>
@@ -7966,6 +8015,7 @@
     <x:mergeCell ref="B70:E70"/>
     <x:mergeCell ref="B71:E71"/>
     <x:mergeCell ref="B72:E72"/>
+    <x:mergeCell ref="B73:E73"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="457">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -805,6 +805,18 @@
     <x:t>1511234</x:t>
   </x:si>
   <x:si>
+    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0781 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1144-933</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511232</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -817,18 +829,6 @@
     <x:t>1511233</x:t>
   </x:si>
   <x:si>
-    <x:t>C-24 SM City Rosario, Gen. Trias Dr.,, Tejeros Convention,, Rosario, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0781 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1144-933</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511232</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELL EVER MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -847,6 +847,18 @@
     <x:t>CELLBLITZ MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>SM CITY BATANGAS, PALLOCAN KANLURAN, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 23- 019R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1095-163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511194</x:t>
+  </x:si>
+  <x:si>
     <x:t>LG05 SM MARKETMALL, BUROL I, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -862,21 +874,21 @@
     <x:t>Caesar Allen Centeno</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY BATANGAS, PALLOCAN KANLURAN, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 23- 019R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1095-163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511194</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-020R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1156-896</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511192</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY BACOOR CZ430, HABAY II, Bacoor City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -889,21 +901,33 @@
     <x:t>1511225</x:t>
   </x:si>
   <x:si>
-    <x:t>WALTERMART CABUYAO KM 47 NATIONAL HIWAY, BANLIC, Cabuyao City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-020R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1156-896</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511192</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1111-408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511278</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511193</x:t>
+  </x:si>
+  <x:si>
     <x:t>108 WALTERMART SILANG GEN AGUINALDO HIGHWAY, SAN VICENTE II, Silang, Cavite</x:t>
   </x:si>
   <x:si>
@@ -916,6 +940,18 @@
     <x:t>1511206</x:t>
   </x:si>
   <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511224</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -928,42 +964,6 @@
     <x:t>1511223</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511224</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467-24R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1096-022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511193</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-24-451R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1111-408</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511278</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -1147,6 +1147,18 @@
     <x:t>1511222</x:t>
   </x:si>
   <x:si>
+    <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0775 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1192-904</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511231</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
   </x:si>
   <x:si>
@@ -1159,21 +1171,21 @@
     <x:t>1511270</x:t>
   </x:si>
   <x:si>
-    <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0775 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1192-904</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511231</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>AYALA MALLS SERIN JUNCTION EAST, SILANG, Tagaytay City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-20-01-0883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1087-228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511275</x:t>
+  </x:si>
+  <x:si>
     <x:t>LEVEL 3, 306A, BRGY. TEJERO, General Trias, Cavite</x:t>
   </x:si>
   <x:si>
@@ -1186,18 +1198,6 @@
     <x:t>1511240</x:t>
   </x:si>
   <x:si>
-    <x:t>AYALA MALLS SERIN JUNCTION EAST, SILANG, Tagaytay City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-20-01-0883</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1087-228</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511275</x:t>
-  </x:si>
-  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -1213,9 +1213,36 @@
     <x:t>1511761</x:t>
   </x:si>
   <x:si>
+    <x:t>GIZHUB GADGETS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95 CZK-16 2nd Floor SM San Mateo General Luna Street, Ampid 1, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-0004C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1219-996</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511284</x:t>
+  </x:si>
+  <x:si>
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-26-03-2518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1172-434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507965</x:t>
+  </x:si>
+  <x:si>
     <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
   </x:si>
   <x:si>
@@ -1249,18 +1276,6 @@
     <x:t>43A-3-2026-1171-081</x:t>
   </x:si>
   <x:si>
-    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-26-03-2518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1172-434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507965</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
   </x:si>
   <x:si>
@@ -1315,6 +1330,30 @@
     <x:t>1511277</x:t>
   </x:si>
   <x:si>
+    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-03-2015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1173-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511758</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-18-02-2106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1176-385</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511760</x:t>
+  </x:si>
+  <x:si>
     <x:t>Octagon 2nd floor, Robinson Place Lipa Robinsons Place Lipa, Mataas na Lupa, Lipa City, Batangas</x:t>
   </x:si>
   <x:si>
@@ -1327,28 +1366,43 @@
     <x:t>1511759</x:t>
   </x:si>
   <x:si>
-    <x:t>Octagon 2nd floor Cyberzone SM City Lipa Ayala Highway, Maraouy, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-18-02-2106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1176-385</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511760</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microvalley, 2nd floor Cyberzone SM City Batangas SM Batangas, Pallocan West, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-03-2015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1173-016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511758</x:t>
+    <x:t>YUXU CELLPHONE AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTC2-K106 B47 Xentro Mall E. Rodriguez Highway Cor.Reyes, Manggahan, Rodriguez (Montalban), Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-325-455R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1216-073</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511285</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTC-K-127 Tanay  Town Center F.T Catapusan, Plaza  Aldea, Tanay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-325-453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1217-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511286</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTC2-K119 Montaban Town Center E. Rodriguez, San Jose, Rodriguez (Montalban), Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-325-454R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1218-177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511287</x:t>
   </x:si>
   <x:si>
     <x:t>CELLBOY INC.</x:t>
@@ -5330,10 +5384,10 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46083.2322339931</x:v>
+        <x:v>46080.4532551852</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
         <x:v>263</x:v>
@@ -5342,7 +5396,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46097.1495293519</x:v>
+        <x:v>46097.1461728357</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>245</x:v>
@@ -5368,10 +5422,10 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46080.4532551852</x:v>
+        <x:v>46083.2322339931</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>267</x:v>
@@ -5380,7 +5434,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46097.1461728357</x:v>
+        <x:v>46097.1495293519</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>245</x:v>
@@ -5444,22 +5498,22 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46069.278571956</x:v>
+        <x:v>46069.3514850347</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46067</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
         <x:v>277</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46100.3884108912</x:v>
+        <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -5473,31 +5527,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="G23" s="14" t="s">
+      <x:c r="H23" s="16">
+        <x:v>46069.278571956</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46069.3514850347</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
+      <x:c r="K23" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46100.3884108912</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
@@ -5520,10 +5574,10 @@
         <x:v>286</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46084.0854516898</x:v>
+        <x:v>46084.0996762384</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46144</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
         <x:v>287</x:v>
@@ -5532,7 +5586,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46093.3956400694</x:v>
+        <x:v>46097.241468588</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>245</x:v>
@@ -5558,10 +5612,10 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46084.0996762384</x:v>
+        <x:v>46084.0854516898</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46094</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
         <x:v>291</x:v>
@@ -5570,7 +5624,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46097.241468588</x:v>
+        <x:v>46093.3956400694</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>245</x:v>
@@ -5596,10 +5650,10 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46069.1542109954</x:v>
+        <x:v>46073.1441202083</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46035</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
         <x:v>296</x:v>
@@ -5608,10 +5662,10 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46097.2466610301</x:v>
+        <x:v>46100.4005466667</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
@@ -5634,10 +5688,10 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46084.2189288542</x:v>
+        <x:v>46069.3573124306</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46133</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
         <x:v>300</x:v>
@@ -5646,7 +5700,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46093.3723926852</x:v>
+        <x:v>46097.2426396643</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
         <x:v>245</x:v>
@@ -5672,19 +5726,19 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46084.2250188542</x:v>
+        <x:v>46069.1542109954</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46144</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
         <x:v>304</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L28" s="18">
-        <x:v>46093.3804507639</x:v>
+        <x:v>46097.2466610301</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
         <x:v>245</x:v>
@@ -5710,10 +5764,10 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46069.3573124306</x:v>
+        <x:v>46084.2250188542</x:v>
       </x:c>
       <x:c r="I29" s="16">
-        <x:v>46100</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J29" s="15" t="s">
         <x:v>308</x:v>
@@ -5722,7 +5776,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="18">
-        <x:v>46097.2426396643</x:v>
+        <x:v>46093.3804507639</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
         <x:v>245</x:v>
@@ -5748,22 +5802,22 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="H30" s="16">
-        <x:v>46073.1441202083</x:v>
+        <x:v>46084.2189288542</x:v>
       </x:c>
       <x:c r="I30" s="16">
-        <x:v>46030</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J30" s="15" t="s">
         <x:v>312</x:v>
       </x:c>
       <x:c r="K30" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L30" s="18">
-        <x:v>46100.4005466667</x:v>
+        <x:v>46093.3723926852</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
@@ -5877,7 +5931,7 @@
         <x:v>46100.3754893056</x:v>
       </x:c>
       <x:c r="M33" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -6067,7 +6121,7 @@
         <x:v>46100.2987549074</x:v>
       </x:c>
       <x:c r="M38" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -6280,7 +6334,7 @@
         <x:v>376</x:v>
       </x:c>
       <x:c r="H44" s="16">
-        <x:v>46097.4214954398</x:v>
+        <x:v>46092.1012814815</x:v>
       </x:c>
       <x:c r="I44" s="16">
         <x:v>46100</x:v>
@@ -6292,10 +6346,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="18">
-        <x:v>46100.2966699421</x:v>
+        <x:v>46097.1408234491</x:v>
       </x:c>
       <x:c r="M44" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
@@ -6318,7 +6372,7 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="H45" s="16">
-        <x:v>46092.1012814815</x:v>
+        <x:v>46097.4214954398</x:v>
       </x:c>
       <x:c r="I45" s="16">
         <x:v>46100</x:v>
@@ -6330,10 +6384,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="18">
-        <x:v>46097.1408234491</x:v>
+        <x:v>46100.2966699421</x:v>
       </x:c>
       <x:c r="M45" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
@@ -6356,22 +6410,22 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="H46" s="16">
-        <x:v>46069.1217257292</x:v>
+        <x:v>46069.2327997454</x:v>
       </x:c>
       <x:c r="I46" s="16">
-        <x:v>46157</x:v>
+        <x:v>46049</x:v>
       </x:c>
       <x:c r="J46" s="15" t="s">
         <x:v>386</x:v>
       </x:c>
       <x:c r="K46" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L46" s="18">
-        <x:v>46097.3375062153</x:v>
+        <x:v>46100.3816829514</x:v>
       </x:c>
       <x:c r="M46" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
@@ -6394,22 +6448,22 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="H47" s="16">
-        <x:v>46069.2327997454</x:v>
+        <x:v>46069.1217257292</x:v>
       </x:c>
       <x:c r="I47" s="16">
-        <x:v>46049</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J47" s="15" t="s">
         <x:v>390</x:v>
       </x:c>
       <x:c r="K47" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="18">
-        <x:v>46100.3816829514</x:v>
+        <x:v>46097.3375062153</x:v>
       </x:c>
       <x:c r="M47" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
@@ -6470,10 +6524,10 @@
         <x:v>399</x:v>
       </x:c>
       <x:c r="H49" s="16">
-        <x:v>46084.3419451968</x:v>
+        <x:v>46104.1922695255</x:v>
       </x:c>
       <x:c r="I49" s="16">
-        <x:v>46084.3419617014</x:v>
+        <x:v>46104.1922873958</x:v>
       </x:c>
       <x:c r="J49" s="15" t="s">
         <x:v>400</x:v>
@@ -6482,10 +6536,10 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L49" s="18">
-        <x:v>46090.3480933681</x:v>
+        <x:v>46104.342277338</x:v>
       </x:c>
       <x:c r="M49" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="16.798828" customHeight="1">
@@ -6493,34 +6547,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C50" s="14" t="s">
-        <x:v>396</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="D50" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E50" s="14" t="s">
-        <x:v>401</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F50" s="14" t="s">
-        <x:v>402</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G50" s="14" t="s">
-        <x:v>403</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="H50" s="16">
-        <x:v>46085.1627479398</x:v>
+        <x:v>46085.1709247338</x:v>
       </x:c>
       <x:c r="I50" s="16">
-        <x:v>46085.1627651505</x:v>
+        <x:v>46085.1709419676</x:v>
       </x:c>
       <x:c r="J50" s="15" t="s">
-        <x:v>404</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="K50" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L50" s="18">
-        <x:v>46090.3453534259</x:v>
+        <x:v>46090.3337014815</x:v>
       </x:c>
       <x:c r="M50" s="14" t="s">
         <x:v>27</x:v>
@@ -6531,34 +6585,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C51" s="14" t="s">
-        <x:v>396</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="D51" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E51" s="14" t="s">
-        <x:v>405</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="F51" s="14" t="s">
-        <x:v>406</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="G51" s="14" t="s">
-        <x:v>407</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="H51" s="16">
-        <x:v>46085.1662527662</x:v>
+        <x:v>46084.3419451968</x:v>
       </x:c>
       <x:c r="I51" s="16">
-        <x:v>46085.1662689699</x:v>
+        <x:v>46084.3419617014</x:v>
       </x:c>
       <x:c r="J51" s="15" t="s">
-        <x:v>404</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="K51" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L51" s="18">
-        <x:v>46090.3437343634</x:v>
+        <x:v>46090.3480933681</x:v>
       </x:c>
       <x:c r="M51" s="14" t="s">
         <x:v>27</x:v>
@@ -6569,34 +6623,34 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C52" s="14" t="s">
-        <x:v>396</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="D52" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E52" s="14" t="s">
-        <x:v>408</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="F52" s="14" t="s">
-        <x:v>409</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="G52" s="14" t="s">
-        <x:v>410</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="H52" s="16">
-        <x:v>46085.1709247338</x:v>
+        <x:v>46085.1627479398</x:v>
       </x:c>
       <x:c r="I52" s="16">
-        <x:v>46085.1709419676</x:v>
+        <x:v>46085.1627651505</x:v>
       </x:c>
       <x:c r="J52" s="15" t="s">
-        <x:v>411</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="K52" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L52" s="18">
-        <x:v>46090.3337014815</x:v>
+        <x:v>46090.3453534259</x:v>
       </x:c>
       <x:c r="M52" s="14" t="s">
         <x:v>27</x:v>
@@ -6604,40 +6658,40 @@
     </x:row>
     <x:row r="53" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B53" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C53" s="14" t="s">
-        <x:v>412</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="D53" s="15" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E53" s="14" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="G53" s="14" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="H53" s="16">
+        <x:v>46085.1662527662</x:v>
+      </x:c>
+      <x:c r="I53" s="16">
+        <x:v>46085.1662689699</x:v>
+      </x:c>
+      <x:c r="J53" s="15" t="s">
         <x:v>413</x:v>
       </x:c>
-      <x:c r="F53" s="14" t="s">
-        <x:v>414</x:v>
-      </x:c>
-      <x:c r="G53" s="14" t="s">
-        <x:v>415</x:v>
-      </x:c>
-      <x:c r="H53" s="16">
-        <x:v>46084.1579541898</x:v>
-      </x:c>
-      <x:c r="I53" s="16">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J53" s="15" t="s">
-        <x:v>416</x:v>
-      </x:c>
       <x:c r="K53" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L53" s="18">
-        <x:v>46093.4169326042</x:v>
+        <x:v>46090.3437343634</x:v>
       </x:c>
       <x:c r="M53" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="16.798828" customHeight="1">
@@ -6645,34 +6699,34 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C54" s="14" t="s">
-        <x:v>283</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="D54" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E54" s="14" t="s">
-        <x:v>417</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F54" s="14" t="s">
-        <x:v>418</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="G54" s="14" t="s">
-        <x:v>419</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="H54" s="16">
-        <x:v>46084.1080380324</x:v>
+        <x:v>46084.1579541898</x:v>
       </x:c>
       <x:c r="I54" s="16">
-        <x:v>46103</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J54" s="15" t="s">
-        <x:v>420</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="K54" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L54" s="18">
-        <x:v>46097.2478153472</x:v>
+        <x:v>46093.4169326042</x:v>
       </x:c>
       <x:c r="M54" s="14" t="s">
         <x:v>245</x:v>
@@ -6683,7 +6737,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C55" s="14" t="s">
-        <x:v>421</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D55" s="15" t="s">
         <x:v>61</x:v>
@@ -6698,10 +6752,10 @@
         <x:v>424</x:v>
       </x:c>
       <x:c r="H55" s="16">
-        <x:v>46083.0788057755</x:v>
+        <x:v>46084.1080380324</x:v>
       </x:c>
       <x:c r="I55" s="16">
-        <x:v>46084</x:v>
+        <x:v>46103</x:v>
       </x:c>
       <x:c r="J55" s="15" t="s">
         <x:v>425</x:v>
@@ -6710,10 +6764,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L55" s="18">
-        <x:v>46083.1042250116</x:v>
+        <x:v>46097.2478153472</x:v>
       </x:c>
       <x:c r="M55" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="16.798828" customHeight="1">
@@ -6721,37 +6775,37 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C56" s="14" t="s">
-        <x:v>357</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D56" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E56" s="14" t="s">
-        <x:v>426</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="F56" s="14" t="s">
-        <x:v>427</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="G56" s="14" t="s">
-        <x:v>428</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="H56" s="16">
-        <x:v>46084.1627466204</x:v>
+        <x:v>46083.0788057755</x:v>
       </x:c>
       <x:c r="I56" s="16">
-        <x:v>46060</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J56" s="15" t="s">
-        <x:v>429</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="K56" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L56" s="18">
-        <x:v>46100.392939537</x:v>
+        <x:v>46083.1042250116</x:v>
       </x:c>
       <x:c r="M56" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="16.798828" customHeight="1">
@@ -6759,37 +6813,37 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="C57" s="14" t="s">
-        <x:v>391</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="D57" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E57" s="14" t="s">
-        <x:v>430</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="F57" s="14" t="s">
-        <x:v>431</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="G57" s="14" t="s">
-        <x:v>432</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="H57" s="16">
-        <x:v>46086.1144463079</x:v>
+        <x:v>46084.1627466204</x:v>
       </x:c>
       <x:c r="I57" s="16">
-        <x:v>46097</x:v>
+        <x:v>46060</x:v>
       </x:c>
       <x:c r="J57" s="15" t="s">
-        <x:v>433</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="K57" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L57" s="18">
-        <x:v>46090.2703739352</x:v>
+        <x:v>46100.392939537</x:v>
       </x:c>
       <x:c r="M57" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="16.798828" customHeight="1">
@@ -6803,28 +6857,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E58" s="14" t="s">
-        <x:v>434</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F58" s="14" t="s">
-        <x:v>435</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G58" s="14" t="s">
-        <x:v>436</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="H58" s="16">
-        <x:v>46087.1643336806</x:v>
+        <x:v>46086.099798588</x:v>
       </x:c>
       <x:c r="I58" s="16">
-        <x:v>46104</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="J58" s="15" t="s">
-        <x:v>437</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="K58" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L58" s="18">
-        <x:v>46090.2727784143</x:v>
+        <x:v>46090.2691152778</x:v>
       </x:c>
       <x:c r="M58" s="14" t="s">
         <x:v>99</x:v>
@@ -6841,28 +6895,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E59" s="14" t="s">
-        <x:v>438</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F59" s="14" t="s">
-        <x:v>439</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="G59" s="14" t="s">
-        <x:v>440</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="H59" s="16">
-        <x:v>46086.099798588</x:v>
+        <x:v>46087.1643336806</x:v>
       </x:c>
       <x:c r="I59" s="16">
-        <x:v>46098</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="J59" s="15" t="s">
-        <x:v>441</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="K59" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L59" s="18">
-        <x:v>46090.2691152778</x:v>
+        <x:v>46090.2727784143</x:v>
       </x:c>
       <x:c r="M59" s="14" t="s">
         <x:v>99</x:v>
@@ -6870,10 +6924,10 @@
     </x:row>
     <x:row r="60" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B60" s="14" t="s">
-        <x:v>170</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C60" s="14" t="s">
-        <x:v>442</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D60" s="15" t="s">
         <x:v>61</x:v>
@@ -6888,19 +6942,19 @@
         <x:v>445</x:v>
       </x:c>
       <x:c r="H60" s="16">
-        <x:v>46098.290884375</x:v>
+        <x:v>46086.1144463079</x:v>
       </x:c>
       <x:c r="I60" s="16">
-        <x:v>45997</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J60" s="15" t="s">
         <x:v>446</x:v>
       </x:c>
       <x:c r="K60" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L60" s="18">
-        <x:v>46098.3188767824</x:v>
+        <x:v>46090.2703739352</x:v>
       </x:c>
       <x:c r="M60" s="14" t="s">
         <x:v>99</x:v>
@@ -6908,7 +6962,7 @@
     </x:row>
     <x:row r="61" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B61" s="14" t="s">
-        <x:v>170</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C61" s="14" t="s">
         <x:v>447</x:v>
@@ -6926,131 +6980,239 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="H61" s="16">
-        <x:v>46092.9637875116</x:v>
+        <x:v>46104.1653972107</x:v>
       </x:c>
       <x:c r="I61" s="16">
-        <x:v>46094</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="J61" s="15" t="s">
         <x:v>451</x:v>
       </x:c>
       <x:c r="K61" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L61" s="18">
-        <x:v>46093.3109466551</x:v>
+        <x:v>46104.3486613194</x:v>
       </x:c>
       <x:c r="M61" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B62" s="14" t="s">
-        <x:v>170</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C62" s="14" t="s">
-        <x:v>452</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D62" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E62" s="14" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="F62" s="14" t="s">
+      <x:c r="G62" s="14" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="G62" s="14" t="s">
+      <x:c r="H62" s="16">
+        <x:v>46104.177447419</x:v>
+      </x:c>
+      <x:c r="I62" s="16">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J62" s="15" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="H62" s="16">
+      <x:c r="K62" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L62" s="18">
+        <x:v>46104.3503927546</x:v>
+      </x:c>
+      <x:c r="M62" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B63" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C63" s="14" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="D63" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E63" s="14" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="F63" s="14" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="G63" s="14" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="H63" s="16">
+        <x:v>46104.1835884259</x:v>
+      </x:c>
+      <x:c r="I63" s="16">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J63" s="15" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="K63" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L63" s="18">
+        <x:v>46104.3519977083</x:v>
+      </x:c>
+      <x:c r="M63" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B64" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C64" s="14" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="D64" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E64" s="14" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="G64" s="14" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="H64" s="16">
+        <x:v>46098.290884375</x:v>
+      </x:c>
+      <x:c r="I64" s="16">
+        <x:v>45997</x:v>
+      </x:c>
+      <x:c r="J64" s="15" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="K64" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L64" s="18">
+        <x:v>46098.3188767824</x:v>
+      </x:c>
+      <x:c r="M64" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B65" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C65" s="14" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="D65" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E65" s="14" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="G65" s="14" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="H65" s="16">
+        <x:v>46092.9637875116</x:v>
+      </x:c>
+      <x:c r="I65" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J65" s="15" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="K65" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L65" s="18">
+        <x:v>46093.3109466551</x:v>
+      </x:c>
+      <x:c r="M65" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B66" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C66" s="14" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="D66" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E66" s="14" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="F66" s="14" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="G66" s="14" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="H66" s="16">
         <x:v>46083.0936215278</x:v>
       </x:c>
-      <x:c r="I62" s="16">
+      <x:c r="I66" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J62" s="15" t="s">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="K62" s="17" t="n">
+      <x:c r="J66" s="15" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="K66" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L62" s="18">
+      <x:c r="L66" s="18">
         <x:v>46083.1543707755</x:v>
       </x:c>
-      <x:c r="M62" s="14" t="s">
+      <x:c r="M66" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B65" s="19" t="s">
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B69" s="19" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="C65" s="20" t="s"/>
-      <x:c r="D65" s="20" t="s"/>
-      <x:c r="E65" s="21" t="s"/>
-      <x:c r="F65" s="21" t="s"/>
-    </x:row>
-    <x:row r="66" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B66" s="22" t="s">
+      <x:c r="C69" s="20" t="s"/>
+      <x:c r="D69" s="20" t="s"/>
+      <x:c r="E69" s="21" t="s"/>
+      <x:c r="F69" s="21" t="s"/>
+    </x:row>
+    <x:row r="70" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B70" s="22" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C66" s="23" t="s"/>
-      <x:c r="D66" s="23" t="s"/>
-      <x:c r="E66" s="23" t="s"/>
-      <x:c r="F66" s="24" t="s">
+      <x:c r="C70" s="23" t="s"/>
+      <x:c r="D70" s="23" t="s"/>
+      <x:c r="E70" s="23" t="s"/>
+      <x:c r="F70" s="24" t="s">
         <x:v>204</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B67" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C67" s="26" t="s"/>
-      <x:c r="D67" s="26" t="s"/>
-      <x:c r="E67" s="26" t="s"/>
-      <x:c r="F67" s="27" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B68" s="25" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C68" s="26" t="s"/>
-      <x:c r="D68" s="26" t="s"/>
-      <x:c r="E68" s="26" t="s"/>
-      <x:c r="F68" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B69" s="25" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C69" s="26" t="s"/>
-      <x:c r="D69" s="26" t="s"/>
-      <x:c r="E69" s="26" t="s"/>
-      <x:c r="F69" s="27" t="n">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B70" s="25" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C70" s="26" t="s"/>
-      <x:c r="D70" s="26" t="s"/>
-      <x:c r="E70" s="26" t="s"/>
-      <x:c r="F70" s="27" t="n">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:28" ht="18" customHeight="1">
       <x:c r="B71" s="25" t="s">
-        <x:v>110</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C71" s="26" t="s"/>
       <x:c r="D71" s="26" t="s"/>
@@ -7061,7 +7223,7 @@
     </x:row>
     <x:row r="72" spans="1:28" ht="18" customHeight="1">
       <x:c r="B72" s="25" t="s">
-        <x:v>170</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C72" s="26" t="s"/>
       <x:c r="D72" s="26" t="s"/>
@@ -7070,21 +7232,61 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B73" s="28" t="s">
+    <x:row r="73" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B73" s="25" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C73" s="26" t="s"/>
+      <x:c r="D73" s="26" t="s"/>
+      <x:c r="E73" s="26" t="s"/>
+      <x:c r="F73" s="27" t="n">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B74" s="25" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C74" s="26" t="s"/>
+      <x:c r="D74" s="26" t="s"/>
+      <x:c r="E74" s="26" t="s"/>
+      <x:c r="F74" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B75" s="25" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C75" s="26" t="s"/>
+      <x:c r="D75" s="26" t="s"/>
+      <x:c r="E75" s="26" t="s"/>
+      <x:c r="F75" s="27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B76" s="25" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C76" s="26" t="s"/>
+      <x:c r="D76" s="26" t="s"/>
+      <x:c r="E76" s="26" t="s"/>
+      <x:c r="F76" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B77" s="28" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="C73" s="29" t="s"/>
-      <x:c r="D73" s="29" t="s"/>
-      <x:c r="E73" s="29" t="s"/>
-      <x:c r="F73" s="30" t="n">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C77" s="29" t="s"/>
+      <x:c r="D77" s="29" t="s"/>
+      <x:c r="E77" s="29" t="s"/>
+      <x:c r="F77" s="30" t="n">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
     <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8007,15 +8209,15 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B65:F65"/>
-    <x:mergeCell ref="B66:E66"/>
-    <x:mergeCell ref="B67:E67"/>
-    <x:mergeCell ref="B68:E68"/>
-    <x:mergeCell ref="B69:E69"/>
+    <x:mergeCell ref="B69:F69"/>
     <x:mergeCell ref="B70:E70"/>
     <x:mergeCell ref="B71:E71"/>
     <x:mergeCell ref="B72:E72"/>
     <x:mergeCell ref="B73:E73"/>
+    <x:mergeCell ref="B74:E74"/>
+    <x:mergeCell ref="B75:E75"/>
+    <x:mergeCell ref="B76:E76"/>
+    <x:mergeCell ref="B77:E77"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IV-A-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="479">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -661,15 +661,27 @@
     <x:t>1511906</x:t>
   </x:si>
   <x:si>
+    <x:t>ARMANDO A. ABECILLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>blk.21 lot1 japan st. san marino subd., salawag, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-AT-03055C-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1222-017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1529828</x:t>
+  </x:si>
+  <x:si>
     <x:t>CHRISTOPHER I. PALLESCO</x:t>
   </x:si>
   <x:si>
     <x:t>Block 3 Lot 12 Phase 1 Lavanya Subdivision, Bacao 2, General Trias, Cavite</x:t>
   </x:si>
   <x:si>
-    <x:t>DD-AT-03055C-2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>43A-3-2026-1210-786</x:t>
   </x:si>
   <x:si>
@@ -940,6 +952,18 @@
     <x:t>1511206</x:t>
   </x:si>
   <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511223</x:t>
+  </x:si>
+  <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -952,18 +976,6 @@
     <x:t>1511224</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511223</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
@@ -1174,6 +1186,18 @@
     <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>LEVEL 3, 306A, BRGY. TEJERO, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-05-0452-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1084-395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511240</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYALA MALLS SERIN JUNCTION EAST, SILANG, Tagaytay City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -1184,18 +1208,6 @@
   </x:si>
   <x:si>
     <x:t>1511275</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEVEL 3, 306A, BRGY. TEJERO, General Trias, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-05-0452-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1084-395</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511240</x:t>
   </x:si>
   <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
@@ -5014,10 +5026,10 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46100.3734511921</x:v>
+        <x:v>46105.0657206366</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46100.3886071759</x:v>
+        <x:v>46105.1083022685</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>216</x:v>
@@ -5026,7 +5038,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46100.3957177662</x:v>
+        <x:v>46105.1161564931</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>27</x:v>
@@ -5037,32 +5049,32 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>212</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>213</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46100.3657890856</x:v>
+        <x:v>46100.3734511921</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46100.3731746412</x:v>
+        <x:v>46100.3886071759</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46100.3869012616</x:v>
+        <x:v>46100.3957177662</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>27</x:v>
@@ -5073,35 +5085,35 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>220</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s"/>
       <x:c r="E11" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="16">
+        <x:v>46100.3657890856</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46100.3731746412</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46091.3061033796</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46091.3108077083</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>224</x:v>
-      </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>230</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46091.3131892477</x:v>
+        <x:v>46100.3869012616</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
@@ -5109,32 +5121,32 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s"/>
       <x:c r="E12" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="16">
+        <x:v>46091.3061033796</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46091.3108077083</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46093.1459465972</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46093.1585187731</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>229</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46093.1595409143</x:v>
+        <x:v>46091.3131892477</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>99</x:v>
@@ -5145,35 +5157,35 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s"/>
       <x:c r="E13" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="H13" s="16">
+        <x:v>46093.1459465972</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46093.1585187731</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46104.2283957986</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46104.2427159028</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>234</x:v>
-      </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46104.2658305093</x:v>
+        <x:v>46093.1595409143</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
@@ -5181,73 +5193,71 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s"/>
       <x:c r="E14" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46104.2283957986</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46104.2427159028</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46098.0792632986</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46098.0878978819</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>239</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46098.0997679745</x:v>
+        <x:v>46104.2658305093</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46098.0792632986</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46098.0878978819</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46090.2418365857</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46090.2418534606</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>244</x:v>
-      </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46093.3049920255</x:v>
+        <x:v>46098.0997679745</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
@@ -5255,37 +5265,37 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46090.2418365857</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46090.2418534606</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46090.2558238542</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46090.2558400116</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>249</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46097.2890797917</x:v>
+        <x:v>46093.3049920255</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
@@ -5293,75 +5303,75 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="H17" s="16">
+        <x:v>46090.2558238542</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46090.2558400116</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
         <x:v>253</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46090.210999456</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46090.211015162</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>254</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46093.3080127546</x:v>
+        <x:v>46097.2890797917</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="H18" s="16">
+        <x:v>46090.210999456</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46090.211015162</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46083.2380494329</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>259</x:v>
-      </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46097.1564439468</x:v>
+        <x:v>46093.3080127546</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
@@ -5369,7 +5379,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>255</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>61</x:v>
@@ -5384,7 +5394,7 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46080.4532551852</x:v>
+        <x:v>46083.2380494329</x:v>
       </x:c>
       <x:c r="I19" s="16">
         <x:v>46100</x:v>
@@ -5396,10 +5406,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46097.1461728357</x:v>
+        <x:v>46097.1564439468</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -5407,7 +5417,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>255</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>61</x:v>
@@ -5422,10 +5432,10 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46083.2322339931</x:v>
+        <x:v>46080.4532551852</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46112</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>267</x:v>
@@ -5434,10 +5444,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46097.1495293519</x:v>
+        <x:v>46097.1461728357</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
@@ -5445,37 +5455,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>268</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="H21" s="16">
+        <x:v>46083.2322339931</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
         <x:v>271</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46083.2599218056</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>272</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46097.1652390856</x:v>
+        <x:v>46097.1495293519</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
@@ -5483,37 +5493,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
+      <x:c r="H22" s="16">
+        <x:v>46083.2599218056</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46069.3514850347</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46097.2437384259</x:v>
+        <x:v>46097.1652390856</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -5521,7 +5531,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>273</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>61</x:v>
@@ -5536,22 +5546,22 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46069.278571956</x:v>
+        <x:v>46069.3514850347</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46067</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
         <x:v>281</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46100.3884108912</x:v>
+        <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
@@ -5559,37 +5569,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>283</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="s">
+      <x:c r="H24" s="16">
+        <x:v>46069.278571956</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="G24" s="14" t="s">
+      <x:c r="K24" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46100.3884108912</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46084.0996762384</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46097.241468588</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
@@ -5597,7 +5607,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>283</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
         <x:v>61</x:v>
@@ -5612,10 +5622,10 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46084.0854516898</x:v>
+        <x:v>46084.0996762384</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46144</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
         <x:v>291</x:v>
@@ -5624,10 +5634,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46093.3956400694</x:v>
+        <x:v>46097.241468588</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
@@ -5635,37 +5645,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="s">
+      <x:c r="G26" s="14" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="s">
+      <x:c r="H26" s="16">
+        <x:v>46084.0854516898</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46073.1441202083</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="s">
-        <x:v>296</x:v>
-      </x:c>
       <x:c r="K26" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46100.4005466667</x:v>
+        <x:v>46093.3956400694</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
@@ -5673,7 +5683,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
         <x:v>61</x:v>
@@ -5688,22 +5698,22 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46069.3573124306</x:v>
+        <x:v>46073.1441202083</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46100</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
         <x:v>300</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46097.2426396643</x:v>
+        <x:v>46100.4005466667</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
@@ -5711,7 +5721,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
         <x:v>61</x:v>
@@ -5726,22 +5736,22 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46069.1542109954</x:v>
+        <x:v>46069.3573124306</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46035</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
         <x:v>304</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="18">
-        <x:v>46097.2466610301</x:v>
+        <x:v>46097.2426396643</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
@@ -5749,7 +5759,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C29" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D29" s="15" t="s">
         <x:v>61</x:v>
@@ -5764,22 +5774,22 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46084.2250188542</x:v>
+        <x:v>46069.1542109954</x:v>
       </x:c>
       <x:c r="I29" s="16">
-        <x:v>46144</x:v>
+        <x:v>46035</x:v>
       </x:c>
       <x:c r="J29" s="15" t="s">
         <x:v>308</x:v>
       </x:c>
       <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L29" s="18">
-        <x:v>46093.3804507639</x:v>
+        <x:v>46097.2466610301</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
@@ -5787,7 +5797,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C30" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D30" s="15" t="s">
         <x:v>61</x:v>
@@ -5817,7 +5827,7 @@
         <x:v>46093.3723926852</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
@@ -5825,37 +5835,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C31" s="14" t="s">
-        <x:v>313</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D31" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E31" s="14" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="F31" s="14" t="s">
+      <x:c r="G31" s="14" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="G31" s="14" t="s">
+      <x:c r="H31" s="16">
+        <x:v>46084.2250188542</x:v>
+      </x:c>
+      <x:c r="I31" s="16">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="H31" s="16">
-        <x:v>46069.2178798032</x:v>
-      </x:c>
-      <x:c r="I31" s="16">
-        <x:v>46051</x:v>
-      </x:c>
-      <x:c r="J31" s="15" t="s">
-        <x:v>317</x:v>
-      </x:c>
       <x:c r="K31" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="18">
-        <x:v>46097.2456397685</x:v>
+        <x:v>46093.3804507639</x:v>
       </x:c>
       <x:c r="M31" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
@@ -5863,37 +5873,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C32" s="14" t="s">
-        <x:v>318</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D32" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E32" s="14" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="F32" s="14" t="s">
+      <x:c r="G32" s="14" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="G32" s="14" t="s">
+      <x:c r="H32" s="16">
+        <x:v>46069.2178798032</x:v>
+      </x:c>
+      <x:c r="I32" s="16">
+        <x:v>46051</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="H32" s="16">
-        <x:v>46073.1251625463</x:v>
-      </x:c>
-      <x:c r="I32" s="16">
-        <x:v>45619</x:v>
-      </x:c>
-      <x:c r="J32" s="15" t="s">
-        <x:v>322</x:v>
-      </x:c>
       <x:c r="K32" s="17" t="n">
-        <x:v>11280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L32" s="18">
-        <x:v>46099.1200232986</x:v>
+        <x:v>46097.2456397685</x:v>
       </x:c>
       <x:c r="M32" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
@@ -5901,7 +5911,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C33" s="14" t="s">
-        <x:v>318</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D33" s="15" t="s">
         <x:v>61</x:v>
@@ -5916,22 +5926,22 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="H33" s="16">
-        <x:v>46069.3717699074</x:v>
+        <x:v>46073.1251625463</x:v>
       </x:c>
       <x:c r="I33" s="16">
-        <x:v>46066</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J33" s="15" t="s">
         <x:v>326</x:v>
       </x:c>
       <x:c r="K33" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L33" s="18">
-        <x:v>46100.3754893056</x:v>
+        <x:v>46099.1200232986</x:v>
       </x:c>
       <x:c r="M33" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
@@ -5939,37 +5949,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C34" s="14" t="s">
-        <x:v>327</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D34" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E34" s="14" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="F34" s="14" t="s">
+      <x:c r="G34" s="14" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="G34" s="14" t="s">
+      <x:c r="H34" s="16">
+        <x:v>46069.3717699074</x:v>
+      </x:c>
+      <x:c r="I34" s="16">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="H34" s="16">
-        <x:v>46083.2443981019</x:v>
-      </x:c>
-      <x:c r="I34" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="s">
-        <x:v>331</x:v>
-      </x:c>
       <x:c r="K34" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L34" s="18">
-        <x:v>46097.1600206018</x:v>
+        <x:v>46100.3754893056</x:v>
       </x:c>
       <x:c r="M34" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
@@ -5977,37 +5987,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C35" s="14" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="D35" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E35" s="14" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="F35" s="14" t="s">
+      <x:c r="G35" s="14" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="G35" s="14" t="s">
+      <x:c r="H35" s="16">
+        <x:v>46083.2443981019</x:v>
+      </x:c>
+      <x:c r="I35" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="s">
         <x:v>335</x:v>
-      </x:c>
-      <x:c r="H35" s="16">
-        <x:v>46084.1225139699</x:v>
-      </x:c>
-      <x:c r="I35" s="16">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="s">
-        <x:v>336</x:v>
       </x:c>
       <x:c r="K35" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L35" s="18">
-        <x:v>46097.3505144329</x:v>
+        <x:v>46097.1600206018</x:v>
       </x:c>
       <x:c r="M35" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
@@ -6015,37 +6025,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C36" s="14" t="s">
-        <x:v>337</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="D36" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E36" s="14" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="F36" s="14" t="s">
+      <x:c r="G36" s="14" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="G36" s="14" t="s">
+      <x:c r="H36" s="16">
+        <x:v>46084.1225139699</x:v>
+      </x:c>
+      <x:c r="I36" s="16">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="H36" s="16">
-        <x:v>46073.1541139005</x:v>
-      </x:c>
-      <x:c r="I36" s="16">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J36" s="15" t="s">
-        <x:v>341</x:v>
-      </x:c>
       <x:c r="K36" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L36" s="18">
-        <x:v>46099.1584012616</x:v>
+        <x:v>46097.3505144329</x:v>
       </x:c>
       <x:c r="M36" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
@@ -6053,37 +6063,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C37" s="14" t="s">
-        <x:v>342</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="D37" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E37" s="14" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
         <x:v>343</x:v>
       </x:c>
-      <x:c r="F37" s="14" t="s">
+      <x:c r="G37" s="14" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="G37" s="14" t="s">
+      <x:c r="H37" s="16">
+        <x:v>46073.1541139005</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="H37" s="16">
-        <x:v>46083.252116412</x:v>
-      </x:c>
-      <x:c r="I37" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J37" s="15" t="s">
-        <x:v>346</x:v>
-      </x:c>
       <x:c r="K37" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L37" s="18">
-        <x:v>46097.1628986343</x:v>
+        <x:v>46099.1584012616</x:v>
       </x:c>
       <x:c r="M37" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
@@ -6091,37 +6101,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C38" s="14" t="s">
-        <x:v>347</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="D38" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E38" s="14" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="F38" s="14" t="s">
+      <x:c r="G38" s="14" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="H38" s="16">
-        <x:v>46097.4788515162</x:v>
+        <x:v>46083.252116412</x:v>
       </x:c>
       <x:c r="I38" s="16">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J38" s="15" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="K38" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="18">
-        <x:v>46100.2987549074</x:v>
+        <x:v>46097.1628986343</x:v>
       </x:c>
       <x:c r="M38" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
@@ -6129,37 +6139,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C39" s="14" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="D39" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E39" s="14" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="F39" s="14" t="s">
+      <x:c r="G39" s="14" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="G39" s="14" t="s">
+      <x:c r="H39" s="16">
+        <x:v>46097.4788515162</x:v>
+      </x:c>
+      <x:c r="I39" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="s">
         <x:v>355</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
-        <x:v>46069.3341180556</x:v>
-      </x:c>
-      <x:c r="I39" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J39" s="15" t="s">
-        <x:v>356</x:v>
       </x:c>
       <x:c r="K39" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="18">
-        <x:v>46097.244735544</x:v>
+        <x:v>46100.2987549074</x:v>
       </x:c>
       <x:c r="M39" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
@@ -6167,13 +6177,13 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C40" s="14" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="D40" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E40" s="14" t="s">
-        <x:v>333</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="F40" s="14" t="s">
         <x:v>358</x:v>
@@ -6182,10 +6192,10 @@
         <x:v>359</x:v>
       </x:c>
       <x:c r="H40" s="16">
-        <x:v>46084.1513040509</x:v>
+        <x:v>46069.3341180556</x:v>
       </x:c>
       <x:c r="I40" s="16">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J40" s="15" t="s">
         <x:v>360</x:v>
@@ -6194,10 +6204,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L40" s="18">
-        <x:v>46097.2494578472</x:v>
+        <x:v>46097.244735544</x:v>
       </x:c>
       <x:c r="M40" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
@@ -6211,31 +6221,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E41" s="14" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="F41" s="14" t="s">
+      <x:c r="G41" s="14" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="G41" s="14" t="s">
+      <x:c r="H41" s="16">
+        <x:v>46084.1513040509</x:v>
+      </x:c>
+      <x:c r="I41" s="16">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J41" s="15" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="H41" s="16">
-        <x:v>46073.1135088426</x:v>
-      </x:c>
-      <x:c r="I41" s="16">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J41" s="15" t="s">
-        <x:v>365</x:v>
-      </x:c>
       <x:c r="K41" s="17" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L41" s="18">
-        <x:v>46097.2511403241</x:v>
+        <x:v>46097.2494578472</x:v>
       </x:c>
       <x:c r="M41" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
@@ -6243,7 +6253,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C42" s="14" t="s">
-        <x:v>361</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="D42" s="15" t="s">
         <x:v>61</x:v>
@@ -6258,22 +6268,22 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="H42" s="16">
-        <x:v>46069.1151616435</x:v>
+        <x:v>46073.1135088426</x:v>
       </x:c>
       <x:c r="I42" s="16">
-        <x:v>46172</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J42" s="15" t="s">
         <x:v>369</x:v>
       </x:c>
       <x:c r="K42" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L42" s="18">
-        <x:v>46097.343386956</x:v>
+        <x:v>46097.2511403241</x:v>
       </x:c>
       <x:c r="M42" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="16.798828" customHeight="1">
@@ -6281,7 +6291,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C43" s="14" t="s">
-        <x:v>361</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="D43" s="15" t="s">
         <x:v>61</x:v>
@@ -6296,22 +6306,22 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="H43" s="16">
-        <x:v>46084.3311976389</x:v>
+        <x:v>46069.1151616435</x:v>
       </x:c>
       <x:c r="I43" s="16">
-        <x:v>46070</x:v>
+        <x:v>46172</x:v>
       </x:c>
       <x:c r="J43" s="15" t="s">
         <x:v>373</x:v>
       </x:c>
       <x:c r="K43" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L43" s="18">
-        <x:v>46093.3668852546</x:v>
+        <x:v>46097.343386956</x:v>
       </x:c>
       <x:c r="M43" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="16.798828" customHeight="1">
@@ -6319,7 +6329,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C44" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="D44" s="15" t="s">
         <x:v>61</x:v>
@@ -6334,22 +6344,22 @@
         <x:v>376</x:v>
       </x:c>
       <x:c r="H44" s="16">
-        <x:v>46092.1012814815</x:v>
+        <x:v>46084.3311976389</x:v>
       </x:c>
       <x:c r="I44" s="16">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J44" s="15" t="s">
         <x:v>377</x:v>
       </x:c>
       <x:c r="K44" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L44" s="18">
-        <x:v>46097.1408234491</x:v>
+        <x:v>46093.3668852546</x:v>
       </x:c>
       <x:c r="M44" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="16.798828" customHeight="1">
@@ -6372,7 +6382,7 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="H45" s="16">
-        <x:v>46097.4214954398</x:v>
+        <x:v>46092.1012814815</x:v>
       </x:c>
       <x:c r="I45" s="16">
         <x:v>46100</x:v>
@@ -6384,10 +6394,10 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L45" s="18">
-        <x:v>46100.2966699421</x:v>
+        <x:v>46097.1408234491</x:v>
       </x:c>
       <x:c r="M45" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="16.798828" customHeight="1">
@@ -6395,37 +6405,37 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C46" s="14" t="s">
-        <x:v>382</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D46" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E46" s="14" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="F46" s="14" t="s">
+      <x:c r="G46" s="14" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="G46" s="14" t="s">
+      <x:c r="H46" s="16">
+        <x:v>46097.4214954398</x:v>
+      </x:c>
+      <x:c r="I46" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J46" s="15" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="H46" s="16">
-        <x:v>46069.2327997454</x:v>
-      </x:c>
-      <x:c r="I46" s="16">
-        <x:v>46049</x:v>
-      </x:c>
-      <x:c r="J46" s="15" t="s">
-        <x:v>386</x:v>
-      </x:c>
       <x:c r="K46" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L46" s="18">
-        <x:v>46100.3816829514</x:v>
+        <x:v>46100.2966699421</x:v>
       </x:c>
       <x:c r="M46" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="16.798828" customHeight="1">
@@ -6433,7 +6443,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C47" s="14" t="s">
-        <x:v>382</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="D47" s="15" t="s">
         <x:v>61</x:v>
@@ -6463,7 +6473,7 @@
         <x:v>46097.3375062153</x:v>
       </x:c>
       <x:c r="M47" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="16.798828" customHeight="1">
@@ -6471,75 +6481,75 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C48" s="14" t="s">
-        <x:v>391</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="D48" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E48" s="14" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="F48" s="14" t="s">
+      <x:c r="G48" s="14" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="G48" s="14" t="s">
+      <x:c r="H48" s="16">
+ 